--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -15,6 +15,7 @@
     <sheet name="입출고" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="개발일지" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="처방" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="시험대비 원료맵" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1525,8 +1526,192 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>불안할 때 읽는 전략 메모 — '안 팔릴까' 걱정될 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>이 메모는 불안이 올라올 때 다시 읽는 곳이다. 결론부터 — 지금 방향이 맞다. 승부는 포뮬러가 아니라 '한 명을 정확히 겨누는 데'서 난다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>① 기본기: 이 7종이면 유화·점증·방부·pH·가용화·안정성을 한 바퀴 다 익힌다. 수분·진정 스킨케어 포뮬레이터 기본기는 확실히 선다. (선크림·세안·고난도 활성은 지금 안 건드리는 게 맞다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>② 포뮬러는 해자가 아니다: 전성분은 법적으로 공개된다. 좋은 제품은 '입장권'일 뿐 차별점이 아니다 — 안 갈라지고·안 상하고·pH 맞으면 이미 '팔 수 있는 상태'다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>③ 희귀 원료로 승부하지 마라: 스토리는 좋아도 MOQ·수급·단가가 1인·저자본 브랜드를 정확히 죽인다. 리오더 때 원료가 단종되면 제품이 멈춘다. 흔하고 안정적인 원료로 가는 지금 선택이 옳다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>④ 차별화는 '넣은 원료'가 아니라 '뺀 규율'에서 나온다: 말라세지아-세이프(먹이 오일 배제)+무향. 흔한 원료로 만든 독한 컨셉이 곧 USP — 원료가 아니라 철학이 USP다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>⑤ 안 팔리는 진짜 이유는 품질이 아니라 '누구의 어떤 문제를 한 줄로 못 말해서'다. 리스크는 포뮬러가 아니라 (a)한 명의 타깃 (b)그가 나를 발견할 경로 (c)왜 나여야 하나 한 문장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>⑥ 지금 할 하나: 히어로 크림 100g 한 배치(원료는 20배치분 넉넉) → 포지셔닝 한 문장 적기 → 지루성·트러블 실사용자 3~5명에게 샘플, '내 얘기 같나? 돈 주고 살 것 같나?'만 묻기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>⑦ 포지셔닝 한 문장 초안: "말라세지아에게 먹이 안 주는, 무향 진정 크림 — 성분 따지다 지친 지성 피부를 위해."</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A86:B86"/>
@@ -13536,4 +13721,904 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원료↔시험 매핑 — 엑셀 26종을 맞춤형화장품조제관리사 시험 분류·사용한도로</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★=시험 빈출/함정 포인트. 사용한도는 식약처 「화장품 안전기준 등에 관한 규정」 기준 — 제조·판매 전 최신 고시 반드시 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원료</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INCI</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엑셀 역할</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 분류</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도·고시 포인트</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 빈출 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글리세린</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glycerin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습제(휴멕턴트)·수성원료</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음(일반원료)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표 다가알코올 보습제, 수상</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나이아신아마이드</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niacinamide</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미백 기능성 고시 주성분 / 활성</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미백 고시 함량 2~5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★빈출: 미백 주성분·2~5% 암기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다중 히알루론산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hyaluronic Acids</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습제(고분자 휴멕턴트)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분자량별 보습, 수용성 고분자</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베타글루칸</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beta-Glucan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성(진정)·고분자 다당류</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진정 유효성분</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베타인</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betaine</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습제(휴멕턴트)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아미노산계 보습제</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아연피카</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zinc PCA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성(피지·수렴)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zinc PCA 피지조절</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">알란토인</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allantoin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성(진정·각질)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진정·보습 보조</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔탄검</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xanthan Gum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">점증제</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">점증제(천연 고분자)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표 천연 점증제, 선분산</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정제수</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">용제</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수성원료(용제·기제)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기제, 순도·미생물 관리 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로판디올</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propanediol</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보습제·용제(다가알코올)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글리콜계, 방부 보조력</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCT오일</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caprylic/Capric Triglyceride</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유성원료(에스터 오일·에몰리언트)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caprylic/Capric Triglyceride</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디메치콘</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dimethicone</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유성원료(실리콘)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실리콘 오일, 발림·보호막</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몬타노브68</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유화제</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계면활성제(비이온 유화제)+고급지방알코올</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O/W 유화제, HLB·유화 개념</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세틸알코올</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cetyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고급지방알코올(유성·보조유화)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">점도·유화 안정화</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스쿠알란</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Squalane</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유성원료(에몰리언트)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안정성 높은 보습 오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시어버터</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Butyrospermum Parkii Butter</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유성원료(식물성 버터)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고형 유지, 에몰리언트</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">올리브유화왁스</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cetearyl Olivate &amp; Sorbitan Olivate</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유화제</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계면활성제(비이온 유화제)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">올리브 유래 O/W 유화제</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토코페롤(비타민E)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tocopherol</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">항산화제</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산화방지제</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음(산화방지 목적)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★분류주의: 산화방지제(보존제 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폴리글리세릴-4 카프레이트</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyglyceryl-4 Caprate</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가용화제</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계면활성제(비이온 가용화제)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워시오프 가용화·세정 보조</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">호호바오일</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simmondsia Chinensis Seed Oil</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유성원료(왁스 에스터 오일)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피지 유사 왁스 에스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,2-헥산다이올</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,2-Hexanediol</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방부제</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다가알코올(보습·방부 보조)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★지정 보존제 아님(사용제한 목록 미등재)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★함정: 방부력 있어도 법적 보존제 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녹차추출물</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camellia Sinensis Leaf Extract</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식물추출물(활성)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수용성 추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마데카소사이드</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madecassoside</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식물추출물 활성(센텔라)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진정 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판테놀(B5)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panthenol</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성(보습·진정)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로비타민 B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페녹시에탄올</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방부제</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보존제(사용제한 원료)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★사용한도 1.0%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★최빈출: 보존제·한도 1.0% 필수암기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구연산</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Citric Acid</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pH조절</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pH 조절제</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citric acid, pH 5 안팎 조절</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F29"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -16,6 +16,8 @@
     <sheet name="개발일지" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="처방" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="시험대비 원료맵" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="시험→사업 활용" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="실습↔시험 개념" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1731,6 +1733,724 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왼쪽(시험 핵심)을 외우되, 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열 질문은 ODM/공장 미팅에서 그대로 던질 체크리스트. 수치·목록은 최신 고시로 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분류(시험 영역)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 핵심 암기</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→ 사업 활용</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ODM·발주 미팅 질문(그대로 물어볼 것)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주의/메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[법] 영업 종류·책임판매업</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP) 기준</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내 사업 형태 확정: 직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매는 내가·제조품질은 공장 — 역할 경계 어디까지?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★조제관리사 자격=맞춤형판매업 선임요건. 자격 자체가 사업 자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[법] 표시·기재·광고</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전성분 표시의무·기재사항, 부당표시광고(치료·의학적 효능 금지)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세페이지·라벨의 '하면 안 되는 말' 경계 = 진정·무향 카피 리스크 관리</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라벨 시안(전성분 함량순·착향 알레르겐 표기) 검수해주나? 표시광고 가이드 제공?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치료·항염·살균·병명 금지(읽어보기 핵심제약과 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조품질] 사용제한 보존제</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 제품 구분</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방부 시스템 설계·검증을 공장에 요구하는 기준이 생김</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방부 시스템 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온이라 한도 안 넘나?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,2-헥산다이올은 '지정 보존제 아님'(함정) — 책임 방부성분 따로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조품질] 자외선차단·선크림</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자외선차단성분 목록·최대함량, 자차=기능성화장품 심사/보고</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선크림은 '위탁+기능성 인증' 전제 — 직접 제조 대상 아님</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필 번호? 원료 수급 안정적?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장 2~3순위. 히어로 검증 뒤에</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조품질] 기능성 주성분(미백·주름)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미백(나이아신아마이드 2~5%·알부틴·아스코르빈산 유도체), 주름(레티놀·아데노신) 고시 성분·함량</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 기능성 보고/심사 대행 요청</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화(레티놀 변색 등) 데이터?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나이아신아마이드 이미 보유·히어로에 2% → 미백 표방 여부는 전략 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조품질] 배합금지 원료</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용할 수 없는 원료 목록</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수입·신규 원료, 해외 처방 검토 시 1차 필터</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전성분에 국내 배합금지·사용한도 초과 성분 없나? 원료 CoA·MSDS 제공?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해외 인기 성분이 국내 금지인 경우 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[유통안전] 유래물질·미생물 한도</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중금속(납·비소·수은 등)·포름알데히드 등 한도, 미생물 한도(총호기성생균 등)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출고 전 안전관리 시험성적서 확보 = 품질 신뢰·CS 방어</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출고 로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체는?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안 주면 리스크 — 발주 계약서에 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[유통안전] 착향제 알레르기 성분</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">착향 알레르기 유발성분 표시 대상 목록</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다도기=무향이라 유리: '무향·착향 알레르겐 0' 소구 가능</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무향이 곧 USP이자 규제 리스크 최소화</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[유통안전] pH·안정성·사용기한</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유형별 pH 기준, 안정성(가속·장기) 개념</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용기한·보관조건의 과학적 근거 = 라벨·CS 뒷받침</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안정성 데이터로 사용기한 산정? 개봉후사용기간(PAO) 표기 근거?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">읽어보기 '안정성 테스트' 섹션과 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[맞춤형] 혼합·소분·위생</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내용물+원료 혼합 가능/불가, 소분, 작업장 위생·장비 소독</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'맞춤형판매업' 직접 운영 시 핵심 역량 — 상담→조제 차별화</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(자체검토) 벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지되나?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조제관리사 자격의 직접 수익화 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[맞춤형/제조] 계면활성제·세안</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계면활성제 4분류(음이온/양이온/양쪽성/비이온), 세정 원리</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폼클렌저 등 세안 라인 기획 시 베이스 선택 기준</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 타깃 적합?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초기엔 위탁 권장(설비·충전 부담)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실습↔시험 개념 — 내가 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성분은 「시험대비 원료맵」에서 봤다. 여기는 제형·공정·안정성·위생·장비 — 시험 비중이 가장 큰 영역이자, 내가 이미 손으로 하는 일. 수치·기준은 최신 고시로 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분류(실습 영역)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내가 하는 것 (엑셀 근거)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→ 시험 개념 (외울 것)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→ 사업 활용</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주의/메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제형 분류]</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 제형을 직접 설계·제조</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화장품 유형 분류, 유화형(O/W)·가용화·분산 제형 구분, 리브온/워시오프</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라인업 설계·제품유형 신고 기준, 어디까지 직접/위탁할지 선 긋기</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리브온(토너·크림)은 방부·향을 더 보수적으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[배합 설계·전성분]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 소량 정밀계량</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전성분 표시=함량 많은 순, 1% 이하·착향제·색소는 순서 무관, q.s. 개념</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라벨 전성분 표기 검수·ODM 처방과 대조하는 눈</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★처방 시트가 곧 전성분 표기 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조 공정]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수상(A) 70~75℃ 가열 / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산, 유화 순서</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가용화·유화·분산 공정, 상(phase) 개념, 가열·냉각·투입 순서</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공정 표준화=재현성 → 품질 일관성(리오더·CS 방어)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냉각군(방부·열에 약한 활성)은 40℃ 이하에서 투입</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[유화 안정성]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">층분리·크리밍·오일링을 온도·전단(호모 HZ-400)·유화제 3요소로 교정</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유화 안정성, 유화제 HLB·유화형(O/W·W/O), 상분리 원인</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안정한 처방=반품·클레임 방지, ODM 샘플 평가 기준</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">점도↑(잔탄검)도 기름방울 크리밍을 막는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[안정성 시험]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45℃(가속)·RT·4℃·동결융해 보관 + 원심분리(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안정성 시험(가속·장기·가혹), 경시변화, 유통화장품 안전관리</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★사용기한·개봉후사용기간(PAO) 산정 근거 = ODM에 요구할 핵심 데이터</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">투명 바이알로 변색·냄새·pH 눈 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[pH 관리]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 5.0~5.5, 구연산 희석액 한 방울씩 적정, pH미터 교정(버퍼 4·7)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피부 약산성, 유형별 pH 기준, pH 측정법</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자극 최소화의 과학적 근거, 민감·지성 타깃 소구 포인트</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물 든 제품만 측정, 되직하면 정제수 1:1 희석 후 측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[방부·미생물]</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용, 오염 증상 관찰</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보존제 사용한도, 미생물 한도, 방부력(챌린지) 시험 개념</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방부력 시험성적서를 ODM에 요구, 사용기한 설정 근거</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물+영양=미생물 배지. 헥산다이올은 지정 보존제 아님(책임 방부성분 따로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[산화·원료 보관]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관(입출고·셀러)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산화방지제, 원료 보관조건, 비의도적 변질·유래물질</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원료 자재관리(CoA·로트·유효기간) → 품질·원가 통제</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[작업장 위생·혼합소분]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70% 에탄올로 도구·용기·손 소독, 향·색 전용도구, 완전 건조</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">맞춤형 혼합·소분 작업장 위생, 교차오염 방지, 손 소독</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★맞춤형판매업 매장 운영 표준 = 조제관리사 실무 핵심(직접 수익화)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미생물 오염이 자가제조 최대 리스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[장비·계량]</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정밀저울 0.01g(소량)·벤치저울(대량), 호모나이저, 오버헤드 교반, pH미터</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">혼합·소분 장비·기구, 계량 정확도·오차</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소량 생산 설비 vs 위탁 판단, 맞춤형 매장 장비 구비 기준</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1% 이하는 정밀저울 — 큰 저울로 재면 처방이 망가진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[제조 기록·배치]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개발일지에 날짜·제품·배치량g·판정 기록, '한 번에 한 변수'</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제조번호·제조기록서(뱃치기록), 제조일·사용기한 관리(CGMP 개념)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로트 추적성=리콜·CS 대응력, ODM 품질계약의 기준</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">접은 실험도 '이 방향 아님' 데이터 — 기록 보존</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -1710,8 +1710,124 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공부하다 '이 개념이 어느 시트에도 안 걸리네' 싶은 게 나오면 Claude에게 — 해당 시트에 그 칸만 채워 넣는다. 수치·목록은 항상 최신 식약처 고시로 재확인.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A111:B111"/>
     <mergeCell ref="A103:B103"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A26:B26"/>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -811,7 +811,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>시트 8개 지도</t>
+          <t>시트 11개 지도</t>
         </is>
       </c>
     </row>
@@ -911,10 +911,27 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>전체 흐름 한눈에</t>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험대비 원료맵 : 보유 원료 26종을 시험 분류·사용한도로 매핑(필터·틀고정). 조제관리사 공부용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실습↔시험 개념 : 제형·공정·안정성·위생·장비 실습을 시험 과목2·4 개념+사업 활용으로 묶음.</t>
         </is>
       </c>
     </row>
@@ -926,31 +943,14 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>[만들기] 레시피 고름 → 만듦 → 개발일지에 기록(사용감·분리mm·pH·판정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>[고치기] 이슈 → 트러블슈팅에서 '관련 역할' 확인 → 원료 시트에서 그 역할로 필터 → 바꿀 원료 선택 → 다음 아이디어.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>[사기]   원료 사면 → 입출고 한 줄(구매) → 원료 '현재고' 자동 ↑.</t>
+          <t xml:space="preserve">시험→사업 활용 : 외운 이론을 ODM 발주·제품 기획 체크리스트로 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>전체 흐름 한눈에</t>
         </is>
       </c>
     </row>
@@ -962,62 +962,62 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>[만들기] 레시피 고름 → 만듦 → 개발일지에 기록(사용감·분리mm·pH·판정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>[고치기] 이슈 → 트러블슈팅에서 '관련 역할' 확인 → 원료 시트에서 그 역할로 필터 → 바꿀 원료 선택 → 다음 아이디어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>[사기]   원료 사면 → 입출고 한 줄(구매) → 원료 '현재고' 자동 ↑.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>[재고]   만들면 → 개발일지 배치량g → 쓴 원료가 처방 %대로 자동 ↓.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>★ 재고가 자동으로 맞춰지는 원리</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>현재고 = 최초보유 + 구매(입출고) + 조정(입출고) − 제조사용(개발일지 배치량 × 처방%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>원료를 사면 → '입출고'에 [날짜·원료·구매·수량g] 한 줄.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>제품을 만들면 → '개발일지'에 [날짜·제품·배치량g] 한 줄 → 쓴 원료가 자동 차감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>흘리거나 버리면 → '입출고'에 구분 '조정', 수량g에 음수(-).</t>
         </is>
       </c>
     </row>
@@ -1029,14 +1029,31 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>현재고가 빨갛게(음수) 뜨면 그 원료는 '사야 함' 신호.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>매일 쓰는 법</t>
+          <t>원료를 사면 → '입출고'에 [날짜·원료·구매·수량g] 한 줄.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>제품을 만들면 → '개발일지'에 [날짜·제품·배치량g] 한 줄 → 쓴 원료가 자동 차감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>흘리거나 버리면 → '입출고'에 구분 '조정', 수량g에 음수(-).</t>
         </is>
       </c>
     </row>
@@ -1048,31 +1065,14 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>① 필터: 각 표 머리글의 ▼ 버튼으로 상·제품·판정·역할 등으로 걸러 본다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>② 새 줄: 표 맨 아래 줄에 바로 입력하면 수식·드롭다운이 자동으로 따라 확장된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>③ 한 번에 한 변수만 바꾼다 — 그래야 뭐가 효과였는지 안다.</t>
+          <t>현재고가 빨갛게(음수) 뜨면 그 원료는 '사야 함' 신호.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>매일 쓰는 법</t>
         </is>
       </c>
     </row>
@@ -1084,50 +1084,50 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>① 필터: 각 표 머리글의 ▼ 버튼으로 상·제품·판정·역할 등으로 걸러 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>② 새 줄: 표 맨 아래 줄에 바로 입력하면 수식·드롭다운이 자동으로 따라 확장된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>③ 한 번에 한 변수만 바꾼다 — 그래야 뭐가 효과였는지 안다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>④ 실패도 '접기'로 기록 — 안 되는 방향을 지우는 것도 전진.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>이슈가 나면 — 이렇게 고친다 (핵심 루프)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>개발일지에 사용감·이슈·분리mm·pH를 적는다 → '트러블슈팅'에서 그 증상 줄을 찾는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>그 줄의 '관련 역할'(예: 끈적임→보습)을 보고 → '원료' 시트에서 역할=그 값으로 필터 → 바꿀 후보 원료가 한눈에.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>'조정'대로 한 축만 골라 개발일지 '다음 아이디어'에 적는다(예: 글리세린 1%p↓ + 베타인으로 대체).</t>
         </is>
       </c>
     </row>
@@ -1139,62 +1139,62 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>개발일지에 사용감·이슈·분리mm·pH를 적는다 → '트러블슈팅'에서 그 증상 줄을 찾는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>그 줄의 '관련 역할'(예: 끈적임→보습)을 보고 → '원료' 시트에서 역할=그 값으로 필터 → 바꿀 후보 원료가 한눈에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>'조정'대로 한 축만 골라 개발일지 '다음 아이디어'에 적는다(예: 글리세린 1%p↓ + 베타인으로 대체).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>다음에 만들 땐 그 '다음 아이디어'가 이번 배치의 '바꾼것', '기준(base)'엔 직전 버전을 적는다.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>접힌 것도 '이 방향은 아니다' 데이터 — 지우지 말고 남긴다.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>원료 '역할' 12종 (필터·트러블슈팅 공통 어휘)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>용제 = 바탕 물. / 보습 = 수분 잡기(글리세린·베타인·HA). / 활성 = 효능(피지·진정·톤).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>유화제 = 물·기름 섞기(몬타노브68). / 점증제 = 되기 만들기(잔탄검). / 유상·에몰리언트 = 오일·지방알코올.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>감촉·실리콘 = 매끈함(디메치콘). / 향료 = 향(다도기는 무향 원칙). / 방부제 = 세균·곰팡이 방지.</t>
         </is>
       </c>
     </row>
@@ -1206,62 +1206,62 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
+          <t>용제 = 바탕 물. / 보습 = 수분 잡기(글리세린·베타인·HA). / 활성 = 효능(피지·진정·톤).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>유화제 = 물·기름 섞기(몬타노브68). / 점증제 = 되기 만들기(잔탄검). / 유상·에몰리언트 = 오일·지방알코올.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>감촉·실리콘 = 매끈함(디메치콘). / 향료 = 향(다도기는 무향 원칙). / 방부제 = 세균·곰팡이 방지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>항산화제 = 산패 방지(토코페롤). / pH조절 = 산도 맞춤(구연산). / 가용화제 = 오일을 물에 풀기(워시오프).</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>→ 자세한 '역할 설명'은 원료 시트의 E열에 역할마다 붙어 있다.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>안정성 테스트란 (45℃·RT·4℃·동결융해)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>제품이 '시간이 지나도 안 변하는지' 보는 시험. 같은 배치를 조건별로 나눠 두고 1·2·4·8주 관찰한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>45℃=고온(가속). 더우면 변질이 빨라져 '미래를 미리' 본다 — 분리·변색·냄새·pH 변화가 여기서 먼저 터진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>RT=Room Temperature(상온)=실제 사용 근사·대조군. 4℃=냉장(굳음·결정). 동결융해=얼렸다 녹였다 반복(유화 견고성).</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>둘 곳: 45℃는 발효기/인큐베이터, RT는 직사광 없는 서랍, 4℃·냉동은 냉장고. 투명 바이알에 담아 눈으로 비교.</t>
+          <t>제품이 '시간이 지나도 안 변하는지' 보는 시험. 같은 배치를 조건별로 나눠 두고 1·2·4·8주 관찰한다.</t>
         </is>
       </c>
     </row>
@@ -1285,62 +1285,62 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
+          <t>45℃=고온(가속). 더우면 변질이 빨라져 '미래를 미리' 본다 — 분리·변색·냄새·pH 변화가 여기서 먼저 터진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>RT=Room Temperature(상온)=실제 사용 근사·대조군. 4℃=냉장(굳음·결정). 동결융해=얼렸다 녹였다 반복(유화 견고성).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>둘 곳: 45℃는 발효기/인큐베이터, RT는 직사광 없는 서랍, 4℃·냉동은 냉장고. 투명 바이알에 담아 눈으로 비교.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>개발일지 예시 '안정성 45C/RT 등록' = 이 배치를 45℃와 상온에 넣어 안정성 관찰을 시작한다는 뜻.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>초보 용어 사전</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="47" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="70" ht="47" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>수상(A)=물에 녹는 것(물·보습·수용성 활성) / 유상(B)=기름에 녹는 것(오일·유화제·지방알코올) / 냉각첨가(C)=식힌 뒤 넣는 열에 약한 것(방부·향·일부 활성).</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>유화 = 물과 기름을 유화제+강한 교반(호모)으로 안 갈라지게 섞는 것(로션·크림).</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>%p(퍼센트포인트) = 배합 % 숫자를 그만큼 올리/내리기(글리세린 5%→4% = 1%p↓).</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>배치 = 한 번에 만드는 양(연습은 100g). base = 이번 실험의 출발 버전.</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>선분산 = 검(잔탄)을 물에 넣기 전 글리세린에 미리 개어 두는 것(뭉침·피시아이 방지).</t>
+          <t>유화 = 물과 기름을 유화제+강한 교반(호모)으로 안 갈라지게 섞는 것(로션·크림).</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>리브온 = 씻어내지 않고 피부에 남는 제품(토너·크림) → 향·보존을 더 보수적으로.</t>
+          <t>%p(퍼센트포인트) = 배합 % 숫자를 그만큼 올리/내리기(글리세린 5%→4% = 1%p↓).</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>말라세지아-세이프 = 피부 효모가 먹는 C11~24 지방산 오일을 뺀 것(우리 오일=스쿠알란·MCT·디메치콘).</t>
+          <t>배치 = 한 번에 만드는 양(연습은 100g). base = 이번 실험의 출발 버전.</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1388,31 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>pH = 산성/염기성 척도(0~14). 피부는 약산성 5 안팎. 물 든 제품만 측정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>레시피를 늘리고 싶을 때</t>
+          <t>선분산 = 검(잔탄)을 물에 넣기 전 글리세린에 미리 개어 두는 것(뭉침·피시아이 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>리브온 = 씻어내지 않고 피부에 남는 제품(토너·크림) → 향·보존을 더 보수적으로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>말라세지아-세이프 = 피부 효모가 먹는 C11~24 지방산 오일을 뺀 것(우리 오일=스쿠알란·MCT·디메치콘).</t>
         </is>
       </c>
     </row>
@@ -1407,167 +1424,150 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
+          <t>pH = 산성/염기성 척도(0~14). 피부는 약산성 5 안팎. 물 든 제품만 측정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>레시피를 늘리고 싶을 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
           <t>나(Claude)에게 말하면 레시피 카드 + 처방 표 + (새 원료면) 원료 행을 추가해 재생성한다.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>재생성해도 네가 적은 '입출고·개발일지'와 도구 '보유·메모'는 그대로 보존된다.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>직접 늘릴 땐: 처방 표에 [제품·원료·상·퍼센트] 행을 추가하면 재고 연계가 자동으로 걸린다.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>핵심 제약 (브랜드 = 다도기 지성·진정)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>말라세지아-세이프: C11~24 지방산 오일 배제(스쿠알란·MCT·디메치콘만).</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>무향: 향료 자극 배제. 화장품 표방 규칙: 치료·완화·항염·살균·병명 금지.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>pH 4.5~6.0(이 레시피 5.0~5.5), 물 든 제품은 반드시 방부, 소량 제조·1개월 내 사용.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>안전·위생 (꼭)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>작업 전 70% 알코올로 도구·용기·손 소독 — 미생물이 자가제조 최대 리스크.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>소량(50~100g)으로, 라벨·기록 철저, 가열·향 작업은 환기되는 곳에서.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>자가제조는 R&amp;D(개발)용 — 판매는 처방 완성 후 공장(OEM/ODM) 통해. 규제는 식약처 기준 재확인.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="5" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>⚠ %·공정·pH는 설계·연습 기준(예시). 제조 전 TDS·pH·방부력·사용기한·전성분 검증. 화장품 표방 규칙 준수.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>불안할 때 읽는 전략 메모 — '안 팔릴까' 걱정될 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>이 메모는 불안이 올라올 때 다시 읽는 곳이다. 결론부터 — 지금 방향이 맞다. 승부는 포뮬러가 아니라 '한 명을 정확히 겨누는 데'서 난다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>① 기본기: 이 7종이면 유화·점증·방부·pH·가용화·안정성을 한 바퀴 다 익힌다. 수분·진정 스킨케어 포뮬레이터 기본기는 확실히 선다. (선크림·세안·고난도 활성은 지금 안 건드리는 게 맞다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>② 포뮬러는 해자가 아니다: 전성분은 법적으로 공개된다. 좋은 제품은 '입장권'일 뿐 차별점이 아니다 — 안 갈라지고·안 상하고·pH 맞으면 이미 '팔 수 있는 상태'다.</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>③ 희귀 원료로 승부하지 마라: 스토리는 좋아도 MOQ·수급·단가가 1인·저자본 브랜드를 정확히 죽인다. 리오더 때 원료가 단종되면 제품이 멈춘다. 흔하고 안정적인 원료로 가는 지금 선택이 옳다.</t>
+          <t>이 메모는 불안이 올라올 때 다시 읽는 곳이다. 결론부터 — 지금 방향이 맞다. 승부는 포뮬러가 아니라 '한 명을 정확히 겨누는 데'서 난다.</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>④ 차별화는 '넣은 원료'가 아니라 '뺀 규율'에서 나온다: 말라세지아-세이프(먹이 오일 배제)+무향. 흔한 원료로 만든 독한 컨셉이 곧 USP — 원료가 아니라 철학이 USP다.</t>
+          <t>① 기본기: 이 7종이면 유화·점증·방부·pH·가용화·안정성을 한 바퀴 다 익힌다. 수분·진정 스킨케어 포뮬레이터 기본기는 확실히 선다. (선크림·세안·고난도 활성은 지금 안 건드리는 게 맞다)</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>⑤ 안 팔리는 진짜 이유는 품질이 아니라 '누구의 어떤 문제를 한 줄로 못 말해서'다. 리스크는 포뮬러가 아니라 (a)한 명의 타깃 (b)그가 나를 발견할 경로 (c)왜 나여야 하나 한 문장.</t>
+          <t>② 포뮬러는 해자가 아니다: 전성분은 법적으로 공개된다. 좋은 제품은 '입장권'일 뿐 차별점이 아니다 — 안 갈라지고·안 상하고·pH 맞으면 이미 '팔 수 있는 상태'다.</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>⑥ 지금 할 하나: 히어로 크림 100g 한 배치(원료는 20배치분 넉넉) → 포지셔닝 한 문장 적기 → 지루성·트러블 실사용자 3~5명에게 샘플, '내 얘기 같나? 돈 주고 살 것 같나?'만 묻기.</t>
+          <t>③ 희귀 원료로 승부하지 마라: 스토리는 좋아도 MOQ·수급·단가가 1인·저자본 브랜드를 정확히 죽인다. 리오더 때 원료가 단종되면 제품이 멈춘다. 흔하고 안정적인 원료로 가는 지금 선택이 옳다.</t>
         </is>
       </c>
     </row>
@@ -1627,14 +1627,31 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>⑦ 포지셔닝 한 문장 초안: "말라세지아에게 먹이 안 주는, 무향 진정 크림 — 성분 따지다 지친 지성 피부를 위해."</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
+          <t>④ 차별화는 '넣은 원료'가 아니라 '뺀 규율'에서 나온다: 말라세지아-세이프(먹이 오일 배제)+무향. 흔한 원료로 만든 독한 컨셉이 곧 USP — 원료가 아니라 철학이 USP다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>⑤ 안 팔리는 진짜 이유는 품질이 아니라 '누구의 어떤 문제를 한 줄로 못 말해서'다. 리스크는 포뮬러가 아니라 (a)한 명의 타깃 (b)그가 나를 발견할 경로 (c)왜 나여야 하나 한 문장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>⑥ 지금 할 하나: 히어로 크림 100g 한 배치(원료는 20배치분 넉넉) → 포지셔닝 한 문장 적기 → 지루성·트러블 실사용자 3~5명에게 샘플, '내 얘기 같나? 돈 주고 살 것 같나?'만 묻기.</t>
         </is>
       </c>
     </row>
@@ -1646,31 +1663,14 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
+          <t>⑦ 포지셔닝 한 문장 초안: "말라세지아에게 먹이 안 주는, 무향 진정 크림 — 성분 따지다 지친 지성 피부를 위해."</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
+          <t xml:space="preserve">핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
+          <t xml:space="preserve">[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
         </is>
       </c>
     </row>
@@ -1706,14 +1706,31 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
+          <t xml:space="preserve">[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
         </is>
       </c>
     </row>
@@ -1725,31 +1742,14 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="30" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
+          <t xml:space="preserve">한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
+          <t xml:space="preserve">이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
+          <t xml:space="preserve">「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
+          <t xml:space="preserve">「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
+          <t xml:space="preserve">「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
+          <t xml:space="preserve">시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
         </is>
       </c>
     </row>
@@ -1821,29 +1821,65 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">공부하다 '이 개념이 어느 시트에도 안 걸리네' 싶은 게 나오면 Claude에게 — 해당 시트에 그 칸만 채워 넣는다. 수치·목록은 항상 최신 식약처 고시로 재확인.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -15,11 +15,15 @@
     <sheet name="입출고" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="개발일지" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="처방" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="시험대비 원료맵" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="시험→사업 활용" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="실습↔시험 개념" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="시험대비 원료맵" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="시험→사업 활용" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="실습↔시험 개념" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'시험대비 원료맵'!$A$3:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'시험→사업 활용'!$A$3:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'실습↔시험 개념'!$A$3:$E$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -278,6 +282,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>174</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>205</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>264</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -672,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -919,7 +1103,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험대비 원료맵 : 보유 원료 26종을 시험 분류·사용한도로 매핑(필터·틀고정). 조제관리사 공부용.</t>
+          <t>시험대비 원료맵 : 보유 원료 26종을 시험 분류·사용한도로 매핑(필터·틀고정). 조제관리사 공부용.</t>
         </is>
       </c>
     </row>
@@ -931,7 +1115,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">실습↔시험 개념 : 제형·공정·안정성·위생·장비 실습을 시험 과목2·4 개념+사업 활용으로 묶음.</t>
+          <t>실습↔시험 개념 : 제형·공정·안정성·위생·장비 실습을 시험 과목2·4 개념+사업 활용으로 묶음.</t>
         </is>
       </c>
     </row>
@@ -943,7 +1127,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험→사업 활용 : 외운 이론을 ODM 발주·제품 기획 체크리스트로 전환.</t>
+          <t>시험→사업 활용 : 외운 이론을 ODM 발주·제품 기획 체크리스트로 전환.</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1854,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
+          <t>확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1866,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
+          <t>핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1878,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
+          <t>[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1890,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
+          <t>[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1902,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
+          <t>시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1914,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
+          <t>지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
         </is>
       </c>
     </row>
@@ -1742,14 +1926,14 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
+          <t>한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
+          <t>시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1945,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
+          <t>이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1957,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
+          <t>「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1969,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
+          <t>「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1981,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
+          <t>「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1993,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
+          <t>시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +2005,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
+          <t>공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
         </is>
       </c>
     </row>
@@ -1833,7 +2017,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
+          <t>암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
         </is>
       </c>
     </row>
@@ -1845,7 +2029,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
+          <t>득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
         </is>
       </c>
     </row>
@@ -1857,747 +2041,757 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">공부하다 '이 개념이 어느 시트에도 안 걸리네' 싶은 게 나오면 Claude에게 — 해당 시트에 그 칸만 채워 넣는다. 수치·목록은 항상 최신 식약처 고시로 재확인.</t>
+          <t>공부하다 '이 개념이 어느 시트에도 안 걸리네' 싶은 게 나오면 Claude에게 — 해당 시트에 그 칸만 채워 넣는다. 수치·목록은 항상 최신 식약처 고시로 재확인.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A89:B89"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A89:B89"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A106:B106"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
+          <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">왼쪽(시험 핵심)을 외우되, 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열 질문은 ODM/공장 미팅에서 그대로 던질 체크리스트. 수치·목록은 최신 고시로 재확인.</t>
+          <t>왼쪽(시험 핵심)을 외우되, 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열 질문은 ODM/공장 미팅에서 그대로 던질 체크리스트. 수치·목록은 최신 고시로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류(시험 영역)</t>
+          <t>분류(시험 영역)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 핵심 암기</t>
+          <t>시험 핵심 암기</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">→ 사업 활용</t>
+          <t>→ 사업 활용</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODM·발주 미팅 질문(그대로 물어볼 것)</t>
+          <t>ODM·발주 미팅 질문(그대로 물어볼 것)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주의/메모</t>
+          <t>주의/메모</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[법] 영업 종류·책임판매업</t>
+          <t>[법] 영업 종류·책임판매업</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP) 기준</t>
+          <t>책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP) 기준</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">내 사업 형태 확정: 직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
+          <t>내 사업 형태 확정: 직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매는 내가·제조품질은 공장 — 역할 경계 어디까지?</t>
+          <t>제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매는 내가·제조품질은 공장 — 역할 경계 어디까지?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">★조제관리사 자격=맞춤형판매업 선임요건. 자격 자체가 사업 자산</t>
+          <t>★조제관리사 자격=맞춤형판매업 선임요건. 자격 자체가 사업 자산</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[법] 표시·기재·광고</t>
+          <t>[법] 표시·기재·광고</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전성분 표시의무·기재사항, 부당표시광고(치료·의학적 효능 금지)</t>
+          <t>전성분 표시의무·기재사항, 부당표시광고(치료·의학적 효능 금지)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상세페이지·라벨의 '하면 안 되는 말' 경계 = 진정·무향 카피 리스크 관리</t>
+          <t>상세페이지·라벨의 '하면 안 되는 말' 경계 = 진정·무향 카피 리스크 관리</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">라벨 시안(전성분 함량순·착향 알레르겐 표기) 검수해주나? 표시광고 가이드 제공?</t>
+          <t>라벨 시안(전성분 함량순·착향 알레르겐 표기) 검수해주나? 표시광고 가이드 제공?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">치료·항염·살균·병명 금지(읽어보기 핵심제약과 동일)</t>
+          <t>치료·항염·살균·병명 금지(읽어보기 핵심제약과 동일)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조품질] 사용제한 보존제</t>
+          <t>[제조품질] 사용제한 보존제</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 제품 구분</t>
+          <t>보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 제품 구분</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">방부 시스템 설계·검증을 공장에 요구하는 기준이 생김</t>
+          <t>방부 시스템 설계·검증을 공장에 요구하는 기준이 생김</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">방부 시스템 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온이라 한도 안 넘나?</t>
+          <t>방부 시스템 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온이라 한도 안 넘나?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2-헥산다이올은 '지정 보존제 아님'(함정) — 책임 방부성분 따로 확인</t>
+          <t>1,2-헥산다이올은 '지정 보존제 아님'(함정) — 책임 방부성분 따로 확인</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조품질] 자외선차단·선크림</t>
+          <t>[제조품질] 자외선차단·선크림</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">자외선차단성분 목록·최대함량, 자차=기능성화장품 심사/보고</t>
+          <t>자외선차단성분 목록·최대함량, 자차=기능성화장품 심사/보고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">선크림은 '위탁+기능성 인증' 전제 — 직접 제조 대상 아님</t>
+          <t>선크림은 '위탁+기능성 인증' 전제 — 직접 제조 대상 아님</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필 번호? 원료 수급 안정적?</t>
+          <t>자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필 번호? 원료 수급 안정적?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장 2~3순위. 히어로 검증 뒤에</t>
+          <t>확장 2~3순위. 히어로 검증 뒤에</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조품질] 기능성 주성분(미백·주름)</t>
+          <t>[제조품질] 기능성 주성분(미백·주름)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">미백(나이아신아마이드 2~5%·알부틴·아스코르빈산 유도체), 주름(레티놀·아데노신) 고시 성분·함량</t>
+          <t>미백(나이아신아마이드 2~5%·알부틴·아스코르빈산 유도체), 주름(레티놀·아데노신) 고시 성분·함량</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 기능성 보고/심사 대행 요청</t>
+          <t>'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 기능성 보고/심사 대행 요청</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화(레티놀 변색 등) 데이터?</t>
+          <t>기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화(레티놀 변색 등) 데이터?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">나이아신아마이드 이미 보유·히어로에 2% → 미백 표방 여부는 전략 선택</t>
+          <t>나이아신아마이드 이미 보유·히어로에 2% → 미백 표방 여부는 전략 선택</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조품질] 배합금지 원료</t>
+          <t>[제조품질] 배합금지 원료</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용할 수 없는 원료 목록</t>
+          <t>사용할 수 없는 원료 목록</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">수입·신규 원료, 해외 처방 검토 시 1차 필터</t>
+          <t>수입·신규 원료, 해외 처방 검토 시 1차 필터</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">전성분에 국내 배합금지·사용한도 초과 성분 없나? 원료 CoA·MSDS 제공?</t>
+          <t>전성분에 국내 배합금지·사용한도 초과 성분 없나? 원료 CoA·MSDS 제공?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">해외 인기 성분이 국내 금지인 경우 주의</t>
+          <t>해외 인기 성분이 국내 금지인 경우 주의</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[유통안전] 유래물질·미생물 한도</t>
+          <t>[유통안전] 유래물질·미생물 한도</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">중금속(납·비소·수은 등)·포름알데히드 등 한도, 미생물 한도(총호기성생균 등)</t>
+          <t>중금속(납·비소·수은 등)·포름알데히드 등 한도, 미생물 한도(총호기성생균 등)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">출고 전 안전관리 시험성적서 확보 = 품질 신뢰·CS 방어</t>
+          <t>출고 전 안전관리 시험성적서 확보 = 품질 신뢰·CS 방어</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">출고 로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체는?</t>
+          <t>출고 로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체는?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">안 주면 리스크 — 발주 계약서에 명시</t>
+          <t>안 주면 리스크 — 발주 계약서에 명시</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[유통안전] 착향제 알레르기 성분</t>
+          <t>[유통안전] 착향제 알레르기 성분</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">착향 알레르기 유발성분 표시 대상 목록</t>
+          <t>착향 알레르기 유발성분 표시 대상 목록</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">다도기=무향이라 유리: '무향·착향 알레르겐 0' 소구 가능</t>
+          <t>다도기=무향이라 유리: '무향·착향 알레르겐 0' 소구 가능</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
+          <t>향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">무향이 곧 USP이자 규제 리스크 최소화</t>
+          <t>무향이 곧 USP이자 규제 리스크 최소화</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[유통안전] pH·안정성·사용기한</t>
+          <t>[유통안전] pH·안정성·사용기한</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">유형별 pH 기준, 안정성(가속·장기) 개념</t>
+          <t>유형별 pH 기준, 안정성(가속·장기) 개념</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용기한·보관조건의 과학적 근거 = 라벨·CS 뒷받침</t>
+          <t>사용기한·보관조건의 과학적 근거 = 라벨·CS 뒷받침</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">안정성 데이터로 사용기한 산정? 개봉후사용기간(PAO) 표기 근거?</t>
+          <t>안정성 데이터로 사용기한 산정? 개봉후사용기간(PAO) 표기 근거?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">읽어보기 '안정성 테스트' 섹션과 연결</t>
+          <t>읽어보기 '안정성 테스트' 섹션과 연결</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[맞춤형] 혼합·소분·위생</t>
+          <t>[맞춤형] 혼합·소분·위생</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">내용물+원료 혼합 가능/불가, 소분, 작업장 위생·장비 소독</t>
+          <t>내용물+원료 혼합 가능/불가, 소분, 작업장 위생·장비 소독</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">'맞춤형판매업' 직접 운영 시 핵심 역량 — 상담→조제 차별화</t>
+          <t>'맞춤형판매업' 직접 운영 시 핵심 역량 — 상담→조제 차별화</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">(자체검토) 벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지되나?</t>
+          <t>(자체검토) 벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지되나?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">조제관리사 자격의 직접 수익화 경로</t>
+          <t>조제관리사 자격의 직접 수익화 경로</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[맞춤형/제조] 계면활성제·세안</t>
+          <t>[맞춤형/제조] 계면활성제·세안</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">계면활성제 4분류(음이온/양이온/양쪽성/비이온), 세정 원리</t>
+          <t>계면활성제 4분류(음이온/양이온/양쪽성/비이온), 세정 원리</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">폼클렌저 등 세안 라인 기획 시 베이스 선택 기준</t>
+          <t>폼클렌저 등 세안 라인 기획 시 베이스 선택 기준</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 타깃 적합?</t>
+          <t>세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 타깃 적합?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">초기엔 위탁 권장(설비·충전 부담)</t>
+          <t>초기엔 위탁 권장(설비·충전 부담)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:E14"/>
   <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실습↔시험 개념 — 내가 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
+          <t>실습↔시험 개념 — 내가 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">성분은 「시험대비 원료맵」에서 봤다. 여기는 제형·공정·안정성·위생·장비 — 시험 비중이 가장 큰 영역이자, 내가 이미 손으로 하는 일. 수치·기준은 최신 고시로 재확인.</t>
+          <t>성분은 「시험대비 원료맵」에서 봤다. 여기는 제형·공정·안정성·위생·장비 — 시험 비중이 가장 큰 영역이자, 내가 이미 손으로 하는 일. 수치·기준은 최신 고시로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류(실습 영역)</t>
+          <t>분류(실습 영역)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">내가 하는 것 (엑셀 근거)</t>
+          <t>내가 하는 것 (엑셀 근거)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">→ 시험 개념 (외울 것)</t>
+          <t>→ 시험 개념 (외울 것)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">→ 사업 활용</t>
+          <t>→ 사업 활용</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주의/메모</t>
+          <t>주의/메모</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제형 분류]</t>
+          <t>[제형 분류]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 제형을 직접 설계·제조</t>
+          <t>토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 제형을 직접 설계·제조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">화장품 유형 분류, 유화형(O/W)·가용화·분산 제형 구분, 리브온/워시오프</t>
+          <t>화장품 유형 분류, 유화형(O/W)·가용화·분산 제형 구분, 리브온/워시오프</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">라인업 설계·제품유형 신고 기준, 어디까지 직접/위탁할지 선 긋기</t>
+          <t>라인업 설계·제품유형 신고 기준, 어디까지 직접/위탁할지 선 긋기</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">리브온(토너·크림)은 방부·향을 더 보수적으로</t>
+          <t>리브온(토너·크림)은 방부·향을 더 보수적으로</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[배합 설계·전성분]</t>
+          <t>[배합 설계·전성분]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 소량 정밀계량</t>
+          <t>처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 소량 정밀계량</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전성분 표시=함량 많은 순, 1% 이하·착향제·색소는 순서 무관, q.s. 개념</t>
+          <t>전성분 표시=함량 많은 순, 1% 이하·착향제·색소는 순서 무관, q.s. 개념</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">라벨 전성분 표기 검수·ODM 처방과 대조하는 눈</t>
+          <t>라벨 전성분 표기 검수·ODM 처방과 대조하는 눈</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">★처방 시트가 곧 전성분 표기 초안</t>
+          <t>★처방 시트가 곧 전성분 표기 초안</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조 공정]</t>
+          <t>[제조 공정]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">수상(A) 70~75℃ 가열 / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산, 유화 순서</t>
+          <t>수상(A) 70~75℃ 가열 / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산, 유화 순서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">가용화·유화·분산 공정, 상(phase) 개념, 가열·냉각·투입 순서</t>
+          <t>가용화·유화·분산 공정, 상(phase) 개념, 가열·냉각·투입 순서</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">공정 표준화=재현성 → 품질 일관성(리오더·CS 방어)</t>
+          <t>공정 표준화=재현성 → 품질 일관성(리오더·CS 방어)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">냉각군(방부·열에 약한 활성)은 40℃ 이하에서 투입</t>
+          <t>냉각군(방부·열에 약한 활성)은 40℃ 이하에서 투입</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[유화 안정성]</t>
+          <t>[유화 안정성]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">층분리·크리밍·오일링을 온도·전단(호모 HZ-400)·유화제 3요소로 교정</t>
+          <t>층분리·크리밍·오일링을 온도·전단(호모 HZ-400)·유화제 3요소로 교정</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">유화 안정성, 유화제 HLB·유화형(O/W·W/O), 상분리 원인</t>
+          <t>유화 안정성, 유화제 HLB·유화형(O/W·W/O), 상분리 원인</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">안정한 처방=반품·클레임 방지, ODM 샘플 평가 기준</t>
+          <t>안정한 처방=반품·클레임 방지, ODM 샘플 평가 기준</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">점도↑(잔탄검)도 기름방울 크리밍을 막는다</t>
+          <t>점도↑(잔탄검)도 기름방울 크리밍을 막는다</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[안정성 시험]</t>
+          <t>[안정성 시험]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">45℃(가속)·RT·4℃·동결융해 보관 + 원심분리(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
+          <t>45℃(가속)·RT·4℃·동결융해 보관 + 원심분리(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">안정성 시험(가속·장기·가혹), 경시변화, 유통화장품 안전관리</t>
+          <t>안정성 시험(가속·장기·가혹), 경시변화, 유통화장품 안전관리</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">★사용기한·개봉후사용기간(PAO) 산정 근거 = ODM에 요구할 핵심 데이터</t>
+          <t>★사용기한·개봉후사용기간(PAO) 산정 근거 = ODM에 요구할 핵심 데이터</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">투명 바이알로 변색·냄새·pH 눈 비교</t>
+          <t>투명 바이알로 변색·냄새·pH 눈 비교</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[pH 관리]</t>
+          <t>[pH 관리]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">목표 5.0~5.5, 구연산 희석액 한 방울씩 적정, pH미터 교정(버퍼 4·7)</t>
+          <t>목표 5.0~5.5, 구연산 희석액 한 방울씩 적정, pH미터 교정(버퍼 4·7)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">피부 약산성, 유형별 pH 기준, pH 측정법</t>
+          <t>피부 약산성, 유형별 pH 기준, pH 측정법</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">자극 최소화의 과학적 근거, 민감·지성 타깃 소구 포인트</t>
+          <t>자극 최소화의 과학적 근거, 민감·지성 타깃 소구 포인트</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">물 든 제품만 측정, 되직하면 정제수 1:1 희석 후 측정</t>
+          <t>물 든 제품만 측정, 되직하면 정제수 1:1 희석 후 측정</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[방부·미생물]</t>
+          <t>[방부·미생물]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용, 오염 증상 관찰</t>
+          <t>페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용, 오염 증상 관찰</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보존제 사용한도, 미생물 한도, 방부력(챌린지) 시험 개념</t>
+          <t>보존제 사용한도, 미생물 한도, 방부력(챌린지) 시험 개념</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">방부력 시험성적서를 ODM에 요구, 사용기한 설정 근거</t>
+          <t>방부력 시험성적서를 ODM에 요구, 사용기한 설정 근거</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">물+영양=미생물 배지. 헥산다이올은 지정 보존제 아님(책임 방부성분 따로)</t>
+          <t>물+영양=미생물 배지. 헥산다이올은 지정 보존제 아님(책임 방부성분 따로)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[산화·원료 보관]</t>
+          <t>[산화·원료 보관]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관(입출고·셀러)</t>
+          <t>토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관(입출고·셀러)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">산화방지제, 원료 보관조건, 비의도적 변질·유래물질</t>
+          <t>산화방지제, 원료 보관조건, 비의도적 변질·유래물질</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">원료 자재관리(CoA·로트·유효기간) → 품질·원가 통제</t>
+          <t>원료 자재관리(CoA·로트·유효기간) → 품질·원가 통제</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
+          <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[작업장 위생·혼합소분]</t>
+          <t>[작업장 위생·혼합소분]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">70% 에탄올로 도구·용기·손 소독, 향·색 전용도구, 완전 건조</t>
+          <t>70% 에탄올로 도구·용기·손 소독, 향·색 전용도구, 완전 건조</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">맞춤형 혼합·소분 작업장 위생, 교차오염 방지, 손 소독</t>
+          <t>맞춤형 혼합·소분 작업장 위생, 교차오염 방지, 손 소독</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">★맞춤형판매업 매장 운영 표준 = 조제관리사 실무 핵심(직접 수익화)</t>
+          <t>★맞춤형판매업 매장 운영 표준 = 조제관리사 실무 핵심(직접 수익화)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 오염이 자가제조 최대 리스크</t>
+          <t>미생물 오염이 자가제조 최대 리스크</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[장비·계량]</t>
+          <t>[장비·계량]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">정밀저울 0.01g(소량)·벤치저울(대량), 호모나이저, 오버헤드 교반, pH미터</t>
+          <t>정밀저울 0.01g(소량)·벤치저울(대량), 호모나이저, 오버헤드 교반, pH미터</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">혼합·소분 장비·기구, 계량 정확도·오차</t>
+          <t>혼합·소분 장비·기구, 계량 정확도·오차</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">소량 생산 설비 vs 위탁 판단, 맞춤형 매장 장비 구비 기준</t>
+          <t>소량 생산 설비 vs 위탁 판단, 맞춤형 매장 장비 구비 기준</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1% 이하는 정밀저울 — 큰 저울로 재면 처방이 망가진다</t>
+          <t>1% 이하는 정밀저울 — 큰 저울로 재면 처방이 망가진다</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[제조 기록·배치]</t>
+          <t>[제조 기록·배치]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">개발일지에 날짜·제품·배치량g·판정 기록, '한 번에 한 변수'</t>
+          <t>개발일지에 날짜·제품·배치량g·판정 기록, '한 번에 한 변수'</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">제조번호·제조기록서(뱃치기록), 제조일·사용기한 관리(CGMP 개념)</t>
+          <t>제조번호·제조기록서(뱃치기록), 제조일·사용기한 관리(CGMP 개념)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">로트 추적성=리콜·CS 대응력, ODM 품질계약의 기준</t>
+          <t>로트 추적성=리콜·CS 대응력, ODM 품질계약의 기준</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">접은 실험도 '이 방향 아님' 데이터 — 기록 보존</t>
+          <t>접은 실험도 '이 방향 아님' 데이터 — 기록 보존</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:E14"/>
   <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2609,7 +2803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:G321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2618,6 +2812,7 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="66" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2633,6 +2828,11 @@
           <t>[① 쉬움 — 유화 없음, 첫 실험용]   시크 진정 토너   ·   토너(비유화)   ·   sebum-calm-toner</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -3262,6 +3462,11 @@
           <t>[② 토너 변주 — 활성 농도↑, 유화 없음]   진정 밸런스 앰플   ·   앰플(비유화·고농축)   ·   sebum-calm-ampoule</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -3947,6 +4152,11 @@
           <t>[③ 점증 연습 — 잔탄검 분산]   진정 수분 젤   ·   젤(비유화·점증)   ·   soothing-gel</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -4576,6 +4786,11 @@
           <t>[④ 무수 오일 블렌딩 — 가열·유화·방부 없음]   딥 클렌징 오일 (닦아내기)   ·   클렌징오일(무수)   ·   sebum-calm-cleansing-oil</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -4890,6 +5105,11 @@
           <t>[⑤ 무수+가용화제 — 물 만나면 유백색 유화·헹굼]   워시오프 클렌징 오일   ·   클렌징오일(무수·가용화)   ·   sebum-calm-wash-cleansing-oil</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
@@ -5239,6 +5459,11 @@
           <t>[⑥ 유화 입문 — 오일 ~8%, 가벼운 에멀전]   밸런스 진정 로션   ·   로션(유화·경량)   ·   sebum-calm-lotion</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="17" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -6097,6 +6322,11 @@
       <c r="A265" s="6" t="inlineStr">
         <is>
           <t>[⑦ 유화 완성 — 히어로 v2, 오일 ~17%]   시크 진정 밸런스 크림 (히어로)   ·   크림(유화·리치)   ·   sebum-calm-cream</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
         </is>
       </c>
     </row>
@@ -6937,8 +7167,8 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="A239:F239"/>
-    <mergeCell ref="A301:F301"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A160:F160"/>
@@ -6975,8 +7205,8 @@
     <mergeCell ref="A241:F241"/>
     <mergeCell ref="A250:F250"/>
     <mergeCell ref="A315:F315"/>
+    <mergeCell ref="A237:F237"/>
     <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A237:F237"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A172:F172"/>
@@ -6998,9 +7228,9 @@
     <mergeCell ref="A204:F204"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A269:F269"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A269:F269"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A254:F254"/>
@@ -7140,6 +7370,7 @@
     <mergeCell ref="A196:F196"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14596,900 +14827,905 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원료↔시험 매핑 — 엑셀 26종을 맞춤형화장품조제관리사 시험 분류·사용한도로</t>
+          <t>원료↔시험 매핑 — 엑셀 26종을 맞춤형화장품조제관리사 시험 분류·사용한도로</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">★=시험 빈출/함정 포인트. 사용한도는 식약처 「화장품 안전기준 등에 관한 규정」 기준 — 제조·판매 전 최신 고시 반드시 재확인.</t>
+          <t>★=시험 빈출/함정 포인트. 사용한도는 식약처 「화장품 안전기준 등에 관한 규정」 기준 — 제조·판매 전 최신 고시 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원료</t>
+          <t>원료</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INCI</t>
+          <t>INCI</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">엑셀 역할</t>
+          <t>엑셀 역할</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 분류</t>
+          <t>시험 분류</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도·고시 포인트</t>
+          <t>사용한도·고시 포인트</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시험 빈출 메모</t>
+          <t>시험 빈출 메모</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">글리세린</t>
+          <t>글리세린</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glycerin</t>
+          <t>Glycerin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습</t>
+          <t>보습</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습제(휴멕턴트)·수성원료</t>
+          <t>보습제(휴멕턴트)·수성원료</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음(일반원료)</t>
+          <t>사용한도 없음(일반원료)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">대표 다가알코올 보습제, 수상</t>
+          <t>대표 다가알코올 보습제, 수상</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">나이아신아마이드</t>
+          <t>나이아신아마이드</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niacinamide</t>
+          <t>Niacinamide</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미백 기능성 고시 주성분 / 활성</t>
+          <t>미백 기능성 고시 주성분 / 활성</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미백 고시 함량 2~5%</t>
+          <t>미백 고시 함량 2~5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">★빈출: 미백 주성분·2~5% 암기</t>
+          <t>★빈출: 미백 주성분·2~5% 암기</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">다중 히알루론산</t>
+          <t>다중 히알루론산</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyaluronic Acids</t>
+          <t>Hyaluronic Acids</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습</t>
+          <t>보습</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습제(고분자 휴멕턴트)</t>
+          <t>보습제(고분자 휴멕턴트)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">분자량별 보습, 수용성 고분자</t>
+          <t>분자량별 보습, 수용성 고분자</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">베타글루칸</t>
+          <t>베타글루칸</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beta-Glucan</t>
+          <t>Beta-Glucan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성(진정)·고분자 다당류</t>
+          <t>활성(진정)·고분자 다당류</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">진정 유효성분</t>
+          <t>진정 유효성분</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">베타인</t>
+          <t>베타인</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betaine</t>
+          <t>Betaine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습</t>
+          <t>보습</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습제(휴멕턴트)</t>
+          <t>보습제(휴멕턴트)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">아미노산계 보습제</t>
+          <t>아미노산계 보습제</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">아연피카</t>
+          <t>아연피카</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zinc PCA</t>
+          <t>Zinc PCA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성(피지·수렴)</t>
+          <t>활성(피지·수렴)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zinc PCA 피지조절</t>
+          <t>Zinc PCA 피지조절</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">알란토인</t>
+          <t>알란토인</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allantoin</t>
+          <t>Allantoin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성(진정·각질)</t>
+          <t>활성(진정·각질)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">진정·보습 보조</t>
+          <t>진정·보습 보조</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">잔탄검</t>
+          <t>잔탄검</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xanthan Gum</t>
+          <t>Xanthan Gum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">점증제</t>
+          <t>점증제</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">점증제(천연 고분자)</t>
+          <t>점증제(천연 고분자)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">대표 천연 점증제, 선분산</t>
+          <t>대표 천연 점증제, 선분산</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">정제수</t>
+          <t>정제수</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">용제</t>
+          <t>용제</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">수성원료(용제·기제)</t>
+          <t>수성원료(용제·기제)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">기제, 순도·미생물 관리 대상</t>
+          <t>기제, 순도·미생물 관리 대상</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로판디올</t>
+          <t>프로판디올</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Propanediol</t>
+          <t>Propanediol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습</t>
+          <t>보습</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">보습제·용제(다가알코올)</t>
+          <t>보습제·용제(다가알코올)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">글리콜계, 방부 보조력</t>
+          <t>글리콜계, 방부 보조력</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCT오일</t>
+          <t>MCT오일</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caprylic/Capric Triglyceride</t>
+          <t>Caprylic/Capric Triglyceride</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">유상·에몰리언트</t>
+          <t>유상·에몰리언트</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">유성원료(에스터 오일·에몰리언트)</t>
+          <t>유성원료(에스터 오일·에몰리언트)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caprylic/Capric Triglyceride</t>
+          <t>Caprylic/Capric Triglyceride</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">디메치콘</t>
+          <t>디메치콘</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimethicone</t>
+          <t>Dimethicone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">감촉·실리콘</t>
+          <t>감촉·실리콘</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">유성원료(실리콘)</t>
+          <t>유성원료(실리콘)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">실리콘 오일, 발림·보호막</t>
+          <t>실리콘 오일, 발림·보호막</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">몬타노브68</t>
+          <t>몬타노브68</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
+          <t>Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">유화제</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">계면활성제(비이온 유화제)+고급지방알코올</t>
+          <t>계면활성제(비이온 유화제)+고급지방알코올</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">O/W 유화제, HLB·유화 개념</t>
+          <t>O/W 유화제, HLB·유화 개념</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">세틸알코올</t>
+          <t>세틸알코올</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cetyl Alcohol</t>
+          <t>Cetyl Alcohol</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">유상·에몰리언트</t>
+          <t>유상·에몰리언트</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">고급지방알코올(유성·보조유화)</t>
+          <t>고급지방알코올(유성·보조유화)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">점도·유화 안정화</t>
+          <t>점도·유화 안정화</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">스쿠알란</t>
+          <t>스쿠알란</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Squalane</t>
+          <t>Squalane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">유상·에몰리언트</t>
+          <t>유상·에몰리언트</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">유성원료(에몰리언트)</t>
+          <t>유성원료(에몰리언트)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">안정성 높은 보습 오일</t>
+          <t>안정성 높은 보습 오일</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">시어버터</t>
+          <t>시어버터</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Butyrospermum Parkii Butter</t>
+          <t>Butyrospermum Parkii Butter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">유상·에몰리언트</t>
+          <t>유상·에몰리언트</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">유성원료(식물성 버터)</t>
+          <t>유성원료(식물성 버터)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">고형 유지, 에몰리언트</t>
+          <t>고형 유지, 에몰리언트</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">올리브유화왁스</t>
+          <t>올리브유화왁스</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cetearyl Olivate &amp; Sorbitan Olivate</t>
+          <t>Cetearyl Olivate &amp; Sorbitan Olivate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">유화제</t>
+          <t>유화제</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">계면활성제(비이온 유화제)</t>
+          <t>계면활성제(비이온 유화제)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">올리브 유래 O/W 유화제</t>
+          <t>올리브 유래 O/W 유화제</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">토코페롤(비타민E)</t>
+          <t>토코페롤(비타민E)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tocopherol</t>
+          <t>Tocopherol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">항산화제</t>
+          <t>항산화제</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">산화방지제</t>
+          <t>산화방지제</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음(산화방지 목적)</t>
+          <t>사용한도 없음(산화방지 목적)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">★분류주의: 산화방지제(보존제 아님)</t>
+          <t>★분류주의: 산화방지제(보존제 아님)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">폴리글리세릴-4 카프레이트</t>
+          <t>폴리글리세릴-4 카프레이트</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polyglyceryl-4 Caprate</t>
+          <t>Polyglyceryl-4 Caprate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">가용화제</t>
+          <t>가용화제</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">계면활성제(비이온 가용화제)</t>
+          <t>계면활성제(비이온 가용화제)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">워시오프 가용화·세정 보조</t>
+          <t>워시오프 가용화·세정 보조</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">호호바오일</t>
+          <t>호호바오일</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simmondsia Chinensis Seed Oil</t>
+          <t>Simmondsia Chinensis Seed Oil</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">유상·에몰리언트</t>
+          <t>유상·에몰리언트</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">유성원료(왁스 에스터 오일)</t>
+          <t>유성원료(왁스 에스터 오일)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">피지 유사 왁스 에스터</t>
+          <t>피지 유사 왁스 에스터</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2-헥산다이올</t>
+          <t>1,2-헥산다이올</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1,2-Hexanediol</t>
+          <t>1,2-Hexanediol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">방부제</t>
+          <t>방부제</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">다가알코올(보습·방부 보조)</t>
+          <t>다가알코올(보습·방부 보조)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">★지정 보존제 아님(사용제한 목록 미등재)</t>
+          <t>★지정 보존제 아님(사용제한 목록 미등재)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">★함정: 방부력 있어도 법적 보존제 아님</t>
+          <t>★함정: 방부력 있어도 법적 보존제 아님</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">녹차추출물</t>
+          <t>녹차추출물</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camellia Sinensis Leaf Extract</t>
+          <t>Camellia Sinensis Leaf Extract</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물추출물(활성)</t>
+          <t>식물추출물(활성)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">수용성 추출물</t>
+          <t>수용성 추출물</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">마데카소사이드</t>
+          <t>마데카소사이드</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madecassoside</t>
+          <t>Madecassoside</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물추출물 활성(센텔라)</t>
+          <t>식물추출물 활성(센텔라)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">진정 활성</t>
+          <t>진정 활성</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">판테놀(B5)</t>
+          <t>판테놀(B5)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panthenol</t>
+          <t>Panthenol</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성(보습·진정)</t>
+          <t>활성(보습·진정)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로비타민 B5</t>
+          <t>프로비타민 B5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">페녹시에탄올</t>
+          <t>페녹시에탄올</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phenoxyethanol</t>
+          <t>Phenoxyethanol</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">방부제</t>
+          <t>방부제</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">보존제(사용제한 원료)</t>
+          <t>보존제(사용제한 원료)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">★사용한도 1.0%</t>
+          <t>★사용한도 1.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">★최빈출: 보존제·한도 1.0% 필수암기</t>
+          <t>★최빈출: 보존제·한도 1.0% 필수암기</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">구연산</t>
+          <t>구연산</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Citric Acid</t>
+          <t>Citric Acid</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pH조절</t>
+          <t>pH조절</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pH 조절제</t>
+          <t>pH 조절제</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용한도 없음</t>
+          <t>사용한도 없음</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">citric acid, pH 5 안팎 조절</t>
+          <t>citric acid, pH 5 안팎 조절</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:F29"/>
   <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -307,6 +307,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -332,6 +335,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -357,6 +363,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -382,6 +391,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -407,6 +419,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -432,6 +447,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -457,6 +475,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -553,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="처방표" displayName="처방표" ref="A3:F92" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="처방표" displayName="처방표" ref="A3:F108" headerRowCount="1">
   <autoFilter ref="A3:F92"/>
   <tableColumns count="6">
     <tableColumn id="1" name="제품"/>
@@ -2047,13 +2068,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A1:B1"/>
@@ -2062,7 +2083,7 @@
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2803,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G321"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7155,15 +7176,772 @@
         </is>
       </c>
     </row>
+    <row r="323" ht="26" customHeight="1">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>[⑧ 미니멀 변주 — 히어로에서 활성 3종만]   시크 진정 크림 (미니멀 3종)   ·   크림(유화·리치)   ·   sebum-calm-cream-minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="32" customHeight="1">
+      <c r="A324" s="7" t="inlineStr">
+        <is>
+          <t>컨셉 │ 히어로 크림을 활성 핵심 3종으로 좁힌 미니멀 버전. 베이스(유화·보습·방부)는 히어로 v2와 동일, 활성만 나이아신아마이드·시카·베타글루칸으로 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="17" customHeight="1">
+      <c r="A325" s="8" t="inlineStr">
+        <is>
+          <t>설계 이유 (왜 이렇게 만들었나)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="17" customHeight="1">
+      <c r="A326" s="9" t="inlineStr">
+        <is>
+          <t>· 히어로 v2에서 활성을 '핵심 3종'으로 좁힌 미니멀 버전 — 유화·보습·방부 베이스는 그대로 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="17" customHeight="1">
+      <c r="A327" s="9" t="inlineStr">
+        <is>
+          <t>· 활성 3종만 남긴다: 나이아신아마이드(피지·장벽·톤) · 마데카소사이드(시카 진정) · 베타글루칸(진정+수분).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="17" customHeight="1">
+      <c r="A328" s="9" t="inlineStr">
+        <is>
+          <t>· 역할이 겹치던 아연PCA·알란토인·판테놀과, 갈변 리스크가 있는 녹차추출물은 뺐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="17" customHeight="1">
+      <c r="A329" s="9" t="inlineStr">
+        <is>
+          <t>· 활성이 적을수록 자극 변수·갈변 리스크가 줄고, 무엇이 효과를 냈는지 해석이 쉽다 — '정직한' 처방 훈련.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="17" customHeight="1">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>· 뺀 자리는 정제수로 채워 합 100% 유지(유상 ~17%·세이프 에몰리언트 구성은 히어로와 동일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="17" customHeight="1">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>특징 │ 활성 3종 미니멀  ·  말라세지아-세이프  ·  무향  ·  히어로 v2 베이스 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="10" t="inlineStr">
+        <is>
+          <t>원료</t>
+        </is>
+      </c>
+      <c r="B332" s="10" t="inlineStr">
+        <is>
+          <t>INCI</t>
+        </is>
+      </c>
+      <c r="C332" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="D332" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E332" s="10" t="inlineStr">
+        <is>
+          <t>g(100g)</t>
+        </is>
+      </c>
+      <c r="F332" s="10" t="inlineStr">
+        <is>
+          <t>이 원료가 하는 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="32" customHeight="1">
+      <c r="A333" s="11" t="inlineStr">
+        <is>
+          <t>정제수</t>
+        </is>
+      </c>
+      <c r="B333" s="12" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C333" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D333" s="14" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E333" s="14" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F333" s="12" t="inlineStr">
+        <is>
+          <t>모든 성분을 녹이는 바탕(제품의 대부분을 차지).  ※베이스(q.s. 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="32" customHeight="1">
+      <c r="A334" s="11" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="B334" s="12" t="inlineStr">
+        <is>
+          <t>Glycerin</t>
+        </is>
+      </c>
+      <c r="C334" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D334" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E334" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F334" s="12" t="inlineStr">
+        <is>
+          <t>수분을 끌어당기는 대표 보습제. 잔탄검을 미리 개는 매개로도 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="32" customHeight="1">
+      <c r="A335" s="11" t="inlineStr">
+        <is>
+          <t>나이아신아마이드</t>
+        </is>
+      </c>
+      <c r="B335" s="12" t="inlineStr">
+        <is>
+          <t>Niacinamide</t>
+        </is>
+      </c>
+      <c r="C335" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D335" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E335" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F335" s="12" t="inlineStr">
+        <is>
+          <t>비타민B3. 피지·모공·피부톤·장벽을 두루 돕는 대표 활성.  ※핵심 활성 ①(민감 시 2%부터 시작)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="32" customHeight="1">
+      <c r="A336" s="11" t="inlineStr">
+        <is>
+          <t>베타글루칸</t>
+        </is>
+      </c>
+      <c r="B336" s="12" t="inlineStr">
+        <is>
+          <t>Beta-Glucan</t>
+        </is>
+      </c>
+      <c r="C336" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D336" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E336" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F336" s="12" t="inlineStr">
+        <is>
+          <t>진정+수분. 예민한 피부를 달랜다.  ※핵심 활성 ②(진정+수분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="17" customHeight="1">
+      <c r="A337" s="11" t="inlineStr">
+        <is>
+          <t>프로판디올</t>
+        </is>
+      </c>
+      <c r="B337" s="12" t="inlineStr">
+        <is>
+          <t>Propanediol</t>
+        </is>
+      </c>
+      <c r="C337" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D337" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E337" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F337" s="12" t="inlineStr">
+        <is>
+          <t>보습하면서 방부를 거드는 보조 폴리올.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="32" customHeight="1">
+      <c r="A338" s="11" t="inlineStr">
+        <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="B338" s="12" t="inlineStr">
+        <is>
+          <t>Xanthan Gum</t>
+        </is>
+      </c>
+      <c r="C338" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D338" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E338" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F338" s="12" t="inlineStr">
+        <is>
+          <t>천연 점증제. 젤·에멀전에 점도와 안정성을 준다(글리세린에 선분산).  ※글리세린 선분산</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="32" customHeight="1">
+      <c r="A339" s="11" t="inlineStr">
+        <is>
+          <t>다중 히알루론산</t>
+        </is>
+      </c>
+      <c r="B339" s="12" t="inlineStr">
+        <is>
+          <t>Hyaluronic Acids</t>
+        </is>
+      </c>
+      <c r="C339" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D339" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E339" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" s="12" t="inlineStr">
+        <is>
+          <t>분자 크기별 히알루론산으로 층층이 수분 충전(유분 없이 보습).  ※미리 불려 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="32" customHeight="1">
+      <c r="A340" s="11" t="inlineStr">
+        <is>
+          <t>몬타노브68</t>
+        </is>
+      </c>
+      <c r="B340" s="12" t="inlineStr">
+        <is>
+          <t>Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
+        </is>
+      </c>
+      <c r="C340" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D340" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E340" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F340" s="12" t="inlineStr">
+        <is>
+          <t>물과 기름을 섞어주는 유화제(글루코사이드계·세이프).  ※유화제(세이프)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="17" customHeight="1">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>세틸알코올</t>
+        </is>
+      </c>
+      <c r="B341" s="12" t="inlineStr">
+        <is>
+          <t>Cetyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C341" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D341" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E341" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F341" s="12" t="inlineStr">
+        <is>
+          <t>유화를 안정화하고 바디·발림감을 주는 지방알코올.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="17" customHeight="1">
+      <c r="A342" s="11" t="inlineStr">
+        <is>
+          <t>스쿠알란</t>
+        </is>
+      </c>
+      <c r="B342" s="12" t="inlineStr">
+        <is>
+          <t>Squalane</t>
+        </is>
+      </c>
+      <c r="C342" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D342" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E342" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F342" s="12" t="inlineStr">
+        <is>
+          <t>가볍고 안정적인 보습 오일. 피부 유래라 순함(세이프).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="17" customHeight="1">
+      <c r="A343" s="11" t="inlineStr">
+        <is>
+          <t>MCT오일</t>
+        </is>
+      </c>
+      <c r="B343" s="12" t="inlineStr">
+        <is>
+          <t>Caprylic/Capric Triglyceride</t>
+        </is>
+      </c>
+      <c r="C343" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D343" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E343" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F343" s="12" t="inlineStr">
+        <is>
+          <t>아주 가벼운 오일. 세정·발림 베이스(C8/C10·세이프).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="17" customHeight="1">
+      <c r="A344" s="11" t="inlineStr">
+        <is>
+          <t>디메치콘</t>
+        </is>
+      </c>
+      <c r="B344" s="12" t="inlineStr">
+        <is>
+          <t>Dimethicone</t>
+        </is>
+      </c>
+      <c r="C344" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D344" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E344" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F344" s="12" t="inlineStr">
+        <is>
+          <t>실키한 발림과 얇은 보호막을 주는 실리콘.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="32" customHeight="1">
+      <c r="A345" s="11" t="inlineStr">
+        <is>
+          <t>마데카소사이드</t>
+        </is>
+      </c>
+      <c r="B345" s="12" t="inlineStr">
+        <is>
+          <t>Madecassoside</t>
+        </is>
+      </c>
+      <c r="C345" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D345" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E345" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F345" s="12" t="inlineStr">
+        <is>
+          <t>병풀(시카)의 진정 핵심 성분.  ※핵심 활성 ③(시카 진정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="17" customHeight="1">
+      <c r="A346" s="11" t="inlineStr">
+        <is>
+          <t>페녹시에탄올</t>
+        </is>
+      </c>
+      <c r="B346" s="12" t="inlineStr">
+        <is>
+          <t>Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="C346" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D346" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E346" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F346" s="12" t="inlineStr">
+        <is>
+          <t>세균·곰팡이를 막는 방부제(물 든 제품엔 필수).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="17" customHeight="1">
+      <c r="A347" s="11" t="inlineStr">
+        <is>
+          <t>1,2-헥산다이올</t>
+        </is>
+      </c>
+      <c r="B347" s="12" t="inlineStr">
+        <is>
+          <t>1,2-Hexanediol</t>
+        </is>
+      </c>
+      <c r="C347" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D347" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E347" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F347" s="12" t="inlineStr">
+        <is>
+          <t>방부를 돕고 보습도 하는 부스터.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="32" customHeight="1">
+      <c r="A348" s="11" t="inlineStr">
+        <is>
+          <t>구연산</t>
+        </is>
+      </c>
+      <c r="B348" s="12" t="inlineStr">
+        <is>
+          <t>Citric Acid</t>
+        </is>
+      </c>
+      <c r="C348" s="16" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D348" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E348" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F348" s="12" t="inlineStr">
+        <is>
+          <t>산도(pH)를 피부에 맞게 낮추는 조절제.  ※pH 5.0~5.5 q.s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="17" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B349" s="18" t="n"/>
+      <c r="C349" s="18" t="n"/>
+      <c r="D349" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E349" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F349" s="18" t="n"/>
+    </row>
+    <row r="350" ht="17" customHeight="1">
+      <c r="A350" s="8" t="inlineStr">
+        <is>
+          <t>만드는 법</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="47" customHeight="1">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>① 준비·동선: 도구·용기·교반날을 70% 알코올로 소독. 비커는 100g 배치 기준 수상 A=250mL(HS5Pro 위), 유상 B=100mL(중탕용), 냉각 C는 유산지/소형 비커에 계량(200g면 500mL/250mL). ★가열·유화·냄새나는 계량은 '클린벤치 밖'(환기), 식힌 뒤 충전·마무리만 클린벤치 안.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="17" customHeight="1">
+      <c r="A352" s="9" t="inlineStr">
+        <is>
+          <t>★ 계량·비커 (처음이면 꼭 — 100g 배치 기준):</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="32" customHeight="1">
+      <c r="A353" s="9" t="inlineStr">
+        <is>
+          <t>– 저울 2개를 나눠 쓴다: 정제수·오일처럼 많은 양은 벤치저울(0.1g 단위), 활성·검·보존제·향처럼 1% 이하 소량은 정밀저울(0.01g 단위). 소량을 큰 저울로 재면 오차가 처방을 망친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="32" customHeight="1">
+      <c r="A354" s="9" t="inlineStr">
+        <is>
+          <t>– 분말·점성 원료: 저울에 유산지(칭량지)를 깔고 → 영점(TARE 버튼) → 원료를 담는다. 글리세린·오일 같은 액체는 '받을 비커'를 올리고 TARE 후 바로 부어 넣는다(유산지에 눌어붙음 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="17" customHeight="1">
+      <c r="A355" s="9" t="inlineStr">
+        <is>
+          <t>– 정제수는 '맨 마지막에 100g을 맞추는 잔량'으로 넣는다(다른 걸 다 더하고 남는 양).</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="17" customHeight="1">
+      <c r="A356" s="9" t="inlineStr">
+        <is>
+          <t>– 비커 크기 = 내용물의 약 2~2.5배(가열·교반 때 넘침 방지). 200g 배치면 한 단계 큰 비커로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="17" customHeight="1">
+      <c r="A357" s="9" t="inlineStr">
+        <is>
+          <t>– 흘리면 닦고 다시. 통에 손·젖은 도구 넣지 않기(오염). 소량은 깨끗한 스패출러로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="32" customHeight="1">
+      <c r="A358" s="9" t="inlineStr">
+        <is>
+          <t>② 상 나눠 계량: 수상 A(정제수·글리세린·판테놀·검) / 유상 B(오일·세틸알코올·몬타노브68) / 냉각 C(보존제·향·열 약한 활성)는 대기. 검은 글리세린에 선분산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="32" customHeight="1">
+      <c r="A359" s="9" t="inlineStr">
+        <is>
+          <t>③ 수상 A 가열: HS5Pro 비커에 자석교반자(stir bar)를 넣고 중속 교반 + ★온도 프로브를 'A 액체'에 꽂아 70~75℃ 제어(상판 온도 아님).</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="32" customHeight="1">
+      <c r="A360" s="9" t="inlineStr">
+        <is>
+          <t>④ 유상 B 가열: 냄비 중탕으로 70~75℃까지 '용해'(교반보다 완전 용해가 중요). 별도 디지털 온도계로 B 확인(감 X). (항온수조 OB-2Pro는 아직 미보유라 중탕으로 대체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="32" customHeight="1">
+      <c r="A361" s="9" t="inlineStr">
+        <is>
+          <t>⑤ 두 상 70~75℃에서 약 20분 유지(완전 용해+미생물 부담↓). 시계접시·뚜껑으로 덮어 증발을 줄이고, 합치기 직전 줄어든 무게만큼 뜨거운 정제수로 보충.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="32" customHeight="1">
+      <c r="A362" s="9" t="inlineStr">
+        <is>
+          <t>⑥ 합치기 전: 수상의 자석교반자를 회수 막대로 빼둔다(호모 날 충돌 방지). 두 상 온도를 ±5℃로 맞춘다(어긋나면 유화가 안 붙는다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="32" customHeight="1">
+      <c r="A363" s="9" t="inlineStr">
+        <is>
+          <t>⑦ 유화(HZ-400): 유상 B를 수상 A에 부으며 호모나이저 날이 충분히 잠기게 세우고 2~5분 고속. 비커 벽 따라 천천히 이동해 전체를 균질화. ★유화는 오직 호모 몫 — 마그네틱·손젓기는 전단이 부족해 분리된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="17" customHeight="1">
+      <c r="A364" s="9" t="inlineStr">
+        <is>
+          <t>⑧ '붙으면'(뽀얀 크림색) 호모를 멈춘다. 오래 돌리면 기포·점도 저하 → 바로 냉각 교반으로 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="32" customHeight="1">
+      <c r="A365" s="9" t="inlineStr">
+        <is>
+          <t>⑨ 냉각 교반(OC-15S): 오버헤드 패들을 바닥서 1~2cm 띄우고 저속으로 40℃까지. 소용돌이가 깊으면 공기를 말아 기포가 된다. 묽은 로션은 HS5Pro 마그네틱만으로도 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="17" customHeight="1">
+      <c r="A366" s="9" t="inlineStr">
+        <is>
+          <t>⑩ 40℃ 이하서 냉각첨가 C: 보존제(페녹시+헥산다이올)·향·열 약한 활성. 뜨거울 때 넣으면 날아가거나 변질된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="32" customHeight="1">
+      <c r="A367" s="9" t="inlineStr">
+        <is>
+          <t>⑪ pH: 30℃대~실온에서 pH미터(교정 후)로 측정 → 5.0~5.5로 보정(구연산 희석액 한 방울씩, 다시 측정). 증발분은 정제수로 총량 100g 맞춤.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="32" customHeight="1">
+      <c r="A368" s="9" t="inlineStr">
+        <is>
+          <t>⑫ ★당일 유화 판정(LC-8S 원심): 15mL 튜브에 ~10g씩 2개(무게 대칭) → 3,000rpm·30분 → 분리층(오일링/크리밍/침전) mm 확인 → 개발일지 '분리mm'에 숫자로 기록. 0이면 안정성 큐로, 있으면 튜닝/접기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="32" customHeight="1">
+      <c r="A369" s="9" t="inlineStr">
+        <is>
+          <t>⑬ 충전·안정성: 클린벤치 안에서 소독한 용기에 충전. 투명 바이알에 4조건(45℃·실온·4℃·냉동융해)+대조군 소분, 1·2·4·8주 관찰(45℃는 발효기/인큐베이터).</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="32" customHeight="1">
+      <c r="A370" s="9" t="inlineStr">
+        <is>
+          <t>★ 크림(유상↑): 유상 완전 용해에 시간 더 / 호모는 '더 짧게 확실히'(점도 높아 기포 위험) / 오버헤드 냉각은 '더 길게'(굳기 전 C 투입).</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="17" customHeight="1">
+      <c r="A371" s="9" t="inlineStr">
+        <is>
+          <t>★ pH 스트립 읽는 법:</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="32" customHeight="1">
+      <c r="A372" s="9" t="inlineStr">
+        <is>
+          <t>– 스트립을 액에 1초 담갔다 빼고, 10~15초 뒤(설명서 시간) 색이 멈췄을 때 '자연광'에서 통에 인쇄된 색표와 맞춘다(형광등 아래는 색이 왜곡된다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="32" customHeight="1">
+      <c r="A373" s="9" t="inlineStr">
+        <is>
+          <t>– 색표 두 칸 사이로 보이면 중간값으로 읽는다(예: 5와 5.5 사이면 ≈5.2). 0.2~0.5 눈금의 정밀 스트립을 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="17" customHeight="1">
+      <c r="A374" s="9" t="inlineStr">
+        <is>
+          <t>– 크림·젤처럼 되직해 색이 안 보이면 정제수와 1:1로 풀어서 잰다(묽혀도 pH는 거의 그대로).</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="17" customHeight="1">
+      <c r="A375" s="9" t="inlineStr">
+        <is>
+          <t>– 색이 금세 바래니 빼서 오래 두지 말고 바로 판독. 젖은 손·금속이 스트립에 닿지 않게.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="17" customHeight="1">
+      <c r="A376" s="9" t="inlineStr">
+        <is>
+          <t>– 목표 5.0~5.5. 더 정확히는 pH 미터(보정액으로 교정 후 사용). 스트립은 ±0.3 오차가 정상이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="32" customHeight="1">
+      <c r="A377" s="9" t="inlineStr">
+        <is>
+          <t>★ 흔한 실수: 두 상 온도 안 맞춤(분리) / 자석바 안 빼고 호모(충돌) / 호모 과다(기포·점도↓) / 식기 전 C 투입(열 파괴).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="211">
+  <mergeCells count="248">
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A133:F133"/>
     <mergeCell ref="A317:F317"/>
     <mergeCell ref="A198:F198"/>
     <mergeCell ref="A238:F238"/>
+    <mergeCell ref="A351:F351"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A369:F369"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
@@ -7173,6 +7951,7 @@
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A160:F160"/>
     <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A331:F331"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A150:F150"/>
     <mergeCell ref="A32:F32"/>
@@ -7181,6 +7960,7 @@
     <mergeCell ref="A303:F303"/>
     <mergeCell ref="A321:F321"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A373:F373"/>
     <mergeCell ref="A318:F318"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A134:F134"/>
@@ -7189,25 +7969,32 @@
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A152:F152"/>
     <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A323:F323"/>
     <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A372:F372"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A249:F249"/>
     <mergeCell ref="A320:F320"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A202:F202"/>
     <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A266:F266"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A260:F260"/>
+    <mergeCell ref="A358:F358"/>
     <mergeCell ref="A241:F241"/>
     <mergeCell ref="A250:F250"/>
     <mergeCell ref="A315:F315"/>
+    <mergeCell ref="A355:F355"/>
     <mergeCell ref="A237:F237"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A360:F360"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A172:F172"/>
     <mergeCell ref="A212:F212"/>
@@ -7242,11 +8029,13 @@
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="A240:F240"/>
     <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A377:F377"/>
     <mergeCell ref="A125:F125"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A362:F362"/>
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="A167:F167"/>
     <mergeCell ref="A48:F48"/>
@@ -7263,6 +8052,7 @@
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A359:F359"/>
     <mergeCell ref="A153:F153"/>
     <mergeCell ref="A162:F162"/>
     <mergeCell ref="A54:F54"/>
@@ -7272,7 +8062,10 @@
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="A208:F208"/>
     <mergeCell ref="A268:F268"/>
+    <mergeCell ref="A330:F330"/>
     <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A366:F366"/>
+    <mergeCell ref="A375:F375"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A56:F56"/>
@@ -7288,18 +8081,22 @@
     <mergeCell ref="A307:F307"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A203:F203"/>
+    <mergeCell ref="A374:F374"/>
     <mergeCell ref="A181:F181"/>
     <mergeCell ref="A309:F309"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A361:F361"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="A244:F244"/>
     <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A371:F371"/>
     <mergeCell ref="A140:F140"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A171:F171"/>
     <mergeCell ref="A165:F165"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="A253:F253"/>
+    <mergeCell ref="A324:F324"/>
     <mergeCell ref="A299:F299"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A93:F93"/>
@@ -7307,6 +8104,7 @@
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A173:F173"/>
     <mergeCell ref="A295:F295"/>
+    <mergeCell ref="A353:F353"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="A143:F143"/>
@@ -7315,7 +8113,10 @@
     <mergeCell ref="A270:F270"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A310:F310"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A368:F368"/>
+    <mergeCell ref="A350:F350"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A300:F300"/>
@@ -7324,10 +8125,13 @@
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A370:F370"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A256:F256"/>
     <mergeCell ref="A271:F271"/>
     <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A354:F354"/>
+    <mergeCell ref="A363:F363"/>
     <mergeCell ref="A316:F316"/>
     <mergeCell ref="A246:F246"/>
     <mergeCell ref="A128:F128"/>
@@ -7335,9 +8139,14 @@
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A326:F326"/>
+    <mergeCell ref="A364:F364"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A356:F356"/>
+    <mergeCell ref="A365:F365"/>
     <mergeCell ref="A192:F192"/>
     <mergeCell ref="A248:F248"/>
+    <mergeCell ref="A376:F376"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="A297:F297"/>
     <mergeCell ref="A57:F57"/>
@@ -7348,11 +8157,13 @@
     <mergeCell ref="A194:F194"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A367:F367"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A209:F209"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A327:F327"/>
     <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A211:F211"/>
@@ -7361,10 +8172,12 @@
     <mergeCell ref="A201:F201"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A352:F352"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="A132:F132"/>
     <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A325:F325"/>
     <mergeCell ref="A146:F146"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A196:F196"/>
@@ -12243,7 +13056,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B4:B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"시크 진정 토너,진정 밸런스 앰플,진정 수분 젤,딥 클렌징 오일 (닦아내기),워시오프 클렌징 오일,밸런스 진정 로션,시크 진정 밸런스 크림 (히어로)"</formula1>
+      <formula1>"시크 진정 토너,진정 밸런스 앰플,진정 수분 젤,딥 클렌징 오일 (닦아내기),워시오프 클렌징 오일,밸런스 진정 로션,시크 진정 밸런스 크림 (히어로),시크 진정 크림 (미니멀 3종)"</formula1>
     </dataValidation>
     <dataValidation sqref="F4:F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ok,실패"</formula1>
@@ -12265,7 +13078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14810,6 +15623,454 @@
         <v/>
       </c>
       <c r="F92" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>정제수</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E93" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F93" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F94" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>나이아신아마이드</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F95" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>베타글루칸</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F96" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>프로판디올</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F97" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E98" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F98" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>다중 히알루론산</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F99" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>몬타노브68</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F100" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>세틸알코올</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F101" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>스쿠알란</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E102" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F102" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>MCT오일</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F103" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>디메치콘</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F104" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>마데카소사이드</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F105" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>페녹시에탄올</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E106" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F106" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>1,2-헥산다이올</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F107" s="14">
+        <f>[@퍼센트]/100*[@제조누계g]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>시크 진정 크림 (미니멀 3종)</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>구연산</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E108" s="14">
+        <f>SUMIF(개발일지표[제품],[@제품],개발일지표[배치량g])</f>
+        <v/>
+      </c>
+      <c r="F108" s="14">
         <f>[@퍼센트]/100*[@제조누계g]</f>
         <v/>
       </c>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -15,15 +15,12 @@
     <sheet name="입출고" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="개발일지" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="처방" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="시험대비 원료맵" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="시험→사업 활용" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="실습↔시험 개념" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="시험 핵심개념" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="시험대비 원료맵" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="시험→사업 활용" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="실습↔시험 개념" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'시험대비 원료맵'!$A$3:$F$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'시험→사업 활용'!$A$3:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'실습↔시험 개념'!$A$3:$E$14</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -139,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -199,6 +196,9 @@
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,6 +500,20 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="실습시험표" displayName="실습시험표" ref="A3:E21" headerRowCount="1">
+  <autoFilter ref="A3:E21"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="분류(실습 영역)"/>
+    <tableColumn id="2" name="내가 하는 것 (엑셀 근거)"/>
+    <tableColumn id="3" name="→ 시험 개념 (외울 것)"/>
+    <tableColumn id="4" name="→ 사업 활용"/>
+    <tableColumn id="5" name="주의/메모"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="원료표" displayName="원료표" ref="A3:M29" headerRowCount="1">
   <autoFilter ref="A3:M29"/>
@@ -583,6 +597,51 @@
     <tableColumn id="4" name="퍼센트"/>
     <tableColumn id="5" name="제조누계g"/>
     <tableColumn id="6" name="사용g"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="핵심개념표" displayName="핵심개념표" ref="A3:E33" headerRowCount="1">
+  <autoFilter ref="A3:E33"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="과목·영역"/>
+    <tableColumn id="2" name="핵심 개념"/>
+    <tableColumn id="3" name="꼭 외울 것 (수치·목록)"/>
+    <tableColumn id="4" name="실험/개발 연계"/>
+    <tableColumn id="5" name="사업 연계"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="원료시험맵표" displayName="원료시험맵표" ref="A3:H29" headerRowCount="1">
+  <autoFilter ref="A3:H29"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="원료"/>
+    <tableColumn id="2" name="INCI"/>
+    <tableColumn id="3" name="엑셀 역할"/>
+    <tableColumn id="4" name="시험 분류"/>
+    <tableColumn id="5" name="사용한도·고시 포인트"/>
+    <tableColumn id="6" name="시험 빈출 메모"/>
+    <tableColumn id="7" name="실험/개발 연계"/>
+    <tableColumn id="8" name="사업 연계"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="시험사업표" displayName="시험사업표" ref="A3:E20" headerRowCount="1">
+  <autoFilter ref="A3:E20"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="분류(시험 영역)"/>
+    <tableColumn id="2" name="시험 핵심 암기"/>
+    <tableColumn id="3" name="→ 사업 활용"/>
+    <tableColumn id="4" name="ODM·발주 미팅 질문(그대로 물어볼 것)"/>
+    <tableColumn id="5" name="주의/메모"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -2073,8 +2132,8 @@
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A1:B1"/>
@@ -2084,7 +2143,7 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A114:B114"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2096,361 +2155,1176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>원료↔시험 매핑 — 보유 26종을 시험 분류·사용한도 + 실험/사업 연계로</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>왼쪽(시험 핵심)을 외우되, 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열 질문은 ODM/공장 미팅에서 그대로 던질 체크리스트. 수치·목록은 최신 고시로 재확인.</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>★=시험 빈출/함정. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>분류(시험 영역)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>시험 핵심 암기</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>→ 사업 활용</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ODM·발주 미팅 질문(그대로 물어볼 것)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>주의/메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[법] 영업 종류·책임판매업</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP) 기준</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>내 사업 형태 확정: 직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매는 내가·제조품질은 공장 — 역할 경계 어디까지?</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>★조제관리사 자격=맞춤형판매업 선임요건. 자격 자체가 사업 자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[법] 표시·기재·광고</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>전성분 표시의무·기재사항, 부당표시광고(치료·의학적 효능 금지)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>상세페이지·라벨의 '하면 안 되는 말' 경계 = 진정·무향 카피 리스크 관리</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>라벨 시안(전성분 함량순·착향 알레르겐 표기) 검수해주나? 표시광고 가이드 제공?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>치료·항염·살균·병명 금지(읽어보기 핵심제약과 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[제조품질] 사용제한 보존제</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 제품 구분</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>방부 시스템 설계·검증을 공장에 요구하는 기준이 생김</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>방부 시스템 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온이라 한도 안 넘나?</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1,2-헥산다이올은 '지정 보존제 아님'(함정) — 책임 방부성분 따로 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[제조품질] 자외선차단·선크림</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>자외선차단성분 목록·최대함량, 자차=기능성화장품 심사/보고</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>선크림은 '위탁+기능성 인증' 전제 — 직접 제조 대상 아님</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필 번호? 원료 수급 안정적?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>확장 2~3순위. 히어로 검증 뒤에</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>[제조품질] 기능성 주성분(미백·주름)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>미백(나이아신아마이드 2~5%·알부틴·아스코르빈산 유도체), 주름(레티놀·아데노신) 고시 성분·함량</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 기능성 보고/심사 대행 요청</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화(레티놀 변색 등) 데이터?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>나이아신아마이드 이미 보유·히어로에 2% → 미백 표방 여부는 전략 선택</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>[제조품질] 배합금지 원료</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>사용할 수 없는 원료 목록</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>수입·신규 원료, 해외 처방 검토 시 1차 필터</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>전성분에 국내 배합금지·사용한도 초과 성분 없나? 원료 CoA·MSDS 제공?</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>해외 인기 성분이 국내 금지인 경우 주의</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>[유통안전] 유래물질·미생물 한도</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>중금속(납·비소·수은 등)·포름알데히드 등 한도, 미생물 한도(총호기성생균 등)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>출고 전 안전관리 시험성적서 확보 = 품질 신뢰·CS 방어</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>출고 로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체는?</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>안 주면 리스크 — 발주 계약서에 명시</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>[유통안전] 착향제 알레르기 성분</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>착향 알레르기 유발성분 표시 대상 목록</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>다도기=무향이라 유리: '무향·착향 알레르겐 0' 소구 가능</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>무향이 곧 USP이자 규제 리스크 최소화</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>[유통안전] pH·안정성·사용기한</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>유형별 pH 기준, 안정성(가속·장기) 개념</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>사용기한·보관조건의 과학적 근거 = 라벨·CS 뒷받침</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>안정성 데이터로 사용기한 산정? 개봉후사용기간(PAO) 표기 근거?</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>읽어보기 '안정성 테스트' 섹션과 연결</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>[맞춤형] 혼합·소분·위생</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>내용물+원료 혼합 가능/불가, 소분, 작업장 위생·장비 소독</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>'맞춤형판매업' 직접 운영 시 핵심 역량 — 상담→조제 차별화</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>(자체검토) 벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지되나?</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>조제관리사 자격의 직접 수익화 경로</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>[맞춤형/제조] 계면활성제·세안</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>계면활성제 4분류(음이온/양이온/양쪽성/비이온), 세정 원리</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>폼클렌저 등 세안 라인 기획 시 베이스 선택 기준</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 타깃 적합?</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>초기엔 위탁 권장(설비·충전 부담)</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>원료</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>INCI</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>엑셀 역할</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>시험 분류</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>사용한도·고시 포인트</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>시험 빈출 메모</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>실험/개발 연계</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>사업 연계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Glycerin</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>보습제(휴멕턴트)·수성원료</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음(일반원료)</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>대표 다가알코올 보습제, 수상</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>수상 보습·잔탄 선분산 매개</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>저가 범용, 전성분 상위 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>나이아신아마이드</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Niacinamide</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>미백 기능성 고시 주성분/활성</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>미백 고시 함량 2~5%</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>★빈출: 미백 주성분·2~5% 암기</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>완전용해 확인, 2~4% 사용</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>미백 '보고' 시 주성분(2~5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>다중 히알루론산</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Hyaluronic Acids</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>보습제(고분자 휴멕턴트)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>분자량별 보습, 수용성 고분자</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>전날 불려 사용(분말)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>'다중 수분' 소구·분자량 스토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>베타글루칸</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Beta-Glucan</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>활성(진정)·고분자 다당류</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>진정 유효성분</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>냉장 보관, 수상 진정</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>진정 서사 핵심 성분</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>베타인</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Betaine</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>보습제(휴멕턴트)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>아미노산계 보습제</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>끈적임 줄이는 대체 보습</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>저자극 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>아연피카</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Zinc PCA</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>활성(피지·수렴)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Zinc PCA 피지조절</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>수상, 피지·수렴</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>지성 타깃 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>알란토인</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Allantoin</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>활성(진정·각질)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>진정·보습 보조</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>용해 느림, 충분히 교반</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>저자극 보조 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Xanthan Gum</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>점증제</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>점증제(천연 고분자)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>대표 천연 점증제, 선분산</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>글리세린 선분산(피시아이 방지)</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>'천연 점증' 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>정제수</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>용제</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>수성원료(용제·기제)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>기제, 순도·미생물 관리 대상</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>잔량(q.s.) 100g 맞춤</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>용수 규격=품질관리 기본</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>프로판디올</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Propanediol</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>보습제·용제(다가알코올)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>글리콜계, 방부 보조력</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>방부 보조 폴리올</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>'파라벤프리' 방부 서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>MCT오일</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Caprylic/Capric Triglyceride</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>유성원료(에스터 오일)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Caprylic/Capric Triglyceride</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>경량 에몰리언트·말라세지아세이프</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>지성용 가벼운 유분</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>디메치콘</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Dimethicone</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>유성원료(실리콘)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>실리콘 오일, 발림·보호막</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>발림·얇은 보호막</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>실키 사용감(실리콘은 포지셔닝 선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>몬타노브68</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>유화제</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제(비이온 유화제)+고급지방알코올</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>O/W 유화제, HLB·유화 개념</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>O/W 유화, 유화온도 70~75℃</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>'글루코사이드계 순한 유화' 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>세틸알코올</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Cetyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>고급지방알코올(보조유화)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>점도·유화 안정화</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>점도·유화 안정</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>바디·사용감 조절</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>스쿠알란</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Squalane</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>유성원료(에몰리언트)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>안정성 높은 보습 오일</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>안정 보습오일·세이프</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>'피부 유사' 서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="47" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>시어버터</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Butyrospermum Parkii Butter</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>유성원료(식물성 버터)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>고형 유지, 에몰리언트</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>v2 미사용(C11~24 지방산)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>바디 등 타제형 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="47" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>올리브유화왁스</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Cetearyl Olivate &amp; Sorbitan Olivate</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>유화제</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제(비이온 유화제)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>올리브 유래 O/W 유화제</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>v2 미사용(말라세지아 회색지대)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>타제형 유화</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>토코페롤(비타민E)</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Tocopherol</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>항산화제</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>산화방지제</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음(산화방지 목적)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>★분류주의: 산화방지제(보존제 아님)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>오일 산패 방지</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>★전성분 역할 표기 정확</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>폴리글리세릴-4 카프레이트</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Polyglyceryl-4 Caprate</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>가용화제</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제(비이온 가용화제)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>워시오프 가용화·세정 보조</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>워시오프 가용화(미보유)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>클렌징 라인 전제 원료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="47" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>호호바오일</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Simmondsia Chinensis Seed Oil</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>유상·에몰리언트</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>유성원료(왁스 에스터 오일)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>피지 유사 왁스 에스터</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>v2 미사용(말라세지아 먹이)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>헤어·바디 등 타제형</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>1,2-헥산다이올</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>1,2-Hexanediol</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>방부제</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>다가알코올(보습·방부 보조)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>★지정 보존제 아님(목록 미등재)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>★함정: 방부력 있어도 법적 보존제 아님</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>방부 부스터, 페녹시 병용</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>★책임 방부성분 별도 명시 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="47" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>녹차추출물</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Camellia Sinensis Leaf Extract</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>식물추출물(활성)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>수용성 추출물</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>냉장·갈변 주의, 수용성</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>항산화 소구(미니멀서는 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>마데카소사이드</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Madecassoside</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>식물추출물 활성(센텔라)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>진정 활성</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>냉동 보관, 시카 진정</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>★'시카' 마케팅 키워드</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>판테놀(B5)</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Panthenol</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>활성(보습·진정)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>프로비타민 B5</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>보습·진정 보조</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>범용 보조 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>페녹시에탄올</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>방부제</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한 원료)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>★사용한도 1.0%</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>★최빈출: 보존제·한도 1.0% 필수암기</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>40℃ 이하 투입, 한도 1.0%</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>★방부 핵심·한도 준수 입증</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>구연산</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Citric Acid</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>pH조절</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>pH 조절제</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>사용한도 없음</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>citric acid, pH 조절</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>pH 5.0~5.5 적정</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>약산성 자극저감 근거</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E14"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2460,361 +3334,1080 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>실습↔시험 개념 — 내가 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>성분은 「시험대비 원료맵」에서 봤다. 여기는 제형·공정·안정성·위생·장비 — 시험 비중이 가장 큰 영역이자, 내가 이미 손으로 하는 일. 수치·기준은 최신 고시로 재확인.</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>왼쪽(시험 핵심)을 외우되 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열은 ODM 미팅 체크리스트. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>분류(실습 영역)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>내가 하는 것 (엑셀 근거)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>→ 시험 개념 (외울 것)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>분류(시험 영역)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>시험 핵심 암기</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>→ 사업 활용</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>ODM·발주 미팅 질문(그대로 물어볼 것)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>주의/메모</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[제형 분류]</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 제형을 직접 설계·제조</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>화장품 유형 분류, 유화형(O/W)·가용화·분산 제형 구분, 리브온/워시오프</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>라인업 설계·제품유형 신고 기준, 어디까지 직접/위탁할지 선 긋기</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>리브온(토너·크림)은 방부·향을 더 보수적으로</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[배합 설계·전성분]</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 소량 정밀계량</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>전성분 표시=함량 많은 순, 1% 이하·착향제·색소는 순서 무관, q.s. 개념</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>라벨 전성분 표기 검수·ODM 처방과 대조하는 눈</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>★처방 시트가 곧 전성분 표기 초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[제조 공정]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>수상(A) 70~75℃ 가열 / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산, 유화 순서</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>가용화·유화·분산 공정, 상(phase) 개념, 가열·냉각·투입 순서</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>공정 표준화=재현성 → 품질 일관성(리오더·CS 방어)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>냉각군(방부·열에 약한 활성)은 40℃ 이하에서 투입</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[유화 안정성]</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>층분리·크리밍·오일링을 온도·전단(호모 HZ-400)·유화제 3요소로 교정</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>유화 안정성, 유화제 HLB·유화형(O/W·W/O), 상분리 원인</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>안정한 처방=반품·클레임 방지, ODM 샘플 평가 기준</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>점도↑(잔탄검)도 기름방울 크리밍을 막는다</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>[안정성 시험]</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>45℃(가속)·RT·4℃·동결융해 보관 + 원심분리(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>안정성 시험(가속·장기·가혹), 경시변화, 유통화장품 안전관리</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>★사용기한·개봉후사용기간(PAO) 산정 근거 = ODM에 요구할 핵심 데이터</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>투명 바이알로 변색·냄새·pH 눈 비교</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>[pH 관리]</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>목표 5.0~5.5, 구연산 희석액 한 방울씩 적정, pH미터 교정(버퍼 4·7)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>피부 약산성, 유형별 pH 기준, pH 측정법</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>자극 최소화의 과학적 근거, 민감·지성 타깃 소구 포인트</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>물 든 제품만 측정, 되직하면 정제수 1:1 희석 후 측정</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>[방부·미생물]</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용, 오염 증상 관찰</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>보존제 사용한도, 미생물 한도, 방부력(챌린지) 시험 개념</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>방부력 시험성적서를 ODM에 요구, 사용기한 설정 근거</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>물+영양=미생물 배지. 헥산다이올은 지정 보존제 아님(책임 방부성분 따로)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>[산화·원료 보관]</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관(입출고·셀러)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>산화방지제, 원료 보관조건, 비의도적 변질·유래물질</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>원료 자재관리(CoA·로트·유효기간) → 품질·원가 통제</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>[작업장 위생·혼합소분]</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>70% 에탄올로 도구·용기·손 소독, 향·색 전용도구, 완전 건조</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>맞춤형 혼합·소분 작업장 위생, 교차오염 방지, 손 소독</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>★맞춤형판매업 매장 운영 표준 = 조제관리사 실무 핵심(직접 수익화)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>미생물 오염이 자가제조 최대 리스크</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>[장비·계량]</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>정밀저울 0.01g(소량)·벤치저울(대량), 호모나이저, 오버헤드 교반, pH미터</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>혼합·소분 장비·기구, 계량 정확도·오차</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>소량 생산 설비 vs 위탁 판단, 맞춤형 매장 장비 구비 기준</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1% 이하는 정밀저울 — 큰 저울로 재면 처방이 망가진다</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>[제조 기록·배치]</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>개발일지에 날짜·제품·배치량g·판정 기록, '한 번에 한 변수'</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>제조번호·제조기록서(뱃치기록), 제조일·사용기한 관리(CGMP 개념)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>로트 추적성=리콜·CS 대응력, ODM 품질계약의 기준</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>접은 실험도 '이 방향 아님' 데이터 — 기록 보존</t>
+    <row r="4" ht="62" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>[법] 영업 종류·책임판매업</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매 vs 제조품질 역할 경계는?</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>★조제관리사 자격=맞판 선임요건. 자격 자체가 사업 자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="47" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>[법] 표시·기재·광고</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>전성분 표시의무, 부당표시광고(치료·의학적 효능 금지)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>라벨·상세페이지의 '하면 안 되는 말' 경계 관리</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>라벨 시안(전성분 함량순·착향 알레르겐) 검수해주나? 표시광고 가이드 제공?</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>치료·항염·살균·병명 금지(문구검사와 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="47" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] 사용제한 보존제</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 구분</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>방부 시스템 설계·검증을 공장에 요구하는 기준</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>방부 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온 한도 안 넘나?</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>1,2-헥산다이올=지정 보존제 아님(함정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="47" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] 자외선차단·선크림</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>자외선차단성분 목록·최대함량, 자차=기능성(심사/보고)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>선크림은 '위탁+기능성 인증' 전제</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필? 원료 수급?</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>확장 2~3순위. 히어로 검증 뒤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="47" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] 기능성 주성분(미백·주름)</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>미백(나이아신아마이드 2~5%·알부틴), 주름(아데노신 0.04%·레티놀) 고시</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 보고/심사 대행</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화 데이터?</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>나이아신아마이드 보유·히어로 2% → 미백 표방은 전략 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="47" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] 배합금지 원료</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>사용할 수 없는 원료 목록</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>수입·신규 원료, 해외 처방 1차 필터</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>전성분에 국내 배합금지·한도 초과 없나? 원료 CoA·MSDS 제공?</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>해외 인기 성분이 국내 금지인 경우 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] CGMP 문서화</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>제조기록서·제조번호·일탈·재작업·교육</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>개발일지 기록 습관 → 위탁 품질계약 눈높이</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>로트별 기록·CoA·일탈처리 SOP 주나? 리콜 절차는?</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>추적성=리콜·CS 방어력</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="47" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>[제조품질] 위해평가·MoS</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>위험성확인→위험성결정→노출평가→위해도결정, 안전역(MoS)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>신규·고농도 활성 도입 판단틀</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>원료 안전성자료(독성·MoS) 제공? 처방 농도 안전역 근거?</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>활성 농도 상향 시 과학적 근거 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="47" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>[유통안전] 유래물질·미생물 한도</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>중금속(납20·비소10·수은1 등)·미생물(기타 1,000 CFU/g) 한도</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>출고 전 안전관리 시험성적서=품질 신뢰·CS 방어</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체?</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>계약서에 시험성적서 제공 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>[유통안전] 착향 알레르기 성분</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>지정 25종, 씻는 0.01%/안 씻는 0.001% 초과 표시</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>무향=알레르겐 0 소구 가능</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>무향이 곧 USP이자 규제 리스크 최소화</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>[유통안전] 포장·용기</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>용기 재질 적합성, 안전용기·포장, 내용물-용기 상용성</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>자/에어리스/펌프 선택·PCR 친환경 소구</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>내용물-용기 상용성(용출·흡착) 시험? 안전용기 대상? PCR 옵션?</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>용기선택이 안정성·브랜드 메시지 좌우</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>[유통안전] pH·안정성·사용기한</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>유형별 pH 기준, 안정성(가속·장기), PAO</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>사용기한·보관조건의 과학적 근거=라벨·CS 뒷받침</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>안정성 데이터로 사용기한/PAO 산정? 보관조건 표기 근거?</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>무리한 장기 표기 리스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>[맞춤형] 혼합·소분·위생</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>내용물+원료 혼합 가능/불가, 소분, 작업장 위생·소독</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>'맞춤형판매업' 직접 운영 핵심 역량(상담→조제)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지?</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>조제관리사 자격의 직접 수익화 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>[맞춤형] 피부측정·상담</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>피부 생리·타입·측정 지식</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>피부진단→맞춤 추천 콘텐츠·서비스로 객단가↑</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>(자체검토) 측정기기·상담 프로토콜 표준화 가능?</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>전문성=신뢰·재구매</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="47" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>[맞춤형/제조] 계면활성제·세안</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제 4분류(음/양/양쪽성/비이온), 세정 원리·자극도</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>폼클렌저 등 세안 라인 베이스 선택 기준</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 적합?</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>초기엔 위탁 권장(설비·충전 부담)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="47" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>[법] 온라인판매·개인정보</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>전자상거래·개인정보보호 표시의무(화장품법 밖이나 판매 필수)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>자사몰·스마트스토어 고지·청약철회 운영</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>플랫폼 입점 시 표시사항 자동 충족? 광고 심의 지원?</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>판매 채널 운영의 법적 기본</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>[법] 수입·통관</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>해외 원료·완제 수입 시 표준통관예정보고 등 절차</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>해외 성분 소싱 시 절차·비용·기간 파악</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>원료 수입대행·통관·검역 책임 주체? 리드타임?</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>해외 트렌드 성분 도입 리스크</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>실습↔시험 개념 — 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>성분은 「시험대비 원료맵」 참조. 여기는 제형·공정·안정성·위생·장비. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>분류(실습 영역)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>내가 하는 것 (엑셀 근거)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>→ 시험 개념 (외울 것)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>→ 사업 활용</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>주의/메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="47" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>[제형 분류]</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 직접 설계·제조</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>화장품 유형 분류, 유화형(O/W)·가용화·분산 구분, 리브온/워시오프</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>라인업 설계·제품유형 신고, 직접/위탁 경계</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>리브온(토너·크림)은 방부·향을 더 보수적으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="47" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>[배합 설계·전성분]</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 정밀계량</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>전성분=함량 많은 순, 1%이하·착향·색소는 순서 무관, q.s.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>라벨 전성분 검수·ODM 처방 대조</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>★처방 시트가 곧 전성분 표기 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="47" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>[제조 공정]</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>수상(A) 70~75℃ / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>가용화·유화·분산 공정, 상(phase), 가열·냉각·투입 순서</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>공정 표준화=재현성→품질 일관성(CS 방어)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>냉각군(방부·열 약한 활성)은 40℃ 이하 투입</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="47" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>[유화 안정성]</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>층분리·크리밍·오일링을 온도·전단(호모)·유화제 3요소로 교정</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>유화 안정성, 유화제 HLB·유화형, 상분리 원인</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>안정 처방=반품·클레임 방지, ODM 샘플 평가</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>점도↑(잔탄검)도 크리밍을 막는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="47" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>[안정성 시험]</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>45℃·RT·4℃·동결융해 + 원심(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>안정성 시험(가속·장기·가혹), 경시변화</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>★사용기한·PAO 산정 근거=ODM에 요구할 데이터</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>투명 바이알로 변색·냄새·pH 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="47" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>[pH 관리]</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>목표 5.0~5.5, 구연산 희석액 적정, pH미터 교정(버퍼 4·7)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>피부 약산성, 유형별 pH 기준, pH 측정법</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>자극 최소화 근거, 민감·지성 소구</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>물 든 제품만 측정, 되직하면 정제수 1:1 희석</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="47" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>[방부·미생물]</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>보존제 사용한도, 미생물 한도, 방부력(챌린지)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>방부력 시험성적서를 ODM에 요구, 사용기한 근거</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>물+영양=미생물 배지. 헥산다이올=지정 보존제 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="47" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>[산화·원료 보관]</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>산화방지제, 원료 보관조건, 비의도 변질·유래물질</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>원료 자재관리(CoA·로트·유효기간)→품질·원가</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>[작업장 위생·혼합소분]</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>70% 에탄올 소독, 향·색 전용도구, 완전 건조</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>맞춤형 혼합·소분 위생, 교차오염 방지, 손 소독</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>★맞판 매장 운영 표준=조제관리사 실무 핵심</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>미생물 오염이 자가제조 최대 리스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>[장비·계량]</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>정밀저울 0.01g(소량)·벤치저울(대량), 호모·오버헤드·pH미터</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>혼합·소분 장비·기구, 계량 정확도·오차</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>소량 생산 vs 위탁 판단, 매장 장비 기준</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>1% 이하는 정밀저울 — 큰 저울은 처방을 망친다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>[제조 기록·배치]</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>개발일지에 날짜·제품·배치량g·판정, '한 번에 한 변수'</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>제조번호·제조기록서(뱃치기록), 제조일·사용기한(CGMP)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>로트 추적성=리콜·CS 대응, ODM 품질계약 기준</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>접은 실험도 '이 방향 아님' 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>[계면활성제·유화이론]</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>몬타노브68로 O/W 유화, 두 상 70~75℃</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제 4분류·HLB·유화형</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>세안·클렌징 라인 베이스 판단</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>자극순 양이온&gt;음이온&gt;양쪽성&gt;비이온</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>[점증·유변]</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>잔탄검 0.1%p 단위 점도 조절, 선분산</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>점증제·요변성·점도 개념</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>사용감 설계=차별화</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>피시아이=검을 물에 바로 넣어 생김</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>[관능평가]</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>성상·색·향·사용감 바이알 비교, 표준품 대조</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>관능평가·비교시료·채점 기준</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>품질 합부·배치 재현 기준</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>주관 줄이려 기준·대조군 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>[색소·착색]</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>다도기 무색 지향(코치닐 등 미사용)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>색소 분류(염료·안료·레이크)·사용제한 색소</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>무색=규제·변색 리스크↓ 소구</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>색조 확장 시 색소 한도 학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>[표시·라벨 실습]</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>처방%→전성분 함량순 초안, 주의사항·PAO 표기</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>전성분·기재사항 규칙, PAO·사용기한</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>라벨 셀프 검수→ODM 대조</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>1%이하·착향·색소는 순서 무관</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>[계량·검교정]</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>정밀저울 0.01g, 저울 영점·주기 점검</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>계량 정확도·오차·검교정 개념</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>소량생산 품질·원가 통제</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>검교정 안 하면 처방 재현성↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>[원료 입고·자재관리]</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>입출고 장부, CoA·로트·유효기간, 보관조건 분리</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>원자재 관리·보관조건·비의도 변질</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>재고·원가·품질 동시 통제</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>CoA 없는 원료=품질 불확실</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -16093,901 +17686,875 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>원료↔시험 매핑 — 엑셀 26종을 맞춤형화장품조제관리사 시험 분류·사용한도로</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>시험 핵심개념 — 맞춤형화장품조제관리사 과목1~4 핵심을 수치·목록으로</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>★=시험 빈출/함정 포인트. 사용한도는 식약처 「화장품 안전기준 등에 관한 규정」 기준 — 제조·판매 전 최신 고시 반드시 재확인.</t>
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>원료</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>INCI</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>엑셀 역할</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>시험 분류</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>사용한도·고시 포인트</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>시험 빈출 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>글리세린</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Glycerin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>보습제(휴멕턴트)·수성원료</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>사용한도 없음(일반원료)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>대표 다가알코올 보습제, 수상</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>나이아신아마이드</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Niacinamide</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>미백 기능성 고시 주성분 / 활성</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>미백 고시 함량 2~5%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>★빈출: 미백 주성분·2~5% 암기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>다중 히알루론산</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hyaluronic Acids</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>보습제(고분자 휴멕턴트)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>분자량별 보습, 수용성 고분자</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>베타글루칸</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Beta-Glucan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>활성(진정)·고분자 다당류</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>진정 유효성분</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>베타인</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Betaine</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>보습제(휴멕턴트)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>아미노산계 보습제</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>아연피카</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Zinc PCA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>활성(피지·수렴)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Zinc PCA 피지조절</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>알란토인</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Allantoin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>활성(진정·각질)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>진정·보습 보조</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>잔탄검</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Xanthan Gum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>점증제</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>점증제(천연 고분자)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>대표 천연 점증제, 선분산</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>정제수</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>용제</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>수성원료(용제·기제)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>기제, 순도·미생물 관리 대상</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>프로판디올</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Propanediol</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>보습제·용제(다가알코올)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>글리콜계, 방부 보조력</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MCT오일</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Caprylic/Capric Triglyceride</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>유상·에몰리언트</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>유성원료(에스터 오일·에몰리언트)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Caprylic/Capric Triglyceride</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>디메치콘</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dimethicone</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>감촉·실리콘</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>유성원료(실리콘)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>실리콘 오일, 발림·보호막</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>몬타노브68</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>유화제</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>계면활성제(비이온 유화제)+고급지방알코올</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>O/W 유화제, HLB·유화 개념</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>세틸알코올</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Cetyl Alcohol</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>유상·에몰리언트</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>고급지방알코올(유성·보조유화)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>점도·유화 안정화</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스쿠알란</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Squalane</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>유상·에몰리언트</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>유성원료(에몰리언트)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>안정성 높은 보습 오일</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>시어버터</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Butyrospermum Parkii Butter</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>유상·에몰리언트</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>유성원료(식물성 버터)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>고형 유지, 에몰리언트</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>올리브유화왁스</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cetearyl Olivate &amp; Sorbitan Olivate</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>유화제</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>계면활성제(비이온 유화제)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>올리브 유래 O/W 유화제</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>토코페롤(비타민E)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tocopherol</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>항산화제</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>산화방지제</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>사용한도 없음(산화방지 목적)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>★분류주의: 산화방지제(보존제 아님)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>폴리글리세릴-4 카프레이트</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Polyglyceryl-4 Caprate</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>가용화제</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>계면활성제(비이온 가용화제)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>워시오프 가용화·세정 보조</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>호호바오일</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Simmondsia Chinensis Seed Oil</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>유상·에몰리언트</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>유성원료(왁스 에스터 오일)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>피지 유사 왁스 에스터</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1,2-헥산다이올</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1,2-Hexanediol</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>방부제</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>다가알코올(보습·방부 보조)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>★지정 보존제 아님(사용제한 목록 미등재)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>★함정: 방부력 있어도 법적 보존제 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>녹차추출물</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Camellia Sinensis Leaf Extract</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>식물추출물(활성)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>수용성 추출물</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>마데카소사이드</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Madecassoside</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>식물추출물 활성(센텔라)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>진정 활성</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>판테놀(B5)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Panthenol</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>활성(보습·진정)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>프로비타민 B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>페녹시에탄올</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Phenoxyethanol</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>방부제</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>보존제(사용제한 원료)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>★사용한도 1.0%</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>★최빈출: 보존제·한도 1.0% 필수암기</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>구연산</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Citric Acid</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>pH조절</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>pH 조절제</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>사용한도 없음</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>citric acid, pH 5 안팎 조절</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>과목·영역</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>핵심 개념</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>꼭 외울 것 (수치·목록)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>실험/개발 연계</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>사업 연계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="47" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>화장품 정의</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>인체를 청결·미화하고 매력을 더하며 피부·모발을 건강하게 유지·증진. 인체 작용이 '경미'. 의약품(치료·예방)과 구분.</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>히어로는 '진정·보습 화장품' — 효능 과장 불가</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>상세페이지 카피의 법적 경계선</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="47" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>화장품 유형</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>기초·색조·두발·인체세정용·방향용·눈화장용·면도용·체취방지 등(시행규칙 별표). 유형별 표시·안전기준 상이.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>7종 제형이 각 유형에 매핑됨</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>품목 유형 구분→신고·표시 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="47" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>영업 3종</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>①제조업(등록) ②책임판매업(등록) ③맞춤형화장품판매업(신고). 맞판은 '조제관리사' 선임 의무.</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>직접제조 전 단계=R&amp;D</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>★자격=맞판 선임요건·사업 진입권</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="47" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>기능성화장품</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>미백·주름개선·자외선차단·염모·제모·탈모완화·여드름완화(인체세정)·아토피건조완화·튼살완화 등. '심사' 또는 '보고' 필요.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>미백 주성분(나이아신아마이드) 보유</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>기능성 표방=심사/보고 비용·기간 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="47" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>표시·기재사항</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>명칭·영업자 상호/주소·제조번호·사용기한 또는 개봉후사용기간(PAO)·내용량·전성분·사용 시 주의사항·기능성 문구 등.</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>라벨 초안 작성 능력</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>ODM 라벨 시안 검수 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>전성분 표시 규칙</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>함량 많은 순 기재. 단 1% 이하 성분·착향제·색소는 순서 무관. 착향제는 '향료'로 표기 가능(알레르기 유발성분은 예외로 성분명).</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>처방 %표가 곧 전성분 초안</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>라벨 정확성=반품·행정처분 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>부당표시·광고 금지</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>의약품 오인(치료·예방), 기능성/유기농 오인, 사실과 다른 소비자 기만 표현 금지.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>'항염·살균·병명' 금지(문구검사)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>진정·무향 카피 리스크 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="47" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>원료 분류</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·탄화수소·실리콘)/계면활성제/보습제/고분자(점증)/활성/색소/보존제/착향제.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>보유 26종이 각 분류에 해당</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>CoA·규격서 읽는 눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="47" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>계면활성제 4분류</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>음이온(세정·기포)·양이온(살균·헤어컨디셔닝)·양쪽성(저자극)·비이온(유화·가용화). 자극 세기: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>몬타노브68=비이온 유화제</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>세안 라인 베이스 선택 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>친수-친유 균형값. HLB 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화는 15~18).</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>크림=O/W → 유화제 HLB 맞춤</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>처방 안정성의 이론 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>유화·가용화·분산</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>유화=안 섞이는 두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일을 투명 분산. 분산=고체 입자를 액에 퍼뜨림.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>크림=유화, 워시오프=가용화</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>제형 기획·제품유형 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="47" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>점증제·유변학</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성 부여. 분말 검은 글리세린 선분산 후 투입(뭉침 방지).</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>잔탄검 0.1%p 단위 점도 튜닝</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>사용감 차별화 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="77" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>보존제 사용한도</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>페녹시에탄올 1.0% · 벤질알코올 1.0% · 소르빅애씨드 0.6% · 벤조익애씨드 0.5% · 파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올은 지정 보존제 아님.</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>페녹시+헥산다이올 방부</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>★챌린지테스트·방부 설계 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="47" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>산화방지제 ≠ 보존제</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>토코페롤·BHT 등은 '산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 법적 분류·목적이 다름(혼동 함정).</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>토코페롤로 오일 산패 방지</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>전성분 역할 표기 정확성</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>기능성 주성분·함량</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU·레티닐팔미테이트 10,000IU.</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>나이아신아마이드 2~4% 사용 중</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>미백 '보고' 시 주성분 스펙</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="47" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>CGMP</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>우수화장품 제조·품질관리기준. 3요소=인적자원·시설·원자재. 문서화: 제조기록서·제조번호·일탈·재작업·교육.</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>개발일지=배치기록서 축소판</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>ODM이 CGMP 업소인지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="92" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>중금속·유해물질 한도</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈화장 35)·디옥산 100·포름알데하이드 2,000·프탈레이트(DBP+BBP+DEHP) 100. 메탄올 0.2(v/v)%.</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>비의도 유래물질 개념</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>출고 로트별 시험성적서 요구</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>미생물 한도</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>영·유아용/눈화장용 500 · 물휴지 세균·진균 각 100 · 기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>소독·방부·1개월 내 사용</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>미생물 시험성적서 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="47" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>pH 기준</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>영유아·눈화장·색조·두발·면도·로션/크림/영양 등 특정 액상류 pH 3.0~9.0 (물로 씻어내는 제품 제외).</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>목표 pH 5.0~5.5 적정</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>자극 저감·라벨 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>내용량 기준</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>제품 3개 평균 내용량이 표기량의 97% 이상.</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>충진량 관리</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>과충진 원가·미달 CS 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="47" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>착향 알레르기 성분</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>식약처 지정 유발성분(약 25종). 사용 후 씻어내는 제품 0.01%·씻어내지 않는 제품 0.001% 초과 시 성분명 표시.</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>다도기=무향 → 알레르겐 0</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>★무향이 규제·소구 동시 이점</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>안정성 시험</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>장기·가속(45℃)·가혹(동결융해·광)·개봉후. 경시변화로 사용기한·PAO 산정.</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>4조건 보관+원심 실습</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>사용기한 설정 과학적 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="47" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>맞춤형화장품 정의</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>제조·수입된 화장품 '내용물'에 다른 내용물 또는 식약처장이 정한 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>혼합·소분 개념</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>맞판 매장 사업 모델</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="47" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>혼합·소분 금지 원료</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>사용제한 원료(보존제·자외선차단제·색소 등)·기능성 주성분(심사/보고된 경우 제외)은 임의 혼합 불가.</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>방부·자차 임의 추가 불가</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>조제 상담의 법적 한계</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>조제관리사 의무</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>혼합·소분 안전·품질·위생관리, 오염 방지, 기구·작업자 위생.</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>70% 에탄올 소독·전용도구</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>자격의 직접 수익화(매장 운영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="47" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>피부 구조</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>표피(기저·유극·과립·투명·각질층)·진피(콜라겐·엘라스틴·섬유아세포)·피하지방. 멜라노사이트=기저층.</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>진정·보습 타깃 이해</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>맞춤 상담·소구 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="47" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>각질층·장벽·NMF</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>벽돌(각질세포)+시멘트(세라마이드 등 세포간지질) 구조. NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>HA·글리세린·세이프 유분으로 장벽 보습</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>'장벽·진정' 브랜드 서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="47" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>모발 구조</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질(메둘라). 주성분 케라틴, 디설파이드(S-S) 결합.</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>헤어 라인 확장 시 기초</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>라인 확장 판단</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>관능평가</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점 기준으로 주관 최소화.</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>바이알 변색·냄새·pH 눈 비교</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>품질 합부·배치 재현 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>위해평가 4단계</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>위험성 확인 → 위험성 결정 → 노출평가 → 위해도 결정. 안전역(MoS)으로 판단.</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>활성 농도 상향 판단틀</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>신규·고농도 원료 도입 근거</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F29"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -603,22 +603,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="핵심개념표" displayName="핵심개념표" ref="A3:E33" headerRowCount="1">
-  <autoFilter ref="A3:E33"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="핵심개념표" displayName="핵심개념표" ref="A3:F33" headerRowCount="1">
+  <autoFilter ref="A3:F33"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="과목·영역"/>
     <tableColumn id="2" name="핵심 개념"/>
     <tableColumn id="3" name="꼭 외울 것 (수치·목록)"/>
-    <tableColumn id="4" name="실험/개발 연계"/>
-    <tableColumn id="5" name="사업 연계"/>
+    <tableColumn id="4" name="쉽게 말하면 (풀이)"/>
+    <tableColumn id="5" name="실험/개발 연계"/>
+    <tableColumn id="6" name="사업 연계"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="원료시험맵표" displayName="원료시험맵표" ref="A3:H29" headerRowCount="1">
-  <autoFilter ref="A3:H29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="원료시험맵표" displayName="원료시험맵표" ref="A3:H54" headerRowCount="1">
+  <autoFilter ref="A3:H54"/>
   <tableColumns count="8">
     <tableColumn id="1" name="원료"/>
     <tableColumn id="2" name="INCI"/>
@@ -2127,12 +2128,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A89:B89"/>
@@ -2142,8 +2143,8 @@
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2155,30 +2156,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>원료↔시험 매핑 — 보유 26종을 시험 분류·사용한도 + 실험/사업 연계로</t>
+          <t>원료↔시험 매핑 — 보유 26종 + 시험 전용 원료(미보유) 사전</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>★=시험 빈출/함정. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+          <t>★=시험 빈출/함정. '엑셀 역할=시험용(미보유)'로 필터하면 시험 전용 원료만 모아 볼 수 있다. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2393,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="17" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
           <t>베타인</t>
@@ -2476,7 +2477,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="17" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
           <t>알란토인</t>
@@ -2746,7 +2747,7 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>계면활성제(비이온 유화제)+고급지방알코올</t>
+          <t>계면활성제(비이온)+고급지방알코올</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -2766,7 +2767,7 @@
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>'글루코사이드계 순한 유화' 소구</t>
+          <t>'순한 유화' 소구</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2962,7 @@
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>사용한도 없음(산화방지 목적)</t>
+          <t>사용한도 없음(산화방지)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -3102,7 +3103,7 @@
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>★책임 방부성분 별도 명시 필요</t>
+          <t>★책임 방부성분 별도 명시</t>
         </is>
       </c>
     </row>
@@ -3313,6 +3314,1056 @@
       <c r="H29" s="23" t="inlineStr">
         <is>
           <t>약산성 자극저감 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="47" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>메틸파라벤</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Methylparaben</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>단일 0.4%·혼합 0.8%</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>★파라벤 한도(단일0.4/혼합0.8) 빈출</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>다도기 미사용(페녹시 채택)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>'파라벤프리' 소구 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>프로필파라벤</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Propylparaben</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>프로필·부틸파라벤 단일/혼합 0.14%</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>★장쇄 파라벤은 더 엄격(0.14%)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>트렌드상 기피 성분</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>벤질알코올</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Benzyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)+착향</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>보존 목적 1.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>향료이자 보존제(이중역할) 주의</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>미사용(무향 원칙과 상충)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>무향 포지션과 배치</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>소르빅애씨드</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Sorbic Acid</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>유기산계, pH 낮아야 효과</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>천연계 방부 대안</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>벤조익애씨드</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Benzoic Acid</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>안식향산, 산성서 효과</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>DMDM하이단토인</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>DMDM Hydantoin</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>0.6%(포름알데하이드 방출)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>★포름알데하이드 방출 보존제(기피)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>'노 포름알데하이드' 신뢰</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="47" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>메칠이소치아졸리논</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Methylisothiazolinone</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>보존제(사용제한)</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>씻어내는 제품 0.0015%</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>★MIT/CMIT 알레르기·리브온 금지 빈출</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>리브온 금지 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>징크옥사이드</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Zinc Oxide</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>자외선차단(무기)·기능성</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>최대 25%</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>★무기자차 대표, 백탁</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>선크림 확장 시</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>자차=기능성 인증 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>티타늄디옥사이드</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Titanium Dioxide</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>자외선차단(무기)·기능성</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>최대 25%</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>무기자차, 산란 방식</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>확장 시</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="47" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>에칠헥실메톡시신나메이트</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Ethylhexyl Methoxycinnamate</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>자외선차단(유기)·기능성</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>최대 7.5%</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>대표 유기자차</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>확장 시</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="47" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>부틸메톡시디벤조일메탄</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Butyl Methoxydibenzoylmethane</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>자외선차단(유기)·기능성</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>최대 5%</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>아보벤존, UVA·광안정성 이슈</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>확장 시</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>알부틴</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Arbutin</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>미백 기능성 주성분</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>2~5%</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>★미백 고시 성분(하이드로퀴논 유도체)</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>미백 라인 옵션</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>아스코빌글루코사이드</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Ascorbyl Glucoside</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>미백 기능성 주성분</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>비타민C 유도체(안정형)</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>미백 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>레티놀</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Retinol</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>주름개선 기능성 주성분</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>2,500 IU</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>★단위가 IU(함량주의)·변색</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>안티에이징 라인</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>아데노신</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Adenosine</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>주름개선 기능성 주성분</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>★주름 고시 0.04% 빈출</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>주름 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>살리실릭애씨드</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Salicylic Acid</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>사용제한/여드름(세정) 기능성</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>보존 목적 0.5%·여드름 세정 0.5%</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>★BHA, 영유아 사용제한 빈출</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>지성 세안 라인 옵션</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>하이드로퀴논</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Hydroquinone</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>★배합금지(일반화장품)</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>화장품 사용금지(의약품)</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>★'미백'이라고 넣으면 안 됨(함정)</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>절대 미사용</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>해외직구 성분 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>스테로이드</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Corticosteroids</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>★배합금지</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>사용금지(의약품)</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>진정 강력해도 금지 — 함정</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>절대 미사용</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>'무스테로이드' 신뢰</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>소듐라우레스설페이트</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Sodium Laureth Sulfate</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>음이온 계면활성제(세정)</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>★SLES, 대표 세정 음이온</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>세안 라인 위탁 시</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>저자극 버전 선택 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>코카미도프로필베타인</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Cocamidopropyl Betaine</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>양쪽성 계면활성제(세정)</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>저자극, 베이비·민감 세안</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>세안 라인</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>민감 타깃 적합</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>세트리모늄클로라이드</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Cetrimonium Chloride</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>양이온 계면활성제(헤어)</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>제품별 사용한도</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>헤어 린스·대전방지(양이온)</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>헤어 확장</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>산화철</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Iron Oxides</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>착색제(무기안료)</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>허용 색소</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>색조 대표 무기안료</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>색조 확장 시</t>
+        </is>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>무색 원칙과 별개</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>타르색소(예: 적색201호)</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>CI 번호</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>착색제(타르색소)</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>품목·부위별 사용제한</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>★눈 주위·점막 사용제한 빈출</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>색조 시 색소 한도 학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="47" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>리모넨</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Limonene</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>착향 알레르기 유발성분</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>씻는 0.01%/안 씻는 0.001% 초과 표시</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>★25종 중 대표(감귤향)</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>다도기 무향=해당없음</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>무향이 알레르겐 0 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>리날룰</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>Linalool</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>시험용(미보유)</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>착향 알레르기 유발성분</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>동일 표시기준</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>★라벤더향 대표 알레르겐</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>무향</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17686,27 +18737,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>시험 핵심개념 — 맞춤형화장품조제관리사 과목1~4 핵심을 수치·목록으로</t>
+          <t>시험 핵심개념 — 맞춤형화장품조제관리사 과목1~4 핵심(암기용 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+          <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 'C열=외우기용 / D열=쉬운 풀이'. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
@@ -17728,16 +18780,21 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>쉽게 말하면 (풀이)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>실험/개발 연계</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>사업 연계</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="47" customHeight="1">
+    <row r="4" ht="77" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17750,21 +18807,26 @@
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>인체를 청결·미화하고 매력을 더하며 피부·모발을 건강하게 유지·증진. 인체 작용이 '경미'. 의약품(치료·예방)과 구분.</t>
+          <t>인체를 청결·미화하고 매력을 더하며 피부·모발을 건강히 유지·증진. 인체 작용 '경미'. 의약품(치료·예방)과 구분.</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
+          <t>화장품은 '꾸미고 가꾸는' 데까지예요. 병을 '고치는' 건 의약품 몫이라, 효과를 세게 말하면 법에 걸립니다. 다도기 크림도 '진정에 도움'까지만.</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
           <t>히어로는 '진정·보습 화장품' — 효능 과장 불가</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>상세페이지 카피의 법적 경계선</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="47" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17777,21 +18839,26 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>기초·색조·두발·인체세정용·방향용·눈화장용·면도용·체취방지 등(시행규칙 별표). 유형별 표시·안전기준 상이.</t>
+          <t>기초·색조·두발·인체세정·방향·눈화장·면도용 등(시행규칙 별표). 유형별 표시·안전기준 상이.</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>7종 제형이 각 유형에 매핑됨</t>
+          <t>화장품은 쓰임새별로 칸이 나뉘어요(기초·색조·세안·향수…). 내 제품이 어느 칸이냐에 따라 지킬 규칙이 달라집니다.</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>품목 유형 구분→신고·표시 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="47" customHeight="1">
+          <t>7종 제형이 각 유형에 매핑</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>유형 구분→신고·표시 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="77" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17804,21 +18871,26 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>①제조업(등록) ②책임판매업(등록) ③맞춤형화장품판매업(신고). 맞판은 '조제관리사' 선임 의무.</t>
+          <t>①제조업(등록) ②책임판매업(등록) ③맞춤형화장품판매업(신고). 맞판은 조제관리사 선임 의무.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
+          <t>만드는 사람·책임지고 파는 사람·섞어 맞춰 파는 사람이 따로 등록돼요. 조제관리사 자격이 있어야 맞춤형 매장을 열 수 있어 — 자격이 곧 사업 허가증.</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
           <t>직접제조 전 단계=R&amp;D</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>★자격=맞판 선임요건·사업 진입권</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="47" customHeight="1">
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>★자격=맞판 선임요건·진입권</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17831,21 +18903,26 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>미백·주름개선·자외선차단·염모·제모·탈모완화·여드름완화(인체세정)·아토피건조완화·튼살완화 등. '심사' 또는 '보고' 필요.</t>
+          <t>미백·주름·자외선차단·염모·제모·탈모완화·여드름완화(세정)·아토피건조완화·튼살 등. 심사 또는 보고.</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
+          <t>'미백·주름개선'처럼 특별한 효과를 광고하려면 나라의 심사·보고를 받아야 하는 제품군이에요. 그냥 보습 크림은 여기 해당 안 됨.</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
           <t>미백 주성분(나이아신아마이드) 보유</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>기능성 표방=심사/보고 비용·기간 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="47" customHeight="1">
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>기능성 표방=심사/보고 비용·기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17858,21 +18935,26 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>명칭·영업자 상호/주소·제조번호·사용기한 또는 개봉후사용기간(PAO)·내용량·전성분·사용 시 주의사항·기능성 문구 등.</t>
+          <t>명칭·영업자·제조번호·사용기한 또는 개봉후사용기간(PAO)·내용량·전성분·주의사항·기능성 문구 등.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
+          <t>용기·상자에 '반드시 적어야 하는 것들'의 목록이에요. 하나라도 빠지면 판매를 못 합니다.</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
           <t>라벨 초안 작성 능력</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>ODM 라벨 시안 검수 기준</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1">
+    <row r="9" ht="77" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17885,21 +18967,26 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>함량 많은 순 기재. 단 1% 이하 성분·착향제·색소는 순서 무관. 착향제는 '향료'로 표기 가능(알레르기 유발성분은 예외로 성분명).</t>
+          <t>함량 많은 순 기재. 단 1% 이하 성분·착향제·색소는 순서 무관. 착향제는 '향료'로 표기 가능(알레르겐은 성분명).</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
+          <t>성분을 '많이 든 순서'로 적는 게 원칙이에요. 단 아주 조금(1% 이하) 든 것·향·색소는 순서를 안 지켜도 됩니다.</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
           <t>처방 %표가 곧 전성분 초안</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>라벨 정확성=반품·행정처분 방지</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>라벨 정확성=반품·처분 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
           <t>1.화장품법</t>
@@ -17917,16 +19004,21 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
+          <t>'낫는다·치료·살균' 같은 의약품스러운 말, 거짓·과장은 금지예요. 진정·무향은 사실 그대로만 말합니다.</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
           <t>'항염·살균·병명' 금지(문구검사)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>진정·무향 카피 리스크 관리</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="47" customHeight="1">
+    <row r="11" ht="77" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -17939,21 +19031,26 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·탄화수소·실리콘)/계면활성제/보습제/고분자(점증)/활성/색소/보존제/착향제.</t>
+          <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·실리콘)/계면활성제/보습/고분자(점증)/활성/색소/보존제/착향.</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
+          <t>화장품 원료는 큰 가족으로 나뉘어요 — 물 쪽, 기름 쪽, 둘을 섞어주는 것, 보습, 걸쭉하게, 효능, 색, 방부, 향. 내 26종도 다 이 가족 중 하나.</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
           <t>보유 26종이 각 분류에 해당</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>CoA·규격서 읽는 눈</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="47" customHeight="1">
+    <row r="12" ht="77" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -17966,21 +19063,26 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>음이온(세정·기포)·양이온(살균·헤어컨디셔닝)·양쪽성(저자극)·비이온(유화·가용화). 자극 세기: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
+          <t>음이온(세정)·양이온(살균·헤어)·양쪽성(저자극)·비이온(유화·가용화). 자극: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
+          <t>물과 기름은 원래 안 섞이는데 그 사이를 중개하는 게 계면활성제예요. 네 종류가 있고 자극 세기가 달라요(양이온이 제일 세고 비이온이 제일 순함).</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
           <t>몬타노브68=비이온 유화제</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>세안 라인 베이스 선택 기준</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="47" customHeight="1">
+    <row r="13" ht="77" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -17993,21 +19095,26 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>친수-친유 균형값. HLB 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화는 15~18).</t>
+          <t>친수-친유 균형값. 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화 15~18).</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
+          <t>유화제가 '물을 더 좋아하냐 기름을 더 좋아하냐'를 숫자로 매긴 거예요. 이 숫자로 내 크림(물 베이스=O/W)에 맞는 유화제를 고릅니다.</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
           <t>크림=O/W → 유화제 HLB 맞춤</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>처방 안정성의 이론 근거</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="47" customHeight="1">
+    <row r="14" ht="77" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -18020,21 +19127,26 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>유화=안 섞이는 두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일을 투명 분산. 분산=고체 입자를 액에 퍼뜨림.</t>
+          <t>유화=두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일 투명 분산. 분산=고체 입자를 액에.</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
+          <t>셋 다 '안 섞이는 걸 섞는' 기술이에요. 크림처럼 뽀얗게 섞으면 유화, 소량 기름을 투명하게 녹이면 가용화, 가루를 퍼뜨리면 분산.</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
           <t>크림=유화, 워시오프=가용화</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>제형 기획·제품유형 결정</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="47" customHeight="1">
+    <row r="15" ht="62" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -18047,15 +19159,20 @@
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성 부여. 분말 검은 글리세린 선분산 후 투입(뭉침 방지).</t>
+          <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성. 분말 검은 글리세린 선분산 후 투입.</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
+          <t>묽은 액을 걸쭉하게 만드는 게 점증제예요. 잔탄검은 꼭 글리세린에 먼저 개서 넣어야 쌀알 같은 덩어리(피시아이)가 안 생겨요.</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
           <t>잔탄검 0.1%p 단위 점도 튜닝</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>사용감 차별화 설계</t>
         </is>
@@ -18074,21 +19191,26 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>페녹시에탄올 1.0% · 벤질알코올 1.0% · 소르빅애씨드 0.6% · 벤조익애씨드 0.5% · 파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올은 지정 보존제 아님.</t>
+          <t>페녹시에탄올 1.0%·벤질알코올 1.0%·소르빅애씨드 0.6%·파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올=지정 보존제 아님.</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
+          <t>물이 든 화장품은 세균이 자라 반드시 방부가 필요해요. 단 보존제마다 '여기까지만' 쓰라는 한도가 있어요(페녹시에탄올은 1.0%).</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
           <t>페녹시+헥산다이올 방부</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>★챌린지테스트·방부 설계 기준</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="47" customHeight="1">
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -18101,21 +19223,26 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>토코페롤·BHT 등은 '산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 법적 분류·목적이 다름(혼동 함정).</t>
+          <t>토코페롤·BHT는 '산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 목적·분류가 다름.</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
+          <t>토코페롤은 '기름이 쩐내 나는 것'을 막지, 세균을 막는 게 아니에요. 시험에서 보존제랑 헷갈리게 내는 단골 함정.</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
           <t>토코페롤로 오일 산패 방지</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>전성분 역할 표기 정확성</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1">
+    <row r="18" ht="77" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -18128,21 +19255,26 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU·레티닐팔미테이트 10,000IU.</t>
+          <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU.</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>나이아신아마이드 2~4% 사용 중</t>
+          <t>미백·주름 효과를 인정받으려면 '정해진 성분을 정해진 양'으로 넣어야 해요. 많다고 좋은 게 아니라 고시 범위를 지키는 게 핵심.</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
+          <t>나이아신아마이드 2~4% 사용</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
           <t>미백 '보고' 시 주성분 스펙</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="47" customHeight="1">
+    <row r="19" ht="62" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
           <t>2.제조품질</t>
@@ -18155,21 +19287,26 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>우수화장품 제조·품질관리기준. 3요소=인적자원·시설·원자재. 문서화: 제조기록서·제조번호·일탈·재작업·교육.</t>
+          <t>우수화장품 제조·품질관리기준. 3요소=인적자원·시설·원자재. 문서화: 제조기록서·제조번호·일탈·재작업.</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
+          <t>화장품을 '깨끗하고 늘 똑같이' 만들기 위한 공장 관리 규칙이에요. 내가 쓰는 개발일지가 바로 이 기록의 작은 버전.</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
           <t>개발일지=배치기록서 축소판</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>ODM이 CGMP 업소인지 확인</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="92" customHeight="1">
+    <row r="20" ht="107" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18182,21 +19319,26 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈화장 35)·디옥산 100·포름알데하이드 2,000·프탈레이트(DBP+BBP+DEHP) 100. 메탄올 0.2(v/v)%.</t>
+          <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈 35)·디옥산 100·포름알데하이드 2,000·프탈레이트 100. 메탄올 0.2%.</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
+          <t>일부러 넣진 않아도 원료에 미량 섞여 들어올 수 있는 나쁜 물질들의 '넘으면 안 되는 선'이에요. 출고 전 시험으로 확인합니다.</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
           <t>비의도 유래물질 개념</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>출고 로트별 시험성적서 요구</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="62" customHeight="1">
+    <row r="21" ht="77" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18209,21 +19351,26 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>영·유아용/눈화장용 500 · 물휴지 세균·진균 각 100 · 기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
+          <t>영유아·눈화장 500·물휴지 세균·진균 각 100·기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
+          <t>완제품에 있어도 되는 세균 수의 한계예요. 아기·눈 제품은 더 엄격(500), 대장균·녹농균·황색포도상구균은 아예 나오면 안 됩니다.</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
           <t>소독·방부·1개월 내 사용</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>미생물 시험성적서 확보</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="47" customHeight="1">
+    <row r="22" ht="77" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18236,21 +19383,26 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>영유아·눈화장·색조·두발·면도·로션/크림/영양 등 특정 액상류 pH 3.0~9.0 (물로 씻어내는 제품 제외).</t>
+          <t>영유아·눈화장·색조·로션/크림 등 특정 액상류 pH 3.0~9.0(물로 씻어내는 제품 제외).</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
+          <t>피부에 바르는 많은 제품은 pH 3.0~9.0 안에 들어야 해요. 다도기는 피부와 같은 약산성(5.0~5.5)으로 더 좁게 맞춥니다.</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
           <t>목표 pH 5.0~5.5 적정</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>자극 저감·라벨 근거</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
+    <row r="23" ht="62" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18268,16 +19420,21 @@
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
+          <t>'50mL'이라 적었으면 실제로도 그만큼(평균 97% 이상) 들어 있어야 한다는 뜻이에요. 덜 넣으면 안 됩니다.</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
           <t>충진량 관리</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>과충진 원가·미달 CS 방지</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="47" customHeight="1">
+    <row r="24" ht="77" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18290,21 +19447,26 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>식약처 지정 유발성분(약 25종). 사용 후 씻어내는 제품 0.01%·씻어내지 않는 제품 0.001% 초과 시 성분명 표시.</t>
+          <t>지정 유발성분(약 25종). 씻어내는 0.01%·씻어내지 않는 0.001% 초과 시 성분명 표시.</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
+          <t>향료 속엔 알레르기를 일으킬 수 있는 25종이 있어, 일정량 넘으면 이름을 따로 표시해야 해요. 다도기는 무향이라 이 걱정이 없습니다.</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
           <t>다도기=무향 → 알레르겐 0</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>★무향이 규제·소구 동시 이점</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
+    <row r="25" ht="77" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
           <t>3.유통안전</t>
@@ -18322,16 +19484,21 @@
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
+          <t>제품이 시간·온도가 지나도 안 변하는지 미리 괴롭혀 보는 시험이에요(45℃, 얼렸다 녹였다). 이 결과로 '언제까지 쓰세요'를 정합니다.</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
           <t>4조건 보관+원심 실습</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>사용기한 설정 과학적 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="47" customHeight="1">
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>사용기한 설정 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18344,21 +19511,26 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>제조·수입된 화장품 '내용물'에 다른 내용물 또는 식약처장이 정한 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
+          <t>제조·수입된 '내용물'에 다른 내용물/식약처 허용 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
+          <t>이미 만들어진 내용물에 뭘 더 섞거나, 덜어 담아 파는 게 맞춤형화장품이에요. 매장에서 '맞춤 조제'하는 모델.</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
           <t>혼합·소분 개념</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>맞판 매장 사업 모델</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="47" customHeight="1">
+    <row r="27" ht="62" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18371,21 +19543,26 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>사용제한 원료(보존제·자외선차단제·색소 등)·기능성 주성분(심사/보고된 경우 제외)은 임의 혼합 불가.</t>
+          <t>사용제한 원료(보존제·자외선차단·색소)·기능성 주성분(심사/보고된 경우 제외)은 임의 혼합 불가.</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
+          <t>맞춤형이라고 아무거나 섞으면 안 돼요. 보존제·자외선차단제·기능성 주성분은 매장에서 임의로 추가하는 게 금지됩니다.</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
           <t>방부·자차 임의 추가 불가</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>조제 상담의 법적 한계</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="28" ht="62" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18403,16 +19580,21 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
+          <t>맞춤형 매장에서 섞고 나누는 일을 안전·위생적으로 책임지는 사람이 조제관리사예요. 소독·오염방지가 핵심 임무.</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
           <t>70% 에탄올 소독·전용도구</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>자격의 직접 수익화(매장 운영)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="47" customHeight="1">
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>자격의 직접 수익화(매장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="62" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18425,21 +19607,26 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>표피(기저·유극·과립·투명·각질층)·진피(콜라겐·엘라스틴·섬유아세포)·피하지방. 멜라노사이트=기저층.</t>
+          <t>표피(기저·유극·과립·투명·각질)·진피(콜라겐·엘라스틴·섬유아세포)·피하. 멜라노사이트=기저층.</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
+          <t>피부는 3층(표피·진피·피하)이에요. 색을 만드는 멜라닌 공장(멜라노사이트)은 표피 맨 아래 기저층에 있습니다.</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
           <t>진정·보습 타깃 이해</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>맞춤 상담·소구 근거</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="47" customHeight="1">
+    <row r="30" ht="77" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18452,21 +19639,26 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>벽돌(각질세포)+시멘트(세라마이드 등 세포간지질) 구조. NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
+          <t>벽돌(각질)+시멘트(세포간지질·세라마이드). NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>HA·글리세린·세이프 유분으로 장벽 보습</t>
+          <t>피부 맨 바깥은 벽돌(각질)과 시멘트(지질)로 쌓은 담벼락이에요. 이 담이 튼튼해야 수분이 안 새요 — 다도기가 노리는 '장벽·진정'.</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
+          <t>HA·글리세린·세이프 유분 보습</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
           <t>'장벽·진정' 브랜드 서사</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1">
+    <row r="31" ht="62" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18479,21 +19671,26 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질(메둘라). 주성분 케라틴, 디설파이드(S-S) 결합.</t>
+          <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질. 주성분 케라틴, 디설파이드(S-S) 결합.</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
+          <t>머리카락은 3겹(겉껍질·속·심)이고 케라틴 단백질이 주재료예요. 파마·염색이 바로 이 구조를 건드리는 것.</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
           <t>헤어 라인 확장 시 기초</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>라인 확장 판단</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
+    <row r="32" ht="62" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18506,21 +19703,26 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점 기준으로 주관 최소화.</t>
+          <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점으로 주관 최소화.</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
+          <t>기계 말고 '사람의 눈·코·손'으로 색·향·발림을 평가하는 거예요. 기준 샘플과 비교해서 주관을 줄입니다.</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
           <t>바이알 변색·냄새·pH 눈 비교</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>품질 합부·배치 재현 기준</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
+    <row r="33" ht="77" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
@@ -18533,15 +19735,20 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>위험성 확인 → 위험성 결정 → 노출평가 → 위해도 결정. 안전역(MoS)으로 판단.</t>
+          <t>위험성 확인→위험성 결정→노출평가→위해도 결정. 안전역(MoS)으로 판단.</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
+          <t>이 성분이 '얼마나 위험한지→얼마나 노출되는지→그래서 안전한지'를 순서대로 따지는 방법이에요. 활성 농도를 올릴지 판단할 때 씁니다.</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
           <t>활성 농도 상향 판단틀</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>신규·고농도 원료 도입 근거</t>
         </is>
@@ -18549,8 +19756,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -501,14 +501,15 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="실습시험표" displayName="실습시험표" ref="A3:E21" headerRowCount="1">
-  <autoFilter ref="A3:E21"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="실습시험표" displayName="실습시험표" ref="A3:F21" headerRowCount="1">
+  <autoFilter ref="A3:F21"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="분류(실습 영역)"/>
     <tableColumn id="2" name="내가 하는 것 (엑셀 근거)"/>
     <tableColumn id="3" name="→ 시험 개념 (외울 것)"/>
-    <tableColumn id="4" name="→ 사업 활용"/>
-    <tableColumn id="5" name="주의/메모"/>
+    <tableColumn id="4" name="쉽게 말하면 (풀이)"/>
+    <tableColumn id="5" name="→ 사업 활용"/>
+    <tableColumn id="6" name="주의/메모"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -635,14 +636,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="시험사업표" displayName="시험사업표" ref="A3:E20" headerRowCount="1">
-  <autoFilter ref="A3:E20"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="시험사업표" displayName="시험사업표" ref="A3:F20" headerRowCount="1">
+  <autoFilter ref="A3:F20"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="분류(시험 영역)"/>
     <tableColumn id="2" name="시험 핵심 암기"/>
-    <tableColumn id="3" name="→ 사업 활용"/>
-    <tableColumn id="4" name="ODM·발주 미팅 질문(그대로 물어볼 것)"/>
-    <tableColumn id="5" name="주의/메모"/>
+    <tableColumn id="3" name="쉽게 말하면 (풀이)"/>
+    <tableColumn id="4" name="→ 사업 활용"/>
+    <tableColumn id="5" name="ODM·발주 미팅 질문(그대로 물어볼 것)"/>
+    <tableColumn id="6" name="주의/메모"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -2128,13 +2130,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="A1:B1"/>
@@ -2143,7 +2145,7 @@
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4385,27 +4387,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로</t>
+          <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로 (암기 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>왼쪽(시험 핵심)을 외우되 오른쪽(사업 활용·발주 질문)으로 써먹는다. D열은 ODM 미팅 체크리스트. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+          <t>왼쪽(시험 핵심)을 외우되 오른쪽(사업 활용·발주 질문)으로 써먹는다. 'C열=쉬운 풀이'. ODM 미팅 체크리스트는 E열. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
@@ -4422,21 +4425,26 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
+          <t>쉽게 말하면 (풀이)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
           <t>→ 사업 활용</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>ODM·발주 미팅 질문(그대로 물어볼 것)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>주의/메모</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="62" customHeight="1">
+    <row r="4" ht="92" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
           <t>[법] 영업 종류·책임판매업</t>
@@ -4449,21 +4457,26 @@
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
+          <t>화장품 사업은 역할별로 등록이 나뉘어요. 공장을 안 돌리면 '책임판매업'만 등록하고 제조는 공장에 맡기면 돼요 — 조제관리사 자격은 '맞춤형 매장'을 열 때의 필수 자격.</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
           <t>직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매 vs 제조품질 역할 경계는?</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>★조제관리사 자격=맞판 선임요건. 자격 자체가 사업 자산</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="47" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>[법] 표시·기재·광고</t>
@@ -4476,21 +4489,26 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
+          <t>라벨·상세페이지엔 '해도 되는 말'과 '안 되는 말'이 법으로 갈려요. 치료·의학적 효과를 암시하면 걸립니다.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
           <t>라벨·상세페이지의 '하면 안 되는 말' 경계 관리</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>라벨 시안(전성분 함량순·착향 알레르겐) 검수해주나? 표시광고 가이드 제공?</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>치료·항염·살균·병명 금지(문구검사와 동일)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="47" customHeight="1">
+    <row r="6" ht="77" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>[제조품질] 사용제한 보존제</t>
@@ -4503,21 +4521,26 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
+          <t>방부 성분은 종류마다 '최대 이만큼만' 쓰라는 한도가 있어요. 공장에 '한도 안 넘었는지, 방부력 시험했는지' 당당히 물을 근거가 됩니다.</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
           <t>방부 시스템 설계·검증을 공장에 요구하는 기준</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>방부 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온 한도 안 넘나?</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>1,2-헥산다이올=지정 보존제 아님(함정)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="47" customHeight="1">
+    <row r="7" ht="77" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>[제조품질] 자외선차단·선크림</t>
@@ -4530,21 +4553,26 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
+          <t>선크림은 자외선차단 성분을 정해진 한도로 쓰고 '기능성'으로 인증받아야 하는 제품이에요. 혼자 만들 게 아니라 위탁+인증 전제.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
           <t>선크림은 '위탁+기능성 인증' 전제</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필? 원료 수급?</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>확장 2~3순위. 히어로 검증 뒤</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="47" customHeight="1">
+    <row r="8" ht="77" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
           <t>[제조품질] 기능성 주성분(미백·주름)</t>
@@ -4557,21 +4585,26 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
+          <t>미백·주름을 광고하려면 '정해진 성분을 정해진 양'으로 넣고 나라에 보고/심사해야 해요. 내가 가진 나이아신아마이드가 바로 미백 주성분.</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
           <t>'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 보고/심사 대행</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화 데이터?</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>나이아신아마이드 보유·히어로 2% → 미백 표방은 전략 선택</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="47" customHeight="1">
+    <row r="9" ht="62" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>[제조품질] 배합금지 원료</t>
@@ -4584,21 +4617,26 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
+          <t>아예 화장품에 못 쓰는 성분 목록이에요. 해외 처방을 들여올 때 이 목록으로 먼저 걸러야 사고가 안 납니다.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
           <t>수입·신규 원료, 해외 처방 1차 필터</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>전성분에 국내 배합금지·한도 초과 없나? 원료 CoA·MSDS 제공?</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>해외 인기 성분이 국내 금지인 경우 주의</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="77" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
           <t>[제조품질] CGMP 문서화</t>
@@ -4611,21 +4649,26 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
+          <t>공장이 '언제·뭘·얼마나' 만들었는지 다 기록으로 남기는 체계예요. 내 개발일지 습관이 이 눈높이와 같아 위탁 계약 때 요구 수준을 압니다.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
           <t>개발일지 기록 습관 → 위탁 품질계약 눈높이</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>로트별 기록·CoA·일탈처리 SOP 주나? 리콜 절차는?</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>추적성=리콜·CS 방어력</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="47" customHeight="1">
+    <row r="11" ht="77" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
           <t>[제조품질] 위해평가·MoS</t>
@@ -4638,21 +4681,26 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
+          <t>성분이 안전한지를 '위험성×노출량'으로 따져 여유(안전역)를 보는 방법이에요. 활성 농도를 올릴지 과학적으로 판단할 때 씁니다.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
           <t>신규·고농도 활성 도입 판단틀</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>원료 안전성자료(독성·MoS) 제공? 처방 농도 안전역 근거?</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>활성 농도 상향 시 과학적 근거 필요</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="47" customHeight="1">
+    <row r="12" ht="77" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
           <t>[유통안전] 유래물질·미생물 한도</t>
@@ -4665,21 +4713,26 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
+          <t>원료에 딸려올 수 있는 중금속·세균 수에 '넘으면 안 되는 선'이 있어요. 출고 전 시험성적서를 받아야 품질을 증명하고 클레임을 막습니다.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
           <t>출고 전 안전관리 시험성적서=품질 신뢰·CS 방어</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체?</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>계약서에 시험성적서 제공 명시</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="47" customHeight="1">
+    <row r="13" ht="77" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t>[유통안전] 착향 알레르기 성분</t>
@@ -4692,21 +4745,26 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
+          <t>향료 속 알레르기 유발 25종은 일정량 넘으면 표시 의무가 있어요. 다도기는 무향이라 이 부담이 아예 없다는 게 강점.</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
           <t>무향=알레르겐 0 소구 가능</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>무향이 곧 USP이자 규제 리스크 최소화</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="47" customHeight="1">
+    <row r="14" ht="77" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>[유통안전] 포장·용기</t>
@@ -4719,21 +4777,26 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
+          <t>용기 재질이 내용물과 안 맞으면 성분이 녹아나오거나 흡착돼요. 자/펌프/에어리스 선택이 안정성과 브랜드 메시지를 좌우합니다.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
           <t>자/에어리스/펌프 선택·PCR 친환경 소구</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>내용물-용기 상용성(용출·흡착) 시험? 안전용기 대상? PCR 옵션?</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>용기선택이 안정성·브랜드 메시지 좌우</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="77" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
           <t>[유통안전] pH·안정성·사용기한</t>
@@ -4746,21 +4809,26 @@
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
+          <t>'언제까지 쓰세요(사용기한·개봉후기간)'는 감이 아니라 안정성 데이터로 정해요. 라벨과 CS의 과학적 뒷받침이 됩니다.</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
           <t>사용기한·보관조건의 과학적 근거=라벨·CS 뒷받침</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>안정성 데이터로 사용기한/PAO 산정? 보관조건 표기 근거?</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>무리한 장기 표기 리스크</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="47" customHeight="1">
+    <row r="16" ht="77" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
           <t>[맞춤형] 혼합·소분·위생</t>
@@ -4773,21 +4841,26 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
+          <t>맞춤형 매장은 '어디까지 섞어도 되는지'와 위생이 핵심이에요. 이 역량이 곧 상담→조제 차별화이자 자격의 직접 수익화.</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
           <t>'맞춤형판매업' 직접 운영 핵심 역량(상담→조제)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지?</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>조제관리사 자격의 직접 수익화 경로</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t>[맞춤형] 피부측정·상담</t>
@@ -4800,21 +4873,26 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
+          <t>피부 생리·타입을 알면 '진단→맞춤 추천'을 해줄 수 있어요. 전문성이 신뢰와 객단가로 이어집니다.</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
           <t>피부진단→맞춤 추천 콘텐츠·서비스로 객단가↑</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>(자체검토) 측정기기·상담 프로토콜 표준화 가능?</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>전문성=신뢰·재구매</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="47" customHeight="1">
+    <row r="18" ht="62" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>[맞춤형/제조] 계면활성제·세안</t>
@@ -4827,21 +4905,26 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
+          <t>세안 제품의 베이스는 계면활성제인데 종류마다 세정력·자극이 달라요. 민감·지성 타깃이면 저자극 쪽을 골라야 합니다.</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
           <t>폼클렌저 등 세안 라인 베이스 선택 기준</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 적합?</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>초기엔 위탁 권장(설비·충전 부담)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="47" customHeight="1">
+    <row r="19" ht="62" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
           <t>[법] 온라인판매·개인정보</t>
@@ -4854,21 +4937,26 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
+          <t>온라인 판매는 화장품법 밖이지만 전자상거래·개인정보 표시의무를 지켜야 해요. 자사몰·스마트스토어 운영의 기본.</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
           <t>자사몰·스마트스토어 고지·청약철회 운영</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>플랫폼 입점 시 표시사항 자동 충족? 광고 심의 지원?</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>판매 채널 운영의 법적 기본</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="77" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
           <t>[법] 수입·통관</t>
@@ -4881,15 +4969,20 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
+          <t>해외 원료·완제를 들여오려면 통관 보고 등 절차가 있어요. 소싱 전에 절차·비용·기간을 알아야 리드타임 사고를 막습니다.</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
           <t>해외 성분 소싱 시 절차·비용·기간 파악</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>원료 수입대행·통관·검역 책임 주체? 리드타임?</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>해외 트렌드 성분 도입 리스크</t>
         </is>
@@ -4897,8 +4990,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4913,27 +5006,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>실습↔시험 개념 — 배치마다 하는 일을 시험 개념·사업으로 묶기 (과목2·4 집중)</t>
+          <t>실습↔시험 개념 — 배치마다 하는 일을 시험 개념·사업으로 (암기 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>성분은 「시험대비 원료맵」 참조. 여기는 제형·공정·안정성·위생·장비. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+          <t>성분은 「시험대비 원료맵」 참조. 여기는 제형·공정·안정성·위생·장비. 'D열=쉬운 풀이'. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
@@ -4955,16 +5049,21 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>쉽게 말하면 (풀이)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>→ 사업 활용</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>주의/메모</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="47" customHeight="1">
+    <row r="4" ht="77" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
           <t>[제형 분류]</t>
@@ -4982,16 +5081,21 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
+          <t>내가 만드는 7가지가 사실 시험의 '유화/가용화/분산', '씻어내는/안 씻는' 분류 그 자체예요. 크림은 유화, 워시오프는 가용화.</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
           <t>라인업 설계·제품유형 신고, 직접/위탁 경계</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>리브온(토너·크림)은 방부·향을 더 보수적으로</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="47" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>[배합 설계·전성분]</t>
@@ -5009,16 +5113,21 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
+          <t>처방 %를 많은 순으로 적으면 그게 바로 전성분 표기 초안이에요. 1% 이하·향·색소만 순서를 안 지켜도 됩니다.</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
           <t>라벨 전성분 검수·ODM 처방 대조</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>★처방 시트가 곧 전성분 표기 초안</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="47" customHeight="1">
+    <row r="6" ht="77" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>[제조 공정]</t>
@@ -5036,16 +5145,21 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
+          <t>수상은 데우고, 유상은 녹이고, 열에 약한 건 식은 뒤(40℃↓) 넣는 '순서'가 공정 핵심이에요. 순서를 지켜야 매번 같은 품질이 나옵니다.</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
           <t>공정 표준화=재현성→품질 일관성(CS 방어)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>냉각군(방부·열 약한 활성)은 40℃ 이하 투입</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="47" customHeight="1">
+    <row r="7" ht="77" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>[유화 안정성]</t>
@@ -5063,16 +5177,21 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
+          <t>물·기름이 갈라지는 건 ①온도 ②호모(전단) ③유화제, 세 가지로 잡아요. 점도를 올리면 기름방울이 못 떠올라 더 안정됩니다.</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
           <t>안정 처방=반품·클레임 방지, ODM 샘플 평가</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>점도↑(잔탄검)도 크리밍을 막는다</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="47" customHeight="1">
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
           <t>[안정성 시험]</t>
@@ -5090,16 +5209,21 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
+          <t>45℃·동결융해로 미리 괴롭혀 변하는지 봐요. 이 결과가 '사용기한·개봉후기간'의 근거이고 ODM에 요구할 데이터.</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
           <t>★사용기한·PAO 산정 근거=ODM에 요구할 데이터</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>투명 바이알로 변색·냄새·pH 비교</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="47" customHeight="1">
+    <row r="9" ht="77" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>[pH 관리]</t>
@@ -5117,16 +5241,21 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
+          <t>피부가 약산성이라 제품도 거기 맞춰요(5.0~5.5). 구연산을 한 방울씩 넣어 맞추고 pH미터는 버퍼로 교정 후 씁니다.</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
           <t>자극 최소화 근거, 민감·지성 소구</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>물 든 제품만 측정, 되직하면 정제수 1:1 희석</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="47" customHeight="1">
+    <row r="10" ht="77" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
           <t>[방부·미생물]</t>
@@ -5144,16 +5273,21 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
+          <t>물+영양분은 세균의 밥상이라 방부가 필수예요. 단 헥산다이올은 법적 보존제가 아니라 책임 방부성분(페녹시)이 따로 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
           <t>방부력 시험성적서를 ODM에 요구, 사용기한 근거</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>물+영양=미생물 배지. 헥산다이올=지정 보존제 아님</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="47" customHeight="1">
+    <row r="11" ht="62" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
           <t>[산화·원료 보관]</t>
@@ -5171,16 +5305,21 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
+          <t>기름은 산소를 만나면 쩐내가 나요(산화). 토코페롤로 늦추고, 원료는 성질대로 냉장·냉동·방습 나눠 보관합니다.</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
           <t>원료 자재관리(CoA·로트·유효기간)→품질·원가</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
+    <row r="12" ht="77" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
           <t>[작업장 위생·혼합소분]</t>
@@ -5198,16 +5337,21 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
+          <t>자가제조·맞춤형의 최대 리스크는 미생물 오염이에요. 70% 알코올 소독·전용 도구가 시험(맞춤형 위생)이자 매장 운영 표준.</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
           <t>★맞판 매장 운영 표준=조제관리사 실무 핵심</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>미생물 오염이 자가제조 최대 리스크</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="47" customHeight="1">
+    <row r="13" ht="77" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t>[장비·계량]</t>
@@ -5225,16 +5369,21 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
+          <t>1% 이하 소량은 정밀저울(0.01g), 많은 양은 큰 저울로 나눠 재요. 소량을 큰 저울로 재면 오차가 처방 전체를 망칩니다.</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
           <t>소량 생산 vs 위탁 판단, 매장 장비 기준</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>1% 이하는 정밀저울 — 큰 저울은 처방을 망친다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="47" customHeight="1">
+    <row r="14" ht="77" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>[제조 기록·배치]</t>
@@ -5252,16 +5401,21 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
+          <t>제조번호·배치기록(언제·뭘·얼마나)이 CGMP 핵심이에요. 이 추적성이 있어야 문제가 나도 어느 로트인지 찾아 대응합니다.</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
           <t>로트 추적성=리콜·CS 대응, ODM 품질계약 기준</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>접은 실험도 '이 방향 아님' 데이터</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="62" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
           <t>[계면활성제·유화이론]</t>
@@ -5279,16 +5433,21 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
+          <t>몬타노브로 물·기름을 섞는 게 유화인데, 계면활성제는 4종류이고 자극 세기가 달라요(비이온이 제일 순함).</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
           <t>세안·클렌징 라인 베이스 판단</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>자극순 양이온&gt;음이온&gt;양쪽성&gt;비이온</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="77" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
           <t>[점증·유변]</t>
@@ -5306,16 +5465,21 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
+          <t>잔탄검 양으로 '되기(점도)'를 조절하는 게 유변학이에요. 검을 물에 바로 넣으면 쌀알 덩어리(피시아이)가 생깁니다.</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
           <t>사용감 설계=차별화</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>피시아이=검을 물에 바로 넣어 생김</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t>[관능평가]</t>
@@ -5333,16 +5497,21 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
+          <t>기계가 아니라 사람 감각으로 색·향·발림을 평가하되, 기준 샘플과 비교해 주관을 줄이는 방법이에요.</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
           <t>품질 합부·배치 재현 기준</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>주관 줄이려 기준·대조군 사용</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="62" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>[색소·착색]</t>
@@ -5360,16 +5529,21 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
+          <t>색소는 염료·안료·레이크로 나뉘고 부위별 사용제한이 있어요. 다도기는 무색이라 변색·규제 리스크가 적다는 게 장점.</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
           <t>무색=규제·변색 리스크↓ 소구</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>색조 확장 시 색소 한도 학습</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
+    <row r="19" ht="77" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
           <t>[표시·라벨 실습]</t>
@@ -5387,16 +5561,21 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
+          <t>처방 %를 그대로 전성분 함량순 초안으로 옮기고 주의사항·개봉후기간까지 적어보는 연습이에요. ODM 라벨과 대조할 눈이 생깁니다.</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
           <t>라벨 셀프 검수→ODM 대조</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>1%이하·착향·색소는 순서 무관</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="62" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
           <t>[계량·검교정]</t>
@@ -5414,16 +5593,21 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
+          <t>저울도 주기적으로 영점·교정을 해줘야 믿을 수 있어요. 검교정을 안 하면 같은 처방도 매번 달라집니다.</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
           <t>소량생산 품질·원가 통제</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>검교정 안 하면 처방 재현성↓</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
+    <row r="21" ht="77" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t>[원료 입고·자재관리]</t>
@@ -5441,10 +5625,15 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
+          <t>원료 받을 때 CoA(성적서)·로트·유효기간을 적고 성질대로 보관하는 게 자재관리예요. 재고·원가·품질을 한꺼번에 통제합니다.</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
           <t>재고·원가·품질 동시 통제</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>CoA 없는 원료=품질 불확실</t>
         </is>
@@ -5452,8 +5641,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,36 @@
       <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FF404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -110,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,11 +162,26 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -192,11 +237,26 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -296,7 +356,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -306,7 +366,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -324,7 +386,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -334,7 +396,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -352,7 +416,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPr id="4" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -362,7 +426,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -380,7 +446,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPr id="5" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -390,7 +456,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -408,7 +476,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPr id="6" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -418,7 +486,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -436,7 +506,7 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPr id="7" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -446,7 +516,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -464,11 +536,74 @@
     <ext cx="4381500" cy="6524625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPr id="8" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>322</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4381500" cy="6524625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="5210175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -495,21 +630,6 @@
     <tableColumn id="4" name="조정 — 한 번에 하나만"/>
     <tableColumn id="5" name="관련 역할"/>
     <tableColumn id="6" name="왜"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="실습시험표" displayName="실습시험표" ref="A3:F21" headerRowCount="1">
-  <autoFilter ref="A3:F21"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="분류(실습 영역)"/>
-    <tableColumn id="2" name="내가 하는 것 (엑셀 근거)"/>
-    <tableColumn id="3" name="→ 시험 개념 (외울 것)"/>
-    <tableColumn id="4" name="쉽게 말하면 (풀이)"/>
-    <tableColumn id="5" name="→ 사업 활용"/>
-    <tableColumn id="6" name="주의/메모"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -590,7 +710,7 @@
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="처방표" displayName="처방표" ref="A3:F108" headerRowCount="1">
-  <autoFilter ref="A3:F92"/>
+  <autoFilter ref="A3:F108"/>
   <tableColumns count="6">
     <tableColumn id="1" name="제품"/>
     <tableColumn id="2" name="원료"/>
@@ -598,53 +718,6 @@
     <tableColumn id="4" name="퍼센트"/>
     <tableColumn id="5" name="제조누계g"/>
     <tableColumn id="6" name="사용g"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="핵심개념표" displayName="핵심개념표" ref="A3:F33" headerRowCount="1">
-  <autoFilter ref="A3:F33"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="과목·영역"/>
-    <tableColumn id="2" name="핵심 개념"/>
-    <tableColumn id="3" name="꼭 외울 것 (수치·목록)"/>
-    <tableColumn id="4" name="쉽게 말하면 (풀이)"/>
-    <tableColumn id="5" name="실험/개발 연계"/>
-    <tableColumn id="6" name="사업 연계"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="원료시험맵표" displayName="원료시험맵표" ref="A3:H54" headerRowCount="1">
-  <autoFilter ref="A3:H54"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="원료"/>
-    <tableColumn id="2" name="INCI"/>
-    <tableColumn id="3" name="엑셀 역할"/>
-    <tableColumn id="4" name="시험 분류"/>
-    <tableColumn id="5" name="사용한도·고시 포인트"/>
-    <tableColumn id="6" name="시험 빈출 메모"/>
-    <tableColumn id="7" name="실험/개발 연계"/>
-    <tableColumn id="8" name="사업 연계"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="시험사업표" displayName="시험사업표" ref="A3:F20" headerRowCount="1">
-  <autoFilter ref="A3:F20"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="분류(시험 영역)"/>
-    <tableColumn id="2" name="시험 핵심 암기"/>
-    <tableColumn id="3" name="쉽게 말하면 (풀이)"/>
-    <tableColumn id="4" name="→ 사업 활용"/>
-    <tableColumn id="5" name="ODM·발주 미팅 질문(그대로 물어볼 것)"/>
-    <tableColumn id="6" name="주의/메모"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -939,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1078,7 +1151,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>시트 11개 지도</t>
+          <t>시트 8개 지도</t>
         </is>
       </c>
     </row>
@@ -1178,27 +1251,10 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>시험대비 원료맵 : 보유 원료 26종을 시험 분류·사용한도로 매핑(필터·틀고정). 조제관리사 공부용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>실습↔시험 개념 : 제형·공정·안정성·위생·장비 실습을 시험 과목2·4 개념+사업 활용으로 묶음.</t>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>전체 흐름 한눈에</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1266,31 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>시험→사업 활용 : 외운 이론을 ODM 발주·제품 기획 체크리스트로 전환.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>전체 흐름 한눈에</t>
+          <t>[만들기] 레시피 고름 → 만듦 → 개발일지에 기록(사용감·분리mm·pH·판정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>[고치기] 이슈 → 트러블슈팅에서 '관련 역할' 확인 → 원료 시트에서 그 역할로 필터 → 바꿀 원료 선택 → 다음 아이디어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>[사기]   원료 사면 → 입출고 한 줄(구매) → 원료 '현재고' 자동 ↑.</t>
         </is>
       </c>
     </row>
@@ -1229,54 +1302,54 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>[만들기] 레시피 고름 → 만듦 → 개발일지에 기록(사용감·분리mm·pH·판정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+          <t>[재고]   만들면 → 개발일지 배치량g → 쓴 원료가 처방 %대로 자동 ↓.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>★ 재고가 자동으로 맞춰지는 원리</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>[고치기] 이슈 → 트러블슈팅에서 '관련 역할' 확인 → 원료 시트에서 그 역할로 필터 → 바꿀 원료 선택 → 다음 아이디어.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>현재고 = 최초보유 + 구매(입출고) + 조정(입출고) − 제조사용(개발일지 배치량 × 처방%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>[사기]   원료 사면 → 입출고 한 줄(구매) → 원료 '현재고' 자동 ↑.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>원료를 사면 → '입출고'에 [날짜·원료·구매·수량g] 한 줄.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>[재고]   만들면 → 개발일지 배치량g → 쓴 원료가 처방 %대로 자동 ↓.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>★ 재고가 자동으로 맞춰지는 원리</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>제품을 만들면 → '개발일지'에 [날짜·제품·배치량g] 한 줄 → 쓴 원료가 자동 차감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1284,7 +1357,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>현재고 = 최초보유 + 구매(입출고) + 조정(입출고) − 제조사용(개발일지 배치량 × 처방%).</t>
+          <t>흘리거나 버리면 → '입출고'에 구분 '조정', 수량g에 음수(-).</t>
         </is>
       </c>
     </row>
@@ -1296,31 +1369,14 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>원료를 사면 → '입출고'에 [날짜·원료·구매·수량g] 한 줄.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>제품을 만들면 → '개발일지'에 [날짜·제품·배치량g] 한 줄 → 쓴 원료가 자동 차감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>흘리거나 버리면 → '입출고'에 구분 '조정', 수량g에 음수(-).</t>
+          <t>현재고가 빨갛게(음수) 뜨면 그 원료는 '사야 함' 신호.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>매일 쓰는 법</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1388,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>현재고가 빨갛게(음수) 뜨면 그 원료는 '사야 함' 신호.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>매일 쓰는 법</t>
+          <t>① 필터: 각 표 머리글의 ▼ 버튼으로 상·제품·판정·역할 등으로 걸러 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>② 새 줄: 표 맨 아래 줄에 바로 입력하면 수식·드롭다운이 자동으로 따라 확장된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>③ 한 번에 한 변수만 바꾼다 — 그래야 뭐가 효과였는지 안다.</t>
         </is>
       </c>
     </row>
@@ -1351,50 +1424,50 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>① 필터: 각 표 머리글의 ▼ 버튼으로 상·제품·판정·역할 등으로 걸러 본다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+          <t>④ 실패도 '접기'로 기록 — 안 되는 방향을 지우는 것도 전진.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>이슈가 나면 — 이렇게 고친다 (핵심 루프)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>② 새 줄: 표 맨 아래 줄에 바로 입력하면 수식·드롭다운이 자동으로 따라 확장된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>개발일지에 사용감·이슈·분리mm·pH를 적는다 → '트러블슈팅'에서 그 증상 줄을 찾는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>③ 한 번에 한 변수만 바꾼다 — 그래야 뭐가 효과였는지 안다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>그 줄의 '관련 역할'(예: 끈적임→보습)을 보고 → '원료' 시트에서 역할=그 값으로 필터 → 바꿀 후보 원료가 한눈에.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>④ 실패도 '접기'로 기록 — 안 되는 방향을 지우는 것도 전진.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>이슈가 나면 — 이렇게 고친다 (핵심 루프)</t>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>'조정'대로 한 축만 골라 개발일지 '다음 아이디어'에 적는다(예: 글리세린 1%p↓ + 베타인으로 대체).</t>
         </is>
       </c>
     </row>
@@ -1406,11 +1479,11 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>개발일지에 사용감·이슈·분리mm·pH를 적는다 → '트러블슈팅'에서 그 증상 줄을 찾는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
+          <t>다음에 만들 땐 그 '다음 아이디어'가 이번 배치의 '바꾼것', '기준(base)'엔 직전 버전을 적는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1418,50 +1491,50 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>그 줄의 '관련 역할'(예: 끈적임→보습)을 보고 → '원료' 시트에서 역할=그 값으로 필터 → 바꿀 후보 원료가 한눈에.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+          <t>접힌 것도 '이 방향은 아니다' 데이터 — 지우지 말고 남긴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>원료 '역할' 12종 (필터·트러블슈팅 공통 어휘)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>'조정'대로 한 축만 골라 개발일지 '다음 아이디어'에 적는다(예: 글리세린 1%p↓ + 베타인으로 대체).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>용제 = 바탕 물. / 보습 = 수분 잡기(글리세린·베타인·HA). / 활성 = 효능(피지·진정·톤).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>다음에 만들 땐 그 '다음 아이디어'가 이번 배치의 '바꾼것', '기준(base)'엔 직전 버전을 적는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>유화제 = 물·기름 섞기(몬타노브68). / 점증제 = 되기 만들기(잔탄검). / 유상·에몰리언트 = 오일·지방알코올.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>접힌 것도 '이 방향은 아니다' 데이터 — 지우지 말고 남긴다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>원료 '역할' 12종 (필터·트러블슈팅 공통 어휘)</t>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>감촉·실리콘 = 매끈함(디메치콘). / 향료 = 향(다도기는 무향 원칙). / 방부제 = 세균·곰팡이 방지.</t>
         </is>
       </c>
     </row>
@@ -1473,11 +1546,11 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>용제 = 바탕 물. / 보습 = 수분 잡기(글리세린·베타인·HA). / 활성 = 효능(피지·진정·톤).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
+          <t>항산화제 = 산패 방지(토코페롤). / pH조절 = 산도 맞춤(구연산). / 가용화제 = 오일을 물에 풀기(워시오프).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1485,50 +1558,50 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>유화제 = 물·기름 섞기(몬타노브68). / 점증제 = 되기 만들기(잔탄검). / 유상·에몰리언트 = 오일·지방알코올.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+          <t>→ 자세한 '역할 설명'은 원료 시트의 E열에 역할마다 붙어 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>안정성 테스트란 (45℃·RT·4℃·동결융해)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>감촉·실리콘 = 매끈함(디메치콘). / 향료 = 향(다도기는 무향 원칙). / 방부제 = 세균·곰팡이 방지.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>제품이 '시간이 지나도 안 변하는지' 보는 시험. 같은 배치를 조건별로 나눠 두고 1·2·4·8주 관찰한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>항산화제 = 산패 방지(토코페롤). / pH조절 = 산도 맞춤(구연산). / 가용화제 = 오일을 물에 풀기(워시오프).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>45℃=고온(가속). 더우면 변질이 빨라져 '미래를 미리' 본다 — 분리·변색·냄새·pH 변화가 여기서 먼저 터진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>→ 자세한 '역할 설명'은 원료 시트의 E열에 역할마다 붙어 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>안정성 테스트란 (45℃·RT·4℃·동결융해)</t>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>RT=Room Temperature(상온)=실제 사용 근사·대조군. 4℃=냉장(굳음·결정). 동결융해=얼렸다 녹였다 반복(유화 견고성).</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1613,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>제품이 '시간이 지나도 안 변하는지' 보는 시험. 같은 배치를 조건별로 나눠 두고 1·2·4·8주 관찰한다.</t>
+          <t>둘 곳: 45℃는 발효기/인큐베이터, RT는 직사광 없는 서랍, 4℃·냉동은 냉장고. 투명 바이알에 담아 눈으로 비교.</t>
         </is>
       </c>
     </row>
@@ -1552,54 +1625,54 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>45℃=고온(가속). 더우면 변질이 빨라져 '미래를 미리' 본다 — 분리·변색·냄새·pH 변화가 여기서 먼저 터진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+          <t>개발일지 예시 '안정성 45C/RT 등록' = 이 배치를 45℃와 상온에 넣어 안정성 관찰을 시작한다는 뜻.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>초보 용어 사전</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="47" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>RT=Room Temperature(상온)=실제 사용 근사·대조군. 4℃=냉장(굳음·결정). 동결융해=얼렸다 녹였다 반복(유화 견고성).</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>수상(A)=물에 녹는 것(물·보습·수용성 활성) / 유상(B)=기름에 녹는 것(오일·유화제·지방알코올) / 냉각첨가(C)=식힌 뒤 넣는 열에 약한 것(방부·향·일부 활성).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>둘 곳: 45℃는 발효기/인큐베이터, RT는 직사광 없는 서랍, 4℃·냉동은 냉장고. 투명 바이알에 담아 눈으로 비교.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>유화 = 물과 기름을 유화제+강한 교반(호모)으로 안 갈라지게 섞는 것(로션·크림).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>개발일지 예시 '안정성 45C/RT 등록' = 이 배치를 45℃와 상온에 넣어 안정성 관찰을 시작한다는 뜻.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>초보 용어 사전</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="47" customHeight="1">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>%p(퍼센트포인트) = 배합 % 숫자를 그만큼 올리/내리기(글리세린 5%→4% = 1%p↓).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1607,7 +1680,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>수상(A)=물에 녹는 것(물·보습·수용성 활성) / 유상(B)=기름에 녹는 것(오일·유화제·지방알코올) / 냉각첨가(C)=식힌 뒤 넣는 열에 약한 것(방부·향·일부 활성).</t>
+          <t>배치 = 한 번에 만드는 양(연습은 100g). base = 이번 실험의 출발 버전.</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1692,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>유화 = 물과 기름을 유화제+강한 교반(호모)으로 안 갈라지게 섞는 것(로션·크림).</t>
+          <t>선분산 = 검(잔탄)을 물에 넣기 전 글리세린에 미리 개어 두는 것(뭉침·피시아이 방지).</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1704,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>%p(퍼센트포인트) = 배합 % 숫자를 그만큼 올리/내리기(글리세린 5%→4% = 1%p↓).</t>
+          <t>리브온 = 씻어내지 않고 피부에 남는 제품(토너·크림) → 향·보존을 더 보수적으로.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1716,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>배치 = 한 번에 만드는 양(연습은 100g). base = 이번 실험의 출발 버전.</t>
+          <t>말라세지아-세이프 = 피부 효모가 먹는 C11~24 지방산 오일을 뺀 것(우리 오일=스쿠알란·MCT·디메치콘).</t>
         </is>
       </c>
     </row>
@@ -1655,31 +1728,14 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>선분산 = 검(잔탄)을 물에 넣기 전 글리세린에 미리 개어 두는 것(뭉침·피시아이 방지).</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>리브온 = 씻어내지 않고 피부에 남는 제품(토너·크림) → 향·보존을 더 보수적으로.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>말라세지아-세이프 = 피부 효모가 먹는 C11~24 지방산 오일을 뺀 것(우리 오일=스쿠알란·MCT·디메치콘).</t>
+          <t>pH = 산성/염기성 척도(0~14). 피부는 약산성 5 안팎. 물 든 제품만 측정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>레시피를 늘리고 싶을 때</t>
         </is>
       </c>
     </row>
@@ -1691,42 +1747,42 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>pH = 산성/염기성 척도(0~14). 피부는 약산성 5 안팎. 물 든 제품만 측정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>레시피를 늘리고 싶을 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+          <t>나(Claude)에게 말하면 레시피 카드 + 처방 표 + (새 원료면) 원료 행을 추가해 재생성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>나(Claude)에게 말하면 레시피 카드 + 처방 표 + (새 원료면) 원료 행을 추가해 재생성한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>재생성해도 네가 적은 '입출고·개발일지'와 도구 '보유·메모'는 그대로 보존된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>재생성해도 네가 적은 '입출고·개발일지'와 도구 '보유·메모'는 그대로 보존된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="32" customHeight="1">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>직접 늘릴 땐: 처방 표에 [제품·원료·상·퍼센트] 행을 추가하면 재고 연계가 자동으로 걸린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>핵심 제약 (브랜드 = 다도기 지성·진정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1734,42 +1790,42 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>직접 늘릴 땐: 처방 표에 [제품·원료·상·퍼센트] 행을 추가하면 재고 연계가 자동으로 걸린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>핵심 제약 (브랜드 = 다도기 지성·진정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+          <t>말라세지아-세이프: C11~24 지방산 오일 배제(스쿠알란·MCT·디메치콘만).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>말라세지아-세이프: C11~24 지방산 오일 배제(스쿠알란·MCT·디메치콘만).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>무향: 향료 자극 배제. 화장품 표방 규칙: 치료·완화·항염·살균·병명 금지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>무향: 향료 자극 배제. 화장품 표방 규칙: 치료·완화·항염·살균·병명 금지.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="32" customHeight="1">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>pH 4.5~6.0(이 레시피 5.0~5.5), 물 든 제품은 반드시 방부, 소량 제조·1개월 내 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>안전·위생 (꼭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>·</t>
@@ -1777,376 +1833,57 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>pH 4.5~6.0(이 레시피 5.0~5.5), 물 든 제품은 반드시 방부, 소량 제조·1개월 내 사용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>안전·위생 (꼭)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+          <t>작업 전 70% 알코올로 도구·용기·손 소독 — 미생물이 자가제조 최대 리스크.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>작업 전 70% 알코올로 도구·용기·손 소독 — 미생물이 자가제조 최대 리스크.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>소량(50~100g)으로, 라벨·기록 철저, 가열·향 작업은 환기되는 곳에서.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>소량(50~100g)으로, 라벨·기록 철저, 가열·향 작업은 환기되는 곳에서.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>자가제조는 R&amp;D(개발)용 — 판매는 처방 완성 후 공장(OEM/ODM) 통해. 규제는 식약처 기준 재확인.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="5" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>⚠ %·공정·pH는 설계·연습 기준(예시). 제조 전 TDS·pH·방부력·사용기한·전성분 검증. 화장품 표방 규칙 준수.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>불안할 때 읽는 전략 메모 — '안 팔릴까' 걱정될 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>이 메모는 불안이 올라올 때 다시 읽는 곳이다. 결론부터 — 지금 방향이 맞다. 승부는 포뮬러가 아니라 '한 명을 정확히 겨누는 데'서 난다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>① 기본기: 이 7종이면 유화·점증·방부·pH·가용화·안정성을 한 바퀴 다 익힌다. 수분·진정 스킨케어 포뮬레이터 기본기는 확실히 선다. (선크림·세안·고난도 활성은 지금 안 건드리는 게 맞다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>② 포뮬러는 해자가 아니다: 전성분은 법적으로 공개된다. 좋은 제품은 '입장권'일 뿐 차별점이 아니다 — 안 갈라지고·안 상하고·pH 맞으면 이미 '팔 수 있는 상태'다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>③ 희귀 원료로 승부하지 마라: 스토리는 좋아도 MOQ·수급·단가가 1인·저자본 브랜드를 정확히 죽인다. 리오더 때 원료가 단종되면 제품이 멈춘다. 흔하고 안정적인 원료로 가는 지금 선택이 옳다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>④ 차별화는 '넣은 원료'가 아니라 '뺀 규율'에서 나온다: 말라세지아-세이프(먹이 오일 배제)+무향. 흔한 원료로 만든 독한 컨셉이 곧 USP — 원료가 아니라 철학이 USP다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>⑤ 안 팔리는 진짜 이유는 품질이 아니라 '누구의 어떤 문제를 한 줄로 못 말해서'다. 리스크는 포뮬러가 아니라 (a)한 명의 타깃 (b)그가 나를 발견할 경로 (c)왜 나여야 하나 한 문장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>⑥ 지금 할 하나: 히어로 크림 100g 한 배치(원료는 20배치분 넉넉) → 포지셔닝 한 문장 적기 → 지루성·트러블 실사용자 3~5명에게 샘플, '내 얘기 같나? 돈 주고 살 것 같나?'만 묻기.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>⑦ 포지셔닝 한 문장 초안: "말라세지아에게 먹이 안 주는, 무향 진정 크림 — 성분 따지다 지친 지성 피부를 위해."</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>확장 로드맵 — 못 배우는 4개(선크림·기능성·세안·무수밤) 어떻게 가져갈까</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>핵심 구분: '다 직접 만든다'가 아니라 '직접 vs 위탁'을 나누는 것. 시험엔 4개 다 '규제·이론'으로 나오지만 만드는 법은 아니다 — 이론은 어차피 시험이 시켜준다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>[직접 손으로 마스터 = R&amp;D·감각·원가통제] 리브온 수분·진정 스킨케어(=지금 이 엑셀, 히어로 완성·검증) → 확장 1순위는 무수 밤·스틱(물이 없어 방부 부담 낮아 1인 제조 현실적).</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>[위탁 OEM/ODM 전제로 '기획만' 공부] 선크림·미백/주름 기능성은 식약처 심사 + SPF·효능시험이 필요 → 혼자 못 만든다. 공장이 처방·인증을 보유. 폼클렌저 등 세안도 초기엔 설비·충전 부담으로 위탁이 합리.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>시험↔사업 겹치기: 선크림·기능성 파트는 '내가 만들 것'이 아니라 'ODM 발주 체크리스트'로 읽어라 — 자외선차단성분 한도·기능성 심사 절차 = 나중에 공장 미팅의 무기. 시험 암기가 곧 발주 역량.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>지금 승부처는 히어로 크림 하나다. 4개 확장은 '히어로가 팔린 뒤'의 일 — 지금 다 벌리면 1인·저자본에서 분산된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="30" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>한 줄: 4개 다 공부는 하되(시험이 시켜줌), 직접 제조는 '리브온 스킨케어 + 무수 밤'까지로 긋고, 선크림·기능성은 '위탁 전제의 기획 지식'으로 가져간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>시험 대비 — 이 엑셀로 맞춤형화장품조제관리사 공부하는 법 (토요일 시작)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>이 엑셀은 조제관리사 시험 이론의 '실습실'이다. 새 개념이 나오면 '내 엑셀·시트 어디에 있지?'로 찾으면 암기가 빨리 붙는다. 아래 3개 시트가 시험↔사업을 잇는다(성분·공정·사업 3축).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>「시험대비 원료맵」 보유 원료 26종을 시험 분류·사용한도로 매핑. ★페녹시에탄올 1.0% · 나이아신아마이드 미백 2~5% · 1,2-헥산다이올은 '지정 보존제 아님'(함정) · 토코페롤=산화방지제.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>「실습↔시험 개념」 제형·공정·안정성·위생·장비 실습을 과목2·4 개념+사업으로 묶음. 시험 비중이 가장 큰 영역이고, 내가 배치마다 하는 일이 곧 암기다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>「시험→사업 활용」 외운 이론을 ODM 발주·제품기획 체크리스트로 전환. D열 질문은 공장·ODM 미팅에서 그대로 던지면 된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="30" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>시험 4과목: ①화장품법의 이해 ②화장품 제조·품질관리 ③유통화장품 안전관리 ④맞춤형화장품의 이해(비중 큼). 합격=전 과목 총점 60% 이상 + 각 과목 만점의 40% 이상.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="30" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>공부 동선: (1)새 개념 나오면 위 3시트에서 '내 엑셀 위치' 찾기 (2)배치 만들 때 공정·안정성·pH·위생을 '시험 용어'로 소리내 되뇌기 (3)선크림·기능성은 '만들 것'이 아니라 'ODM 발주 체크리스트'로 읽기.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="30" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>암기 가성비 순서: ①사용제한 원료(보존제·자외선차단) 최대함량 → ②배합금지 원료 → ③기능성 주성분(미백·주름) → ④비의도적 유래물질·미생물 한도 → ⑤착향제 알레르기 유발성분.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>득점·사업 동시 포인트: 안정성 시험=사용기한·PAO 근거 / 혼합·소분 위생=맞춤형판매업 운영(자격의 직접 수익화) / 처방 %합계=전성분 함량순 표기.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>공부하다 '이 개념이 어느 시트에도 안 걸리네' 싶은 게 나오면 Claude에게 — 해당 시트에 그 칸만 채워 넣는다. 수치·목록은 항상 최신 식약처 고시로 재확인.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A96:B96"/>
+  <mergeCells count="14">
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A66:B66"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A106:B106"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2168,2202 +1905,2201 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>원료↔시험 매핑 — 보유 26종 + 시험 전용 원료(미보유) 사전</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>★=시험 빈출/함정. '엑셀 역할=시험용(미보유)'로 필터하면 시험 전용 원료만 모아 볼 수 있다. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>원료</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>INCI</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>엑셀 역할</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>시험 분류</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>사용한도·고시 포인트</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>시험 빈출 메모</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>실험/개발 연계</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>사업 연계</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Glycerin</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>보습제(휴멕턴트)·수성원료</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음(일반원료)</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>대표 다가알코올 보습제, 수상</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>수상 보습·잔탄 선분산 매개</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>저가 범용, 전성분 상위 노출</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Niacinamide</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>미백 기능성 고시 주성분/활성</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>미백 고시 함량 2~5%</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>★빈출: 미백 주성분·2~5% 암기</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>완전용해 확인, 2~4% 사용</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>미백 '보고' 시 주성분(2~5%)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>다중 히알루론산</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Hyaluronic Acids</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>보습제(고분자 휴멕턴트)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>분자량별 보습, 수용성 고분자</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>전날 불려 사용(분말)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>'다중 수분' 소구·분자량 스토리</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>베타글루칸</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Beta-Glucan</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>활성(진정)·고분자 다당류</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>진정 유효성분</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>냉장 보관, 수상 진정</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>진정 서사 핵심 성분</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>베타인</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Betaine</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>보습제(휴멕턴트)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>아미노산계 보습제</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>끈적임 줄이는 대체 보습</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>저자극 소구</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>아연피카</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Zinc PCA</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>활성(피지·수렴)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>Zinc PCA 피지조절</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>수상, 피지·수렴</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>지성 타깃 포인트</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>알란토인</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Allantoin</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>활성(진정·각질)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>진정·보습 보조</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>용해 느림, 충분히 교반</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>저자극 보조 활성</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>잔탄검</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Xanthan Gum</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>점증제</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>점증제(천연 고분자)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>대표 천연 점증제, 선분산</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>글리세린 선분산(피시아이 방지)</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>'천연 점증' 소구</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>용제</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>수성원료(용제·기제)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>기제, 순도·미생물 관리 대상</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>잔량(q.s.) 100g 맞춤</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>용수 규격=품질관리 기본</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>프로판디올</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Propanediol</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>보습제·용제(다가알코올)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>글리콜계, 방부 보조력</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>방부 보조 폴리올</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>'파라벤프리' 방부 서사</t>
         </is>
       </c>
     </row>
     <row r="14" ht="47" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>MCT오일</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Caprylic/Capric Triglyceride</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>유상·에몰리언트</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>유성원료(에스터 오일)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>Caprylic/Capric Triglyceride</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>경량 에몰리언트·말라세지아세이프</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>지성용 가벼운 유분</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>디메치콘</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Dimethicone</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>감촉·실리콘</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>유성원료(실리콘)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>실리콘 오일, 발림·보호막</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>발림·얇은 보호막</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>실키 사용감(실리콘은 포지셔닝 선택)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>몬타노브68</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Cetearyl Alcohol &amp; Cetearyl Glucoside</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>계면활성제(비이온)+고급지방알코올</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>O/W 유화제, HLB·유화 개념</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>O/W 유화, 유화온도 70~75℃</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>'순한 유화' 소구</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>세틸알코올</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Cetyl Alcohol</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>유상·에몰리언트</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>고급지방알코올(보조유화)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>점도·유화 안정화</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>점도·유화 안정</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>바디·사용감 조절</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>스쿠알란</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Squalane</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>유상·에몰리언트</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>유성원료(에몰리언트)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>안정성 높은 보습 오일</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>안정 보습오일·세이프</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>'피부 유사' 서사</t>
         </is>
       </c>
     </row>
     <row r="19" ht="47" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Butyrospermum Parkii Butter</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>유상·에몰리언트</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>유성원료(식물성 버터)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>고형 유지, 에몰리언트</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>v2 미사용(C11~24 지방산)</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>바디 등 타제형 확장</t>
         </is>
       </c>
     </row>
     <row r="20" ht="47" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Cetearyl Olivate &amp; Sorbitan Olivate</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>유화제</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>계면활성제(비이온 유화제)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>올리브 유래 O/W 유화제</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>v2 미사용(말라세지아 회색지대)</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="28" t="inlineStr">
         <is>
           <t>타제형 유화</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>토코페롤(비타민E)</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Tocopherol</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>항산화제</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>산화방지제</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음(산화방지)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>★분류주의: 산화방지제(보존제 아님)</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>오일 산패 방지</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>★전성분 역할 표기 정확</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>폴리글리세릴-4 카프레이트</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Polyglyceryl-4 Caprate</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>가용화제</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>계면활성제(비이온 가용화제)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>워시오프 가용화·세정 보조</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>워시오프 가용화(미보유)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>클렌징 라인 전제 원료</t>
         </is>
       </c>
     </row>
     <row r="23" ht="47" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Simmondsia Chinensis Seed Oil</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>유상·에몰리언트</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>유성원료(왁스 에스터 오일)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>피지 유사 왁스 에스터</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>v2 미사용(말라세지아 먹이)</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>헤어·바디 등 타제형</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>1,2-헥산다이올</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>1,2-Hexanediol</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>방부제</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>다가알코올(보습·방부 보조)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>★지정 보존제 아님(목록 미등재)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>★함정: 방부력 있어도 법적 보존제 아님</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>방부 부스터, 페녹시 병용</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>★책임 방부성분 별도 명시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="47" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>녹차추출물</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Camellia Sinensis Leaf Extract</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>식물추출물(활성)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>수용성 추출물</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>냉장·갈변 주의, 수용성</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>항산화 소구(미니멀서는 제외)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>마데카소사이드</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Madecassoside</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>식물추출물 활성(센텔라)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>진정 활성</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>냉동 보관, 시카 진정</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H26" s="28" t="inlineStr">
         <is>
           <t>★'시카' 마케팅 키워드</t>
         </is>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>판테놀(B5)</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Panthenol</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>활성(보습·진정)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>프로비타민 B5</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>보습·진정 보조</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="28" t="inlineStr">
         <is>
           <t>범용 보조 활성</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>페녹시에탄올</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Phenoxyethanol</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>방부제</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한 원료)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>★사용한도 1.0%</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>★최빈출: 보존제·한도 1.0% 필수암기</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>40℃ 이하 투입, 한도 1.0%</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="28" t="inlineStr">
         <is>
           <t>★방부 핵심·한도 준수 입증</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Citric Acid</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>pH조절</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>pH 조절제</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>사용한도 없음</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>citric acid, pH 조절</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>pH 5.0~5.5 적정</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>약산성 자극저감 근거</t>
         </is>
       </c>
     </row>
     <row r="30" ht="47" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>메틸파라벤</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Methylparaben</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>단일 0.4%·혼합 0.8%</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>★파라벤 한도(단일0.4/혼합0.8) 빈출</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="28" t="inlineStr">
         <is>
           <t>다도기 미사용(페녹시 채택)</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H30" s="28" t="inlineStr">
         <is>
           <t>'파라벤프리' 소구 가능</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>프로필파라벤</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Propylparaben</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>프로필·부틸파라벤 단일/혼합 0.14%</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>★장쇄 파라벤은 더 엄격(0.14%)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="28" t="inlineStr">
         <is>
           <t>트렌드상 기피 성분</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>벤질알코올</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>Benzyl Alcohol</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)+착향</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>보존 목적 1.0%</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>향료이자 보존제(이중역할) 주의</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>미사용(무향 원칙과 상충)</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>무향 포지션과 배치</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>소르빅애씨드</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Sorbic Acid</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>0.6%</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>유기산계, pH 낮아야 효과</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>천연계 방부 대안</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>벤조익애씨드</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Benzoic Acid</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>안식향산, 산성서 효과</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>DMDM하이단토인</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>DMDM Hydantoin</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>0.6%(포름알데하이드 방출)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="28" t="inlineStr">
         <is>
           <t>★포름알데하이드 방출 보존제(기피)</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="28" t="inlineStr">
         <is>
           <t>'노 포름알데하이드' 신뢰</t>
         </is>
       </c>
     </row>
     <row r="36" ht="47" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>메칠이소치아졸리논</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>Methylisothiazolinone</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>보존제(사용제한)</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>씻어내는 제품 0.0015%</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>★MIT/CMIT 알레르기·리브온 금지 빈출</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="G36" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H36" s="23" t="inlineStr">
+      <c r="H36" s="28" t="inlineStr">
         <is>
           <t>리브온 금지 주의</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>징크옥사이드</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Zinc Oxide</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>자외선차단(무기)·기능성</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>최대 25%</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
+      <c r="F37" s="28" t="inlineStr">
         <is>
           <t>★무기자차 대표, 백탁</t>
         </is>
       </c>
-      <c r="G37" s="23" t="inlineStr">
+      <c r="G37" s="28" t="inlineStr">
         <is>
           <t>선크림 확장 시</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="28" t="inlineStr">
         <is>
           <t>자차=기능성 인증 필요</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>티타늄디옥사이드</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>Titanium Dioxide</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>자외선차단(무기)·기능성</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>최대 25%</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
+      <c r="F38" s="28" t="inlineStr">
         <is>
           <t>무기자차, 산란 방식</t>
         </is>
       </c>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="G38" s="28" t="inlineStr">
         <is>
           <t>확장 시</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H38" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="39" ht="47" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>에칠헥실메톡시신나메이트</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>Ethylhexyl Methoxycinnamate</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>자외선차단(유기)·기능성</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>최대 7.5%</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>대표 유기자차</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="28" t="inlineStr">
         <is>
           <t>확장 시</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="40" ht="47" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>부틸메톡시디벤조일메탄</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>Butyl Methoxydibenzoylmethane</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>자외선차단(유기)·기능성</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>최대 5%</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>아보벤존, UVA·광안정성 이슈</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="G40" s="28" t="inlineStr">
         <is>
           <t>확장 시</t>
         </is>
       </c>
-      <c r="H40" s="23" t="inlineStr">
+      <c r="H40" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>Arbutin</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="28" t="inlineStr">
         <is>
           <t>미백 기능성 주성분</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>2~5%</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>★미백 고시 성분(하이드로퀴논 유도체)</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="28" t="inlineStr">
         <is>
           <t>미백 라인 옵션</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>아스코빌글루코사이드</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>Ascorbyl Glucoside</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="28" t="inlineStr">
         <is>
           <t>미백 기능성 주성분</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
+      <c r="F42" s="28" t="inlineStr">
         <is>
           <t>비타민C 유도체(안정형)</t>
         </is>
       </c>
-      <c r="G42" s="23" t="inlineStr">
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H42" s="23" t="inlineStr">
+      <c r="H42" s="28" t="inlineStr">
         <is>
           <t>미백 소구</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>레티놀</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>Retinol</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>주름개선 기능성 주성분</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>2,500 IU</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="28" t="inlineStr">
         <is>
           <t>★단위가 IU(함량주의)·변색</t>
         </is>
       </c>
-      <c r="G43" s="23" t="inlineStr">
+      <c r="G43" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H43" s="23" t="inlineStr">
+      <c r="H43" s="28" t="inlineStr">
         <is>
           <t>안티에이징 라인</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>아데노신</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>Adenosine</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>주름개선 기능성 주성분</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="28" t="inlineStr">
         <is>
           <t>★주름 고시 0.04% 빈출</t>
         </is>
       </c>
-      <c r="G44" s="23" t="inlineStr">
+      <c r="G44" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H44" s="23" t="inlineStr">
+      <c r="H44" s="28" t="inlineStr">
         <is>
           <t>주름 소구</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>살리실릭애씨드</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>Salicylic Acid</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>사용제한/여드름(세정) 기능성</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>보존 목적 0.5%·여드름 세정 0.5%</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>★BHA, 영유아 사용제한 빈출</t>
         </is>
       </c>
-      <c r="G45" s="23" t="inlineStr">
+      <c r="G45" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H45" s="23" t="inlineStr">
+      <c r="H45" s="28" t="inlineStr">
         <is>
           <t>지성 세안 라인 옵션</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>하이드로퀴논</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>Hydroquinone</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>★배합금지(일반화장품)</t>
         </is>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>화장품 사용금지(의약품)</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="F46" s="28" t="inlineStr">
         <is>
           <t>★'미백'이라고 넣으면 안 됨(함정)</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr">
+      <c r="G46" s="28" t="inlineStr">
         <is>
           <t>절대 미사용</t>
         </is>
       </c>
-      <c r="H46" s="23" t="inlineStr">
+      <c r="H46" s="28" t="inlineStr">
         <is>
           <t>해외직구 성분 주의</t>
         </is>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t>스테로이드</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>Corticosteroids</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>★배합금지</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>사용금지(의약품)</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F47" s="28" t="inlineStr">
         <is>
           <t>진정 강력해도 금지 — 함정</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>절대 미사용</t>
         </is>
       </c>
-      <c r="H47" s="23" t="inlineStr">
+      <c r="H47" s="28" t="inlineStr">
         <is>
           <t>'무스테로이드' 신뢰</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="23" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>소듐라우레스설페이트</t>
         </is>
       </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>Sodium Laureth Sulfate</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>음이온 계면활성제(세정)</t>
         </is>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="F48" s="28" t="inlineStr">
         <is>
           <t>★SLES, 대표 세정 음이온</t>
         </is>
       </c>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G48" s="28" t="inlineStr">
         <is>
           <t>세안 라인 위탁 시</t>
         </is>
       </c>
-      <c r="H48" s="23" t="inlineStr">
+      <c r="H48" s="28" t="inlineStr">
         <is>
           <t>저자극 버전 선택 포인트</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>코카미도프로필베타인</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>Cocamidopropyl Betaine</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="28" t="inlineStr">
         <is>
           <t>양쪽성 계면활성제(세정)</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>저자극, 베이비·민감 세안</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="G49" s="28" t="inlineStr">
         <is>
           <t>세안 라인</t>
         </is>
       </c>
-      <c r="H49" s="23" t="inlineStr">
+      <c r="H49" s="28" t="inlineStr">
         <is>
           <t>민감 타깃 적합</t>
         </is>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>세트리모늄클로라이드</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>Cetrimonium Chloride</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr">
         <is>
           <t>양이온 계면활성제(헤어)</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>제품별 사용한도</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>헤어 린스·대전방지(양이온)</t>
         </is>
       </c>
-      <c r="G50" s="23" t="inlineStr">
+      <c r="G50" s="28" t="inlineStr">
         <is>
           <t>헤어 확장</t>
         </is>
       </c>
-      <c r="H50" s="23" t="inlineStr">
+      <c r="H50" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>산화철</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="28" t="inlineStr">
         <is>
           <t>Iron Oxides</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="28" t="inlineStr">
         <is>
           <t>착색제(무기안료)</t>
         </is>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="28" t="inlineStr">
         <is>
           <t>허용 색소</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="28" t="inlineStr">
         <is>
           <t>색조 대표 무기안료</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="G51" s="28" t="inlineStr">
         <is>
           <t>색조 확장 시</t>
         </is>
       </c>
-      <c r="H51" s="23" t="inlineStr">
+      <c r="H51" s="28" t="inlineStr">
         <is>
           <t>무색 원칙과 별개</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>타르색소(예: 적색201호)</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>CI 번호</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr">
         <is>
           <t>착색제(타르색소)</t>
         </is>
       </c>
-      <c r="E52" s="23" t="inlineStr">
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>품목·부위별 사용제한</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>★눈 주위·점막 사용제한 빈출</t>
         </is>
       </c>
-      <c r="G52" s="23" t="inlineStr">
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>미사용</t>
         </is>
       </c>
-      <c r="H52" s="23" t="inlineStr">
+      <c r="H52" s="28" t="inlineStr">
         <is>
           <t>색조 시 색소 한도 학습</t>
         </is>
       </c>
     </row>
     <row r="53" ht="47" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t>리모넨</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>Limonene</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="28" t="inlineStr">
         <is>
           <t>착향 알레르기 유발성분</t>
         </is>
       </c>
-      <c r="E53" s="23" t="inlineStr">
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>씻는 0.01%/안 씻는 0.001% 초과 표시</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F53" s="28" t="inlineStr">
         <is>
           <t>★25종 중 대표(감귤향)</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>다도기 무향=해당없음</t>
         </is>
       </c>
-      <c r="H53" s="23" t="inlineStr">
+      <c r="H53" s="28" t="inlineStr">
         <is>
           <t>무향이 알레르겐 0 근거</t>
         </is>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>리날룰</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>Linalool</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>시험용(미보유)</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D54" s="28" t="inlineStr">
         <is>
           <t>착향 알레르기 유발성분</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>동일 표시기준</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="28" t="inlineStr">
         <is>
           <t>★라벤더향 대표 알레르겐</t>
         </is>
       </c>
-      <c r="G54" s="23" t="inlineStr">
+      <c r="G54" s="28" t="inlineStr">
         <is>
           <t>무향</t>
         </is>
       </c>
-      <c r="H54" s="23" t="inlineStr">
+      <c r="H54" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4375,9 +4111,6 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -4399,590 +4132,590 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>시험→사업 활용 — 외운 이론을 ODM 발주·제품 기획의 무기로 (암기 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>왼쪽(시험 핵심)을 외우되 오른쪽(사업 활용·발주 질문)으로 써먹는다. 'C열=쉬운 풀이'. ODM 미팅 체크리스트는 E열. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>분류(시험 영역)</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>시험 핵심 암기</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>쉽게 말하면 (풀이)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>→ 사업 활용</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>ODM·발주 미팅 질문(그대로 물어볼 것)</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>주의/메모</t>
         </is>
       </c>
     </row>
     <row r="4" ht="92" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>[법] 영업 종류·책임판매업</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>책임판매업·제조업·맞춤형판매업 구분, 등록/신고, 안전·품질관리(CGMP)</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>화장품 사업은 역할별로 등록이 나뉘어요. 공장을 안 돌리면 '책임판매업'만 등록하고 제조는 공장에 맡기면 돼요 — 조제관리사 자격은 '맞춤형 매장'을 열 때의 필수 자격.</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>직접제조 안 하면 '책임판매업' 등록 + 제조는 ODM 위탁 구조</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>제조소가 CGMP 업소인가? 제조번호·제조일·사용기한 관리? 책임판매 vs 제조품질 역할 경계는?</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>★조제관리사 자격=맞판 선임요건. 자격 자체가 사업 자산</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>[법] 표시·기재·광고</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>전성분 표시의무, 부당표시광고(치료·의학적 효능 금지)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>라벨·상세페이지엔 '해도 되는 말'과 '안 되는 말'이 법으로 갈려요. 치료·의학적 효과를 암시하면 걸립니다.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>라벨·상세페이지의 '하면 안 되는 말' 경계 관리</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>라벨 시안(전성분 함량순·착향 알레르겐) 검수해주나? 표시광고 가이드 제공?</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>치료·항염·살균·병명 금지(문구검사와 동일)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="77" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>[제조품질] 사용제한 보존제</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>보존제 목록·최대함량(페녹시에탄올 1.0% 등), 씻는/안 씻는 구분</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>방부 성분은 종류마다 '최대 이만큼만' 쓰라는 한도가 있어요. 공장에 '한도 안 넘었는지, 방부력 시험했는지' 당당히 물을 근거가 됩니다.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>방부 시스템 설계·검증을 공장에 요구하는 기준</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>방부 성분·함량? 방부력(챌린지) 시험성적서 주나? 리브온 한도 안 넘나?</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>1,2-헥산다이올=지정 보존제 아님(함정)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="77" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>[제조품질] 자외선차단·선크림</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>자외선차단성분 목록·최대함량, 자차=기능성(심사/보고)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>선크림은 자외선차단 성분을 정해진 한도로 쓰고 '기능성'으로 인증받아야 하는 제품이에요. 혼자 만들 게 아니라 위탁+인증 전제.</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>선크림은 '위탁+기능성 인증' 전제</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>자차 성분·함량 고시 범위 내? SPF/PA 시험성적서·기능성 심사필? 원료 수급?</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>확장 2~3순위. 히어로 검증 뒤</t>
         </is>
       </c>
     </row>
     <row r="8" ht="77" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>[제조품질] 기능성 주성분(미백·주름)</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>미백(나이아신아마이드 2~5%·알부틴), 주름(아데노신 0.04%·레티놀) 고시</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>미백·주름을 광고하려면 '정해진 성분을 정해진 양'으로 넣고 나라에 보고/심사해야 해요. 내가 가진 나이아신아마이드가 바로 미백 주성분.</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>'기능성' 표방하려면 고시 성분·함량 지켜 ODM에 보고/심사 대행</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>기능성 보고(심사) 대행 범위? 주성분·함량 고시 내? 안정화 데이터?</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>나이아신아마이드 보유·히어로 2% → 미백 표방은 전략 선택</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>[제조품질] 배합금지 원료</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>사용할 수 없는 원료 목록</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>아예 화장품에 못 쓰는 성분 목록이에요. 해외 처방을 들여올 때 이 목록으로 먼저 걸러야 사고가 안 납니다.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>수입·신규 원료, 해외 처방 1차 필터</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>전성분에 국내 배합금지·한도 초과 없나? 원료 CoA·MSDS 제공?</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>해외 인기 성분이 국내 금지인 경우 주의</t>
         </is>
       </c>
     </row>
     <row r="10" ht="77" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>[제조품질] CGMP 문서화</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>제조기록서·제조번호·일탈·재작업·교육</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>공장이 '언제·뭘·얼마나' 만들었는지 다 기록으로 남기는 체계예요. 내 개발일지 습관이 이 눈높이와 같아 위탁 계약 때 요구 수준을 압니다.</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>개발일지 기록 습관 → 위탁 품질계약 눈높이</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>로트별 기록·CoA·일탈처리 SOP 주나? 리콜 절차는?</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>추적성=리콜·CS 방어력</t>
         </is>
       </c>
     </row>
     <row r="11" ht="77" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>[제조품질] 위해평가·MoS</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>위험성확인→위험성결정→노출평가→위해도결정, 안전역(MoS)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>성분이 안전한지를 '위험성×노출량'으로 따져 여유(안전역)를 보는 방법이에요. 활성 농도를 올릴지 과학적으로 판단할 때 씁니다.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>신규·고농도 활성 도입 판단틀</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>원료 안전성자료(독성·MoS) 제공? 처방 농도 안전역 근거?</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>활성 농도 상향 시 과학적 근거 필요</t>
         </is>
       </c>
     </row>
     <row r="12" ht="77" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>[유통안전] 유래물질·미생물 한도</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>중금속(납20·비소10·수은1 등)·미생물(기타 1,000 CFU/g) 한도</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>원료에 딸려올 수 있는 중금속·세균 수에 '넘으면 안 되는 선'이 있어요. 출고 전 시험성적서를 받아야 품질을 증명하고 클레임을 막습니다.</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>출고 전 안전관리 시험성적서=품질 신뢰·CS 방어</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>로트별 중금속·미생물 시험성적서 주나? 비용 부담 주체?</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>계약서에 시험성적서 제공 명시</t>
         </is>
       </c>
     </row>
     <row r="13" ht="77" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>[유통안전] 착향 알레르기 성분</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>지정 25종, 씻는 0.01%/안 씻는 0.001% 초과 표시</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>향료 속 알레르기 유발 25종은 일정량 넘으면 표시 의무가 있어요. 다도기는 무향이라 이 부담이 아예 없다는 게 강점.</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>무향=알레르겐 0 소구 가능</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>향 무첨가 유지 가능? 원료 자체 잔향·알레르겐 유입 없나?</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>무향이 곧 USP이자 규제 리스크 최소화</t>
         </is>
       </c>
     </row>
     <row r="14" ht="77" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>[유통안전] 포장·용기</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>용기 재질 적합성, 안전용기·포장, 내용물-용기 상용성</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>용기 재질이 내용물과 안 맞으면 성분이 녹아나오거나 흡착돼요. 자/펌프/에어리스 선택이 안정성과 브랜드 메시지를 좌우합니다.</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>자/에어리스/펌프 선택·PCR 친환경 소구</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>내용물-용기 상용성(용출·흡착) 시험? 안전용기 대상? PCR 옵션?</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>용기선택이 안정성·브랜드 메시지 좌우</t>
         </is>
       </c>
     </row>
     <row r="15" ht="77" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>[유통안전] pH·안정성·사용기한</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>유형별 pH 기준, 안정성(가속·장기), PAO</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>'언제까지 쓰세요(사용기한·개봉후기간)'는 감이 아니라 안정성 데이터로 정해요. 라벨과 CS의 과학적 뒷받침이 됩니다.</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>사용기한·보관조건의 과학적 근거=라벨·CS 뒷받침</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>안정성 데이터로 사용기한/PAO 산정? 보관조건 표기 근거?</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>무리한 장기 표기 리스크</t>
         </is>
       </c>
     </row>
     <row r="16" ht="77" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>[맞춤형] 혼합·소분·위생</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>내용물+원료 혼합 가능/불가, 소분, 작업장 위생·소독</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>맞춤형 매장은 '어디까지 섞어도 되는지'와 위생이 핵심이에요. 이 역량이 곧 상담→조제 차별화이자 자격의 직접 수익화.</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>'맞춤형판매업' 직접 운영 핵심 역량(상담→조제)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>벌크 내용물 공급받아 매장서 소분·혼합 모델 가능? 내용물 안정성 유지?</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>조제관리사 자격의 직접 수익화 경로</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>[맞춤형] 피부측정·상담</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>피부 생리·타입·측정 지식</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>피부 생리·타입을 알면 '진단→맞춤 추천'을 해줄 수 있어요. 전문성이 신뢰와 객단가로 이어집니다.</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>피부진단→맞춤 추천 콘텐츠·서비스로 객단가↑</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>(자체검토) 측정기기·상담 프로토콜 표준화 가능?</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>전문성=신뢰·재구매</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>[맞춤형/제조] 계면활성제·세안</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>계면활성제 4분류(음/양/양쪽성/비이온), 세정 원리·자극도</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>세안 제품의 베이스는 계면활성제인데 종류마다 세정력·자극이 달라요. 민감·지성 타깃이면 저자극 쪽을 골라야 합니다.</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>폼클렌저 등 세안 라인 베이스 선택 기준</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>세정 베이스 계면활성제 종류·자극도? 약산성 유지? 민감·지성 적합?</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>초기엔 위탁 권장(설비·충전 부담)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>[법] 온라인판매·개인정보</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>전자상거래·개인정보보호 표시의무(화장품법 밖이나 판매 필수)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>온라인 판매는 화장품법 밖이지만 전자상거래·개인정보 표시의무를 지켜야 해요. 자사몰·스마트스토어 운영의 기본.</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>자사몰·스마트스토어 고지·청약철회 운영</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>플랫폼 입점 시 표시사항 자동 충족? 광고 심의 지원?</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>판매 채널 운영의 법적 기본</t>
         </is>
       </c>
     </row>
     <row r="20" ht="77" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>[법] 수입·통관</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>해외 원료·완제 수입 시 표준통관예정보고 등 절차</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>해외 원료·완제를 들여오려면 통관 보고 등 절차가 있어요. 소싱 전에 절차·비용·기간을 알아야 리드타임 사고를 막습니다.</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>해외 성분 소싱 시 절차·비용·기간 파악</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>원료 수입대행·통관·검역 책임 주체? 리드타임?</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>해외 트렌드 성분 도입 리스크</t>
         </is>
@@ -4994,9 +4727,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -5018,622 +4748,622 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>실습↔시험 개념 — 배치마다 하는 일을 시험 개념·사업으로 (암기 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>성분은 「시험대비 원료맵」 참조. 여기는 제형·공정·안정성·위생·장비. 'D열=쉬운 풀이'. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>분류(실습 영역)</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>내가 하는 것 (엑셀 근거)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>→ 시험 개념 (외울 것)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>쉽게 말하면 (풀이)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>→ 사업 활용</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>주의/메모</t>
         </is>
       </c>
     </row>
     <row r="4" ht="77" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>[제형 분류]</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>토너·앰플·젤·로션·크림·클렌징오일·워시오프 7종 직접 설계·제조</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>화장품 유형 분류, 유화형(O/W)·가용화·분산 구분, 리브온/워시오프</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>내가 만드는 7가지가 사실 시험의 '유화/가용화/분산', '씻어내는/안 씻는' 분류 그 자체예요. 크림은 유화, 워시오프는 가용화.</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>라인업 설계·제품유형 신고, 직접/위탁 경계</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>리브온(토너·크림)은 방부·향을 더 보수적으로</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>[배합 설계·전성분]</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>처방 %합계 100, 정제수 잔량(q.s.), 1% 이하 정밀계량</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>전성분=함량 많은 순, 1%이하·착향·색소는 순서 무관, q.s.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>처방 %를 많은 순으로 적으면 그게 바로 전성분 표기 초안이에요. 1% 이하·향·색소만 순서를 안 지켜도 됩니다.</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>라벨 전성분 검수·ODM 처방 대조</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>★처방 시트가 곧 전성분 표기 초안</t>
         </is>
       </c>
     </row>
     <row r="6" ht="77" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>[제조 공정]</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>수상(A) 70~75℃ / 유상(B) / 냉각첨가(C) 40℃ 이하, 잔탄 선분산</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>가용화·유화·분산 공정, 상(phase), 가열·냉각·투입 순서</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>수상은 데우고, 유상은 녹이고, 열에 약한 건 식은 뒤(40℃↓) 넣는 '순서'가 공정 핵심이에요. 순서를 지켜야 매번 같은 품질이 나옵니다.</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>공정 표준화=재현성→품질 일관성(CS 방어)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>냉각군(방부·열 약한 활성)은 40℃ 이하 투입</t>
         </is>
       </c>
     </row>
     <row r="7" ht="77" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>[유화 안정성]</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>층분리·크리밍·오일링을 온도·전단(호모)·유화제 3요소로 교정</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>유화 안정성, 유화제 HLB·유화형, 상분리 원인</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>물·기름이 갈라지는 건 ①온도 ②호모(전단) ③유화제, 세 가지로 잡아요. 점도를 올리면 기름방울이 못 떠올라 더 안정됩니다.</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>안정 처방=반품·클레임 방지, ODM 샘플 평가</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>점도↑(잔탄검)도 크리밍을 막는다</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>[안정성 시험]</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>45℃·RT·4℃·동결융해 + 원심(LC-8S) 분리mm, 1·2·4·8주 관찰</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>안정성 시험(가속·장기·가혹), 경시변화</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>45℃·동결융해로 미리 괴롭혀 변하는지 봐요. 이 결과가 '사용기한·개봉후기간'의 근거이고 ODM에 요구할 데이터.</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>★사용기한·PAO 산정 근거=ODM에 요구할 데이터</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>투명 바이알로 변색·냄새·pH 비교</t>
         </is>
       </c>
     </row>
     <row r="9" ht="77" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>[pH 관리]</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>목표 5.0~5.5, 구연산 희석액 적정, pH미터 교정(버퍼 4·7)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>피부 약산성, 유형별 pH 기준, pH 측정법</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>피부가 약산성이라 제품도 거기 맞춰요(5.0~5.5). 구연산을 한 방울씩 넣어 맞추고 pH미터는 버퍼로 교정 후 씁니다.</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>자극 최소화 근거, 민감·지성 소구</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>물 든 제품만 측정, 되직하면 정제수 1:1 희석</t>
         </is>
       </c>
     </row>
     <row r="10" ht="77" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>[방부·미생물]</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>페녹시에탄올+1,2-헥산다이올, 도구 소독, 1개월 내 사용</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>보존제 사용한도, 미생물 한도, 방부력(챌린지)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>물+영양분은 세균의 밥상이라 방부가 필수예요. 단 헥산다이올은 법적 보존제가 아니라 책임 방부성분(페녹시)이 따로 있어야 합니다.</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>방부력 시험성적서를 ODM에 요구, 사용기한 근거</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>물+영양=미생물 배지. 헥산다이올=지정 보존제 아님</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>[산화·원료 보관]</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>토코페롤 항산화, 차광·서늘, 냉장/냉동/방습 분리 보관</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>산화방지제, 원료 보관조건, 비의도 변질·유래물질</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>기름은 산소를 만나면 쩐내가 나요(산화). 토코페롤로 늦추고, 원료는 성질대로 냉장·냉동·방습 나눠 보관합니다.</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>원료 자재관리(CoA·로트·유효기간)→품질·원가</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
         </is>
       </c>
     </row>
     <row r="12" ht="77" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>[작업장 위생·혼합소분]</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>70% 에탄올 소독, 향·색 전용도구, 완전 건조</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>맞춤형 혼합·소분 위생, 교차오염 방지, 손 소독</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>자가제조·맞춤형의 최대 리스크는 미생물 오염이에요. 70% 알코올 소독·전용 도구가 시험(맞춤형 위생)이자 매장 운영 표준.</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>★맞판 매장 운영 표준=조제관리사 실무 핵심</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>미생물 오염이 자가제조 최대 리스크</t>
         </is>
       </c>
     </row>
     <row r="13" ht="77" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>[장비·계량]</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>정밀저울 0.01g(소량)·벤치저울(대량), 호모·오버헤드·pH미터</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>혼합·소분 장비·기구, 계량 정확도·오차</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>1% 이하 소량은 정밀저울(0.01g), 많은 양은 큰 저울로 나눠 재요. 소량을 큰 저울로 재면 오차가 처방 전체를 망칩니다.</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>소량 생산 vs 위탁 판단, 매장 장비 기준</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>1% 이하는 정밀저울 — 큰 저울은 처방을 망친다</t>
         </is>
       </c>
     </row>
     <row r="14" ht="77" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>[제조 기록·배치]</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>개발일지에 날짜·제품·배치량g·판정, '한 번에 한 변수'</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>제조번호·제조기록서(뱃치기록), 제조일·사용기한(CGMP)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>제조번호·배치기록(언제·뭘·얼마나)이 CGMP 핵심이에요. 이 추적성이 있어야 문제가 나도 어느 로트인지 찾아 대응합니다.</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>로트 추적성=리콜·CS 대응, ODM 품질계약 기준</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>접은 실험도 '이 방향 아님' 데이터</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>[계면활성제·유화이론]</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>몬타노브68로 O/W 유화, 두 상 70~75℃</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>계면활성제 4분류·HLB·유화형</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>몬타노브로 물·기름을 섞는 게 유화인데, 계면활성제는 4종류이고 자극 세기가 달라요(비이온이 제일 순함).</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>세안·클렌징 라인 베이스 판단</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>자극순 양이온&gt;음이온&gt;양쪽성&gt;비이온</t>
         </is>
       </c>
     </row>
     <row r="16" ht="77" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>[점증·유변]</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>잔탄검 0.1%p 단위 점도 조절, 선분산</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>점증제·요변성·점도 개념</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>잔탄검 양으로 '되기(점도)'를 조절하는 게 유변학이에요. 검을 물에 바로 넣으면 쌀알 덩어리(피시아이)가 생깁니다.</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>사용감 설계=차별화</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>피시아이=검을 물에 바로 넣어 생김</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>[관능평가]</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>성상·색·향·사용감 바이알 비교, 표준품 대조</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>관능평가·비교시료·채점 기준</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>기계가 아니라 사람 감각으로 색·향·발림을 평가하되, 기준 샘플과 비교해 주관을 줄이는 방법이에요.</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>품질 합부·배치 재현 기준</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>주관 줄이려 기준·대조군 사용</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>[색소·착색]</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>다도기 무색 지향(코치닐 등 미사용)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>색소 분류(염료·안료·레이크)·사용제한 색소</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>색소는 염료·안료·레이크로 나뉘고 부위별 사용제한이 있어요. 다도기는 무색이라 변색·규제 리스크가 적다는 게 장점.</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>무색=규제·변색 리스크↓ 소구</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>색조 확장 시 색소 한도 학습</t>
         </is>
       </c>
     </row>
     <row r="19" ht="77" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>[표시·라벨 실습]</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>처방%→전성분 함량순 초안, 주의사항·PAO 표기</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>전성분·기재사항 규칙, PAO·사용기한</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>처방 %를 그대로 전성분 함량순 초안으로 옮기고 주의사항·개봉후기간까지 적어보는 연습이에요. ODM 라벨과 대조할 눈이 생깁니다.</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>라벨 셀프 검수→ODM 대조</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>1%이하·착향·색소는 순서 무관</t>
         </is>
       </c>
     </row>
     <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>[계량·검교정]</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>정밀저울 0.01g, 저울 영점·주기 점검</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>계량 정확도·오차·검교정 개념</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>저울도 주기적으로 영점·교정을 해줘야 믿을 수 있어요. 검교정을 안 하면 같은 처방도 매번 달라집니다.</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>소량생산 품질·원가 통제</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>검교정 안 하면 처방 재현성↓</t>
         </is>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>[원료 입고·자재관리]</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>입출고 장부, CoA·로트·유효기간, 보관조건 분리</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>원자재 관리·보관조건·비의도 변질</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>원료 받을 때 CoA(성적서)·로트·유효기간을 적고 성질대로 보관하는 게 자재관리예요. 재고·원가·품질을 한꺼번에 통제합니다.</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>재고·원가·품질 동시 통제</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>CoA 없는 원료=품질 불확실</t>
         </is>
@@ -5645,9 +5375,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -5657,7 +5384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G377"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10015,6 +9742,11 @@
           <t>[⑧ 미니멀 변주 — 히어로에서 활성 3종만]   시크 진정 크림 (미니멀 3종)   ·   크림(유화·리치)   ·   sebum-calm-cream-minimal</t>
         </is>
       </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>▶ 실험 공정 이미지</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="32" customHeight="1">
       <c r="A324" s="7" t="inlineStr">
@@ -10764,8 +10496,29 @@
         </is>
       </c>
     </row>
+    <row r="379" ht="17" customHeight="1">
+      <c r="A379" s="21" t="inlineStr">
+        <is>
+          <t>[⑨ (확장) 무수 밤·스틱 — 레시피는 히어로 검증·판매 후 착수]</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="17" customHeight="1">
+      <c r="A380" s="22" t="inlineStr">
+        <is>
+          <t>· 물이 없어 방부·유화 부담이 낮아 1인 제조에 현실적 — 읽어보기 '확장 로드맵'의 확장 1순위.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="17" customHeight="1">
+      <c r="A381" s="22" t="inlineStr">
+        <is>
+          <t>· 지금 승부처는 히어로 크림 하나. 무수 밤은 히어로가 물리 배치·검증·판매된 뒤 설계한다(지금 벌리면 분산).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="248">
+  <mergeCells count="251">
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A133:F133"/>
@@ -10778,8 +10531,8 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A301:F301"/>
-    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A160:F160"/>
@@ -10824,8 +10577,8 @@
     <mergeCell ref="A250:F250"/>
     <mergeCell ref="A315:F315"/>
     <mergeCell ref="A355:F355"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A237:F237"/>
-    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A360:F360"/>
     <mergeCell ref="A41:F41"/>
@@ -10848,9 +10601,9 @@
     <mergeCell ref="A204:F204"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A269:F269"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A269:F269"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A254:F254"/>
@@ -10898,6 +10651,7 @@
     <mergeCell ref="A330:F330"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="A366:F366"/>
+    <mergeCell ref="A379:F379"/>
     <mergeCell ref="A375:F375"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A105:F105"/>
@@ -10907,6 +10661,7 @@
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A272:F272"/>
     <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A381:F381"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="A313:F313"/>
@@ -10995,6 +10750,7 @@
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A380:F380"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A327:F327"/>
     <mergeCell ref="A170:F170"/>
@@ -11026,7 +10782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11045,7 +10801,7 @@
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>개발일지에 적은 '사용감·이슈'가 여기 '증상'과 맞는 걸 찾아 '조정'대로 한 축만 바꾼다 → 그 조정을 개발일지 '다음 아이디어'에 적고 다시 만든다.   ┃ '관련 역할'은 원료 시트의 '역할' 값과 같다 — 원료 시트에서 그 역할로 필터하면 바꿀 후보 원료가 한눈에. ┃ %p=퍼센트포인트(%숫자를 그만큼↑/↓). ★한 번에 하나만.</t>
         </is>
@@ -11563,14 +11319,23 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>▼ 불량 판정 레퍼런스 — 만든 결과를 눈으로 대조 (①정상 ②층분리 ③오일링·크리밍 ④피시아이 ⑤이물질오염 ⑥기포)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11607,7 +11372,7 @@
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>지금 가진 원료와 '남은 양(현재고)'을 보는 재고판. 현재고는 자동 계산이라 직접 고치지 않는다 — 사면 '입출고', 쓰면 '개발일지'에 적으면 여기 숫자가 따라 움직인다.   ┃ 역할=고정 11종(필터용) — 트러블슈팅 '관련 역할'과 같은 값이라, 이슈의 그 역할로 여기서 필터하면 바꿀 원료가 보인다. ┃ 상=섞는 단계(A수상·B유상·C냉각·pH) · 세이프=히어로(말라세지아) 적합 O/X · 현재고g=최초보유+구매+조정−제조사용(음수=빨강, 사야 함)</t>
         </is>
@@ -13309,7 +13074,7 @@
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>실험에 쓰는 장비·소모품 모음. 분류·보유로 필터해서 '뭘 더 사야 하나'를 본다. '보유'·'메모'는 네가 고쳐도 재생성 때 보존된다.   ┃ 보유 값: 보유=가지고 있음 · 추천=있으면 좋음(필요 시 구매) · 소모품=떨어지면 보충 · 필수=없으면 시작 금지</t>
         </is>
@@ -14313,7 +14078,7 @@
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>원료를 사거나(구매) 버릴 때(조정) 한 줄씩 쌓는 장부. 여기 적으면 '원료' 시트의 현재고가 자동으로 오르내린다.   ┃ 컬럼: 날짜=기록일 · 원료=아래 칸 클릭해 드롭다운 선택 · 구분=구매 또는 조정 · 수량g=구매는 +, 흘림·폐기는 −(음수)로 · 출처·단가=어디서 얼마에 · 메모=로트·개봉일 등</t>
         </is>
@@ -14352,484 +14117,484 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="22" t="n"/>
+      <c r="A4" s="24" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
+      <c r="A14" s="24" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="F29" s="22" t="n"/>
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="22" t="n"/>
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n"/>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="24" t="n"/>
+      <c r="C42" s="24" t="n"/>
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n"/>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="22" t="n"/>
-      <c r="F43" s="22" t="n"/>
+      <c r="A43" s="24" t="n"/>
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n"/>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="22" t="n"/>
-      <c r="F45" s="22" t="n"/>
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="24" t="n"/>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="24" t="n"/>
+      <c r="D46" s="24" t="n"/>
+      <c r="E46" s="24" t="n"/>
+      <c r="F46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n"/>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="n"/>
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="22" t="n"/>
-      <c r="F48" s="22" t="n"/>
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n"/>
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="22" t="n"/>
-      <c r="F49" s="22" t="n"/>
+      <c r="A49" s="24" t="n"/>
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="24" t="n"/>
+      <c r="D49" s="24" t="n"/>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n"/>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="24" t="n"/>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n"/>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
+      <c r="A51" s="24" t="n"/>
+      <c r="B51" s="24" t="n"/>
+      <c r="C51" s="24" t="n"/>
+      <c r="D51" s="24" t="n"/>
+      <c r="E51" s="24" t="n"/>
+      <c r="F51" s="24" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n"/>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
+      <c r="A52" s="24" t="n"/>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n"/>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="22" t="n"/>
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n"/>
-      <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="22" t="n"/>
+      <c r="A54" s="24" t="n"/>
+      <c r="B54" s="24" t="n"/>
+      <c r="C54" s="24" t="n"/>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="24" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n"/>
-      <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="22" t="n"/>
-      <c r="F55" s="22" t="n"/>
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n"/>
-      <c r="B56" s="22" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="F56" s="22" t="n"/>
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="24" t="n"/>
+      <c r="C56" s="24" t="n"/>
+      <c r="D56" s="24" t="n"/>
+      <c r="E56" s="24" t="n"/>
+      <c r="F56" s="24" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n"/>
-      <c r="B57" s="22" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="22" t="n"/>
-      <c r="E57" s="22" t="n"/>
-      <c r="F57" s="22" t="n"/>
+      <c r="A57" s="24" t="n"/>
+      <c r="B57" s="24" t="n"/>
+      <c r="C57" s="24" t="n"/>
+      <c r="D57" s="24" t="n"/>
+      <c r="E57" s="24" t="n"/>
+      <c r="F57" s="24" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n"/>
-      <c r="B58" s="22" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="22" t="n"/>
-      <c r="E58" s="22" t="n"/>
-      <c r="F58" s="22" t="n"/>
+      <c r="A58" s="24" t="n"/>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="24" t="n"/>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n"/>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="E59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
+      <c r="A59" s="24" t="n"/>
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="24" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n"/>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
-      <c r="F60" s="22" t="n"/>
+      <c r="A60" s="24" t="n"/>
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="24" t="n"/>
+      <c r="D60" s="24" t="n"/>
+      <c r="E60" s="24" t="n"/>
+      <c r="F60" s="24" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n"/>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
-      <c r="F61" s="22" t="n"/>
+      <c r="A61" s="24" t="n"/>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="24" t="n"/>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n"/>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="n"/>
+      <c r="A62" s="24" t="n"/>
+      <c r="B62" s="24" t="n"/>
+      <c r="C62" s="24" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="24" t="n"/>
+      <c r="F62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n"/>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="n"/>
-      <c r="F63" s="22" t="n"/>
+      <c r="A63" s="24" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="24" t="n"/>
+      <c r="D63" s="24" t="n"/>
+      <c r="E63" s="24" t="n"/>
+      <c r="F63" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14882,7 +14647,7 @@
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>배치를 만들고 평가한 걸 한 줄씩 남기는 기록. '제품+배치량g'을 적으면 그 레시피대로 원료가 재고에서 자동 차감된다. 한 번에 한 가지만 바꾼다.   ┃ 컬럼: 제품=드롭다운 · 배치량g=만든 총량(재고 차감의 핵심) · 기준(base)=어느 버전에서 출발 · 바꾼것=이번에 바꾼 한 가지 · 유화ok=유화 성공(ok/실패) · 분리mm=원심(LC-8S) 분리층, 0이면 안정 · pH=측정값(5.0~5.5) · 판정=keeper/튜닝/접기(접은 것도 데이터)</t>
         </is>
@@ -14951,936 +14716,936 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>daily-lotion v2</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>잔탄검 0.4→0.5 (점도 실험)</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="G4" s="22" t="n"/>
-      <c r="H4" s="22" t="n">
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n">
         <v>5.2</v>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>약간 무거움</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>스트링잉(실 늘어짐)</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>접기</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>잔탄 대신 스클레로튬검 시도</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>daily-lotion v2</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>글리세린 5→3 + 베타인 2 추가</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="22" t="n">
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n">
         <v>5.1</v>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t>산뜻·덜 끈적</t>
         </is>
       </c>
-      <c r="J5" s="22" t="n"/>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t>keeper</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="L5" s="24" t="inlineStr">
         <is>
           <t>안정성 45C/RT 등록</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="22" t="n"/>
-      <c r="J6" s="22" t="n"/>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="24" t="n"/>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
+      <c r="K10" s="24" t="n"/>
+      <c r="L10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="22" t="n"/>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="n"/>
+      <c r="L13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="22" t="n"/>
-      <c r="L14" s="22" t="n"/>
+      <c r="A14" s="24" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
+      <c r="L15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="22" t="n"/>
-      <c r="K16" s="22" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="22" t="n"/>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="22" t="n"/>
-      <c r="J22" s="22" t="n"/>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="J23" s="22" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="n"/>
-      <c r="K25" s="22" t="n"/>
-      <c r="L25" s="22" t="n"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
-      <c r="J26" s="22" t="n"/>
-      <c r="K26" s="22" t="n"/>
-      <c r="L26" s="22" t="n"/>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="22" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="22" t="n"/>
-      <c r="L27" s="22" t="n"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="22" t="n"/>
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="22" t="n"/>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="22" t="n"/>
-      <c r="L30" s="22" t="n"/>
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="22" t="n"/>
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="24" t="n"/>
+      <c r="L31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="22" t="n"/>
-      <c r="J32" s="22" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="22" t="n"/>
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="n"/>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="22" t="n"/>
-      <c r="I33" s="22" t="n"/>
-      <c r="J33" s="22" t="n"/>
-      <c r="K33" s="22" t="n"/>
-      <c r="L33" s="22" t="n"/>
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n"/>
-      <c r="H35" s="22" t="n"/>
-      <c r="I35" s="22" t="n"/>
-      <c r="J35" s="22" t="n"/>
-      <c r="K35" s="22" t="n"/>
-      <c r="L35" s="22" t="n"/>
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="22" t="n"/>
-      <c r="I36" s="22" t="n"/>
-      <c r="J36" s="22" t="n"/>
-      <c r="K36" s="22" t="n"/>
-      <c r="L36" s="22" t="n"/>
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="22" t="n"/>
-      <c r="I37" s="22" t="n"/>
-      <c r="J37" s="22" t="n"/>
-      <c r="K37" s="22" t="n"/>
-      <c r="L37" s="22" t="n"/>
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="24" t="n"/>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="24" t="n"/>
+      <c r="I37" s="24" t="n"/>
+      <c r="J37" s="24" t="n"/>
+      <c r="K37" s="24" t="n"/>
+      <c r="L37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="22" t="n"/>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="22" t="n"/>
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="24" t="n"/>
+      <c r="J38" s="24" t="n"/>
+      <c r="K38" s="24" t="n"/>
+      <c r="L38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="22" t="n"/>
-      <c r="J39" s="22" t="n"/>
-      <c r="K39" s="22" t="n"/>
-      <c r="L39" s="22" t="n"/>
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="24" t="n"/>
+      <c r="J39" s="24" t="n"/>
+      <c r="K39" s="24" t="n"/>
+      <c r="L39" s="24" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="22" t="n"/>
-      <c r="I40" s="22" t="n"/>
-      <c r="J40" s="22" t="n"/>
-      <c r="K40" s="22" t="n"/>
-      <c r="L40" s="22" t="n"/>
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+      <c r="L40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="22" t="n"/>
-      <c r="J41" s="22" t="n"/>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="22" t="n"/>
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="24" t="n"/>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="24" t="n"/>
+      <c r="J41" s="24" t="n"/>
+      <c r="K41" s="24" t="n"/>
+      <c r="L41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n"/>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
-      <c r="G42" s="22" t="n"/>
-      <c r="H42" s="22" t="n"/>
-      <c r="I42" s="22" t="n"/>
-      <c r="J42" s="22" t="n"/>
-      <c r="K42" s="22" t="n"/>
-      <c r="L42" s="22" t="n"/>
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="24" t="n"/>
+      <c r="C42" s="24" t="n"/>
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="24" t="n"/>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="24" t="n"/>
+      <c r="J42" s="24" t="n"/>
+      <c r="K42" s="24" t="n"/>
+      <c r="L42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n"/>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="22" t="n"/>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="22" t="n"/>
-      <c r="I43" s="22" t="n"/>
-      <c r="J43" s="22" t="n"/>
-      <c r="K43" s="22" t="n"/>
-      <c r="L43" s="22" t="n"/>
+      <c r="A43" s="24" t="n"/>
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="24" t="n"/>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="22" t="n"/>
-      <c r="J44" s="22" t="n"/>
-      <c r="K44" s="22" t="n"/>
-      <c r="L44" s="22" t="n"/>
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="24" t="n"/>
+      <c r="L44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n"/>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="22" t="n"/>
-      <c r="F45" s="22" t="n"/>
-      <c r="G45" s="22" t="n"/>
-      <c r="H45" s="22" t="n"/>
-      <c r="I45" s="22" t="n"/>
-      <c r="J45" s="22" t="n"/>
-      <c r="K45" s="22" t="n"/>
-      <c r="L45" s="22" t="n"/>
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="24" t="n"/>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="24" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
-      <c r="G46" s="22" t="n"/>
-      <c r="H46" s="22" t="n"/>
-      <c r="I46" s="22" t="n"/>
-      <c r="J46" s="22" t="n"/>
-      <c r="K46" s="22" t="n"/>
-      <c r="L46" s="22" t="n"/>
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="24" t="n"/>
+      <c r="D46" s="24" t="n"/>
+      <c r="E46" s="24" t="n"/>
+      <c r="F46" s="24" t="n"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="n"/>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n"/>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="n"/>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="22" t="n"/>
-      <c r="I47" s="22" t="n"/>
-      <c r="J47" s="22" t="n"/>
-      <c r="K47" s="22" t="n"/>
-      <c r="L47" s="22" t="n"/>
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="n"/>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="22" t="n"/>
-      <c r="F48" s="22" t="n"/>
-      <c r="G48" s="22" t="n"/>
-      <c r="H48" s="22" t="n"/>
-      <c r="I48" s="22" t="n"/>
-      <c r="J48" s="22" t="n"/>
-      <c r="K48" s="22" t="n"/>
-      <c r="L48" s="22" t="n"/>
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="n"/>
+      <c r="L48" s="24" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n"/>
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="22" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="22" t="n"/>
-      <c r="H49" s="22" t="n"/>
-      <c r="I49" s="22" t="n"/>
-      <c r="J49" s="22" t="n"/>
-      <c r="K49" s="22" t="n"/>
-      <c r="L49" s="22" t="n"/>
+      <c r="A49" s="24" t="n"/>
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="24" t="n"/>
+      <c r="D49" s="24" t="n"/>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="24" t="n"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="24" t="n"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="24" t="n"/>
+      <c r="K49" s="24" t="n"/>
+      <c r="L49" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n"/>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
-      <c r="G50" s="22" t="n"/>
-      <c r="H50" s="22" t="n"/>
-      <c r="I50" s="22" t="n"/>
-      <c r="J50" s="22" t="n"/>
-      <c r="K50" s="22" t="n"/>
-      <c r="L50" s="22" t="n"/>
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="24" t="n"/>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n"/>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="22" t="n"/>
-      <c r="H51" s="22" t="n"/>
-      <c r="I51" s="22" t="n"/>
-      <c r="J51" s="22" t="n"/>
-      <c r="K51" s="22" t="n"/>
-      <c r="L51" s="22" t="n"/>
+      <c r="A51" s="24" t="n"/>
+      <c r="B51" s="24" t="n"/>
+      <c r="C51" s="24" t="n"/>
+      <c r="D51" s="24" t="n"/>
+      <c r="E51" s="24" t="n"/>
+      <c r="F51" s="24" t="n"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="24" t="n"/>
+      <c r="L51" s="24" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n"/>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
-      <c r="G52" s="22" t="n"/>
-      <c r="H52" s="22" t="n"/>
-      <c r="I52" s="22" t="n"/>
-      <c r="J52" s="22" t="n"/>
-      <c r="K52" s="22" t="n"/>
-      <c r="L52" s="22" t="n"/>
+      <c r="A52" s="24" t="n"/>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="24" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="24" t="n"/>
+      <c r="L52" s="24" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n"/>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="22" t="n"/>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="22" t="n"/>
-      <c r="I53" s="22" t="n"/>
-      <c r="J53" s="22" t="n"/>
-      <c r="K53" s="22" t="n"/>
-      <c r="L53" s="22" t="n"/>
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n"/>
-      <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="22" t="n"/>
-      <c r="G54" s="22" t="n"/>
-      <c r="H54" s="22" t="n"/>
-      <c r="I54" s="22" t="n"/>
-      <c r="J54" s="22" t="n"/>
-      <c r="K54" s="22" t="n"/>
-      <c r="L54" s="22" t="n"/>
+      <c r="A54" s="24" t="n"/>
+      <c r="B54" s="24" t="n"/>
+      <c r="C54" s="24" t="n"/>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="24" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="24" t="n"/>
+      <c r="J54" s="24" t="n"/>
+      <c r="K54" s="24" t="n"/>
+      <c r="L54" s="24" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n"/>
-      <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="22" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="22" t="n"/>
-      <c r="H55" s="22" t="n"/>
-      <c r="I55" s="22" t="n"/>
-      <c r="J55" s="22" t="n"/>
-      <c r="K55" s="22" t="n"/>
-      <c r="L55" s="22" t="n"/>
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="24" t="n"/>
+      <c r="J55" s="24" t="n"/>
+      <c r="K55" s="24" t="n"/>
+      <c r="L55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n"/>
-      <c r="B56" s="22" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="F56" s="22" t="n"/>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="22" t="n"/>
-      <c r="I56" s="22" t="n"/>
-      <c r="J56" s="22" t="n"/>
-      <c r="K56" s="22" t="n"/>
-      <c r="L56" s="22" t="n"/>
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="24" t="n"/>
+      <c r="C56" s="24" t="n"/>
+      <c r="D56" s="24" t="n"/>
+      <c r="E56" s="24" t="n"/>
+      <c r="F56" s="24" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="24" t="n"/>
+      <c r="I56" s="24" t="n"/>
+      <c r="J56" s="24" t="n"/>
+      <c r="K56" s="24" t="n"/>
+      <c r="L56" s="24" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n"/>
-      <c r="B57" s="22" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="22" t="n"/>
-      <c r="E57" s="22" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="22" t="n"/>
-      <c r="I57" s="22" t="n"/>
-      <c r="J57" s="22" t="n"/>
-      <c r="K57" s="22" t="n"/>
-      <c r="L57" s="22" t="n"/>
+      <c r="A57" s="24" t="n"/>
+      <c r="B57" s="24" t="n"/>
+      <c r="C57" s="24" t="n"/>
+      <c r="D57" s="24" t="n"/>
+      <c r="E57" s="24" t="n"/>
+      <c r="F57" s="24" t="n"/>
+      <c r="G57" s="24" t="n"/>
+      <c r="H57" s="24" t="n"/>
+      <c r="I57" s="24" t="n"/>
+      <c r="J57" s="24" t="n"/>
+      <c r="K57" s="24" t="n"/>
+      <c r="L57" s="24" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n"/>
-      <c r="B58" s="22" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="22" t="n"/>
-      <c r="E58" s="22" t="n"/>
-      <c r="F58" s="22" t="n"/>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="22" t="n"/>
-      <c r="I58" s="22" t="n"/>
-      <c r="J58" s="22" t="n"/>
-      <c r="K58" s="22" t="n"/>
-      <c r="L58" s="22" t="n"/>
+      <c r="A58" s="24" t="n"/>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="24" t="n"/>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="24" t="n"/>
+      <c r="J58" s="24" t="n"/>
+      <c r="K58" s="24" t="n"/>
+      <c r="L58" s="24" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n"/>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="E59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
-      <c r="G59" s="22" t="n"/>
-      <c r="H59" s="22" t="n"/>
-      <c r="I59" s="22" t="n"/>
-      <c r="J59" s="22" t="n"/>
-      <c r="K59" s="22" t="n"/>
-      <c r="L59" s="22" t="n"/>
+      <c r="A59" s="24" t="n"/>
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="24" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="24" t="n"/>
+      <c r="J59" s="24" t="n"/>
+      <c r="K59" s="24" t="n"/>
+      <c r="L59" s="24" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n"/>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
-      <c r="F60" s="22" t="n"/>
-      <c r="G60" s="22" t="n"/>
-      <c r="H60" s="22" t="n"/>
-      <c r="I60" s="22" t="n"/>
-      <c r="J60" s="22" t="n"/>
-      <c r="K60" s="22" t="n"/>
-      <c r="L60" s="22" t="n"/>
+      <c r="A60" s="24" t="n"/>
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="24" t="n"/>
+      <c r="D60" s="24" t="n"/>
+      <c r="E60" s="24" t="n"/>
+      <c r="F60" s="24" t="n"/>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="24" t="n"/>
+      <c r="I60" s="24" t="n"/>
+      <c r="J60" s="24" t="n"/>
+      <c r="K60" s="24" t="n"/>
+      <c r="L60" s="24" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n"/>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
-      <c r="F61" s="22" t="n"/>
-      <c r="G61" s="22" t="n"/>
-      <c r="H61" s="22" t="n"/>
-      <c r="I61" s="22" t="n"/>
-      <c r="J61" s="22" t="n"/>
-      <c r="K61" s="22" t="n"/>
-      <c r="L61" s="22" t="n"/>
+      <c r="A61" s="24" t="n"/>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="24" t="n"/>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+      <c r="I61" s="24" t="n"/>
+      <c r="J61" s="24" t="n"/>
+      <c r="K61" s="24" t="n"/>
+      <c r="L61" s="24" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n"/>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="n"/>
-      <c r="G62" s="22" t="n"/>
-      <c r="H62" s="22" t="n"/>
-      <c r="I62" s="22" t="n"/>
-      <c r="J62" s="22" t="n"/>
-      <c r="K62" s="22" t="n"/>
-      <c r="L62" s="22" t="n"/>
+      <c r="A62" s="24" t="n"/>
+      <c r="B62" s="24" t="n"/>
+      <c r="C62" s="24" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="24" t="n"/>
+      <c r="F62" s="24" t="n"/>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="24" t="n"/>
+      <c r="J62" s="24" t="n"/>
+      <c r="K62" s="24" t="n"/>
+      <c r="L62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n"/>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="n"/>
-      <c r="F63" s="22" t="n"/>
-      <c r="G63" s="22" t="n"/>
-      <c r="H63" s="22" t="n"/>
-      <c r="I63" s="22" t="n"/>
-      <c r="J63" s="22" t="n"/>
-      <c r="K63" s="22" t="n"/>
-      <c r="L63" s="22" t="n"/>
+      <c r="A63" s="24" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="24" t="n"/>
+      <c r="D63" s="24" t="n"/>
+      <c r="E63" s="24" t="n"/>
+      <c r="F63" s="24" t="n"/>
+      <c r="G63" s="24" t="n"/>
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="24" t="n"/>
+      <c r="J63" s="24" t="n"/>
+      <c r="K63" s="24" t="n"/>
+      <c r="L63" s="24" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="n"/>
-      <c r="B64" s="22" t="n"/>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="22" t="n"/>
-      <c r="E64" s="22" t="n"/>
-      <c r="F64" s="22" t="n"/>
-      <c r="G64" s="22" t="n"/>
-      <c r="H64" s="22" t="n"/>
-      <c r="I64" s="22" t="n"/>
-      <c r="J64" s="22" t="n"/>
-      <c r="K64" s="22" t="n"/>
-      <c r="L64" s="22" t="n"/>
+      <c r="A64" s="24" t="n"/>
+      <c r="B64" s="24" t="n"/>
+      <c r="C64" s="24" t="n"/>
+      <c r="D64" s="24" t="n"/>
+      <c r="E64" s="24" t="n"/>
+      <c r="F64" s="24" t="n"/>
+      <c r="G64" s="24" t="n"/>
+      <c r="H64" s="24" t="n"/>
+      <c r="I64" s="24" t="n"/>
+      <c r="J64" s="24" t="n"/>
+      <c r="K64" s="24" t="n"/>
+      <c r="L64" s="24" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="n"/>
-      <c r="B65" s="22" t="n"/>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="22" t="n"/>
-      <c r="E65" s="22" t="n"/>
-      <c r="F65" s="22" t="n"/>
-      <c r="G65" s="22" t="n"/>
-      <c r="H65" s="22" t="n"/>
-      <c r="I65" s="22" t="n"/>
-      <c r="J65" s="22" t="n"/>
-      <c r="K65" s="22" t="n"/>
-      <c r="L65" s="22" t="n"/>
+      <c r="A65" s="24" t="n"/>
+      <c r="B65" s="24" t="n"/>
+      <c r="C65" s="24" t="n"/>
+      <c r="D65" s="24" t="n"/>
+      <c r="E65" s="24" t="n"/>
+      <c r="F65" s="24" t="n"/>
+      <c r="G65" s="24" t="n"/>
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="24" t="n"/>
+      <c r="J65" s="24" t="n"/>
+      <c r="K65" s="24" t="n"/>
+      <c r="L65" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15930,7 +15695,7 @@
       </c>
     </row>
     <row r="2" ht="72" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>레시피의 %를 표로 편 '재고 연계 엔진'. 보통은 안 봐도 된다(레시피는 '레시피' 시트에서 봄) — 재고 자동 차감을 위해 존재한다.   ┃ 컬럼: 제품=제품명 · 원료=한글명 · 상=단계 · 퍼센트=배합% · 제조누계g=개발일지에서 이 제품을 만든 배치량 합(자동) · 사용g=퍼센트×제조누계(원료 시트가 이 값을 빼감)</t>
         </is>
@@ -18934,1010 +18699,1009 @@
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>시험 핵심개념 — 맞춤형화장품조제관리사 과목1~4 핵심(암기용 + 쉬운 풀이)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 'C열=외우기용 / D열=쉬운 풀이'. 수치·목록은 식약처 「화장품 안전기준 등에 관한 규정」·화장품법 기준의 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>과목·영역</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>핵심 개념</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>꼭 외울 것 (수치·목록)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>쉽게 말하면 (풀이)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>실험/개발 연계</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>사업 연계</t>
         </is>
       </c>
     </row>
     <row r="4" ht="77" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>화장품 정의</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>인체를 청결·미화하고 매력을 더하며 피부·모발을 건강히 유지·증진. 인체 작용 '경미'. 의약품(치료·예방)과 구분.</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>화장품은 '꾸미고 가꾸는' 데까지예요. 병을 '고치는' 건 의약품 몫이라, 효과를 세게 말하면 법에 걸립니다. 다도기 크림도 '진정에 도움'까지만.</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>히어로는 '진정·보습 화장품' — 효능 과장 불가</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>상세페이지 카피의 법적 경계선</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>화장품 유형</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>기초·색조·두발·인체세정·방향·눈화장·면도용 등(시행규칙 별표). 유형별 표시·안전기준 상이.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>화장품은 쓰임새별로 칸이 나뉘어요(기초·색조·세안·향수…). 내 제품이 어느 칸이냐에 따라 지킬 규칙이 달라집니다.</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>7종 제형이 각 유형에 매핑</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>유형 구분→신고·표시 기준</t>
         </is>
       </c>
     </row>
     <row r="6" ht="77" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>영업 3종</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>①제조업(등록) ②책임판매업(등록) ③맞춤형화장품판매업(신고). 맞판은 조제관리사 선임 의무.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>만드는 사람·책임지고 파는 사람·섞어 맞춰 파는 사람이 따로 등록돼요. 조제관리사 자격이 있어야 맞춤형 매장을 열 수 있어 — 자격이 곧 사업 허가증.</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>직접제조 전 단계=R&amp;D</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>★자격=맞판 선임요건·진입권</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>기능성화장품</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>미백·주름·자외선차단·염모·제모·탈모완화·여드름완화(세정)·아토피건조완화·튼살 등. 심사 또는 보고.</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>'미백·주름개선'처럼 특별한 효과를 광고하려면 나라의 심사·보고를 받아야 하는 제품군이에요. 그냥 보습 크림은 여기 해당 안 됨.</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>미백 주성분(나이아신아마이드) 보유</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>기능성 표방=심사/보고 비용·기간</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>표시·기재사항</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>명칭·영업자·제조번호·사용기한 또는 개봉후사용기간(PAO)·내용량·전성분·주의사항·기능성 문구 등.</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>용기·상자에 '반드시 적어야 하는 것들'의 목록이에요. 하나라도 빠지면 판매를 못 합니다.</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>라벨 초안 작성 능력</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>ODM 라벨 시안 검수 기준</t>
         </is>
       </c>
     </row>
     <row r="9" ht="77" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>전성분 표시 규칙</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>함량 많은 순 기재. 단 1% 이하 성분·착향제·색소는 순서 무관. 착향제는 '향료'로 표기 가능(알레르겐은 성분명).</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>성분을 '많이 든 순서'로 적는 게 원칙이에요. 단 아주 조금(1% 이하) 든 것·향·색소는 순서를 안 지켜도 됩니다.</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>처방 %표가 곧 전성분 초안</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>라벨 정확성=반품·처분 방지</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>1.화장품법</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>부당표시·광고 금지</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>의약품 오인(치료·예방), 기능성/유기농 오인, 사실과 다른 소비자 기만 표현 금지.</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>'낫는다·치료·살균' 같은 의약품스러운 말, 거짓·과장은 금지예요. 진정·무향은 사실 그대로만 말합니다.</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>'항염·살균·병명' 금지(문구검사)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>진정·무향 카피 리스크 관리</t>
         </is>
       </c>
     </row>
     <row r="11" ht="77" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>원료 분류</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·실리콘)/계면활성제/보습/고분자(점증)/활성/색소/보존제/착향.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>화장품 원료는 큰 가족으로 나뉘어요 — 물 쪽, 기름 쪽, 둘을 섞어주는 것, 보습, 걸쭉하게, 효능, 색, 방부, 향. 내 26종도 다 이 가족 중 하나.</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>보유 26종이 각 분류에 해당</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>CoA·규격서 읽는 눈</t>
         </is>
       </c>
     </row>
     <row r="12" ht="77" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>계면활성제 4분류</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>음이온(세정)·양이온(살균·헤어)·양쪽성(저자극)·비이온(유화·가용화). 자극: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>물과 기름은 원래 안 섞이는데 그 사이를 중개하는 게 계면활성제예요. 네 종류가 있고 자극 세기가 달라요(양이온이 제일 세고 비이온이 제일 순함).</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>몬타노브68=비이온 유화제</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>세안 라인 베이스 선택 기준</t>
         </is>
       </c>
     </row>
     <row r="13" ht="77" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>HLB</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>친수-친유 균형값. 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화 15~18).</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>유화제가 '물을 더 좋아하냐 기름을 더 좋아하냐'를 숫자로 매긴 거예요. 이 숫자로 내 크림(물 베이스=O/W)에 맞는 유화제를 고릅니다.</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>크림=O/W → 유화제 HLB 맞춤</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>처방 안정성의 이론 근거</t>
         </is>
       </c>
     </row>
     <row r="14" ht="77" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>유화·가용화·분산</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>유화=두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일 투명 분산. 분산=고체 입자를 액에.</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>셋 다 '안 섞이는 걸 섞는' 기술이에요. 크림처럼 뽀얗게 섞으면 유화, 소량 기름을 투명하게 녹이면 가용화, 가루를 퍼뜨리면 분산.</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>크림=유화, 워시오프=가용화</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>제형 기획·제품유형 결정</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>점증제·유변학</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성. 분말 검은 글리세린 선분산 후 투입.</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>묽은 액을 걸쭉하게 만드는 게 점증제예요. 잔탄검은 꼭 글리세린에 먼저 개서 넣어야 쌀알 같은 덩어리(피시아이)가 안 생겨요.</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>잔탄검 0.1%p 단위 점도 튜닝</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>사용감 차별화 설계</t>
         </is>
       </c>
     </row>
     <row r="16" ht="77" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>보존제 사용한도</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>페녹시에탄올 1.0%·벤질알코올 1.0%·소르빅애씨드 0.6%·파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올=지정 보존제 아님.</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>물이 든 화장품은 세균이 자라 반드시 방부가 필요해요. 단 보존제마다 '여기까지만' 쓰라는 한도가 있어요(페녹시에탄올은 1.0%).</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>페녹시+헥산다이올 방부</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>★챌린지테스트·방부 설계 기준</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>산화방지제 ≠ 보존제</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>토코페롤·BHT는 '산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 목적·분류가 다름.</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>토코페롤은 '기름이 쩐내 나는 것'을 막지, 세균을 막는 게 아니에요. 시험에서 보존제랑 헷갈리게 내는 단골 함정.</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>토코페롤로 오일 산패 방지</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>전성분 역할 표기 정확성</t>
         </is>
       </c>
     </row>
     <row r="18" ht="77" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>기능성 주성분·함량</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU.</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>미백·주름 효과를 인정받으려면 '정해진 성분을 정해진 양'으로 넣어야 해요. 많다고 좋은 게 아니라 고시 범위를 지키는 게 핵심.</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>나이아신아마이드 2~4% 사용</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>미백 '보고' 시 주성분 스펙</t>
         </is>
       </c>
     </row>
     <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>2.제조품질</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>CGMP</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>우수화장품 제조·품질관리기준. 3요소=인적자원·시설·원자재. 문서화: 제조기록서·제조번호·일탈·재작업.</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>화장품을 '깨끗하고 늘 똑같이' 만들기 위한 공장 관리 규칙이에요. 내가 쓰는 개발일지가 바로 이 기록의 작은 버전.</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>개발일지=배치기록서 축소판</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>ODM이 CGMP 업소인지 확인</t>
         </is>
       </c>
     </row>
     <row r="20" ht="107" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>중금속·유해물질 한도</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈 35)·디옥산 100·포름알데하이드 2,000·프탈레이트 100. 메탄올 0.2%.</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>일부러 넣진 않아도 원료에 미량 섞여 들어올 수 있는 나쁜 물질들의 '넘으면 안 되는 선'이에요. 출고 전 시험으로 확인합니다.</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>비의도 유래물질 개념</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>출고 로트별 시험성적서 요구</t>
         </is>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>미생물 한도</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>영유아·눈화장 500·물휴지 세균·진균 각 100·기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>완제품에 있어도 되는 세균 수의 한계예요. 아기·눈 제품은 더 엄격(500), 대장균·녹농균·황색포도상구균은 아예 나오면 안 됩니다.</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>소독·방부·1개월 내 사용</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>미생물 시험성적서 확보</t>
         </is>
       </c>
     </row>
     <row r="22" ht="77" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>pH 기준</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>영유아·눈화장·색조·로션/크림 등 특정 액상류 pH 3.0~9.0(물로 씻어내는 제품 제외).</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>피부에 바르는 많은 제품은 pH 3.0~9.0 안에 들어야 해요. 다도기는 피부와 같은 약산성(5.0~5.5)으로 더 좁게 맞춥니다.</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>목표 pH 5.0~5.5 적정</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>자극 저감·라벨 근거</t>
         </is>
       </c>
     </row>
     <row r="23" ht="62" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>내용량 기준</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>제품 3개 평균 내용량이 표기량의 97% 이상.</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>'50mL'이라 적었으면 실제로도 그만큼(평균 97% 이상) 들어 있어야 한다는 뜻이에요. 덜 넣으면 안 됩니다.</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>충진량 관리</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>과충진 원가·미달 CS 방지</t>
         </is>
       </c>
     </row>
     <row r="24" ht="77" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>착향 알레르기 성분</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>지정 유발성분(약 25종). 씻어내는 0.01%·씻어내지 않는 0.001% 초과 시 성분명 표시.</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>향료 속엔 알레르기를 일으킬 수 있는 25종이 있어, 일정량 넘으면 이름을 따로 표시해야 해요. 다도기는 무향이라 이 걱정이 없습니다.</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>다도기=무향 → 알레르겐 0</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>★무향이 규제·소구 동시 이점</t>
         </is>
       </c>
     </row>
     <row r="25" ht="77" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>3.유통안전</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>안정성 시험</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>장기·가속(45℃)·가혹(동결융해·광)·개봉후. 경시변화로 사용기한·PAO 산정.</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>제품이 시간·온도가 지나도 안 변하는지 미리 괴롭혀 보는 시험이에요(45℃, 얼렸다 녹였다). 이 결과로 '언제까지 쓰세요'를 정합니다.</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>4조건 보관+원심 실습</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>사용기한 설정 근거</t>
         </is>
       </c>
     </row>
     <row r="26" ht="62" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>맞춤형화장품 정의</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>제조·수입된 '내용물'에 다른 내용물/식약처 허용 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>이미 만들어진 내용물에 뭘 더 섞거나, 덜어 담아 파는 게 맞춤형화장품이에요. 매장에서 '맞춤 조제'하는 모델.</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>혼합·소분 개념</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>맞판 매장 사업 모델</t>
         </is>
       </c>
     </row>
     <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>혼합·소분 금지 원료</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>사용제한 원료(보존제·자외선차단·색소)·기능성 주성분(심사/보고된 경우 제외)은 임의 혼합 불가.</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>맞춤형이라고 아무거나 섞으면 안 돼요. 보존제·자외선차단제·기능성 주성분은 매장에서 임의로 추가하는 게 금지됩니다.</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>방부·자차 임의 추가 불가</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>조제 상담의 법적 한계</t>
         </is>
       </c>
     </row>
     <row r="28" ht="62" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>조제관리사 의무</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>혼합·소분 안전·품질·위생관리, 오염 방지, 기구·작업자 위생.</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>맞춤형 매장에서 섞고 나누는 일을 안전·위생적으로 책임지는 사람이 조제관리사예요. 소독·오염방지가 핵심 임무.</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>70% 에탄올 소독·전용도구</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>자격의 직접 수익화(매장)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="62" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>피부 구조</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>표피(기저·유극·과립·투명·각질)·진피(콜라겐·엘라스틴·섬유아세포)·피하. 멜라노사이트=기저층.</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>피부는 3층(표피·진피·피하)이에요. 색을 만드는 멜라닌 공장(멜라노사이트)은 표피 맨 아래 기저층에 있습니다.</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>진정·보습 타깃 이해</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>맞춤 상담·소구 근거</t>
         </is>
       </c>
     </row>
     <row r="30" ht="77" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>각질층·장벽·NMF</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>벽돌(각질)+시멘트(세포간지질·세라마이드). NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>피부 맨 바깥은 벽돌(각질)과 시멘트(지질)로 쌓은 담벼락이에요. 이 담이 튼튼해야 수분이 안 새요 — 다도기가 노리는 '장벽·진정'.</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>HA·글리세린·세이프 유분 보습</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>'장벽·진정' 브랜드 서사</t>
         </is>
       </c>
     </row>
     <row r="31" ht="62" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>모발 구조</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질. 주성분 케라틴, 디설파이드(S-S) 결합.</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>머리카락은 3겹(겉껍질·속·심)이고 케라틴 단백질이 주재료예요. 파마·염색이 바로 이 구조를 건드리는 것.</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>헤어 라인 확장 시 기초</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>라인 확장 판단</t>
         </is>
       </c>
     </row>
     <row r="32" ht="62" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>관능평가</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점으로 주관 최소화.</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>기계 말고 '사람의 눈·코·손'으로 색·향·발림을 평가하는 거예요. 기준 샘플과 비교해서 주관을 줄입니다.</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>바이알 변색·냄새·pH 눈 비교</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>품질 합부·배치 재현 기준</t>
         </is>
       </c>
     </row>
     <row r="33" ht="77" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>위해평가 4단계</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>위험성 확인→위험성 결정→노출평가→위해도 결정. 안전역(MoS)으로 판단.</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>이 성분이 '얼마나 위험한지→얼마나 노출되는지→그래서 안전한지'를 순서대로 따지는 방법이에요. 활성 농도를 올릴지 판단할 때 씁니다.</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>활성 농도 상향 판단틀</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>신규·고농도 원료 도입 근거</t>
         </is>
@@ -19949,8 +19713,5 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -18,13 +18,14 @@
     <sheet name="사용제한원료" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="유통안전·OEM검수" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="OEM 개발의뢰서" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="표시·광고 컴플라이언스" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="개발→창업 워크플로우" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="교재 이론 목차" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="시험 핵심개념" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="시험대비 원료맵" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="시험→사업 활용" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="실습↔시험 개념" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="브랜드 기획서" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="표시·광고 컴플라이언스" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="개발→창업 워크플로우" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="교재 이론 목차" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="시험 핵심개념" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="시험대비 원료맵" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="시험→사업 활용" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="실습↔시험 개념" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -240,8 +241,16 @@
       <color rgb="001F3B30"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="003A4A6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001F3B6B"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -333,8 +342,28 @@
         <fgColor rgb="00F7FAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A4A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBFCFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F3F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -432,11 +461,113 @@
         <color rgb="00D5DDD9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5DDD9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DDD9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DDD9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5DDD9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5DDD9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DDD9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DDD9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5DDD9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DAE2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5DAE2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DAE2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5DAE2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5DAE2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DAE2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DAE2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5DAE2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5DAE2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DAE2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DAE2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5DAE2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -651,6 +782,28 @@
     <xf numFmtId="0" fontId="37" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1406,7 +1559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2480,6 +2633,18 @@
       <c r="B110" s="4" t="inlineStr">
         <is>
           <t>시트 아래쪽에 공장 첫 문의용 이메일·카톡 템플릿 포함 — 복사해서 바로 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="51" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>브랜드 기획서 : '남에게 다도기가 뭔지' 설명하는 한 장(자사몰·입점·투자 공통 뼈대). PPT 필요하면 이 시트를 슬라이드로 옮긴다. (scripts/brand_plan.py)</t>
         </is>
       </c>
     </row>
@@ -4070,6 +4235,637 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>다도기 · 브랜드/제품 기획서 (Brand &amp; Product One-Pager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>※ 남에게 '다도기가 뭔지' 한 장으로 설명하는 자료. 자사몰 소개·입점 제안·투자 피칭의 공통 뼈대. 파란 글씨는 예시이니 내 값으로 고쳐 쓰세요. PPT가 필요하면 이 섹션들을 슬라이드로 옮기면 됩니다.</t>
+        </is>
+      </c>
+      <c r="B2" s="84" t="n"/>
+      <c r="C2" s="85" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="80" t="inlineStr">
+        <is>
+          <t>1. 브랜드 한 줄 (Elevator Pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>다도기는 ___ 브랜드</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>지성·예민·지루성 피부를 위한, 자극 유발 성분을 뺀 '무향·세이프 오일' 진정 스킨케어 브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="83" t="inlineStr">
+        <is>
+          <t>10초 안에 '누구를 위한 무엇'이 들어가게. 가장 많이 쓸 문장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>태그라인(한 문장)</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>“덜어내서 편안한 피부.”</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>감성 한 줄. 상세페이지·패키지에 재사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>2. 왜 만드나 (미션 · 스토리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>창업자 / 운영</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
+        <is>
+          <t>1인 브랜드, 맞춤형화장품조제관리사 준비, 처방을 직접 설계·검증</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="inlineStr">
+        <is>
+          <t>'진정성'이 1인 브랜드의 최대 무기. 솔직하게.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>미션</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="inlineStr">
+        <is>
+          <t>기름지고 향 강한 진정 크림의 역설을 푼다 — 지성·예민 피부가 안심하고 바르는 제품</t>
+        </is>
+      </c>
+      <c r="C8" s="83" t="inlineStr">
+        <is>
+          <t>'왜 이 브랜드가 세상에 있어야 하나'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>브랜드 스토리(한 줄)</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="inlineStr">
+        <is>
+          <t>내 피부 고민에서 출발 — 맞는 제품이 없어 직접 만들기 시작</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="inlineStr">
+        <is>
+          <t>출발점의 개인적 계기. 공감 포인트.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>3. 문제 / 시장의 결핍  (기획 = 데이터로 '결핍' 선점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>핵심 결핍</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="inlineStr">
+        <is>
+          <t>시중 진정·보습 크림 상당수가 말라세지아 먹이(올리브·코코넛·호호바·버터 등 C11~24 지방산 오일)·향료 포함 → 지루성·예민 피부엔 역효과</t>
+        </is>
+      </c>
+      <c r="C11" s="83" t="inlineStr">
+        <is>
+          <t>경쟁이 못 채운 '빈칸'을 한 문장으로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>데이터 근거(채울 것)</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="inlineStr">
+        <is>
+          <t>네이버 데이터랩 '무향/저자극/지성 진정' 검색추이, 화해·올리브영 리뷰의 불만 키워드</t>
+        </is>
+      </c>
+      <c r="C12" s="83" t="inlineStr">
+        <is>
+          <t>강의 Point01: 숫자로 증명. 실제 작성 때 수치·캡처를 넣으면 설득력↑.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>4. 타겟 고객 (페르소나)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>핵심 타겟</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="inlineStr">
+        <is>
+          <t>20~40대, 지성·복합·지루성·예민 피부, 트러블·번들거림·따가움 경험, 전성분 꼼꼼히 보는 소비자</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="inlineStr">
+        <is>
+          <t>연령·피부·행동을 구체적으로. '모두'는 타겟이 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>고객의 한마디(인용)</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="inlineStr">
+        <is>
+          <t>“진정된다는 크림 바르면 오히려 더 번들거리고 좁쌀 올라와요.”</t>
+        </is>
+      </c>
+      <c r="C15" s="83" t="inlineStr">
+        <is>
+          <t>실제 리뷰 톤의 한 줄이 페르소나를 살아있게 함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>5. 솔루션 / 핵심 컨셉 (POD · 차별점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>3가지 차별점</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="inlineStr">
+        <is>
+          <t>① 말라세지아-세이프 오일 설계(스쿠알란·MCT·디메치콘) ② 무향 ③ 진정+보습+피지 밸런스</t>
+        </is>
+      </c>
+      <c r="C17" s="83" t="inlineStr">
+        <is>
+          <t>경쟁이 따라오기 어려운 '설계 원칙'으로 묶기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>한 줄 차별</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
+        <is>
+          <t>“진정 크림인데 유분 걱정이 없다.”</t>
+        </is>
+      </c>
+      <c r="C18" s="83" t="inlineStr">
+        <is>
+          <t>경쟁 대비 단 한 문장 우위.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>6. 제품 라인업 · 로드맵  (5가지 제품 역할)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>히어로(상징)</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="inlineStr">
+        <is>
+          <t>시크 진정 밸런스 크림 — 브랜드를 대표하는 완성형</t>
+        </is>
+      </c>
+      <c r="C20" s="83" t="inlineStr">
+        <is>
+          <t>강의 Point03: 재고 없는 5가지 역할 프레임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>엔트리(입구)</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="inlineStr">
+        <is>
+          <t>토너 / 수분 젤 — 부담 적은 첫 구매</t>
+        </is>
+      </c>
+      <c r="C21" s="83" t="inlineStr">
+        <is>
+          <t>진입장벽 낮춘 미끼 제품.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="81" t="inlineStr">
+        <is>
+          <t>연결(루틴)</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="inlineStr">
+        <is>
+          <t>세럼 / 앰플 — 히어로와 함께 쓰는 라인</t>
+        </is>
+      </c>
+      <c r="C22" s="83" t="inlineStr">
+        <is>
+          <t>객단가·재구매를 올리는 연결고리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>수익(마진)</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="inlineStr">
+        <is>
+          <t>세트 구성 / 리필</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="inlineStr">
+        <is>
+          <t>마진·완판을 책임지는 구성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>실험(확장)</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="inlineStr">
+        <is>
+          <t>무수 밤 · 워시오프 클렌징 등 (히어로 검증 후 착수)</t>
+        </is>
+      </c>
+      <c r="C24" s="83" t="inlineStr">
+        <is>
+          <t>분산 금지 — 히어로 자리잡은 뒤.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>7. 경쟁 · 포지셔닝  (3C + 1C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="81" t="inlineStr">
+        <is>
+          <t>Customer(고객)</t>
+        </is>
+      </c>
+      <c r="B26" s="82" t="inlineStr">
+        <is>
+          <t>위 페르소나 — 지성·예민·성분 중시</t>
+        </is>
+      </c>
+      <c r="C26" s="83" t="inlineStr">
+        <is>
+          <t>3C+1C: 강의 Part2 프레임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="81" t="inlineStr">
+        <is>
+          <t>Competitor(경쟁)</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="inlineStr">
+        <is>
+          <t>시카·장벽 크림 브랜드 다수 — 대부분 향 포함·범용 타겟, '세이프 오일' 소구는 드묾</t>
+        </is>
+      </c>
+      <c r="C27" s="83" t="inlineStr">
+        <is>
+          <t>경쟁의 약점 = 내 기회.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>Company(자사)</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="inlineStr">
+        <is>
+          <t>직접 R&amp;D·조제관리사·린 1인 운영·세이프 오일 전문성</t>
+        </is>
+      </c>
+      <c r="C28" s="83" t="inlineStr">
+        <is>
+          <t>작아서 할 수 있는 것(속도·진정성)을 강점으로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="81" t="inlineStr">
+        <is>
+          <t>Channel(채널)</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>자사몰 → 올리브영 → 해외 수출(OEM)</t>
+        </is>
+      </c>
+      <c r="C29" s="83" t="inlineStr">
+        <is>
+          <t>채널별 규격·수수료가 기획에 영향.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="81" t="inlineStr">
+        <is>
+          <t>포지셔닝 한 줄</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
+        <is>
+          <t>“지성·예민 전용 × 무향·세이프” = 아직 비어있는 칸 (전문·중가 포지션)</t>
+        </is>
+      </c>
+      <c r="C30" s="83" t="inlineStr">
+        <is>
+          <t>두 축(범용↔전문 / 저가↔고가)에서 내 위치를 한 문장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="80" t="inlineStr">
+        <is>
+          <t>8. 가격 · 마진  (유통 = 마진 방어)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="81" t="inlineStr">
+        <is>
+          <t>히어로 가격대</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="inlineStr">
+        <is>
+          <t>소비자가 2~3만원대 / 목표 원가·마진 ___</t>
+        </is>
+      </c>
+      <c r="C32" s="83" t="inlineStr">
+        <is>
+          <t>심리적 저항선 안에서. Documents\구매대행 '수출 마진계산기'로 수치화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="81" t="inlineStr">
+        <is>
+          <t>채널 수수료 고려</t>
+        </is>
+      </c>
+      <c r="B33" s="82" t="inlineStr">
+        <is>
+          <t>올리브영 등 입점 수수료·행사할인 반영한 공급가 설계</t>
+        </is>
+      </c>
+      <c r="C33" s="83" t="inlineStr">
+        <is>
+          <t>마진이 채널에서 깎이는 걸 미리 방어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="80" t="inlineStr">
+        <is>
+          <t>9. 유통 · 채널 로드맵</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" s="81" t="inlineStr">
+        <is>
+          <t>1단계 — 자사몰</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="inlineStr">
+        <is>
+          <t>브랜드 서사·리뷰·재구매 데이터 축적 (가장 통제력 높고 마진 좋음)</t>
+        </is>
+      </c>
+      <c r="C35" s="83" t="inlineStr">
+        <is>
+          <t>증거(리뷰·판매)를 먼저 쌓기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="27" customHeight="1">
+      <c r="A36" s="81" t="inlineStr">
+        <is>
+          <t>2단계 — 올리브영</t>
+        </is>
+      </c>
+      <c r="B36" s="82" t="inlineStr">
+        <is>
+          <t>자사몰 성과를 근거로 MD 설득·입점</t>
+        </is>
+      </c>
+      <c r="C36" s="83" t="inlineStr">
+        <is>
+          <t>강의 Point02: MD 설득엔 데이터가 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>3단계 — 해외 수출</t>
+        </is>
+      </c>
+      <c r="B37" s="82" t="inlineStr">
+        <is>
+          <t>OEM 생산 → 대상국 규제 대응 후 수출</t>
+        </is>
+      </c>
+      <c r="C37" s="83" t="inlineStr">
+        <is>
+          <t>관련: 글로벌 수출 방향·마진계산기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="80" t="inlineStr">
+        <is>
+          <t>10. 왜 나 / 왜 지금 (1인 창업자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="27" customHeight="1">
+      <c r="A39" s="81" t="inlineStr">
+        <is>
+          <t>강점</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="inlineStr">
+        <is>
+          <t>자격(조제관리사)·직접 처방 설계·빠른 의사결정·낮은 고정비·진정성 있는 스토리</t>
+        </is>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>작음을 약점이 아닌 강점으로 번역.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
+      <c r="A40" s="81" t="inlineStr">
+        <is>
+          <t>리스크 &amp; 보완</t>
+        </is>
+      </c>
+      <c r="B40" s="82" t="inlineStr">
+        <is>
+          <t>경력·자본 한계 → OEM 소량·스톡 용기·자사몰 린스타트로 상쇄</t>
+        </is>
+      </c>
+      <c r="C40" s="83" t="inlineStr">
+        <is>
+          <t>리스크를 먼저 말하면 신뢰가 는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>11. 마일스톤 (한눈 요약)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="79" t="inlineStr">
+        <is>
+          <t>자격 취득 → 책임판매업 등록 → OEM 샘플·검증 → 히어로 출시(자사몰) → 리뷰·재구매 데이터 축적 → 올리브영/해외 수출</t>
+        </is>
+      </c>
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="85" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="80" t="inlineStr">
+        <is>
+          <t>12. 한 줄 요약 (표지 문장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="79" t="inlineStr">
+        <is>
+          <t>“다도기 — 지성·예민 피부를 위한 무향·세이프 진정 스킨케어. 히어로 ‘시크 진정 밸런스 크림’으로 시작한다.”</t>
+        </is>
+      </c>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="85" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5190,7 +5986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -6055,7 +6851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -6441,7 +7237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -7762,7 +8558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -9988,7 +10784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -10605,7 +11401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -9070,7 +9070,7 @@
   <sheetPr>
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -10061,8 +10061,112 @@
         </is>
       </c>
     </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="44" t="inlineStr">
+        <is>
+          <t>소통 전략 — 진정성 + 빠른 소통으로 단골·팬덤을 만든다</t>
+        </is>
+      </c>
+      <c r="B141" s="43"/>
+    </row>
+    <row r="142" spans="1:2" ht="36">
+      <c r="A142" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B142" s="29" t="inlineStr">
+        <is>
+          <t>큰 회사가 못 하는 것 = 속도와 얼굴. 광고비 대신 '만드는 사람이 직접, 빨리 답하고, 바뀐 걸 보여준다'로 이긴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="36">
+      <c r="A143" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B143" s="29" t="inlineStr">
+        <is>
+          <t>빠른 소통: 댓글·DM은 24시간 안에 내가 직접 답장. 시간은 출퇴근 2번으로 고정(24시간 대기 ❌ — 회사와 병행해야 오래 간다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="36">
+      <c r="A144" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B144" s="29" t="inlineStr">
+        <is>
+          <t>반영 공개: 받은 의견 → 다음 실험 → 결과 공개. 예) '끈적하다는 댓글 → 잔탄검 0.5→0.4%로 v3'. 대기업은 처방을 몇 주 만에 못 바꾼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="36">
+      <c r="A145" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B145" s="29" t="inlineStr">
+        <is>
+          <t>진정성: 실패·숫자·결정 이유를 숨기지 않는다. 커 보이려 하지 않기 — '회사 다니며 주말에 만드는 1인 메이커'가 그 자체로 이야기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="36">
+      <c r="A146" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B146" s="29" t="inlineStr">
+        <is>
+          <t>팬덤: 구경꾼을 참여자로 — 용기·제형 굳기·이름·다음 실험 주제를 투표로. 대기자는 '먼저 아는 사람'(개발 소식 먼저, 출시 때 우선 구매).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="36">
+      <c r="A147" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B147" s="29" t="inlineStr">
+        <is>
+          <t>단골(출시 후): 첫 고객 100명은 직접 챙긴다 — 사용 2주 뒤 안부·피드백 → 다음 버전에 반영해 공개. 재구매는 수요검증 S5로 추적.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="18">
+      <c r="A148" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B148" s="29" t="inlineStr">
+        <is>
+          <t>신호: 조회수보다 '같은 사람이 반복해서 다는 댓글 수'·DM 수·대기자 수가 팬덤의 증거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="36">
+      <c r="A149" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B149" s="29" t="inlineStr">
+        <is>
+          <t>⚠ 지킬 선: 집에서 만든 제품은 무료 나눔·체험단도 ❌(판매업 등록·OEM 이후에). 그 전 참여는 투표·댓글·의견만. DM에서도 진단·효능 단정 금지('이걸 쓰면 낫는다' ❌).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A8:B8"/>
@@ -10085,6 +10189,7 @@
     <mergeCell ref="A112:B112"/>
     <mergeCell ref="A121:B121"/>
     <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A141:B141"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -1028,7 +1028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1693,6 +1693,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2745,7 +2752,7 @@
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>업로드 루틴 : 제품 개발과 병렬로 2년간 꾸준히 올리는 원칙·주간 루틴·소재 은행·단계별 목표·끊겼을 때 규칙 + ASMR 영상 포맷·장면 목록·프로필 링크 계획 + 블로그 운영·발행 프롬프트 6종 + 촬영·편집 시작 가이드(장비·폰 설정·3주 연습) + 채널 운영(영상 3채널·블로그 2곳).</t>
+          <t>업로드 루틴 : 제품 개발과 병렬로 2년간 꾸준히 올리는 원칙·주간 루틴·소재 은행·단계별 목표·끊겼을 때 규칙 + ASMR 영상 포맷(다꾸 쇼츠 문법)·장면 목록·콘티 + 프로필 링크 계획 + 블로그 운영·발행 프롬프트 6종 + 처음 하는 사람용 한 흐름: 촬영(장비·세팅 순서·찍는 법) → CapCut 편집 12단계·3주 연습 → 계정 세팅·3채널 업로드 방법 + 채널 운영(영상 3채널·블로그 2곳).</t>
         </is>
       </c>
     </row>
@@ -12747,8 +12754,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <dimension ref="A1:D196"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="43" min="1" max="1"/>
     <col width="44" customWidth="1" style="43" min="2" max="2"/>
@@ -12763,1178 +12770,1427 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="53" customHeight="1" s="43">
+    <row r="2" ht="66" customHeight="1" s="43">
       <c r="A2" s="69" t="inlineStr">
         <is>
-          <t>시간 없는 1인의 해법: 콘텐츠를 따로 만들지 않고 제품 실험·시험 공부에서 뽑는다. 주말 실험 1번 = 콘텐츠 2~3개. 목표는 '잘 만들기'보다 '끊기지 않기'. 주 2개는 기본값 — 해보고 버거우면 주 1개로 낮춰도 된다. 만드는 법은 '수요검증' §2, 기록은 §4. 주력 포맷은 ASMR 제작 과정 영상(§6~§7), 유입은 프로필 링크(§8) + 블로그(§9, 프롬프트 §10), 채널 운영(§13). 촬영·편집이 처음이면 §11~§12부터.</t>
-        </is>
-      </c>
-    </row>
+          <t>시간 없는 1인의 해법: 콘텐츠를 따로 만들지 않고 제품 실험·시험 공부에서 뽑는다. 주말 실험 1번 = 콘텐츠 2~3개. 목표는 '잘 만들기'보다 '끊기지 않기'. 주 2개는 기본값 — 해보고 버거우면 주 1개로 낮춰도 된다. 만드는 법은 '수요검증' §2, 기록은 §4. 주력 포맷은 ASMR 제작 과정 영상(§6~§7, 다꾸 쇼츠 문법), 유입은 프로필 링크(§8) + 블로그(§9, 프롬프트 §10), 채널 운영(§13). 영상이 처음이면 §11 촬영 → §12 편집·3주 연습 → §13 계정 세팅·업로드 순서로 한 번 따라 하면 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="43">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="257" t="inlineStr">
         <is>
           <t>§1. 원칙 6가지</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" s="43">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="140" t="inlineStr">
         <is>
           <t>원칙</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="140" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="140" t="inlineStr">
         <is>
           <t>왜</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n"/>
+      <c r="D5" s="258" t="n"/>
     </row>
     <row r="6" ht="51" customHeight="1" s="43">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="259" t="inlineStr">
         <is>
           <t>① 실험 = 콘텐츠</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="145" t="inlineStr">
         <is>
           <t>주말 실험할 때 폰을 세워두고 찍는다(사진 3장 + 10초 영상 1개). 콘텐츠용 촬영을 따로 잡지 않는다.</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="145" t="inlineStr">
         <is>
           <t>같은 시간을 두 번 쓰지 않는다</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n"/>
+      <c r="D6" s="145" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1" s="43">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="259" t="inlineStr">
         <is>
           <t>② 기본 주 2개, 바닥 주 1개</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="145" t="inlineStr">
         <is>
           <t>비하인드 1개 + 공감·웃김 1개. 바쁜 주는 1개만 올려도 성공으로 친다.</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="145" t="inlineStr">
         <is>
           <t>꾸준함 &gt; 완성도. 한 번 끊기면 다시 시작이 가장 어렵다</t>
         </is>
       </c>
-      <c r="D7" s="24" t="n"/>
+      <c r="D7" s="145" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1" s="43">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="259" t="inlineStr">
         <is>
           <t>③ 몰아서 만들고 나눠 올리기</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="145" t="inlineStr">
         <is>
           <t>일요일 30분에 다음 주 2개를 미리 만들어 예약 업로드.</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="145" t="inlineStr">
         <is>
           <t>평일 밤에 피곤해도 업로드는 자동으로 된다</t>
         </is>
       </c>
-      <c r="D8" s="24" t="n"/>
+      <c r="D8" s="145" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1" s="43">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="259" t="inlineStr">
         <is>
           <t>④ 버퍼 3개</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="145" t="inlineStr">
         <is>
           <t>언제든 올릴 수 있는 예비 콘텐츠 3개를 항상 쌓아둔다(쓰면 다시 채우기).</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="145" t="inlineStr">
         <is>
           <t>야근·아픈 주·시험 주를 버틴다</t>
         </is>
       </c>
-      <c r="D9" s="24" t="n"/>
+      <c r="D9" s="145" t="n"/>
     </row>
     <row r="10" ht="66" customHeight="1" s="43">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="259" t="inlineStr">
         <is>
           <t>⑤ 제작 1번 · 소통 1곳</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="145" t="inlineStr">
         <is>
           <t>영상은 한 번 만들어 인스타·쇼츠·틱톡 3곳에 올리고(영상당 +10~15분), 소통·팬덤은 인스타 한 곳에 모은다. 새로 만들어야 하는 채널(블로그·브랜드 사이트)은 습관이 잡힌 뒤 추가 — §9·§13.</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="145" t="inlineStr">
         <is>
           <t>제작은 그대로, 노출은 3배. 소통까지 흩어지면 1인은 못 버틴다</t>
         </is>
       </c>
-      <c r="D10" s="24" t="n"/>
+      <c r="D10" s="145" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1" s="43">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="259" t="inlineStr">
         <is>
           <t>⑥ 숫자 보고 고치기</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="145" t="inlineStr">
         <is>
           <t>콘텐츠마다 수요검증 §4 로그에 한 줄. 월 1회, 잘 된 3개의 공통점을 한 줄로 정리.</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="145" t="inlineStr">
         <is>
           <t>감이 아니라 데이터로 톤·포맷을 정한다</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n"/>
-    </row>
+      <c r="D11" s="145" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1" s="43">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="257" t="inlineStr">
         <is>
           <t>§2. 주간 루틴 — 제품 · 콘텐츠 · 시험 병렬 (회사 다니면서, 콘텐츠는 주 1시간 안팎 + 블로그 주 1편 60분은 §9)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" s="43">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="140" t="inlineStr">
         <is>
           <t>언제</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="140" t="inlineStr">
         <is>
           <t>제품 개발</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="140" t="inlineStr">
         <is>
           <t>콘텐츠</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="140" t="inlineStr">
         <is>
           <t>시험 (2027.5)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" s="43">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="259" t="inlineStr">
         <is>
           <t>월~목 밤</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="145" t="inlineStr">
         <is>
           <t>쉼. 피곤하면 '역설계' ★히어로 5줄만 읽기</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="145" t="inlineStr">
         <is>
           <t>댓글·DM 답하기 + 스와이프 파일 1개 저장 (10분)</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="145" t="inlineStr">
         <is>
           <t>평일 짧게(출퇴근·점심 등) 교재 1챕터·핵심개념 암기</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="43">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="259" t="inlineStr">
         <is>
           <t>화 · 금</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="145" t="inlineStr">
         <is>
           <t>예약해둔 콘텐츠 자동 업로드 (0분)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="145" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" s="43">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="259" t="inlineStr">
         <is>
           <t>토 오전</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="145" t="inlineStr">
         <is>
           <t>주말 30분 실험(읽어보기 키트 카드) → 개발일지 기록</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="145" t="inlineStr">
         <is>
           <t>실험하면서 ASMR 촬영 — 고정 앵글 + 마이크, §7 장면 위주 (추가 0분)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" s="43">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="259" t="inlineStr">
         <is>
           <t>토 오후</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="145" t="inlineStr">
         <is>
           <t>기출·모의고사 1회분 (2027.2~ 시험기엔 2회)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" s="43">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="259" t="inlineStr">
         <is>
           <t>일 저녁</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="145" t="inlineStr">
         <is>
           <t>처방 '다음 아이디어' 한 줄 (개발일지)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="145" t="inlineStr">
         <is>
           <t>이번 주 촬영분으로 다음 주 2개 제작·예약 + §4 로그 (30분)</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="145" t="inlineStr">
         <is>
           <t>이번 주 외운 것 1장 카드로 정리 → 콘텐츠 소재로 재사용</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1" s="43">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="257" t="inlineStr">
         <is>
           <t>§3. 소재 은행 — 하는 일에서 콘텐츠 뽑기 (새로 만들지 말고 찍기만)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" s="43">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="140" t="inlineStr">
         <is>
           <t>하는 일</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="140" t="inlineStr">
         <is>
           <t>뽑을 콘텐츠</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="140" t="inlineStr">
         <is>
           <t>기법 (수요검증 §2)</t>
         </is>
       </c>
-      <c r="D22" s="27" t="n"/>
+      <c r="D22" s="258" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="43">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="259" t="inlineStr">
         <is>
           <t>원료 도착·언박싱</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="145" t="inlineStr">
         <is>
           <t>'카보머·트로메타민·구연산나트륨 도착 — 만 원대로 시작하는 홈 실험실'</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="145" t="inlineStr">
         <is>
           <t>⑤ 메이커 비하인드</t>
         </is>
       </c>
-      <c r="D23" s="24" t="n"/>
+      <c r="D23" s="145" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="43">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="259" t="inlineStr">
         <is>
           <t>젤 만져보기 실험</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="145" t="inlineStr">
         <is>
           <t>손으로 늘려보는 10초 영상 '카보머 탱글 vs 잔탄검 실 늘어짐'</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="145" t="inlineStr">
         <is>
           <t>⑤ 비하인드 + ① 2초 훅</t>
         </is>
       </c>
-      <c r="D24" s="24" t="n"/>
+      <c r="D24" s="145" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="43">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="259" t="inlineStr">
         <is>
           <t>실패한 배치</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="145" t="inlineStr">
         <is>
           <t>'카보머 중화 안 해서 물이 됨 (실화)' + 비커 사진</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="145" t="inlineStr">
         <is>
           <t>⑤ 실패담</t>
         </is>
       </c>
-      <c r="D25" s="24" t="n"/>
+      <c r="D25" s="145" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1" s="43">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="259" t="inlineStr">
         <is>
           <t>원심분리·pH 측정</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="145" t="inlineStr">
         <is>
           <t>'내 크림 분리 테스트 — 0mm 나와라' 결과 공개</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="145" t="inlineStr">
         <is>
           <t>① 훅 + ⑥ 시리즈('분리 테스트 n회차')</t>
         </is>
       </c>
-      <c r="D26" s="24" t="n"/>
+      <c r="D26" s="145" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1" s="43">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="259" t="inlineStr">
         <is>
           <t>히어로 컨셉</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="145" t="inlineStr">
         <is>
           <t>'지성인의 하루' 시리즈 / 피지 의인화 대화</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="145" t="inlineStr">
         <is>
           <t>③ 의인화 + ⑥ 시리즈화</t>
         </is>
       </c>
-      <c r="D27" s="24" t="n"/>
+      <c r="D27" s="145" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1" s="43">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="259" t="inlineStr">
         <is>
           <t>시험 공부</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="145" t="inlineStr">
         <is>
           <t>'오늘 외운 것: 페녹시에탄올 한도 1.0%' 1장 카드 — 성분 아는 사람이라는 신뢰</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="145" t="inlineStr">
         <is>
           <t>신뢰 콘텐츠 (§3 규정 체크 필수)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n"/>
+      <c r="D28" s="145" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1" s="43">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="259" t="inlineStr">
         <is>
           <t>댓글·DM 질문</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="145" t="inlineStr">
         <is>
           <t>자주 받은 질문을 다음 콘텐츠 주제로 (답변 콘텐츠)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="145" t="inlineStr">
         <is>
           <t>⑦ 댓글 유도 → 다음 소재</t>
         </is>
       </c>
-      <c r="D29" s="24" t="n"/>
+      <c r="D29" s="145" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1" s="43">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="259" t="inlineStr">
         <is>
           <t>이번 주 별일 없음</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="145" t="inlineStr">
         <is>
           <t>버퍼에서 1개 꺼내 올리기 (§1 ④)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="145" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="24" t="n"/>
-    </row>
+      <c r="D30" s="145" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1" s="43">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="257" t="inlineStr">
         <is>
           <t>§4. 2년 단계 — 업로드 목표 (오늘 2026.10 기준)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" s="43">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="140" t="inlineStr">
         <is>
           <t>기간</t>
         </is>
       </c>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="B33" s="140" t="inlineStr">
         <is>
           <t>목표</t>
         </is>
       </c>
-      <c r="C33" s="60" t="inlineStr">
+      <c r="C33" s="140" t="inlineStr">
         <is>
           <t>업로드</t>
         </is>
       </c>
-      <c r="D33" s="60" t="inlineStr">
+      <c r="D33" s="140" t="inlineStr">
         <is>
           <t>수요검증 연결</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" s="43">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="259" t="inlineStr">
         <is>
           <t>2026.11 ~ 2027.1 · 습관 만들기</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="145" t="inlineStr">
         <is>
           <t>3채널 계정 개설·같은 영상 업로드(소통은 인스타), 진지 vs 웃김 A/B로 톤 결정, 버퍼 3개 쌓기</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="145" t="inlineStr">
         <is>
           <t>주 2개 (약 25개)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="145" t="inlineStr">
         <is>
           <t>S0 ~ S1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" s="43">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="259" t="inlineStr">
         <is>
           <t>2027.2 ~ 2027.5 · 시험기</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="145" t="inlineStr">
         <is>
           <t>시험이 우선. 바닥(주 1개)만 지킨다. 시험 공부 카드가 콘텐츠</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="145" t="inlineStr">
         <is>
           <t>주 1개 (약 15개)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="145" t="inlineStr">
         <is>
           <t>S2 대기자 링크 상시 노출</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" s="43">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="259" t="inlineStr">
         <is>
           <t>2027.6 ~ 2027.12 · 자격 취득 후</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="145" t="inlineStr">
         <is>
           <t>잘 된 포맷을 시리즈로 고정, 대기자 → 첫 소량 판매</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="145" t="inlineStr">
         <is>
           <t>주 2~3개 (약 70개)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="145" t="inlineStr">
         <is>
           <t>S3 ~ S5</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" s="43">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="259" t="inlineStr">
         <is>
           <t>2028 · 퇴사 판단</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="145" t="inlineStr">
         <is>
           <t>고객 후기·재구매·OEM 준비 과정까지 공개</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="145" t="inlineStr">
         <is>
           <t>주 3개</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="145" t="inlineStr">
         <is>
           <t>재구매 증거로 퇴사 결정</t>
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="22" customHeight="1" s="43">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="257" t="inlineStr">
         <is>
           <t>§5. 끊겼을 때 규칙</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" s="43">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="140" t="inlineStr">
         <is>
           <t>상황</t>
         </is>
       </c>
-      <c r="B40" s="60" t="inlineStr">
+      <c r="B40" s="140" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
-      <c r="C40" s="60" t="inlineStr">
+      <c r="C40" s="140" t="inlineStr">
         <is>
           <t>왜</t>
         </is>
       </c>
-      <c r="D40" s="27" t="n"/>
+      <c r="D40" s="258" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1" s="43">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="259" t="inlineStr">
         <is>
           <t>2주 이상 못 올렸다</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="145" t="inlineStr">
         <is>
           <t>사과·공지 없이 버퍼 1개 올리고 그냥 다시 시작</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="145" t="inlineStr">
         <is>
           <t>공백은 생각보다 아무도 신경 안 쓴다. 다시 올리는 게 전부</t>
         </is>
       </c>
-      <c r="D41" s="24" t="n"/>
+      <c r="D41" s="145" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1" s="43">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="259" t="inlineStr">
         <is>
           <t>반응이 없다</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="145" t="inlineStr">
         <is>
           <t>4주(8개)는 보고 판단. 1~2개로 판단 금지. 바꿀 땐 한 번에 한 변수만</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="145" t="inlineStr">
         <is>
           <t>초반 반응은 원래 적다</t>
         </is>
       </c>
-      <c r="D42" s="24" t="n"/>
+      <c r="D42" s="145" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1" s="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="259" t="inlineStr">
         <is>
           <t>하기 싫은 주</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B43" s="145" t="inlineStr">
         <is>
           <t>'최소 업로드' — 사진 1장 + 한 줄이면 주 1개 바닥 달성</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="145" t="inlineStr">
         <is>
           <t>끊기지 않는 게 목표</t>
         </is>
       </c>
-      <c r="D43" s="24" t="n"/>
+      <c r="D43" s="145" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1" s="43">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="259" t="inlineStr">
         <is>
           <t>소재가 없다</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="145" t="inlineStr">
         <is>
           <t>§3 소재 은행에서 고르거나, 지난 실험을 '그때 vs 지금'으로 다시 쓰기</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="145" t="inlineStr">
         <is>
           <t>제품을 만들고 있는 한 소재는 계속 생긴다</t>
         </is>
       </c>
-      <c r="D44" s="24" t="n"/>
-    </row>
+      <c r="D44" s="145" t="n"/>
+    </row>
+    <row r="45"/>
     <row r="46" ht="22" customHeight="1" s="43">
-      <c r="A46" s="68" t="inlineStr">
-        <is>
-          <t>§6. ASMR 제작 과정 영상 — 포맷 (15~30초 · 말 없이 소리와 손만)</t>
+      <c r="A46" s="257" t="inlineStr">
+        <is>
+          <t>§6. ASMR 제작 과정 영상 — 포맷 (15~30초 · 말 없이 소리와 손만 · 다꾸 쇼츠 문법)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" s="43">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="140" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B47" s="60" t="inlineStr">
+      <c r="B47" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C47" s="60" t="inlineStr">
+      <c r="C47" s="140" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="D47" s="27" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1" s="43">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>촬영 세팅</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>고정 앵글 1개(위에서 또는 45°) · 한 가지 색 배경 · 창가 자연광 · 투명 유리 비커.</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>매번 같은 세팅 = 브랜드의 화면 톤이 된다</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1" s="43">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="D47" s="258" t="n"/>
+    </row>
+    <row r="48" ht="60" customHeight="1" s="43">
+      <c r="A48" s="259" t="inlineStr">
+        <is>
+          <t>화면 — 위에서 고정 1개</t>
+        </is>
+      </c>
+      <c r="B48" s="145" t="inlineStr">
+        <is>
+          <t>다꾸 쇼츠처럼 위에서 내려다보는 앵글 하나만(또는 45°). 무광 단색 배경 · 창가 자연광 · 투명 유리 비커. 앵글은 바꾸지 않는다. 세팅 순서는 §11.</t>
+        </is>
+      </c>
+      <c r="C48" s="145" t="inlineStr">
+        <is>
+          <t>매번 같은 세팅 = 계정의 화면 톤. 피드에서 '아 그 계정' 하고 알아본다</t>
+        </is>
+      </c>
+      <c r="D48" s="145" t="n"/>
+    </row>
+    <row r="49" ht="60" customHeight="1" s="43">
+      <c r="A49" s="259" t="inlineStr">
+        <is>
+          <t>정돈된 책상</t>
+        </is>
+      </c>
+      <c r="B49" s="145" t="inlineStr">
+        <is>
+          <t>화면 안엔 이번 장면에 쓰는 것만. 원료 병은 라벨이 보이게 한쪽에 일렬, 도구는 나란히. 처음 배치를 사진으로 찍어두고 매번 그 사진대로 놓는다.</t>
+        </is>
+      </c>
+      <c r="C49" s="145" t="inlineStr">
+        <is>
+          <t>다꾸 쇼츠가 '보기 좋은' 이유의 절반은 정리. 화면 안 쓸데없는 물건 0개</t>
+        </is>
+      </c>
+      <c r="D49" s="145" t="n"/>
+    </row>
+    <row r="50" ht="60" customHeight="1" s="43">
+      <c r="A50" s="259" t="inlineStr">
+        <is>
+          <t>손</t>
+        </is>
+      </c>
+      <c r="B50" s="145" t="inlineStr">
+        <is>
+          <t>평소의 1.5배 천천히 — 보여주려고 움직이는 손. 장갑은 한 색으로 고정(검정 니트릴 추천: 흰 크림과 대비가 좋다).</t>
+        </is>
+      </c>
+      <c r="C50" s="145" t="inlineStr">
+        <is>
+          <t>급한 손은 보는 사람도 불안하다. 장갑 색도 브랜드 톤</t>
+        </is>
+      </c>
+      <c r="D50" s="145" t="n"/>
+    </row>
+    <row r="51" ht="60" customHeight="1" s="43">
+      <c r="A51" s="259" t="inlineStr">
         <is>
           <t>소리</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>클립형 마이크를 비커 가까이(2~5만 원대). 에어컨·냉장고 끄기. 말소리·배경음악 없음.</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>소리가 곧 제품. 폰 마이크만으로 시작해도 되지만 마이크 하나로 확 달라진다</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1" s="43">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="B51" s="145" t="inlineStr">
+        <is>
+          <t>핀마이크를 비커 옆 5~10cm에 고정(§11). 긁기·뚜껑 닫기처럼 소리 나는 동작은 마이크 쪽에서. 에어컨·냉장고 끄기. 말소리·배경음악 없음.</t>
+        </is>
+      </c>
+      <c r="C51" s="145" t="inlineStr">
+        <is>
+          <t>소리가 곧 제품. 다꾸의 스티커 떼는 소리 = 우리의 스패출러 긁는 소리</t>
+        </is>
+      </c>
+      <c r="D51" s="145" t="n"/>
+    </row>
+    <row r="52" ht="34" customHeight="1" s="43">
+      <c r="A52" s="259" t="inlineStr">
         <is>
           <t>위생</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B52" s="145" t="inlineStr">
         <is>
           <t>장갑 · 깨끗한 작업대 · 라벨 붙은 원료 병이 화면에 보이게.</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C52" s="145" t="inlineStr">
         <is>
           <t>피부에 바르는 걸 만드는 영상 — 위생이 곧 신뢰</t>
         </is>
       </c>
-      <c r="D50" s="24" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1" s="43">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="D52" s="145" t="n"/>
+    </row>
+    <row r="53" ht="99" customHeight="1" s="43">
+      <c r="A53" s="259" t="inlineStr">
         <is>
           <t>구성</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>첫 1초 = 가장 만족스러운 장면(§7 ★) → 과정 3~4컷 → 마지막 질감 + '출시 알림은 프로필 링크'.</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>15~30초. 첫 1초에서 넘기느냐가 갈린다</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1" s="43">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="B53" s="145" t="inlineStr">
+        <is>
+          <t>첫 1초 = 가장 만족스러운 장면(§7 ★) → 과정 3~4컷(컷당 2~4초) → 마지막 완성 공개(라벨 붙은 용기 + 질감) + '출시 알림은 프로필 링크'.
+촬영은 실제 공정 순서대로 쭉 하고, ★ 장면은 편집에서 맨 앞으로 옮긴다.</t>
+        </is>
+      </c>
+      <c r="C53" s="145" t="inlineStr">
+        <is>
+          <t>15~30초. 첫 1초에서 넘기느냐가 갈린다. 다꾸의 '완성 페이지 공개' = 우리의 완성 용기</t>
+        </is>
+      </c>
+      <c r="D53" s="145" t="n"/>
+    </row>
+    <row r="54" ht="60" customHeight="1" s="43">
+      <c r="A54" s="259" t="inlineStr">
         <is>
           <t>편집</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>CapCut으로 소리에 맞춰 자르기 + 노이즈 제거 + 짧은 자막(원료명·%)만.</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="B54" s="145" t="inlineStr">
+        <is>
+          <t>최소만: 자르기 · 노이즈 감소 · 자막(원료명·%) 1~2개. 전환 효과·배경음악 없음(딱딱 끊기는 하드컷). 단계별 방법은 §12.</t>
+        </is>
+      </c>
+      <c r="C54" s="145" t="inlineStr">
         <is>
           <t>편집은 최소, 소리는 최대 — 편집 공부 없이 바로 시작 가능</t>
         </is>
       </c>
-      <c r="D52" s="24" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1" s="43">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="D54" s="145" t="n"/>
+    </row>
+    <row r="55" ht="47" customHeight="1" s="43">
+      <c r="A55" s="259" t="inlineStr">
         <is>
           <t>위트</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B55" s="145" t="inlineStr">
         <is>
           <t>영상은 차분한 ASMR, 웃음은 자막·캡션 한 줄로. 어느 쪽이 반응 좋은지 수요검증 §4 로그로 비교.</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C55" s="145" t="inlineStr">
         <is>
           <t>예) '카보머: 중화 전엔 물, 중화 후엔 젤리. 나도 월요일엔 물임'</t>
         </is>
       </c>
-      <c r="D53" s="24" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1" s="43">
-      <c r="A55" s="68" t="inlineStr">
-        <is>
-          <t>§7. 장면 목록 — 가진 장비가 그대로 소품 (★ = 첫 1초 후보)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1" s="43">
-      <c r="A56" s="60" t="inlineStr">
+      <c r="D55" s="145" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1" s="43">
+      <c r="A57" s="257" t="inlineStr">
+        <is>
+          <t>§7. 장면 목록 · 콘티 — 가진 장비가 그대로 소품 (★ = 첫 1초 후보)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1" s="43">
+      <c r="A58" s="140" t="inlineStr">
         <is>
           <t>장면</t>
         </is>
       </c>
-      <c r="B56" s="60" t="inlineStr">
+      <c r="B58" s="140" t="inlineStr">
         <is>
           <t>소리 · 화면 포인트</t>
         </is>
       </c>
-      <c r="C56" s="60" t="inlineStr">
+      <c r="C58" s="140" t="inlineStr">
         <is>
           <t>첫 1초</t>
         </is>
       </c>
-      <c r="D56" s="27" t="n"/>
-    </row>
-    <row r="57" ht="36" customHeight="1" s="43">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="D58" s="258" t="n"/>
+    </row>
+    <row r="59" ht="34" customHeight="1" s="43">
+      <c r="A59" s="259" t="inlineStr">
         <is>
           <t>0.01g 저울 계량</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B59" s="145" t="inlineStr">
         <is>
           <t>숫자가 올라가는 화면 + 가루·방울이 톡톡 떨어지는 소리</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C59" s="145" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="36" customHeight="1" s="43">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="D59" s="145" t="n"/>
+    </row>
+    <row r="60" ht="34" customHeight="1" s="43">
+      <c r="A60" s="259" t="inlineStr">
         <is>
           <t>가루 뿌리기 · 분산</t>
         </is>
       </c>
-      <c r="B58" s="24" t="inlineStr">
+      <c r="B60" s="145" t="inlineStr">
         <is>
           <t>물 위에 카보머·잔탄검을 솔솔 뿌리는 장면 + 막대로 젓는 소리</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="C60" s="145" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="36" customHeight="1" s="43">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="D60" s="145" t="n"/>
+    </row>
+    <row r="61" ht="34" customHeight="1" s="43">
+      <c r="A61" s="259" t="inlineStr">
         <is>
           <t>카보머 중화</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B61" s="145" t="inlineStr">
         <is>
           <t>묽던 액체가 트로메타민 몇 방울에 탱글하게 굳는 순간 + pH미터 삑</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C61" s="145" t="inlineStr">
         <is>
           <t>★ 가장 강한 한 컷</t>
         </is>
       </c>
-      <c r="D59" s="24" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1" s="43">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="D61" s="145" t="n"/>
+    </row>
+    <row r="62" ht="34" customHeight="1" s="43">
+      <c r="A62" s="259" t="inlineStr">
         <is>
           <t>호모나이저 유화</t>
         </is>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B62" s="145" t="inlineStr">
         <is>
           <t>윙 소리와 함께 투명 → 우유색으로 바뀌는 장면</t>
         </is>
       </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="C62" s="145" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="D60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="36" customHeight="1" s="43">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="D62" s="145" t="n"/>
+    </row>
+    <row r="63" ht="34" customHeight="1" s="43">
+      <c r="A63" s="259" t="inlineStr">
         <is>
           <t>스패출러 긁기 · 용기 채우기</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B63" s="145" t="inlineStr">
         <is>
           <t>크림을 긁어 담는 소리 — ASMR의 핵심 소리</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C63" s="145" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D61" s="24" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1" s="43">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="D63" s="145" t="n"/>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="43">
+      <c r="A64" s="259" t="inlineStr">
         <is>
           <t>원심분리 결과</t>
         </is>
       </c>
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B64" s="145" t="inlineStr">
         <is>
           <t>튜브 꺼내는 소리 + '분리 0mm' 확인</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C64" s="145" t="inlineStr">
         <is>
           <t>○ (시리즈 '분리 테스트 n회차'로)</t>
         </is>
       </c>
-      <c r="D62" s="24" t="n"/>
-    </row>
-    <row r="63" ht="36" customHeight="1" s="43">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="D64" s="145" t="n"/>
+    </row>
+    <row r="65" ht="34" customHeight="1" s="43">
+      <c r="A65" s="259" t="inlineStr">
+        <is>
+          <t>라벨 붙이기 (다꾸 감성)</t>
+        </is>
+      </c>
+      <c r="B65" s="145" t="inlineStr">
+        <is>
+          <t>용기에 배치번호 라벨을 붙이고 손가락으로 쓸어 누르는 장면 + 스티커 소리</t>
+        </is>
+      </c>
+      <c r="C65" s="145" t="inlineStr">
+        <is>
+          <t>마지막 컷 후보</t>
+        </is>
+      </c>
+      <c r="D65" s="145" t="n"/>
+    </row>
+    <row r="66" ht="47" customHeight="1" s="43">
+      <c r="A66" s="259" t="inlineStr">
+        <is>
+          <t>개발일지 손글씨 (다꾸 감성)</t>
+        </is>
+      </c>
+      <c r="B66" s="145" t="inlineStr">
+        <is>
+          <t>노트에 'Batch 03 · pH 5.5'를 펜으로 적는 소리 — 다이어리 쓰는 화면 그대로</t>
+        </is>
+      </c>
+      <c r="C66" s="145" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D66" s="145" t="n"/>
+    </row>
+    <row r="67" ht="34" customHeight="1" s="43">
+      <c r="A67" s="259" t="inlineStr">
+        <is>
+          <t>완성 용기 정렬 (다꾸 감성)</t>
+        </is>
+      </c>
+      <c r="B67" s="145" t="inlineStr">
+        <is>
+          <t>완성 용기 3개를 나란히 놓는 '톡, 톡, 톡' + 뚜껑 '딸깍'</t>
+        </is>
+      </c>
+      <c r="C67" s="145" t="inlineStr">
+        <is>
+          <t>마지막 컷 후보</t>
+        </is>
+      </c>
+      <c r="D67" s="145" t="n"/>
+    </row>
+    <row r="68" ht="34" customHeight="1" s="43">
+      <c r="A68" s="259" t="inlineStr">
         <is>
           <t>손등 발림 · 손가락 누르기</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B68" s="145" t="inlineStr">
         <is>
           <t>질감 클로즈업 — 마지막 컷 고정</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C68" s="145" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D63" s="24" t="n"/>
-    </row>
-    <row r="65" ht="22" customHeight="1" s="43">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="D68" s="145" t="n"/>
+    </row>
+    <row r="69" ht="34" customHeight="1" s="43">
+      <c r="A69" s="79" t="inlineStr">
+        <is>
+          <t>콘티 = 촬영 전 메모장에 5분. 다꾸 쇼츠도 즉흥처럼 보이지만 순서는 정해져 있다. 아래는 예시(카보머 젤 · 총 20초) — 장면만 바꿔 매번 이 모양으로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1" s="43">
+      <c r="A70" s="140" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B70" s="140" t="inlineStr">
+        <is>
+          <t>장면 · 소리</t>
+        </is>
+      </c>
+      <c r="C70" s="140" t="inlineStr">
+        <is>
+          <t>길이</t>
+        </is>
+      </c>
+      <c r="D70" s="258" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1" s="43">
+      <c r="A71" s="259" t="inlineStr">
+        <is>
+          <t>① 훅 (첫 1초)</t>
+        </is>
+      </c>
+      <c r="B71" s="145" t="inlineStr">
+        <is>
+          <t>트로메타민 한 방울에 액체가 탱글하게 굳는 순간 ★ · 막대 젓는 소리</t>
+        </is>
+      </c>
+      <c r="C71" s="145" t="inlineStr">
+        <is>
+          <t>2초</t>
+        </is>
+      </c>
+      <c r="D71" s="145" t="n"/>
+    </row>
+    <row r="72" ht="34" customHeight="1" s="43">
+      <c r="A72" s="259" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B72" s="145" t="inlineStr">
+        <is>
+          <t>저울에 카보머 가루 계량, 숫자가 올라감 · 가루 톡톡</t>
+        </is>
+      </c>
+      <c r="C72" s="145" t="inlineStr">
+        <is>
+          <t>3초</t>
+        </is>
+      </c>
+      <c r="D72" s="145" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1" s="43">
+      <c r="A73" s="259" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B73" s="145" t="inlineStr">
+        <is>
+          <t>물 위에 솔솔 뿌리기 · 사락사락</t>
+        </is>
+      </c>
+      <c r="C73" s="145" t="inlineStr">
+        <is>
+          <t>3초</t>
+        </is>
+      </c>
+      <c r="D73" s="145" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1" s="43">
+      <c r="A74" s="259" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B74" s="145" t="inlineStr">
+        <is>
+          <t>막대로 천천히 젓기 · 유리 긁는 소리</t>
+        </is>
+      </c>
+      <c r="C74" s="145" t="inlineStr">
+        <is>
+          <t>3초</t>
+        </is>
+      </c>
+      <c r="D74" s="145" t="n"/>
+    </row>
+    <row r="75" ht="34" customHeight="1" s="43">
+      <c r="A75" s="259" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B75" s="145" t="inlineStr">
+        <is>
+          <t>스패출러로 용기에 담기 · 크림 긁는 소리</t>
+        </is>
+      </c>
+      <c r="C75" s="145" t="inlineStr">
+        <is>
+          <t>4초</t>
+        </is>
+      </c>
+      <c r="D75" s="145" t="n"/>
+    </row>
+    <row r="76" ht="22" customHeight="1" s="43">
+      <c r="A76" s="259" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B76" s="145" t="inlineStr">
+        <is>
+          <t>라벨 붙이고 쓸어 누르기 · 스티커 소리</t>
+        </is>
+      </c>
+      <c r="C76" s="145" t="inlineStr">
+        <is>
+          <t>3초</t>
+        </is>
+      </c>
+      <c r="D76" s="145" t="n"/>
+    </row>
+    <row r="77" ht="34" customHeight="1" s="43">
+      <c r="A77" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 마무리</t>
+        </is>
+      </c>
+      <c r="B77" s="145" t="inlineStr">
+        <is>
+          <t>손가락으로 꾹 누르기 + 자막 '출시 알림은 프로필 링크'</t>
+        </is>
+      </c>
+      <c r="C77" s="145" t="inlineStr">
+        <is>
+          <t>2초</t>
+        </is>
+      </c>
+      <c r="D77" s="145" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1" s="43">
+      <c r="A79" s="257" t="inlineStr">
         <is>
           <t>§8. 프로필 링크 · 유입 — 시기별로 링크 대상을 바꾼다</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="28" customHeight="1" s="43">
-      <c r="A66" s="60" t="inlineStr">
+    <row r="80" ht="28" customHeight="1" s="43">
+      <c r="A80" s="140" t="inlineStr">
         <is>
           <t>시기 · 항목</t>
         </is>
       </c>
-      <c r="B66" s="60" t="inlineStr">
+      <c r="B80" s="140" t="inlineStr">
         <is>
           <t>프로필 링크 / 문구</t>
         </is>
       </c>
-      <c r="C66" s="60" t="inlineStr">
+      <c r="C80" s="140" t="inlineStr">
         <is>
           <t>하는 일 · 측정</t>
         </is>
       </c>
-      <c r="D66" s="27" t="n"/>
-    </row>
-    <row r="67" ht="36" customHeight="1" s="43">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="D80" s="258" t="n"/>
+    </row>
+    <row r="81" ht="36" customHeight="1" s="43">
+      <c r="A81" s="259" t="inlineStr">
         <is>
           <t>지금 ~ 2027.5</t>
         </is>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B81" s="145" t="inlineStr">
         <is>
           <t>출시 알림 대기자 폼 (수요검증 S2). 상점 링크 ❌</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C81" s="145" t="inlineStr">
         <is>
           <t>링크 클릭 수 → 대기자 전환율 = 수요 증거. 주 1회 §4 로그에 숫자</t>
         </is>
       </c>
-      <c r="D67" s="24" t="n"/>
-    </row>
-    <row r="68" ht="36" customHeight="1" s="43">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="D81" s="145" t="n"/>
+    </row>
+    <row r="82" ht="36" customHeight="1" s="43">
+      <c r="A82" s="259" t="inlineStr">
         <is>
           <t>자격 취득 후 (2027 중반~)</t>
         </is>
       </c>
-      <c r="B68" s="24" t="inlineStr">
+      <c r="B82" s="145" t="inlineStr">
         <is>
           <t>상점 + 대기자 폼</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C82" s="145" t="inlineStr">
         <is>
           <t>대기자에게 먼저 판매 알림 → 첫 매출 · 재구매 추적(S5)</t>
         </is>
       </c>
-      <c r="D68" s="24" t="n"/>
-    </row>
-    <row r="69" ht="36" customHeight="1" s="43">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="D82" s="145" t="n"/>
+    </row>
+    <row r="83" ht="36" customHeight="1" s="43">
+      <c r="A83" s="259" t="inlineStr">
         <is>
           <t>프로필 소개</t>
         </is>
       </c>
-      <c r="B69" s="24" t="inlineStr">
+      <c r="B83" s="145" t="inlineStr">
         <is>
           <t>'지성·민감 피부용 무향 진정 크림, 직접 개발 중 · 출시 알림 ↓'</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C83" s="145" t="inlineStr">
         <is>
           <t>누구를 위한 무엇인지 + 할 행동 하나</t>
         </is>
       </c>
-      <c r="D69" s="24" t="n"/>
-    </row>
-    <row r="70" ht="22" customHeight="1" s="43">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="D83" s="145" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1" s="43">
+      <c r="A84" s="259" t="inlineStr">
         <is>
           <t>영상 · 캡션 끝</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B84" s="145" t="inlineStr">
         <is>
           <t>매번 '출시 알림은 프로필 링크' 한 줄</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C84" s="145" t="inlineStr">
         <is>
           <t>행동 요청은 하나만</t>
         </is>
       </c>
-      <c r="D70" s="24" t="n"/>
-    </row>
-    <row r="71" ht="36" customHeight="1" s="43">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="D84" s="145" t="n"/>
+    </row>
+    <row r="85" ht="36" customHeight="1" s="43">
+      <c r="A85" s="259" t="inlineStr">
         <is>
           <t>링크가 여러 개일 때</t>
         </is>
       </c>
-      <c r="B71" s="24" t="inlineStr">
+      <c r="B85" s="145" t="inlineStr">
         <is>
           <t>링크 모음 서비스로 하나로 묶고, 맨 위에 시기별 핵심 링크 하나</t>
         </is>
       </c>
-      <c r="C71" s="24" t="inlineStr">
+      <c r="C85" s="145" t="inlineStr">
         <is>
           <t>링크가 많으면 아무것도 안 누른다</t>
         </is>
       </c>
-      <c r="D71" s="24" t="n"/>
-    </row>
-    <row r="72" ht="44" customHeight="1" s="43">
-      <c r="A72" s="79" t="inlineStr">
+      <c r="D85" s="145" t="n"/>
+    </row>
+    <row r="86" ht="44" customHeight="1" s="43">
+      <c r="A86" s="79" t="inlineStr">
         <is>
           <t>⚠ 자격(맞춤형화장품판매업) 또는 OEM 제조 + 책임판매업 등록 전엔 집에서 만든 제품을 팔 수 없다 → 지금 링크는 상점이 아니라 대기자 폼. 나중에 OEM 제품을 팔 때는 홈랩 영상이 '개발 과정'임을 분명히(판매 제품을 집에서 만드는 것처럼 보이면 오인 표현 위험).</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="23" customHeight="1" s="43">
-      <c r="A74" s="68" t="inlineStr">
+    <row r="87"/>
+    <row r="88" ht="23" customHeight="1" s="43">
+      <c r="A88" s="257" t="inlineStr">
         <is>
           <t>§9. 블로그 — 검색으로 찾아오는 사람을 받는다 (네이버 블로그 = 네이버 검색 · 구글은 브랜드 사이트 §13)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="28" customHeight="1" s="43">
-      <c r="A75" s="60" t="inlineStr">
+    <row r="89" ht="28" customHeight="1" s="43">
+      <c r="A89" s="140" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B75" s="60" t="inlineStr">
+      <c r="B89" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C75" s="60" t="inlineStr">
+      <c r="C89" s="140" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="D75" s="27" t="n"/>
-    </row>
-    <row r="76" ht="51" customHeight="1" s="43">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="D89" s="258" t="n"/>
+    </row>
+    <row r="90" ht="51" customHeight="1" s="43">
+      <c r="A90" s="259" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B90" s="145" t="inlineStr">
         <is>
           <t>인스타 = 피드에서 우연히 발견. 블로그 = 고민이 있어서 직접 검색해 찾아옴(구매 의도가 높은 사람).</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C90" s="145" t="inlineStr">
         <is>
           <t>글 한 편이 몇 년간 검색 유입을 만든다 — 2년이면 복리</t>
         </is>
       </c>
-      <c r="D76" s="24" t="n"/>
-    </row>
-    <row r="77" ht="66" customHeight="1" s="43">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="D90" s="145" t="n"/>
+    </row>
+    <row r="91" ht="66" customHeight="1" s="43">
+      <c r="A91" s="259" t="inlineStr">
         <is>
           <t>플랫폼 · 시작 시점</t>
         </is>
       </c>
-      <c r="B77" s="24" t="inlineStr">
+      <c r="B91" s="145" t="inlineStr">
         <is>
           <t>네이버 블로그 추천(화장품은 사기 전에 검색하는 사람이 많고, 나중에 스마트스토어와 같은 생태계). 인스타 습관이 잡힌 뒤 시작 — 4주 연속 주 2개 달성하면.</t>
         </is>
       </c>
-      <c r="C77" s="24" t="inlineStr">
+      <c r="C91" s="145" t="inlineStr">
         <is>
           <t>블로그는 시험 공부 겸용이라 추가 부담이 작다. 구글 유입은 브랜드 사이트로 따로(§13) — 같은 글 복사 ❌</t>
         </is>
       </c>
-      <c r="D77" s="24" t="n"/>
-    </row>
-    <row r="78" ht="51" customHeight="1" s="43">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="D91" s="145" t="n"/>
+    </row>
+    <row r="92" ht="51" customHeight="1" s="43">
+      <c r="A92" s="259" t="inlineStr">
         <is>
           <t>주간 루틴</t>
         </is>
       </c>
-      <c r="B78" s="24" t="inlineStr">
+      <c r="B92" s="145" t="inlineStr">
         <is>
           <t>주 1편, 60분. 이번 주 공부한 성분 1개 또는 개발일지 1건 → §10 프롬프트 ① → ②·③·④ 중 하나 → 사실·사진 직접 채우기 → ⑤ 점검 → 발행.</t>
         </is>
       </c>
-      <c r="C78" s="24" t="inlineStr">
+      <c r="C92" s="145" t="inlineStr">
         <is>
           <t>남에게 설명하듯 쓰는 게 가장 강한 암기법 — 블로그 1편 = 시험 공부 1회</t>
         </is>
       </c>
-      <c r="D78" s="24" t="n"/>
-    </row>
-    <row r="79" ht="51" customHeight="1" s="43">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="D92" s="145" t="n"/>
+    </row>
+    <row r="93" ht="51" customHeight="1" s="43">
+      <c r="A93" s="259" t="inlineStr">
         <is>
           <t>글감 3종 (번갈아)</t>
         </is>
       </c>
-      <c r="B79" s="24" t="inlineStr">
+      <c r="B93" s="145" t="inlineStr">
         <is>
           <t>고민 해결(①층, 예: 지성인데 속건조) / 성분 해설(②층, 시험 공부) / 개발일지(③층, 실험·실패, ASMR 영상 넣기).</t>
         </is>
       </c>
-      <c r="C79" s="24" t="inlineStr">
+      <c r="C93" s="145" t="inlineStr">
         <is>
           <t>비중은 키워드 3층과 같게. 시험대비 원료맵·개발일지 시트가 그대로 글감 창고</t>
         </is>
       </c>
-      <c r="D79" s="24" t="n"/>
-    </row>
-    <row r="80" ht="201" customHeight="1" s="43">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="D93" s="145" t="n"/>
+    </row>
+    <row r="94" ht="201" customHeight="1" s="43">
+      <c r="A94" s="259" t="inlineStr">
         <is>
           <t>키워드 (3층)</t>
         </is>
       </c>
-      <c r="B80" s="24" t="inlineStr">
+      <c r="B94" s="145" t="inlineStr">
         <is>
           <t>① 고민 키워드 (약 50%) — 고객이 자기 고민을 자기 말로 검색. 살 사람이 온다.
 예) '지성 속건조' '지성 피부 수분크림' '번들거림 없는 크림' '민감성 진정 크림' '무향 크림'
@@ -13944,134 +14200,135 @@
 예) '카보머 중화' '원심분리 테스트'</t>
         </is>
       </c>
-      <c r="C80" s="24" t="inlineStr">
+      <c r="C94" s="145" t="inlineStr">
         <is>
           <t>검색량은 네이버 검색광고 키워드 도구(월간 검색수)·데이터랩(추세)으로 직접 확인 — 감으로 판단 금지.
 큰 키워드('수분크림 추천')는 대형 브랜드 몫 → 구체적인 키워드 여러 개로 이긴다.
 질환명(여드름·지루성 피부염)은 제품 효능과 연결 금지 — 지성·번들거림·속건조·민감 같은 피부 타입·상태 단어로.</t>
         </is>
       </c>
-      <c r="D80" s="24" t="n"/>
-    </row>
-    <row r="81" ht="51" customHeight="1" s="43">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="D94" s="145" t="n"/>
+    </row>
+    <row r="95" ht="51" customHeight="1" s="43">
+      <c r="A95" s="259" t="inlineStr">
         <is>
           <t>글 구조</t>
         </is>
       </c>
-      <c r="B81" s="24" t="inlineStr">
+      <c r="B95" s="145" t="inlineStr">
         <is>
           <t>제목 앞쪽에 메인 키워드 → 고민으로 시작하는 도입 → 소제목 4~5개 → 직접 찍은 사진·영상 → 끝에 출시 알림 링크.</t>
         </is>
       </c>
-      <c r="C81" s="24" t="inlineStr">
+      <c r="C95" s="145" t="inlineStr">
         <is>
           <t>직접 해본 사진·기록이 AI 대량 글과의 차이</t>
         </is>
       </c>
-      <c r="D81" s="24" t="n"/>
-    </row>
-    <row r="82" ht="36" customHeight="1" s="43">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="D95" s="145" t="n"/>
+    </row>
+    <row r="96" ht="36" customHeight="1" s="43">
+      <c r="A96" s="259" t="inlineStr">
         <is>
           <t>AI 사용 원칙</t>
         </is>
       </c>
-      <c r="B82" s="24" t="inlineStr">
+      <c r="B96" s="145" t="inlineStr">
         <is>
           <t>AI = 기획·초안·점검 담당. 수치·규제는 교재·고시로 직접 확인. 실험 사진·경험은 직접.</t>
         </is>
       </c>
-      <c r="C82" s="24" t="inlineStr">
+      <c r="C96" s="145" t="inlineStr">
         <is>
           <t>AI가 지어낸 수치 한 줄이 '성분 아는 사람'이라는 신뢰를 깎는다</t>
         </is>
       </c>
-      <c r="D82" s="24" t="n"/>
-    </row>
-    <row r="83" ht="51" customHeight="1" s="43">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="D96" s="145" t="n"/>
+    </row>
+    <row r="97" ht="51" customHeight="1" s="43">
+      <c r="A97" s="259" t="inlineStr">
         <is>
           <t>링크 · 규정</t>
         </is>
       </c>
-      <c r="B83" s="24" t="inlineStr">
+      <c r="B97" s="145" t="inlineStr">
         <is>
           <t>글 끝은 대기자 폼(판매 전). 판매 시작 후엔 블로그도 광고 → 수요검증 §3 기준 적용. 협찬·체험단 글은 협찬 사실 표기.</t>
         </is>
       </c>
-      <c r="C83" s="24" t="inlineStr">
+      <c r="C97" s="145" t="inlineStr">
         <is>
           <t>§8 프로필 링크와 같은 원칙</t>
         </is>
       </c>
-      <c r="D83" s="24" t="n"/>
-    </row>
-    <row r="84" ht="66" customHeight="1" s="43">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="D97" s="145" t="n"/>
+    </row>
+    <row r="98" ht="66" customHeight="1" s="43">
+      <c r="A98" s="259" t="inlineStr">
         <is>
           <t>측정</t>
         </is>
       </c>
-      <c r="B84" s="24" t="inlineStr">
+      <c r="B98" s="145" t="inlineStr">
         <is>
           <t>월 1회: 유입 키워드 상위 5개 · 조회수 · 대기자 폼 클릭을 키워드 층별로 비교 → 대기자를 많이 데려온 층·주제를 다음 달 글감으로. 목표는 조회수가 아니라 대기자.</t>
         </is>
       </c>
-      <c r="C84" s="24" t="inlineStr">
+      <c r="C98" s="145" t="inlineStr">
         <is>
           <t>수요검증 §4 로그에 '블로그' 줄로 기록</t>
         </is>
       </c>
-      <c r="D84" s="24" t="n"/>
-    </row>
-    <row r="85" ht="51" customHeight="1" s="43">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="D98" s="145" t="n"/>
+    </row>
+    <row r="99" ht="51" customHeight="1" s="43">
+      <c r="A99" s="259" t="inlineStr">
         <is>
           <t>목표</t>
         </is>
       </c>
-      <c r="B85" s="24" t="inlineStr">
+      <c r="B99" s="145" t="inlineStr">
         <is>
           <t>2026.12 시작 → 시험(2027.5) 전 성분 해설 약 20편 → 2027년 말 누적 약 50편. (브랜드 사이트 '성분 사전'은 별도 — §13)</t>
         </is>
       </c>
-      <c r="C85" s="24" t="inlineStr">
+      <c r="C99" s="145" t="inlineStr">
         <is>
           <t>시험기에도 유지 가능(공부가 곧 글감)</t>
         </is>
       </c>
-      <c r="D85" s="24" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1" s="43">
-      <c r="A87" s="68" t="inlineStr">
+      <c r="D99" s="145" t="n"/>
+    </row>
+    <row r="100"/>
+    <row r="101" ht="22" customHeight="1" s="43">
+      <c r="A101" s="257" t="inlineStr">
         <is>
           <t>§10. 블로그 발행 프롬프트 6종 — 셀 내용을 그대로 복사해 AI(Claude·ChatGPT 등)에 붙여넣고 [대괄호]만 채운다</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="28" customHeight="1" s="43">
-      <c r="A88" s="60" t="inlineStr">
+    <row r="102" ht="28" customHeight="1" s="43">
+      <c r="A102" s="140" t="inlineStr">
         <is>
           <t>프롬프트 · 언제</t>
         </is>
       </c>
-      <c r="B88" s="140" t="inlineStr">
+      <c r="B102" s="140" t="inlineStr">
         <is>
           <t>본문</t>
         </is>
       </c>
-      <c r="C88" s="144" t="n"/>
-      <c r="D88" s="59" t="n"/>
-    </row>
-    <row r="89" ht="267" customHeight="1" s="43">
-      <c r="A89" s="26" t="inlineStr">
+      <c r="C102" s="144" t="n"/>
+      <c r="D102" s="59" t="n"/>
+    </row>
+    <row r="103" ht="267" customHeight="1" s="43">
+      <c r="A103" s="259" t="inlineStr">
         <is>
           <t>① 키워드 · 제목 기획
 언제: 글 쓰기 전, 주제만 정했을 때</t>
         </is>
       </c>
-      <c r="B89" s="145" t="inlineStr">
+      <c r="B103" s="145" t="inlineStr">
         <is>
           <t>너는 화장품 성분 블로그의 콘텐츠 기획자야.
 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어.
@@ -14085,17 +14342,17 @@
 질환명(여드름·지루성 피부염 등)이 들어간 키워드는 '제품 효능과 연결 불가'라고 표시해.</t>
         </is>
       </c>
-      <c r="C89" s="144" t="n"/>
-      <c r="D89" s="59" t="n"/>
-    </row>
-    <row r="90" ht="402" customHeight="1" s="43">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="C103" s="144" t="n"/>
+      <c r="D103" s="59" t="n"/>
+    </row>
+    <row r="104" ht="402" customHeight="1" s="43">
+      <c r="A104" s="259" t="inlineStr">
         <is>
           <t>② 고민 해결 글 초안
 언제: 피부 고민 하나로 글을 쓸 때 (①층 고민 키워드 · 블로그 글의 절반)</t>
         </is>
       </c>
-      <c r="B90" s="145" t="inlineStr">
+      <c r="B104" s="145" t="inlineStr">
         <is>
           <t>아래 정보로 네이버 블로그 '피부 고민 해결' 글 초안을 써줘. 성분 설명이 아니라 독자의 고민에서 출발하는 글이야.
 [나에 대해] 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어. 말투는 친근하지만 정확하게, 가끔 가벼운 위트 한 줄.
@@ -14119,17 +14376,17 @@
 - '완벽·100%·즉시' 같은 절대 표현, 다른 브랜드 비방·비교 금지.</t>
         </is>
       </c>
-      <c r="C90" s="144" t="n"/>
-      <c r="D90" s="59" t="n"/>
-    </row>
-    <row r="91" ht="342" customHeight="1" s="43">
-      <c r="A91" s="26" t="inlineStr">
+      <c r="C104" s="144" t="n"/>
+      <c r="D104" s="59" t="n"/>
+    </row>
+    <row r="105" ht="342" customHeight="1" s="43">
+      <c r="A105" s="259" t="inlineStr">
         <is>
           <t>③ 성분 해설 글 초안
 언제: 시험 공부한 성분으로 글을 쓸 때 (②층 성분 키워드)</t>
         </is>
       </c>
-      <c r="B91" s="145" t="inlineStr">
+      <c r="B105" s="145" t="inlineStr">
         <is>
           <t>아래 정보로 네이버 블로그 글 초안을 써줘.
 [나에 대해] 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어. 말투는 친근하지만 정확하게, 가끔 가벼운 위트 한 줄.
@@ -14151,17 +14408,17 @@
 - 아직 판매 전이니 구매 유도 문구 대신 출시 알림 안내만.</t>
         </is>
       </c>
-      <c r="C91" s="144" t="n"/>
-      <c r="D91" s="59" t="n"/>
-    </row>
-    <row r="92" ht="327" customHeight="1" s="43">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="C105" s="144" t="n"/>
+      <c r="D105" s="59" t="n"/>
+    </row>
+    <row r="106" ht="327" customHeight="1" s="43">
+      <c r="A106" s="259" t="inlineStr">
         <is>
           <t>④ 개발일지 → 블로그 글
 언제: 주말 실험을 글로 남길 때 (③층 메이커 키워드)</t>
         </is>
       </c>
-      <c r="B92" s="145" t="inlineStr">
+      <c r="B106" s="145" t="inlineStr">
         <is>
           <t>아래 개발일지 기록을 블로그 글로 바꿔줘. 실패도 그대로 살려서 '만드는 사람의 실험 노트'처럼.
 [실험 날짜 · 제품] [ ]
@@ -14183,17 +14440,17 @@
 - 효능 단정 금지 — '내 피부에서는 이랬다' 수준으로. 질병 치료·예방 표현 금지.</t>
         </is>
       </c>
-      <c r="C92" s="144" t="n"/>
-      <c r="D92" s="59" t="n"/>
-    </row>
-    <row r="93" ht="147" customHeight="1" s="43">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="C106" s="144" t="n"/>
+      <c r="D106" s="59" t="n"/>
+    </row>
+    <row r="107" ht="147" customHeight="1" s="43">
+      <c r="A107" s="259" t="inlineStr">
         <is>
           <t>⑤ 발행 전 점검
 언제: 초안을 다 채운 뒤, 발행 직전 (매번 필수)</t>
         </is>
       </c>
-      <c r="B93" s="145" t="inlineStr">
+      <c r="B107" s="145" t="inlineStr">
         <is>
           <t>아래 블로그 초안을 발행 전에 점검해줘. 고쳐 쓰기 전에 문제 목록부터 보여줘.
 1. 사실 점검: 수치·규제·성분 설명 중 근거 확인이 필요한 문장을 전부 뽑고, 왜 확인이 필요한지 적어줘.
@@ -14203,17 +14460,17 @@
 [초안 붙여넣기]</t>
         </is>
       </c>
-      <c r="C93" s="144" t="n"/>
-      <c r="D93" s="59" t="n"/>
-    </row>
-    <row r="94" ht="147" customHeight="1" s="43">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="C107" s="144" t="n"/>
+      <c r="D107" s="59" t="n"/>
+    </row>
+    <row r="108" ht="147" customHeight="1" s="43">
+      <c r="A108" s="259" t="inlineStr">
         <is>
           <t>⑥ 블로그 → 인스타 재활용
 언제: 발행한 글을 ASMR 영상·캡션으로 다시 쓸 때</t>
         </is>
       </c>
-      <c r="B94" s="145" t="inlineStr">
+      <c r="B108" s="145" t="inlineStr">
         <is>
           <t>아래 블로그 글을 인스타 ASMR 제작 과정 영상용으로 바꿔줘.
 1. 영상 자막 3~5개 — 각 15자 이내, 원료명·% 위주
@@ -14223,711 +14480,1431 @@
 [블로그 글 붙여넣기]</t>
         </is>
       </c>
-      <c r="C94" s="144" t="n"/>
-      <c r="D94" s="59" t="n"/>
-    </row>
-    <row r="95" ht="44" customHeight="1" s="43">
-      <c r="A95" s="79" t="inlineStr">
+      <c r="C108" s="144" t="n"/>
+      <c r="D108" s="59" t="n"/>
+    </row>
+    <row r="109" ht="44" customHeight="1" s="43">
+      <c r="A109" s="79" t="inlineStr">
         <is>
           <t>사용 순서: ① 키워드 → 초안은 ② 고민(글의 절반)·③ 성분·④ 개발일지 중 하나 → 수치·사진·경험은 내가 직접 채우고 확인 → ⑤ 점검 → 발행 → ⑥ 인스타 재활용. AI 점검은 1차 필터 — 최종 판단은 '표시·광고 컴플라이언스' 시트와 최신 고시로 사람이 한다.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="22" customHeight="1" s="43">
-      <c r="A97" s="68" t="inlineStr">
-        <is>
-          <t>§11. 촬영·편집 시작하기 — 장비는 폰 + 3가지면 충분 (카메라·짐벌 ❌)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1" s="43">
-      <c r="A98" s="60" t="inlineStr">
+    <row r="110"/>
+    <row r="111" ht="22" customHeight="1" s="43">
+      <c r="A111" s="257" t="inlineStr">
+        <is>
+          <t>§11. 촬영 시작하기 — 장비는 폰 + 3가지면 충분 (카메라·짐벌 ❌)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1" s="43">
+      <c r="A112" s="140" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B98" s="60" t="inlineStr">
+      <c r="B112" s="140" t="inlineStr">
         <is>
           <t>고르는 법</t>
         </is>
       </c>
-      <c r="C98" s="60" t="inlineStr">
+      <c r="C112" s="140" t="inlineStr">
         <is>
           <t>가격대(대략) · 메모</t>
         </is>
       </c>
-      <c r="D98" s="27" t="n"/>
-    </row>
-    <row r="99" ht="36" customHeight="1" s="43">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="D112" s="258" t="n"/>
+    </row>
+    <row r="113" ht="47" customHeight="1" s="43">
+      <c r="A113" s="259" t="inlineStr">
         <is>
           <t>위에서 찍는 폰 거치대</t>
         </is>
       </c>
-      <c r="B99" s="24" t="inlineStr">
-        <is>
-          <t>책상에 집게로 고정하는 탑뷰(오버헤드) 거치대 또는 자바라 암. §6의 '위에서 고정 앵글'용.</t>
-        </is>
-      </c>
-      <c r="C99" s="24" t="inlineStr">
+      <c r="B113" s="145" t="inlineStr">
+        <is>
+          <t>책상 모서리에 집게로 고정하는 탑뷰(오버헤드) 자바라 암. 쿠팡 등에서 '탑뷰 거치대'로 검색.</t>
+        </is>
+      </c>
+      <c r="C113" s="145" t="inlineStr">
         <is>
           <t>1~3만 원</t>
         </is>
       </c>
-      <c r="D99" s="24" t="n"/>
-    </row>
-    <row r="100" ht="36" customHeight="1" s="43">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="D113" s="145" t="n"/>
+    </row>
+    <row r="114" ht="60" customHeight="1" s="43">
+      <c r="A114" s="259" t="inlineStr">
         <is>
           <t>무선 핀마이크</t>
         </is>
       </c>
-      <c r="B100" s="24" t="inlineStr">
-        <is>
-          <t>폰 충전 단자에 수신기를 꽂는 타입(내 폰 단자 확인). 핀을 비커 옆 5~10cm에 집게로 고정.</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
+      <c r="B114" s="145" t="inlineStr">
+        <is>
+          <t>폰에 수신기를 꽂는 타입. 주문 전 내 폰 충전 단자 확인(아이폰 15 이후·갤럭시 = USB-C, 아이폰 14 이전 = 라이트닝).</t>
+        </is>
+      </c>
+      <c r="C114" s="145" t="inlineStr">
         <is>
           <t>2~5만 원 · 소리가 곧 제품</t>
         </is>
       </c>
-      <c r="D100" s="24" t="n"/>
-    </row>
-    <row r="101" ht="36" customHeight="1" s="43">
-      <c r="A101" s="26" t="inlineStr">
+      <c r="D114" s="145" t="n"/>
+    </row>
+    <row r="115" ht="34" customHeight="1" s="43">
+      <c r="A115" s="259" t="inlineStr">
         <is>
           <t>배경판</t>
         </is>
       </c>
-      <c r="B101" s="24" t="inlineStr">
+      <c r="B115" s="145" t="inlineStr">
         <is>
           <t>무광 단색 폼보드·배경지(흰색 또는 연회색). 유광은 빛 반사 ❌.</t>
         </is>
       </c>
-      <c r="C101" s="24" t="inlineStr">
+      <c r="C115" s="145" t="inlineStr">
         <is>
           <t>수천 원</t>
         </is>
       </c>
-      <c r="D101" s="24" t="n"/>
-    </row>
-    <row r="102" ht="36" customHeight="1" s="43">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="D115" s="145" t="n"/>
+    </row>
+    <row r="116" ht="34" customHeight="1" s="43">
+      <c r="A116" s="259" t="inlineStr">
+        <is>
+          <t>니트릴 장갑 (한 색)</t>
+        </is>
+      </c>
+      <c r="B116" s="145" t="inlineStr">
+        <is>
+          <t>색 하나로 고정해 계속 쓴다(§6 손).</t>
+        </is>
+      </c>
+      <c r="C116" s="145" t="inlineStr">
+        <is>
+          <t>수천 원</t>
+        </is>
+      </c>
+      <c r="D116" s="145" t="n"/>
+    </row>
+    <row r="117" ht="34" customHeight="1" s="43">
+      <c r="A117" s="259" t="inlineStr">
         <is>
           <t>조명</t>
         </is>
       </c>
-      <c r="B102" s="24" t="inlineStr">
+      <c r="B117" s="145" t="inlineStr">
         <is>
           <t>주말 낮 창가 자연광이면 생략. 저녁 촬영일 때만 LED 패널 1개.</t>
         </is>
       </c>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="C117" s="145" t="inlineStr">
         <is>
           <t>필요할 때 2~3만 원</t>
         </is>
       </c>
-      <c r="D102" s="24" t="n"/>
-    </row>
-    <row r="103" ht="51" customHeight="1" s="43">
-      <c r="A103" s="26" t="inlineStr">
+      <c r="D117" s="145" t="n"/>
+    </row>
+    <row r="118" ht="60" customHeight="1" s="43">
+      <c r="A118" s="259" t="inlineStr">
         <is>
           <t>이미 있는 것</t>
         </is>
       </c>
-      <c r="B103" s="24" t="inlineStr">
+      <c r="B118" s="145" t="inlineStr">
         <is>
           <t>폰 · 0.01g 저울 · 비커 · 호모나이저 · 원심분리기 = 그대로 소품(§7). 편집은 무료 앱 CapCut 하나.</t>
         </is>
       </c>
-      <c r="C103" s="24" t="inlineStr">
+      <c r="C118" s="145" t="inlineStr">
         <is>
           <t>추가 0원</t>
         </is>
       </c>
-      <c r="D103" s="24" t="n"/>
-    </row>
-    <row r="104" ht="28" customHeight="1" s="43">
-      <c r="A104" s="60" t="inlineStr">
-        <is>
-          <t>폰 설정 (한 번만)</t>
-        </is>
-      </c>
-      <c r="B104" s="60" t="inlineStr">
+      <c r="D118" s="145" t="n"/>
+    </row>
+    <row r="119" ht="28" customHeight="1" s="43">
+      <c r="A119" s="140" t="inlineStr">
+        <is>
+          <t>세팅 순서 (매 촬영 15분)</t>
+        </is>
+      </c>
+      <c r="B119" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C104" s="60" t="inlineStr">
+      <c r="C119" s="140" t="inlineStr">
         <is>
           <t>왜</t>
         </is>
       </c>
-      <c r="D104" s="27" t="n"/>
-    </row>
-    <row r="105" ht="36" customHeight="1" s="43">
-      <c r="A105" s="26" t="inlineStr">
-        <is>
-          <t>화면 · 화질</t>
-        </is>
-      </c>
-      <c r="B105" s="24" t="inlineStr">
-        <is>
-          <t>세로 9:16 · 1080p 60fps · 격자 표시 켜기</t>
-        </is>
-      </c>
-      <c r="C105" s="24" t="inlineStr">
-        <is>
-          <t>60fps면 나중에 슬로우 가능, 격자로 비커를 중앙에</t>
-        </is>
-      </c>
-      <c r="D105" s="24" t="n"/>
-    </row>
-    <row r="106" ht="36" customHeight="1" s="43">
-      <c r="A106" s="26" t="inlineStr">
-        <is>
-          <t>초점·노출 잠금</t>
-        </is>
-      </c>
-      <c r="B106" s="24" t="inlineStr">
-        <is>
-          <t>화면을 길게 눌러 잠그기</t>
-        </is>
-      </c>
-      <c r="C106" s="24" t="inlineStr">
-        <is>
-          <t>안 하면 손이 들어올 때마다 화면이 밝아졌다 어두워졌다</t>
-        </is>
-      </c>
-      <c r="D106" s="24" t="n"/>
-    </row>
-    <row r="107" ht="22" customHeight="1" s="43">
-      <c r="A107" s="26" t="inlineStr">
-        <is>
-          <t>촬영 직전</t>
-        </is>
-      </c>
-      <c r="B107" s="24" t="inlineStr">
-        <is>
-          <t>방해금지·비행기 모드 · 렌즈 닦기</t>
-        </is>
-      </c>
-      <c r="C107" s="24" t="inlineStr">
+      <c r="D119" s="258" t="n"/>
+    </row>
+    <row r="120" ht="22" customHeight="1" s="43">
+      <c r="A120" s="259" t="inlineStr">
+        <is>
+          <t>① 책상</t>
+        </is>
+      </c>
+      <c r="B120" s="145" t="inlineStr">
+        <is>
+          <t>작업대에 얇은 수건 → 그 위에 배경판.</t>
+        </is>
+      </c>
+      <c r="C120" s="145" t="inlineStr">
+        <is>
+          <t>수건이 유리 부딪히는 울림·잡음을 잡는다</t>
+        </is>
+      </c>
+      <c r="D120" s="145" t="n"/>
+    </row>
+    <row r="121" ht="47" customHeight="1" s="43">
+      <c r="A121" s="259" t="inlineStr">
+        <is>
+          <t>② 소품 배치</t>
+        </is>
+      </c>
+      <c r="B121" s="145" t="inlineStr">
+        <is>
+          <t>화면에 들어올 것만, 비커는 중앙, 원료 병은 라벨이 위를 보게 일렬. 첫 배치 사진대로(§6).</t>
+        </is>
+      </c>
+      <c r="C121" s="145" t="inlineStr">
+        <is>
+          <t>계정 톤의 일관성</t>
+        </is>
+      </c>
+      <c r="D121" s="145" t="n"/>
+    </row>
+    <row r="122" ht="34" customHeight="1" s="43">
+      <c r="A122" s="259" t="inlineStr">
+        <is>
+          <t>③ 거치대 + 폰</t>
+        </is>
+      </c>
+      <c r="B122" s="145" t="inlineStr">
+        <is>
+          <t>폰을 비커 바로 위 30~40cm, 세로로. 손이 들어올 여유를 둔다.</t>
+        </is>
+      </c>
+      <c r="C122" s="145" t="inlineStr">
+        <is>
+          <t>너무 가까우면 손이 잘린다</t>
+        </is>
+      </c>
+      <c r="D122" s="145" t="n"/>
+    </row>
+    <row r="123" ht="60" customHeight="1" s="43">
+      <c r="A123" s="259" t="inlineStr">
+        <is>
+          <t>④ 폰 설정 (처음 한 번)</t>
+        </is>
+      </c>
+      <c r="B123" s="145" t="inlineStr">
+        <is>
+          <t>동영상 1080p · 60fps(아이폰: 설정 → 카메라 → 비디오 녹화 / 갤럭시: 카메라 앱 설정) · 격자 표시 켜고 비커를 정중앙 칸에.</t>
+        </is>
+      </c>
+      <c r="C123" s="145" t="inlineStr">
+        <is>
+          <t>60fps면 나중에 슬로우 가능. 한 번 해두면 유지된다</t>
+        </is>
+      </c>
+      <c r="D123" s="145" t="n"/>
+    </row>
+    <row r="124" ht="47" customHeight="1" s="43">
+      <c r="A124" s="259" t="inlineStr">
+        <is>
+          <t>⑤ 초점·노출 잠금</t>
+        </is>
+      </c>
+      <c r="B124" s="145" t="inlineStr">
+        <is>
+          <t>촬영 화면에서 비커를 길게 누르기 → 'AE/AF 잠금'(아이폰) 또는 자물쇠 표시.</t>
+        </is>
+      </c>
+      <c r="C124" s="145" t="inlineStr">
+        <is>
+          <t>안 하면 손이 들어올 때마다 화면이 밝아졌다 어두워졌다 한다</t>
+        </is>
+      </c>
+      <c r="D124" s="145" t="n"/>
+    </row>
+    <row r="125" ht="47" customHeight="1" s="43">
+      <c r="A125" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 마이크</t>
+        </is>
+      </c>
+      <c r="B125" s="145" t="inlineStr">
+        <is>
+          <t>수신기를 폰에 꽂고, 핀(송신기)은 비커 옆 5~10cm 화면 밖에 집게로. 송신기 전원 확인.</t>
+        </is>
+      </c>
+      <c r="C125" s="145" t="inlineStr">
+        <is>
+          <t>잡음 크면 더 가깝게</t>
+        </is>
+      </c>
+      <c r="D125" s="145" t="n"/>
+    </row>
+    <row r="126" ht="34" customHeight="1" s="43">
+      <c r="A126" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 소음 · 알림 끄기</t>
+        </is>
+      </c>
+      <c r="B126" s="145" t="inlineStr">
+        <is>
+          <t>에어컨·냉장고·선풍기 끄기 · 방해금지(또는 비행기) 모드 · 렌즈 닦기.</t>
+        </is>
+      </c>
+      <c r="C126" s="145" t="inlineStr">
         <is>
           <t>알림음·뿌연 화면 방지</t>
         </is>
       </c>
-      <c r="D107" s="24" t="n"/>
-    </row>
-    <row r="108" ht="22" customHeight="1" s="43">
-      <c r="A108" s="26" t="inlineStr">
-        <is>
-          <t>소리 환경</t>
-        </is>
-      </c>
-      <c r="B108" s="24" t="inlineStr">
-        <is>
-          <t>에어컨·냉장고 끄기 · 작업대에 얇은 수건 깔기</t>
-        </is>
-      </c>
-      <c r="C108" s="24" t="inlineStr">
-        <is>
-          <t>테이블 울림·잡음 제거</t>
-        </is>
-      </c>
-      <c r="D108" s="24" t="n"/>
-    </row>
-    <row r="110" ht="22" customHeight="1" s="43">
-      <c r="A110" s="68" t="inlineStr">
-        <is>
-          <t>§12. 3주 연습 — 원료 아끼지 말고 물로 시작</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1" s="43">
-      <c r="A111" s="60" t="inlineStr">
+      <c r="D126" s="145" t="n"/>
+    </row>
+    <row r="127" ht="22" customHeight="1" s="43">
+      <c r="A127" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 테스트 10초</t>
+        </is>
+      </c>
+      <c r="B127" s="145" t="inlineStr">
+        <is>
+          <t>막대로 저어 찍고 이어폰으로 들어보기.</t>
+        </is>
+      </c>
+      <c r="C127" s="145" t="inlineStr">
+        <is>
+          <t>화면보다 소리 먼저 확인</t>
+        </is>
+      </c>
+      <c r="D127" s="145" t="n"/>
+    </row>
+    <row r="128" ht="28" customHeight="1" s="43">
+      <c r="A128" s="140" t="inlineStr">
+        <is>
+          <t>찍는 법</t>
+        </is>
+      </c>
+      <c r="B128" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C128" s="140" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="D128" s="258" t="n"/>
+    </row>
+    <row r="129" ht="34" customHeight="1" s="43">
+      <c r="A129" s="259" t="inlineStr">
+        <is>
+          <t>한 번 녹화 = 동작 하나</t>
+        </is>
+      </c>
+      <c r="B129" s="145" t="inlineStr">
+        <is>
+          <t>녹화 시작 → 2초 가만히 → 동작 3~5초 → 2초 가만히 → 정지.</t>
+        </is>
+      </c>
+      <c r="C129" s="145" t="inlineStr">
+        <is>
+          <t>앞뒤 2초는 편집에서 자를 여유</t>
+        </is>
+      </c>
+      <c r="D129" s="145" t="n"/>
+    </row>
+    <row r="130" ht="34" customHeight="1" s="43">
+      <c r="A130" s="259" t="inlineStr">
+        <is>
+          <t>실제 공정 순서대로</t>
+        </is>
+      </c>
+      <c r="B130" s="145" t="inlineStr">
+        <is>
+          <t>실험 순서 그대로 찍는다. 첫 1초 순서는 편집에서 바꾼다(§6 구성).</t>
+        </is>
+      </c>
+      <c r="C130" s="145" t="inlineStr">
+        <is>
+          <t>실험에 집중 — 추가 시간 0분</t>
+        </is>
+      </c>
+      <c r="D130" s="145" t="n"/>
+    </row>
+    <row r="131" ht="34" customHeight="1" s="43">
+      <c r="A131" s="259" t="inlineStr">
+        <is>
+          <t>★ 장면은 미리 녹화</t>
+        </is>
+      </c>
+      <c r="B131" s="145" t="inlineStr">
+        <is>
+          <t>중화·유화처럼 한 번뿐인 순간은 그 직전에 녹화를 켜두고, 가능하면 2~3번.</t>
+        </is>
+      </c>
+      <c r="C131" s="145" t="inlineStr">
+        <is>
+          <t>놓치면 다시 못 찍는다</t>
+        </is>
+      </c>
+      <c r="D131" s="145" t="n"/>
+    </row>
+    <row r="132" ht="22" customHeight="1" s="43">
+      <c r="A132" s="259" t="inlineStr">
+        <is>
+          <t>망쳐도 계속 찍기</t>
+        </is>
+      </c>
+      <c r="B132" s="145" t="inlineStr">
+        <is>
+          <t>분리·실패 배치도 그대로 찍어둔다.</t>
+        </is>
+      </c>
+      <c r="C132" s="145" t="inlineStr">
+        <is>
+          <t>실패담 = 콘텐츠(§3 소재 은행)</t>
+        </is>
+      </c>
+      <c r="D132" s="145" t="n"/>
+    </row>
+    <row r="133" ht="22" customHeight="1" s="43">
+      <c r="A133" s="259" t="inlineStr">
+        <is>
+          <t>분량</t>
+        </is>
+      </c>
+      <c r="B133" s="145" t="inlineStr">
+        <is>
+          <t>실험 30분에 클립 7~15개면 충분.</t>
+        </is>
+      </c>
+      <c r="C133" s="145" t="inlineStr">
+        <is>
+          <t>영상 2개(다음 주 분량)가 나온다</t>
+        </is>
+      </c>
+      <c r="D133" s="145" t="n"/>
+    </row>
+    <row r="134" ht="34" customHeight="1" s="43">
+      <c r="A134" s="79" t="inlineStr">
+        <is>
+          <t>이번 주 할 일 하나: 거치대 + 핀마이크 주문(폰 단자 확인) → 기다리는 동안 §13 계정 세팅 ①~④ → 도착한 첫 주말 물로 20분 촬영(§12 1주차).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1" s="43">
+      <c r="A136" s="257" t="inlineStr">
+        <is>
+          <t>§12. CapCut 편집 · 3주 연습 — 원료 아끼지 말고 물로 시작 (일요일 30분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1" s="43">
+      <c r="A137" s="140" t="inlineStr">
+        <is>
+          <t>편집 단계</t>
+        </is>
+      </c>
+      <c r="B137" s="140" t="inlineStr">
+        <is>
+          <t>하는 법</t>
+        </is>
+      </c>
+      <c r="C137" s="140" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D137" s="258" t="n"/>
+    </row>
+    <row r="138" ht="47" customHeight="1" s="43">
+      <c r="A138" s="259" t="inlineStr">
+        <is>
+          <t>① 새 프로젝트</t>
+        </is>
+      </c>
+      <c r="B138" s="145" t="inlineStr">
+        <is>
+          <t>CapCut(무료) → 새 프로젝트 → 토요일 클립을 공정 순서대로 모두 선택 → 추가.</t>
+        </is>
+      </c>
+      <c r="C138" s="145" t="inlineStr"/>
+      <c r="D138" s="145" t="n"/>
+    </row>
+    <row r="139" ht="22" customHeight="1" s="43">
+      <c r="A139" s="259" t="inlineStr">
+        <is>
+          <t>② 비율</t>
+        </is>
+      </c>
+      <c r="B139" s="145" t="inlineStr">
+        <is>
+          <t>하단 메뉴 '비율' → 9:16.</t>
+        </is>
+      </c>
+      <c r="C139" s="145" t="inlineStr">
+        <is>
+          <t>릴스·쇼츠·틱톡 공통</t>
+        </is>
+      </c>
+      <c r="D139" s="145" t="n"/>
+    </row>
+    <row r="140" ht="47" customHeight="1" s="43">
+      <c r="A140" s="259" t="inlineStr">
+        <is>
+          <t>③ 자르기 (분할)</t>
+        </is>
+      </c>
+      <c r="B140" s="145" t="inlineStr">
+        <is>
+          <t>클립을 누르고 동작 시작 지점에 흰 세로선 → '분할' → 앞 군더더기 선택 → 삭제. 끝도 같게.</t>
+        </is>
+      </c>
+      <c r="C140" s="145" t="inlineStr">
+        <is>
+          <t>한 컷 2~4초 — 다꾸 쇼츠의 리듬</t>
+        </is>
+      </c>
+      <c r="D140" s="145" t="n"/>
+    </row>
+    <row r="141" ht="34" customHeight="1" s="43">
+      <c r="A141" s="259" t="inlineStr">
+        <is>
+          <t>④ 첫 1초 옮기기</t>
+        </is>
+      </c>
+      <c r="B141" s="145" t="inlineStr">
+        <is>
+          <t>★ 장면 클립을 길게 눌러 맨 앞으로 드래그.</t>
+        </is>
+      </c>
+      <c r="C141" s="145" t="inlineStr">
+        <is>
+          <t>가장 중요한 한 단계</t>
+        </is>
+      </c>
+      <c r="D141" s="145" t="n"/>
+    </row>
+    <row r="142" ht="34" customHeight="1" s="43">
+      <c r="A142" s="259" t="inlineStr">
+        <is>
+          <t>⑤ 지루한 구간 빠르게</t>
+        </is>
+      </c>
+      <c r="B142" s="145" t="inlineStr">
+        <is>
+          <t>젓기처럼 긴 클립 → '속도' → '일반' → 1.3~1.5배.</t>
+        </is>
+      </c>
+      <c r="C142" s="145" t="inlineStr">
+        <is>
+          <t>2배를 넘기면 소리가 어색해진다</t>
+        </is>
+      </c>
+      <c r="D142" s="145" t="n"/>
+    </row>
+    <row r="143" ht="34" customHeight="1" s="43">
+      <c r="A143" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 전환 효과 없음</t>
+        </is>
+      </c>
+      <c r="B143" s="145" t="inlineStr">
+        <is>
+          <t>클립 사이 작은 흰 네모(전환)는 건드리지 않는다.</t>
+        </is>
+      </c>
+      <c r="C143" s="145" t="inlineStr">
+        <is>
+          <t>하드컷이 ASMR에 맞다</t>
+        </is>
+      </c>
+      <c r="D143" s="145" t="n"/>
+    </row>
+    <row r="144" ht="47" customHeight="1" s="43">
+      <c r="A144" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 소리 다듬기</t>
+        </is>
+      </c>
+      <c r="B144" s="145" t="inlineStr">
+        <is>
+          <t>클립 선택 → '음량'으로 클립끼리 크기 맞추기 → '노이즈 감소' 켜기. 배경음악 넣지 않기.</t>
+        </is>
+      </c>
+      <c r="C144" s="145" t="inlineStr">
+        <is>
+          <t>편집에서 제일 시간 쓸 곳</t>
+        </is>
+      </c>
+      <c r="D144" s="145" t="n"/>
+    </row>
+    <row r="145" ht="47" customHeight="1" s="43">
+      <c r="A145" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 필터 하나 고정</t>
+        </is>
+      </c>
+      <c r="B145" s="145" t="inlineStr">
+        <is>
+          <t>'필터' → 밝고 담백한 것 하나(강도 30~50%) → 모두에 적용. 매번 같은 필터.</t>
+        </is>
+      </c>
+      <c r="C145" s="145" t="inlineStr">
+        <is>
+          <t>계정 톤</t>
+        </is>
+      </c>
+      <c r="D145" s="145" t="n"/>
+    </row>
+    <row r="146" ht="73" customHeight="1" s="43">
+      <c r="A146" s="259" t="inlineStr">
+        <is>
+          <t>⑨ 자막 1~2개</t>
+        </is>
+      </c>
+      <c r="B146" s="145" t="inlineStr">
+        <is>
+          <t>'텍스트 추가' → 원료명·%만(예: '카보머 0.5%'), 작고 깔끔한 폰트 · 흰 글씨 + 얇은 그림자. 마지막 컷에 '출시 알림은 프로필 링크'. 위트 한 줄도 여기서(§6).</t>
+        </is>
+      </c>
+      <c r="C146" s="145" t="inlineStr">
+        <is>
+          <t>화면 중간 높이에 — 맨 아래 20%·오른쪽 끝은 좋아요·캡션 버튼에 가린다</t>
+        </is>
+      </c>
+      <c r="D146" s="145" t="n"/>
+    </row>
+    <row r="147" ht="34" customHeight="1" s="43">
+      <c r="A147" s="259" t="inlineStr">
+        <is>
+          <t>⑩ CapCut 엔딩 삭제</t>
+        </is>
+      </c>
+      <c r="B147" s="145" t="inlineStr">
+        <is>
+          <t>타임라인 맨 끝에 CapCut 로고 클립이 붙어 있으면 선택 → 삭제.</t>
+        </is>
+      </c>
+      <c r="C147" s="145" t="inlineStr">
+        <is>
+          <t>워터마크 없는 원본(§13 규칙)</t>
+        </is>
+      </c>
+      <c r="D147" s="145" t="n"/>
+    </row>
+    <row r="148" ht="47" customHeight="1" s="43">
+      <c r="A148" s="259" t="inlineStr">
+        <is>
+          <t>⑪ 내보내기</t>
+        </is>
+      </c>
+      <c r="B148" s="145" t="inlineStr">
+        <is>
+          <t>오른쪽 위 해상도 → 1080p · 30 또는 60fps → 내보내기 → 갤러리 저장.</t>
+        </is>
+      </c>
+      <c r="C148" s="145" t="inlineStr">
+        <is>
+          <t>이 원본 하나를 3채널에 올린다</t>
+        </is>
+      </c>
+      <c r="D148" s="145" t="n"/>
+    </row>
+    <row r="149" ht="34" customHeight="1" s="43">
+      <c r="A149" s="259" t="inlineStr">
+        <is>
+          <t>⑫ 다음 주 재사용</t>
+        </is>
+      </c>
+      <c r="B149" s="145" t="inlineStr">
+        <is>
+          <t>이 프로젝트를 복제해 클립만 바꾸면 필터·자막 스타일이 그대로.</t>
+        </is>
+      </c>
+      <c r="C149" s="145" t="inlineStr">
+        <is>
+          <t>두 번째부터 15분</t>
+        </is>
+      </c>
+      <c r="D149" s="145" t="n"/>
+    </row>
+    <row r="150" ht="30" customHeight="1" s="43">
+      <c r="A150" s="79" t="inlineStr">
+        <is>
+          <t>완성 기준 세 가지: 15~30초 · 첫 1초가 가장 만족스러운 장면 · 소리가 또렷함. 이것만 되면 올린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28" customHeight="1" s="43">
+      <c r="A151" s="140" t="inlineStr">
         <is>
           <t>주차</t>
         </is>
       </c>
-      <c r="B111" s="60" t="inlineStr">
+      <c r="B151" s="140" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
-      <c r="C111" s="60" t="inlineStr">
+      <c r="C151" s="140" t="inlineStr">
         <is>
           <t>통과 기준</t>
         </is>
       </c>
-      <c r="D111" s="27" t="n"/>
-    </row>
-    <row r="112" ht="66" customHeight="1" s="43">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="D151" s="258" t="n"/>
+    </row>
+    <row r="152" ht="60" customHeight="1" s="43">
+      <c r="A152" s="259" t="inlineStr">
         <is>
           <t>1주차 · 촬영만 (20분)</t>
         </is>
       </c>
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>물 따르기 · 막대로 젓기 · 저울에 한 방울씩 떨어뜨리기를 같은 장면으로 거리만 바꿔 3번 찍기.
-컷 규칙: 한 컷 = 동작 하나, 3~5초, 동작 앞뒤 2초 여유.</t>
-        </is>
-      </c>
-      <c r="C112" s="24" t="inlineStr">
-        <is>
-          <t>찍고 바로 이어폰으로 들어보기 — 화면보다 소리 먼저 확인</t>
-        </is>
-      </c>
-      <c r="D112" s="24" t="n"/>
-    </row>
-    <row r="113" ht="96" customHeight="1" s="43">
-      <c r="A113" s="26" t="inlineStr">
+      <c r="B152" s="145" t="inlineStr">
+        <is>
+          <t>물 따르기 · 막대로 젓기 · 저울에 한 방울씩 떨어뜨리기를 §11 세팅 순서대로, 같은 장면을 거리만 바꿔 3번 찍기.</t>
+        </is>
+      </c>
+      <c r="C152" s="145" t="inlineStr">
+        <is>
+          <t>찍고 바로 이어폰으로 들어보기 — 화면보다 소리 먼저</t>
+        </is>
+      </c>
+      <c r="D152" s="145" t="n"/>
+    </row>
+    <row r="153" ht="34" customHeight="1" s="43">
+      <c r="A153" s="259" t="inlineStr">
         <is>
           <t>2주차 · CapCut 편집 (30분)</t>
         </is>
       </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>1주차 영상으로 15초 하나 완성:
-① 새 프로젝트 · 9:16 ② 분할로 앞뒤 군더더기 자르기 ③ 노이즈 감소 켜고 볼륨 맞추기 ④ 제일 좋은 소리를 첫 1초로 ⑤ 자막 1~2개(원료명·%) + 마지막 '출시 알림은 프로필 링크' ⑥ 1080p로 내보내기</t>
-        </is>
-      </c>
-      <c r="C113" s="24" t="inlineStr">
+      <c r="B153" s="145" t="inlineStr">
+        <is>
+          <t>1주차 영상으로 위 편집 단계 ①~⑪ 따라 15초 하나 완성.</t>
+        </is>
+      </c>
+      <c r="C153" s="145" t="inlineStr">
         <is>
           <t>15초 1개 완성. 이번 주는 안 올려도 OK</t>
         </is>
       </c>
-      <c r="D113" s="24" t="n"/>
-    </row>
-    <row r="114" ht="51" customHeight="1" s="43">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="D153" s="145" t="n"/>
+    </row>
+    <row r="154" ht="60" customHeight="1" s="43">
+      <c r="A154" s="259" t="inlineStr">
         <is>
           <t>3주차 · 첫 업로드</t>
         </is>
       </c>
-      <c r="B114" s="24" t="inlineStr">
-        <is>
-          <t>주말 키트의 잔탄검 젤 만들기를 그대로 찍어 첫 영상으로 업로드. 카보머가 오면 다음은 '중화되는 순간'(§7 ★).</t>
-        </is>
-      </c>
-      <c r="C114" s="24" t="inlineStr">
+      <c r="B154" s="145" t="inlineStr">
+        <is>
+          <t>주말 키트의 잔탄검 젤 만들기를 콘티(§7)대로 찍어 §13 업로드 방법으로 첫 영상. 카보머가 오면 다음은 '중화되는 순간'(★).</t>
+        </is>
+      </c>
+      <c r="C154" s="145" t="inlineStr">
         <is>
           <t>완벽 ❌, 올리기 ⭕. 10번째가 1번째보다 나으면 성공</t>
         </is>
       </c>
-      <c r="D114" s="24" t="n"/>
-    </row>
-    <row r="115" ht="28" customHeight="1" s="43">
-      <c r="A115" s="60" t="inlineStr">
+      <c r="D154" s="145" t="n"/>
+    </row>
+    <row r="155" ht="28" customHeight="1" s="43">
+      <c r="A155" s="140" t="inlineStr">
         <is>
           <t>흔한 실수</t>
         </is>
       </c>
-      <c r="B115" s="60" t="inlineStr">
+      <c r="B155" s="140" t="inlineStr">
         <is>
           <t>대신 이렇게</t>
         </is>
       </c>
-      <c r="C115" s="27" t="n"/>
-      <c r="D115" s="27" t="n"/>
-    </row>
-    <row r="116" ht="22" customHeight="1" s="43">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="C155" s="140" t="inlineStr"/>
+      <c r="D155" s="258" t="n"/>
+    </row>
+    <row r="156" ht="34" customHeight="1" s="43">
+      <c r="A156" s="259" t="inlineStr">
         <is>
           <t>장비부터 많이 사기</t>
         </is>
       </c>
-      <c r="B116" s="24" t="inlineStr">
+      <c r="B156" s="145" t="inlineStr">
         <is>
           <t>거치대 + 마이크로 10개 찍어본 뒤 판단</t>
         </is>
       </c>
-      <c r="C116" s="24" t="n"/>
-      <c r="D116" s="24" t="n"/>
-    </row>
-    <row r="117" ht="36" customHeight="1" s="43">
-      <c r="A117" s="26" t="inlineStr">
+      <c r="C156" s="145" t="inlineStr"/>
+      <c r="D156" s="145" t="n"/>
+    </row>
+    <row r="157" ht="34" customHeight="1" s="43">
+      <c r="A157" s="259" t="inlineStr">
         <is>
           <t>편집 화려하게 하기</t>
         </is>
       </c>
-      <c r="B117" s="24" t="inlineStr">
+      <c r="B157" s="145" t="inlineStr">
         <is>
           <t>이 포맷은 편집이 적을수록 좋다 — 소리와 첫 1초가 승부</t>
         </is>
       </c>
-      <c r="C117" s="24" t="n"/>
-      <c r="D117" s="24" t="n"/>
-    </row>
-    <row r="118" ht="22" customHeight="1" s="43">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="C157" s="145" t="inlineStr"/>
+      <c r="D157" s="145" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1" s="43">
+      <c r="A158" s="259" t="inlineStr">
         <is>
           <t>앵글 매번 바꾸기</t>
         </is>
       </c>
-      <c r="B118" s="24" t="inlineStr">
+      <c r="B158" s="145" t="inlineStr">
         <is>
           <t>같은 세팅 반복 = 계정의 화면 톤</t>
         </is>
       </c>
-      <c r="C118" s="24" t="n"/>
-      <c r="D118" s="24" t="n"/>
-    </row>
-    <row r="119" ht="30" customHeight="1" s="43">
-      <c r="A119" s="79" t="inlineStr">
-        <is>
-          <t>이번 주 할 일 하나: 거치대 + 핀마이크 주문 → 도착하면 첫 주말 물로 20분 촬영(1주차).</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1" s="43">
-      <c r="A121" s="68" t="inlineStr">
-        <is>
-          <t>§13. 채널 운영 — 영상은 한 번 만들어 3채널, 블로그는 역할을 나눠 2곳, 소통은 인스타로</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="28" customHeight="1" s="43">
-      <c r="A122" s="60" t="inlineStr">
+      <c r="C158" s="145" t="inlineStr"/>
+      <c r="D158" s="145" t="n"/>
+    </row>
+    <row r="159" ht="22" customHeight="1" s="43">
+      <c r="A159" s="259" t="inlineStr">
+        <is>
+          <t>1~2개 보고 포기</t>
+        </is>
+      </c>
+      <c r="B159" s="145" t="inlineStr">
+        <is>
+          <t>4주(8개)는 보고 판단(§5)</t>
+        </is>
+      </c>
+      <c r="C159" s="145" t="inlineStr"/>
+      <c r="D159" s="145" t="n"/>
+    </row>
+    <row r="161" ht="22" customHeight="1" s="43">
+      <c r="A161" s="257" t="inlineStr">
+        <is>
+          <t>§13. 채널 운영 · 계정 세팅 · 업로드 — 영상은 한 번 만들어 3채널, 블로그는 역할을 나눠 2곳, 소통은 인스타로</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="28" customHeight="1" s="43">
+      <c r="A162" s="140" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B122" s="60" t="inlineStr">
+      <c r="B162" s="140" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="C122" s="60" t="inlineStr">
+      <c r="C162" s="140" t="inlineStr">
         <is>
           <t>운영 규칙</t>
         </is>
       </c>
-      <c r="D122" s="27" t="n"/>
-    </row>
-    <row r="123" ht="36" customHeight="1" s="43">
-      <c r="A123" s="26" t="inlineStr">
+      <c r="D162" s="258" t="n"/>
+    </row>
+    <row r="163" ht="34" customHeight="1" s="43">
+      <c r="A163" s="259" t="inlineStr">
         <is>
           <t>인스타 릴스</t>
         </is>
       </c>
-      <c r="B123" s="24" t="inlineStr">
+      <c r="B163" s="145" t="inlineStr">
         <is>
           <t>집: 단골·팬덤, DM, 투표, 대기자 링크(§8)</t>
         </is>
       </c>
-      <c r="C123" s="24" t="inlineStr">
+      <c r="C163" s="145" t="inlineStr">
         <is>
           <t>24시간 안에 직접 답장(출퇴근 2번). 소통은 여기로 모은다</t>
         </is>
       </c>
-      <c r="D123" s="24" t="n"/>
-    </row>
-    <row r="124" ht="36" customHeight="1" s="43">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="D163" s="145" t="n"/>
+    </row>
+    <row r="164" ht="34" customHeight="1" s="43">
+      <c r="A164" s="259" t="inlineStr">
         <is>
           <t>유튜브 쇼츠</t>
         </is>
       </c>
-      <c r="B124" s="24" t="inlineStr">
+      <c r="B164" s="145" t="inlineStr">
         <is>
           <t>검색: 유튜브·구글 검색에 오래 남아 몇 달 뒤에도 유입</t>
         </is>
       </c>
-      <c r="C124" s="24" t="inlineStr">
+      <c r="C164" s="145" t="inlineStr">
         <is>
           <t>제목·설명에 ①·②층 키워드. 댓글은 짧게 + '자세한 이야기는 인스타'</t>
         </is>
       </c>
-      <c r="D124" s="24" t="n"/>
-    </row>
-    <row r="125" ht="36" customHeight="1" s="43">
-      <c r="A125" s="26" t="inlineStr">
+      <c r="D164" s="145" t="n"/>
+    </row>
+    <row r="165" ht="34" customHeight="1" s="43">
+      <c r="A165" s="259" t="inlineStr">
         <is>
           <t>틱톡</t>
         </is>
       </c>
-      <c r="B125" s="24" t="inlineStr">
+      <c r="B165" s="145" t="inlineStr">
         <is>
           <t>발견: 처음 보는 사람에게 퍼지는 곳 · 첫 1초 반응 테스트</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
+      <c r="C165" s="145" t="inlineStr">
         <is>
           <t>댓글은 짧게 + 인스타로 연결</t>
         </is>
       </c>
-      <c r="D125" s="24" t="n"/>
-    </row>
-    <row r="126" ht="36" customHeight="1" s="43">
-      <c r="A126" s="26" t="inlineStr">
+      <c r="D165" s="145" t="n"/>
+    </row>
+    <row r="166" ht="34" customHeight="1" s="43">
+      <c r="A166" s="259" t="inlineStr">
         <is>
           <t>네이버 블로그</t>
         </is>
       </c>
-      <c r="B126" s="24" t="inlineStr">
+      <c r="B166" s="145" t="inlineStr">
         <is>
           <t>네이버 검색: 경험·일상 톤 — 고민 해결·개발일지(§9)</t>
         </is>
       </c>
-      <c r="C126" s="24" t="inlineStr">
+      <c r="C166" s="145" t="inlineStr">
         <is>
           <t>주 1편</t>
         </is>
       </c>
-      <c r="D126" s="24" t="n"/>
-    </row>
-    <row r="127" ht="51" customHeight="1" s="43">
-      <c r="A127" s="26" t="inlineStr">
+      <c r="D166" s="145" t="n"/>
+    </row>
+    <row r="167" ht="60" customHeight="1" s="43">
+      <c r="A167" s="259" t="inlineStr">
         <is>
           <t>브랜드 사이트</t>
         </is>
       </c>
-      <c r="B127" s="24" t="inlineStr">
+      <c r="B167" s="145" t="inlineStr">
         <is>
           <t>구글 + 네이버 웹문서: 정리형 가이드 '성분 사전'(예: 판테놀 총정리 — 역할·농도·함께 쓰는 성분). 재료 = 시험대비 원료맵</t>
         </is>
       </c>
-      <c r="C127" s="24" t="inlineStr">
+      <c r="C167" s="145" t="inlineStr">
         <is>
           <t>월 2편(새 페이지 또는 기존 페이지 보완). 네이버 루틴이 잡힌 1~2개월 뒤 시작</t>
         </is>
       </c>
-      <c r="D127" s="24" t="n"/>
-    </row>
-    <row r="128" ht="28" customHeight="1" s="43">
-      <c r="A128" s="60" t="inlineStr">
+      <c r="D167" s="145" t="n"/>
+    </row>
+    <row r="168" ht="28" customHeight="1" s="43">
+      <c r="A168" s="140" t="inlineStr">
+        <is>
+          <t>계정 세팅 (하루 저녁 1시간)</t>
+        </is>
+      </c>
+      <c r="B168" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C168" s="140" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D168" s="258" t="n"/>
+    </row>
+    <row r="169" ht="60" customHeight="1" s="43">
+      <c r="A169" s="259" t="inlineStr">
+        <is>
+          <t>① 이름 정하기</t>
+        </is>
+      </c>
+      <c r="B169" s="145" t="inlineStr">
+        <is>
+          <t>3채널 모두 같은 아이디(예: @dadogi.lab). 인스타·유튜브·틱톡에서 각각 검색해 세 곳 다 비어 있는 이름으로.</t>
+        </is>
+      </c>
+      <c r="C169" s="145" t="inlineStr">
+        <is>
+          <t>찾아오는 사람이 헷갈리지 않게</t>
+        </is>
+      </c>
+      <c r="D169" s="145" t="n"/>
+    </row>
+    <row r="170" ht="34" customHeight="1" s="43">
+      <c r="A170" s="259" t="inlineStr">
+        <is>
+          <t>② 브랜드 전용 이메일</t>
+        </is>
+      </c>
+      <c r="B170" s="145" t="inlineStr">
+        <is>
+          <t>새 구글 계정을 하나 만들어 3채널 모두 이걸로 가입. 개인 계정과 분리.</t>
+        </is>
+      </c>
+      <c r="C170" s="145" t="inlineStr">
+        <is>
+          <t>나중에 사업자로 넘길 때 편하다</t>
+        </is>
+      </c>
+      <c r="D170" s="145" t="n"/>
+    </row>
+    <row r="171" ht="73" customHeight="1" s="43">
+      <c r="A171" s="259" t="inlineStr">
+        <is>
+          <t>③ 인스타 개설 · 프로페셔널 전환</t>
+        </is>
+      </c>
+      <c r="B171" s="145" t="inlineStr">
+        <is>
+          <t>프로필 → 상단 아이디 옆 ▼ → 계정 추가 → 새 계정 만들기(개인 계정과 한 폰에서 전환). 설정 → 계정 유형 및 도구 → 프로페셔널 계정으로 전환 → '크리에이터'.</t>
+        </is>
+      </c>
+      <c r="C171" s="145" t="inlineStr">
+        <is>
+          <t>조회·저장·시청 시간 통계가 열린다</t>
+        </is>
+      </c>
+      <c r="D171" s="145" t="n"/>
+    </row>
+    <row r="172" ht="60" customHeight="1" s="43">
+      <c r="A172" s="259" t="inlineStr">
+        <is>
+          <t>④ 인스타 프로필</t>
+        </is>
+      </c>
+      <c r="B172" s="145" t="inlineStr">
+        <is>
+          <t>사진(로고 없으면 완성 용기 탑뷰) · 이름 '다도기 | 지성·민감 진정 크림 개발 중' · 소개·링크는 §8 그대로(링크 = 대기자 폼, 상점 ❌).</t>
+        </is>
+      </c>
+      <c r="C172" s="145" t="inlineStr">
+        <is>
+          <t>누구를 위한 무엇인지 + 할 행동 하나</t>
+        </is>
+      </c>
+      <c r="D172" s="145" t="n"/>
+    </row>
+    <row r="173" ht="22" customHeight="1" s="43">
+      <c r="A173" s="259" t="inlineStr">
+        <is>
+          <t>⑤ 2단계 인증</t>
+        </is>
+      </c>
+      <c r="B173" s="145" t="inlineStr">
+        <is>
+          <t>인스타·구글·틱톡 모두 켜기.</t>
+        </is>
+      </c>
+      <c r="C173" s="145" t="inlineStr">
+        <is>
+          <t>해킹당하면 2년이 날아간다</t>
+        </is>
+      </c>
+      <c r="D173" s="145" t="n"/>
+    </row>
+    <row r="174" ht="73" customHeight="1" s="43">
+      <c r="A174" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 유튜브 채널</t>
+        </is>
+      </c>
+      <c r="B174" s="145" t="inlineStr">
+        <is>
+          <t>같은 구글 계정으로 유튜브 앱 → 프로필 → 채널 만들기(이름 '다도기', 핸들 통일). PC YouTube Studio → 맞춤설정 → 설명에 ①·②층 키워드(§9).</t>
+        </is>
+      </c>
+      <c r="C174" s="145" t="inlineStr">
+        <is>
+          <t>쇼츠는 검색에 오래 남는다</t>
+        </is>
+      </c>
+      <c r="D174" s="145" t="n"/>
+    </row>
+    <row r="175" ht="47" customHeight="1" s="43">
+      <c r="A175" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 틱톡</t>
+        </is>
+      </c>
+      <c r="B175" s="145" t="inlineStr">
+        <is>
+          <t>같은 이메일로 가입 → 아이디 통일 → 소개는 인스타와 같게. 링크 조건은 아래 규칙 참고.</t>
+        </is>
+      </c>
+      <c r="C175" s="145" t="inlineStr"/>
+      <c r="D175" s="145" t="n"/>
+    </row>
+    <row r="176" ht="47" customHeight="1" s="43">
+      <c r="A176" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 새 계정 길들이기 (3~5일)</t>
+        </is>
+      </c>
+      <c r="B176" s="145" t="inlineStr">
+        <is>
+          <t>새 계정으로 하루 10분 다꾸 ASMR·화장품 만들기·크림 ASMR 쇼츠를 보고, 좋은 건 저장 → 컬렉션 '참고'.</t>
+        </is>
+      </c>
+      <c r="C176" s="145" t="inlineStr">
+        <is>
+          <t>피드가 이 장르로 채워지고, 저장한 영상 = 스와이프 파일</t>
+        </is>
+      </c>
+      <c r="D176" s="145" t="n"/>
+    </row>
+    <row r="177" ht="28" customHeight="1" s="43">
+      <c r="A177" s="140" t="inlineStr">
+        <is>
+          <t>업로드 (영상 1개 · 3채널 15분)</t>
+        </is>
+      </c>
+      <c r="B177" s="140" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="C177" s="140" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D177" s="258" t="n"/>
+    </row>
+    <row r="178" ht="86" customHeight="1" s="43">
+      <c r="A178" s="259" t="inlineStr">
+        <is>
+          <t>캡션 (한 번 써서 3곳에)</t>
+        </is>
+      </c>
+      <c r="B178" s="145" t="inlineStr">
+        <is>
+          <t>첫 줄 = 장면 한 줄(예: '카보머가 젤리가 되는 순간 🫧') / 둘째 줄 = 무엇을 만드는 중인지 / '출시 알림은 프로필 링크에서' / 해시태그 3~5개(#화장품만들기 #ASMR #지성피부 #홈랩 #카보머).</t>
+        </is>
+      </c>
+      <c r="C178" s="145" t="inlineStr">
+        <is>
+          <t>효능 표현 금지('여드름 개선' '진정 효과 입증' ❌) — 과정·질감만 말한다(수요검증 §3)</t>
+        </is>
+      </c>
+      <c r="D178" s="145" t="n"/>
+    </row>
+    <row r="179" ht="60" customHeight="1" s="43">
+      <c r="A179" s="259" t="inlineStr">
+        <is>
+          <t>인스타 릴스</t>
+        </is>
+      </c>
+      <c r="B179" s="145" t="inlineStr">
+        <is>
+          <t>+ → 릴스 → 영상 선택 → 커버 편집(완성 용기나 ★ 장면) → 캡션 → 고급 설정 → 예약(화·금 저녁 7~9시) · '프로필 그리드에 표시' 켜기.</t>
+        </is>
+      </c>
+      <c r="C179" s="145" t="inlineStr">
+        <is>
+          <t>커버 = 프로필 격자의 얼굴. 매번 비슷한 톤으로</t>
+        </is>
+      </c>
+      <c r="D179" s="145" t="n"/>
+    </row>
+    <row r="180" ht="73" customHeight="1" s="43">
+      <c r="A180" s="259" t="inlineStr">
+        <is>
+          <t>유튜브 쇼츠</t>
+        </is>
+      </c>
+      <c r="B180" s="145" t="inlineStr">
+        <is>
+          <t>유튜브 앱 + → Shorts → 갤러리에서 영상 선택 → 제목(키워드 앞에, 예: '카보머 중화 ASMR | 지성 피부 진정 크림 만들기') → 공개 범위 → 예약.</t>
+        </is>
+      </c>
+      <c r="C180" s="145" t="inlineStr">
+        <is>
+          <t>설명은 PC YouTube Studio에서 나중에 보완 OK</t>
+        </is>
+      </c>
+      <c r="D180" s="145" t="n"/>
+    </row>
+    <row r="181" ht="47" customHeight="1" s="43">
+      <c r="A181" s="259" t="inlineStr">
+        <is>
+          <t>틱톡</t>
+        </is>
+      </c>
+      <c r="B181" s="145" t="inlineStr">
+        <is>
+          <t>+ → 업로드 → 영상 선택 → 캡션 · 커버 → 게시(앱에 예약이 없으면 화·금 저녁에 직접, 1분).</t>
+        </is>
+      </c>
+      <c r="C181" s="145" t="inlineStr"/>
+      <c r="D181" s="145" t="n"/>
+    </row>
+    <row r="182" ht="73" customHeight="1" s="43">
+      <c r="A182" s="259" t="inlineStr">
+        <is>
+          <t>올린 뒤</t>
+        </is>
+      </c>
+      <c r="B182" s="145" t="inlineStr">
+        <is>
+          <t>첫 1~2시간 댓글엔 바로 답글. 48시간 뒤 수요검증 §4 로그에 한 줄 — 볼 숫자: 평균 시청 시간(끝까지 본 비율) · 저장 · 공유 · '어디서 사요?' 댓글·DM.</t>
+        </is>
+      </c>
+      <c r="C182" s="145" t="inlineStr">
+        <is>
+          <t>좋아요·조회수는 참고만. 판단은 4주(8개) 뒤(§5)</t>
+        </is>
+      </c>
+      <c r="D182" s="145" t="n"/>
+    </row>
+    <row r="183" ht="30" customHeight="1" s="43">
+      <c r="A183" s="79" t="inlineStr">
+        <is>
+          <t>메뉴 이름은 앱 업데이트로 조금씩 바뀐다 — 안 보이면 '+ 누르고 업로드'가 기본 흐름이라는 것만 기억.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="28" customHeight="1" s="43">
+      <c r="A184" s="140" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
-      <c r="B128" s="60" t="inlineStr">
+      <c r="B184" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C128" s="60" t="inlineStr">
+      <c r="C184" s="140" t="inlineStr">
         <is>
           <t>왜</t>
         </is>
       </c>
-      <c r="D128" s="27" t="n"/>
-    </row>
-    <row r="129" ht="36" customHeight="1" s="43">
-      <c r="A129" s="26" t="inlineStr">
+      <c r="D184" s="258" t="n"/>
+    </row>
+    <row r="185" ht="34" customHeight="1" s="43">
+      <c r="A185" s="259" t="inlineStr">
         <is>
           <t>원본 업로드</t>
         </is>
       </c>
-      <c r="B129" s="24" t="inlineStr">
+      <c r="B185" s="145" t="inlineStr">
         <is>
           <t>CapCut에서 내보낸 워터마크 없는 원본을 채널마다 따로 올린다.</t>
         </is>
       </c>
-      <c r="C129" s="24" t="inlineStr">
+      <c r="C185" s="145" t="inlineStr">
         <is>
           <t>다른 앱 로고가 박힌 재업로드는 노출이 준다</t>
         </is>
       </c>
-      <c r="D129" s="24" t="n"/>
-    </row>
-    <row r="130" ht="36" customHeight="1" s="43">
-      <c r="A130" s="26" t="inlineStr">
+      <c r="D185" s="145" t="n"/>
+    </row>
+    <row r="186" ht="47" customHeight="1" s="43">
+      <c r="A186" s="259" t="inlineStr">
         <is>
           <t>블로그 중복 금지</t>
         </is>
       </c>
-      <c r="B130" s="24" t="inlineStr">
+      <c r="B186" s="145" t="inlineStr">
         <is>
           <t>같은 글 복사 ❌. 같은 주제라도 구조를 다시 짠다: 네이버 = '써본 이야기' / 사이트 = '총정리'.</t>
         </is>
       </c>
-      <c r="C130" s="24" t="inlineStr">
+      <c r="C186" s="145" t="inlineStr">
         <is>
           <t>유사 문서로 걸러져 검색 누락·블로그 평가 하락 위험 — 노력 3배, 효과 1배</t>
         </is>
       </c>
-      <c r="D130" s="24" t="n"/>
-    </row>
-    <row r="131" ht="66" customHeight="1" s="43">
-      <c r="A131" s="26" t="inlineStr">
+      <c r="D186" s="145" t="n"/>
+    </row>
+    <row r="187" ht="73" customHeight="1" s="43">
+      <c r="A187" s="259" t="inlineStr">
         <is>
           <t>브랜드 도메인</t>
         </is>
       </c>
-      <c r="B131" s="24" t="inlineStr">
+      <c r="B187" s="145" t="inlineStr">
         <is>
           <t>도메인 구매 → 사이트 빌더(아임웹·워드프레스 등) 연결 → 구글 서치콘솔 + 네이버 서치어드바이저 등록(반나절). 부담되면 티스토리 + 내 도메인 연결이 중간안.</t>
         </is>
       </c>
-      <c r="C131" s="24" t="inlineStr">
+      <c r="C187" s="145" t="inlineStr">
         <is>
           <t>나중에 자사몰과 같은 도메인 → 2년간 쌓은 검색 신뢰가 상점으로 이어진다. 플랫폼 정책이 바뀌어도 남는다</t>
         </is>
       </c>
-      <c r="D131" s="24" t="n"/>
-    </row>
-    <row r="132" ht="36" customHeight="1" s="43">
-      <c r="A132" s="26" t="inlineStr">
+      <c r="D187" s="145" t="n"/>
+    </row>
+    <row r="188" ht="47" customHeight="1" s="43">
+      <c r="A188" s="259" t="inlineStr">
         <is>
           <t>링크 조건</t>
         </is>
       </c>
-      <c r="B132" s="24" t="inlineStr">
+      <c r="B188" s="145" t="inlineStr">
         <is>
           <t>틱톡·쇼츠는 링크에 팔로워 수·계정 유형 조건이 있거나 클릭이 제한될 수 있다 — 개설할 때 확인.</t>
         </is>
       </c>
-      <c r="C132" s="24" t="inlineStr">
+      <c r="C188" s="145" t="inlineStr">
         <is>
           <t>대기자 유입의 주 경로는 인스타 프로필 링크·블로그</t>
         </is>
       </c>
-      <c r="D132" s="24" t="n"/>
-    </row>
-    <row r="133" ht="36" customHeight="1" s="43">
-      <c r="A133" s="26" t="inlineStr">
+      <c r="D188" s="145" t="n"/>
+    </row>
+    <row r="189" ht="34" customHeight="1" s="43">
+      <c r="A189" s="259" t="inlineStr">
         <is>
           <t>유입 경로 측정</t>
         </is>
       </c>
-      <c r="B133" s="24" t="inlineStr">
+      <c r="B189" s="145" t="inlineStr">
         <is>
           <t>대기자 폼에 '어디서 보고 오셨나요?' 항목, 또는 채널별로 다른 링크.</t>
         </is>
       </c>
-      <c r="C133" s="24" t="inlineStr">
+      <c r="C189" s="145" t="inlineStr">
         <is>
           <t>6개월 뒤 채널 정리를 감이 아니라 숫자로</t>
         </is>
       </c>
-      <c r="D133" s="24" t="n"/>
-    </row>
-    <row r="134" ht="36" customHeight="1" s="43">
-      <c r="A134" s="26" t="inlineStr">
+      <c r="D189" s="145" t="n"/>
+    </row>
+    <row r="190" ht="34" customHeight="1" s="43">
+      <c r="A190" s="259" t="inlineStr">
         <is>
           <t>규정</t>
         </is>
       </c>
-      <c r="B134" s="24" t="inlineStr">
+      <c r="B190" s="145" t="inlineStr">
         <is>
           <t>모든 채널에 같은 표시·광고 규칙(수요검증 §3). 판매 후 협찬·광고는 표기.</t>
         </is>
       </c>
-      <c r="C134" s="24" t="inlineStr">
+      <c r="C190" s="145" t="inlineStr">
         <is>
           <t>채널마다 기준이 다르면 실수가 난다</t>
         </is>
       </c>
-      <c r="D134" s="24" t="n"/>
-    </row>
-    <row r="135" ht="28" customHeight="1" s="43">
-      <c r="A135" s="60" t="inlineStr">
+      <c r="D190" s="145" t="n"/>
+    </row>
+    <row r="191" ht="28" customHeight="1" s="43">
+      <c r="A191" s="140" t="inlineStr">
         <is>
           <t>시기</t>
         </is>
       </c>
-      <c r="B135" s="60" t="inlineStr">
+      <c r="B191" s="140" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
-      <c r="C135" s="60" t="inlineStr">
+      <c r="C191" s="140" t="inlineStr">
         <is>
           <t>판단 기준</t>
         </is>
       </c>
-      <c r="D135" s="27" t="n"/>
-    </row>
-    <row r="136" ht="36" customHeight="1" s="43">
-      <c r="A136" s="26" t="inlineStr">
+      <c r="D191" s="258" t="n"/>
+    </row>
+    <row r="192" ht="47" customHeight="1" s="43">
+      <c r="A192" s="259" t="inlineStr">
         <is>
           <t>지금</t>
         </is>
       </c>
-      <c r="B136" s="24" t="inlineStr">
+      <c r="B192" s="145" t="inlineStr">
         <is>
           <t>영상 3채널 동시 시작(같은 영상, 영상당 +10~15분) + 네이버 블로그(§9 시작 조건대로).</t>
         </is>
       </c>
-      <c r="C136" s="24" t="inlineStr">
+      <c r="C192" s="145" t="inlineStr">
         <is>
           <t>업로드가 끊기지 않는 것이 먼저</t>
         </is>
       </c>
-      <c r="D136" s="24" t="n"/>
-    </row>
-    <row r="137" ht="36" customHeight="1" s="43">
-      <c r="A137" s="26" t="inlineStr">
+      <c r="D192" s="145" t="n"/>
+    </row>
+    <row r="193" ht="34" customHeight="1" s="43">
+      <c r="A193" s="259" t="inlineStr">
         <is>
           <t>1~2개월 뒤</t>
         </is>
       </c>
-      <c r="B137" s="24" t="inlineStr">
+      <c r="B193" s="145" t="inlineStr">
         <is>
           <t>브랜드 사이트 오픈 → 성분 사전 월 2편.</t>
         </is>
       </c>
-      <c r="C137" s="24" t="inlineStr">
+      <c r="C193" s="145" t="inlineStr">
         <is>
           <t>구글은 도메인이 쌓이는 데 시간이 걸린다 — 너무 미루지 않기</t>
         </is>
       </c>
-      <c r="D137" s="24" t="n"/>
-    </row>
-    <row r="138" ht="36" customHeight="1" s="43">
-      <c r="A138" s="26" t="inlineStr">
+      <c r="D193" s="145" t="n"/>
+    </row>
+    <row r="194" ht="34" customHeight="1" s="43">
+      <c r="A194" s="259" t="inlineStr">
         <is>
           <t>6개월 뒤</t>
         </is>
       </c>
-      <c r="B138" s="24" t="inlineStr">
+      <c r="B194" s="145" t="inlineStr">
         <is>
           <t>채널별 대기자 수 비교 → 안 되는 채널은 정리, 되는 곳에 집중.</t>
         </is>
       </c>
-      <c r="C138" s="24" t="inlineStr">
+      <c r="C194" s="145" t="inlineStr">
         <is>
           <t>조회수가 아니라 대기자를 데려온 채널</t>
         </is>
       </c>
-      <c r="D138" s="24" t="n"/>
-    </row>
-    <row r="140" ht="30" customHeight="1" s="43">
-      <c r="A140" s="79" t="inlineStr">
+      <c r="D194" s="145" t="n"/>
+    </row>
+    <row r="196" ht="30" customHeight="1" s="43">
+      <c r="A196" s="79" t="inlineStr">
         <is>
           <t>2년 × 평균 주 2개 ≈ 200개 + 블로그 약 50편. 2027년 말 누적 약 110개 — 자격을 딴 날 '이미 보는 사람과 대기자가 있는 상태'로 판매를 시작하는 게 목표.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A97:D97"/>
+  <mergeCells count="29">
+    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="B107:D107"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A161:D161"/>
+    <mergeCell ref="B103:D103"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="B108:D108"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="B92:D92"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="A183:D183"/>
     <mergeCell ref="A46:D46"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="A101:D101"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="B105:D105"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
@@ -33646,6 +34623,7 @@
           <t>1. 비율이 제형을 정한다 — 같은 올리브유화왁스라도 2%(로션)·3%(크림), 같은 오일도 12%(로션)·31%(크림)·85%(밤).</t>
         </is>
       </c>
+      <c r="B22" s="204" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="43">
       <c r="A23" s="182" t="inlineStr">
@@ -33653,6 +34631,7 @@
           <t>2. 숨은 겸직 원료를 보라 — 알로에겔/겔류=활성+점증, 세틸알코올=공유화+바디, 토코페롤=산화방지(≠방부).</t>
         </is>
       </c>
+      <c r="B23" s="204" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="43">
       <c r="A24" s="182" t="inlineStr">
@@ -33660,6 +34639,7 @@
           <t>3. 빠진 것을 보라 — PUFA 오일엔 Vit E, 지용성 활성엔 가용화제, 음이온 세정엔 pH 보정. '무엇이 없나'가 개선 포인트.</t>
         </is>
       </c>
+      <c r="B24" s="204" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="43">
       <c r="A25" s="182" t="inlineStr">
@@ -33667,6 +34647,7 @@
           <t>4. 원료 선택 = 보존 전략 — 호호바(산패 안정)·스쿠알란·MCT는 그 자체로 안정성·피부 적합성을 산다.</t>
         </is>
       </c>
+      <c r="B25" s="204" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1" s="43">
       <c r="A27" s="179" t="inlineStr">

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -2462,7 +2462,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
@@ -2530,7 +2529,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
         <is>
@@ -3510,7 +3508,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113" ht="36" customHeight="1" s="43">
       <c r="A113" s="47" t="inlineStr">
         <is>
@@ -12754,7 +12751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D196"/>
+  <dimension ref="A1:D243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="43" min="1" max="1"/>
@@ -12773,11 +12770,10 @@
     <row r="2" ht="66" customHeight="1" s="43">
       <c r="A2" s="69" t="inlineStr">
         <is>
-          <t>시간 없는 1인의 해법: 콘텐츠를 따로 만들지 않고 제품 실험·시험 공부에서 뽑는다. 주말 실험 1번 = 콘텐츠 2~3개. 목표는 '잘 만들기'보다 '끊기지 않기'. 주 2개는 기본값 — 해보고 버거우면 주 1개로 낮춰도 된다. 만드는 법은 '수요검증' §2, 기록은 §4. 주력 포맷은 ASMR 제작 과정 영상(§6~§7, 다꾸 쇼츠 문법), 유입은 프로필 링크(§8) + 블로그(§9, 프롬프트 §10), 채널 운영(§13). 영상이 처음이면 §11 촬영 → §12 편집·3주 연습 → §13 계정 세팅·업로드 순서로 한 번 따라 하면 된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>시간 없는 1인의 해법: 콘텐츠를 따로 만들지 않고 제품 실험·시험 공부에서 뽑는다. 주말 실험 1번 = 콘텐츠 2~3개. 목표는 '잘 만들기'보다 '끊기지 않기'. 주 2개는 기본값 — 해보고 버거우면 주 1개로 낮춰도 된다. 만드는 법은 '수요검증' §2, 기록은 §4. 주력 포맷은 ASMR 제작 과정 영상(§6~§7, 다꾸 쇼츠 문법), 유입은 프로필 링크(§8) + 블로그(§9, 프롬프트 §10), 채널 운영(§13), 브랜딩·홈페이지·CS(§14). 영상이 처음이면 §11 촬영 → §12 편집·3주 연습 → §13 계정 세팅·업로드 순서로 한 번 따라 하면 된다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="22" customHeight="1" s="43">
       <c r="A4" s="257" t="inlineStr">
         <is>
@@ -12911,7 +12907,6 @@
       </c>
       <c r="D11" s="145" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="22" customHeight="1" s="43">
       <c r="A13" s="257" t="inlineStr">
         <is>
@@ -13051,7 +13046,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="22" customHeight="1" s="43">
       <c r="A21" s="257" t="inlineStr">
         <is>
@@ -13221,7 +13215,6 @@
       </c>
       <c r="D30" s="145" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1" s="43">
       <c r="A32" s="257" t="inlineStr">
         <is>
@@ -13339,7 +13332,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="22" customHeight="1" s="43">
       <c r="A39" s="257" t="inlineStr">
         <is>
@@ -13437,7 +13429,6 @@
       </c>
       <c r="D44" s="145" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46" ht="22" customHeight="1" s="43">
       <c r="A46" s="257" t="inlineStr">
         <is>
@@ -13964,233 +13955,593 @@
       </c>
       <c r="D77" s="145" t="n"/>
     </row>
-    <row r="79" ht="22" customHeight="1" s="43">
-      <c r="A79" s="257" t="inlineStr">
+    <row r="78" ht="34" customHeight="1" s="43">
+      <c r="A78" s="79" t="inlineStr">
+        <is>
+          <t>콘티 B — 'FM 위생 루틴' 풀 과정 ASMR (신뢰형). 첫 1초는 결과 → 자막 '처음부터'로 되감기. 준비 몽타주(②~⑥)는 매 영상 똑같이 = 채널 시그니처. 30초 메인 · 가끔 60초 풀버전</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1" s="43">
+      <c r="A79" s="140" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B79" s="140" t="inlineStr">
+        <is>
+          <t>장면 · 소리</t>
+        </is>
+      </c>
+      <c r="C79" s="140" t="inlineStr">
+        <is>
+          <t>길이 (30초 / 60초)</t>
+        </is>
+      </c>
+      <c r="D79" s="140" t="inlineStr">
+        <is>
+          <t>FM 포인트 · 왜</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1" s="43">
+      <c r="A80" s="259" t="inlineStr">
+        <is>
+          <t>① 훅 (첫 1초)</t>
+        </is>
+      </c>
+      <c r="B80" s="145" t="inlineStr">
+        <is>
+          <t>결과 먼저: 탱글하게 굳는 순간 또는 크림 긁어 담기 ★</t>
+        </is>
+      </c>
+      <c r="C80" s="145" t="inlineStr">
+        <is>
+          <t>1초 / 2초</t>
+        </is>
+      </c>
+      <c r="D80" s="145" t="inlineStr">
+        <is>
+          <t>결과를 먼저 보여줘야 과정을 끝까지 본다(§6 구성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="62" customHeight="1" s="43">
+      <c r="A81" s="259" t="inlineStr">
+        <is>
+          <t>② 되감기 · 환기</t>
+        </is>
+      </c>
+      <c r="B81" s="145" t="inlineStr">
+        <is>
+          <t>자막 '처음부터' + 창문 열기·환기팬 켜기 1컷</t>
+        </is>
+      </c>
+      <c r="C81" s="145" t="inlineStr">
+        <is>
+          <t>0.5초 / 1초</t>
+        </is>
+      </c>
+      <c r="D81" s="145" t="inlineStr">
+        <is>
+          <t>환기는 1컷만. 촬영은 창 닫고 조용한 시간에(차·생활 소음이 ASMR을 망침)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="62" customHeight="1" s="43">
+      <c r="A82" s="259" t="inlineStr">
+        <is>
+          <t>③ 손 소독 · 장갑</t>
+        </is>
+      </c>
+      <c r="B82" s="145" t="inlineStr">
+        <is>
+          <t>손 소독 → 니트릴 장갑 끼고 손목에서 '착' 스냅</t>
+        </is>
+      </c>
+      <c r="C82" s="145" t="inlineStr">
+        <is>
+          <t>1초 / 2초</t>
+        </is>
+      </c>
+      <c r="D82" s="145" t="inlineStr">
+        <is>
+          <t>라텍스 ❌ 니트릴 ⭕(라텍스 알레르기 — 실험실·맞춤형 조제 표준). 검정 한 색(§6 손)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="62" customHeight="1" s="43">
+      <c r="A83" s="259" t="inlineStr">
+        <is>
+          <t>④ 헤어캡 · 마스크 · 보안경</t>
+        </is>
+      </c>
+      <c r="B83" s="145" t="inlineStr">
+        <is>
+          <t>헤어캡 · 마스크 · 보안경 '딸깍'</t>
+        </is>
+      </c>
+      <c r="C83" s="145" t="inlineStr">
+        <is>
+          <t>0.5초 / 2초</t>
+        </is>
+      </c>
+      <c r="D83" s="145" t="inlineStr">
+        <is>
+          <t>화장품 위생의 핵심 = 머리카락·침 차단. 보안경은 분말·pH 조절제(NaOH 등) 다룰 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1" s="43">
+      <c r="A84" s="259" t="inlineStr">
+        <is>
+          <t>⑤ 작업대 소독</t>
+        </is>
+      </c>
+      <c r="B84" s="145" t="inlineStr">
+        <is>
+          <t>70% 에탄올 '칙칙' → 키친타월로 닦기 '뽀득'</t>
+        </is>
+      </c>
+      <c r="C84" s="145" t="inlineStr">
+        <is>
+          <t>1초 / 2초</t>
+        </is>
+      </c>
+      <c r="D84" s="145" t="inlineStr">
+        <is>
+          <t>작업대 → 도구 순서로 소독</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1" s="43">
+      <c r="A85" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 도구 소독</t>
+        </is>
+      </c>
+      <c r="B85" s="145" t="inlineStr">
+        <is>
+          <t>비커 · 스패출러 · 저울 접시에 '칙' + 닦기</t>
+        </is>
+      </c>
+      <c r="C85" s="145" t="inlineStr">
+        <is>
+          <t>0.5초 / 2초</t>
+        </is>
+      </c>
+      <c r="D85" s="145" t="inlineStr">
+        <is>
+          <t>책상만이 아니라 닿는 도구까지 = 진짜 FM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1" s="43">
+      <c r="A86" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 원료 꺼내기</t>
+        </is>
+      </c>
+      <c r="B86" s="145" t="inlineStr">
+        <is>
+          <t>라벨이 위를 보게 일렬 → 하나씩 집어 '톡' 내려놓기</t>
+        </is>
+      </c>
+      <c r="C86" s="145" t="inlineStr">
+        <is>
+          <t>1초 / 3초</t>
+        </is>
+      </c>
+      <c r="D86" s="145" t="inlineStr">
+        <is>
+          <t>라벨이 보이게 = 무엇을 넣는지 투명하게</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="48" customHeight="1" s="43">
+      <c r="A87" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 계량 (반복)</t>
+        </is>
+      </c>
+      <c r="B87" s="145" t="inlineStr">
+        <is>
+          <t>저울 영점 '삑' → 원료 붓기 · 숫자 올라감 + 자막(원료명·%)</t>
+        </is>
+      </c>
+      <c r="C87" s="145" t="inlineStr">
+        <is>
+          <t>8초 / 15초 (원료당 1.5초)</t>
+        </is>
+      </c>
+      <c r="D87" s="145" t="inlineStr">
+        <is>
+          <t>저울 숫자와 자막 %가 맞아야 신뢰. 60초 버전은 원료 5~6개 전부</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1" s="43">
+      <c r="A88" s="259" t="inlineStr">
+        <is>
+          <t>⑨ 가열 · 분산</t>
+        </is>
+      </c>
+      <c r="B88" s="145" t="inlineStr">
+        <is>
+          <t>가루 솔솔 '사락' / 온도계 숫자 클로즈업(예: 75℃)</t>
+        </is>
+      </c>
+      <c r="C88" s="145" t="inlineStr">
+        <is>
+          <t>3초 / 6초</t>
+        </is>
+      </c>
+      <c r="D88" s="145" t="inlineStr">
+        <is>
+          <t>온도 숫자 = 정확하게 만든다는 증거</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34" customHeight="1" s="43">
+      <c r="A89" s="259" t="inlineStr">
+        <is>
+          <t>⑩ 유화 · 중화</t>
+        </is>
+      </c>
+      <c r="B89" s="145" t="inlineStr">
+        <is>
+          <t>호모나이저 '윙'(투명 → 우유색) 또는 중화로 탱글하게 굳는 순간</t>
+        </is>
+      </c>
+      <c r="C89" s="145" t="inlineStr">
+        <is>
+          <t>3초 / 6초</t>
+        </is>
+      </c>
+      <c r="D89" s="145" t="inlineStr">
+        <is>
+          <t>호모나이저는 소리가 커서 편집에서 볼륨 ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1" s="43">
+      <c r="A90" s="259" t="inlineStr">
+        <is>
+          <t>⑪ pH 확인</t>
+        </is>
+      </c>
+      <c r="B90" s="145" t="inlineStr">
+        <is>
+          <t>pH 스트립 색 / pH 미터 숫자 클로즈업</t>
+        </is>
+      </c>
+      <c r="C90" s="145" t="inlineStr">
+        <is>
+          <t>1.5초 / 3초</t>
+        </is>
+      </c>
+      <c r="D90" s="145" t="inlineStr">
+        <is>
+          <t>'확인하고 만든다' 한 컷 — 신뢰 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="34" customHeight="1" s="43">
+      <c r="A91" s="259" t="inlineStr">
+        <is>
+          <t>⑫ 용기 담기</t>
+        </is>
+      </c>
+      <c r="B91" s="145" t="inlineStr">
+        <is>
+          <t>스패출러로 긁어 담기 '긁' + 뚜껑 '딸깍'</t>
+        </is>
+      </c>
+      <c r="C91" s="145" t="inlineStr">
+        <is>
+          <t>4초 / 8초</t>
+        </is>
+      </c>
+      <c r="D91" s="145" t="inlineStr">
+        <is>
+          <t>ASMR 핵심 소리 — 가장 길게</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="76" customHeight="1" s="43">
+      <c r="A92" s="259" t="inlineStr">
+        <is>
+          <t>⑬ 라벨</t>
+        </is>
+      </c>
+      <c r="B92" s="145" t="inlineStr">
+        <is>
+          <t>'시제품 #03 · Batch · 날짜' 라벨 붙이고 쓸어 누르기</t>
+        </is>
+      </c>
+      <c r="C92" s="145" t="inlineStr">
+        <is>
+          <t>2초 / 3초</t>
+        </is>
+      </c>
+      <c r="D92" s="145" t="inlineStr">
+        <is>
+          <t>★ 판매 제품처럼 보이지 않게 '시제품' 표기 — 집에서 만든 것은 판매 불가(제조업 등록 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="62" customHeight="1" s="43">
+      <c r="A93" s="259" t="inlineStr">
+        <is>
+          <t>⑭ 마무리</t>
+        </is>
+      </c>
+      <c r="B93" s="145" t="inlineStr">
+        <is>
+          <t>완성 용기 + 자막 '개발 중 시제품 · 출시 알림은 프로필 링크'</t>
+        </is>
+      </c>
+      <c r="C93" s="145" t="inlineStr">
+        <is>
+          <t>2초 / 3초</t>
+        </is>
+      </c>
+      <c r="D93" s="145" t="inlineStr">
+        <is>
+          <t>캡션 고정 문구: '개발 중인 시제품입니다. 판매 제품은 화장품 제조업체에서 생산합니다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="62" customHeight="1" s="43">
+      <c r="A94" s="259" t="inlineStr">
+        <is>
+          <t>촬영 전 체크</t>
+        </is>
+      </c>
+      <c r="B94" s="145" t="inlineStr">
+        <is>
+          <t>□ 창 닫고 조용한 시간  □ 핀마이크 5~10cm(§11)  □ 저울·온도계·pH 숫자가 화면에  □ 라벨 '시제품'  □ 캡션 고정 문구</t>
+        </is>
+      </c>
+      <c r="C94" s="145" t="inlineStr">
+        <is>
+          <t>합계 ≈ 30초 / 60초</t>
+        </is>
+      </c>
+      <c r="D94" s="145" t="inlineStr">
+        <is>
+          <t>소리는 조용할 때 가까이서 따로 녹음해 덧입혀도 된다(긁기·분말)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" s="43"/>
+    <row r="96" ht="22" customHeight="1" s="43">
+      <c r="A96" s="257" t="inlineStr">
         <is>
           <t>§8. 프로필 링크 · 유입 — 시기별로 링크 대상을 바꾼다</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customHeight="1" s="43">
-      <c r="A80" s="140" t="inlineStr">
+    <row r="97" ht="28" customHeight="1" s="43">
+      <c r="A97" s="140" t="inlineStr">
         <is>
           <t>시기 · 항목</t>
         </is>
       </c>
-      <c r="B80" s="140" t="inlineStr">
+      <c r="B97" s="140" t="inlineStr">
         <is>
           <t>프로필 링크 / 문구</t>
         </is>
       </c>
-      <c r="C80" s="140" t="inlineStr">
+      <c r="C97" s="140" t="inlineStr">
         <is>
           <t>하는 일 · 측정</t>
         </is>
       </c>
-      <c r="D80" s="258" t="n"/>
-    </row>
-    <row r="81" ht="36" customHeight="1" s="43">
-      <c r="A81" s="259" t="inlineStr">
+      <c r="D97" s="258" t="n"/>
+    </row>
+    <row r="98" ht="36" customHeight="1" s="43">
+      <c r="A98" s="259" t="inlineStr">
         <is>
           <t>지금 ~ 2027.5</t>
         </is>
       </c>
-      <c r="B81" s="145" t="inlineStr">
+      <c r="B98" s="145" t="inlineStr">
         <is>
           <t>출시 알림 대기자 폼 (수요검증 S2). 상점 링크 ❌</t>
         </is>
       </c>
-      <c r="C81" s="145" t="inlineStr">
+      <c r="C98" s="145" t="inlineStr">
         <is>
           <t>링크 클릭 수 → 대기자 전환율 = 수요 증거. 주 1회 §4 로그에 숫자</t>
         </is>
       </c>
-      <c r="D81" s="145" t="n"/>
-    </row>
-    <row r="82" ht="36" customHeight="1" s="43">
-      <c r="A82" s="259" t="inlineStr">
+      <c r="D98" s="145" t="n"/>
+    </row>
+    <row r="99" ht="36" customHeight="1" s="43">
+      <c r="A99" s="259" t="inlineStr">
         <is>
           <t>자격 취득 후 (2027 중반~)</t>
         </is>
       </c>
-      <c r="B82" s="145" t="inlineStr">
+      <c r="B99" s="145" t="inlineStr">
         <is>
           <t>상점 + 대기자 폼</t>
         </is>
       </c>
-      <c r="C82" s="145" t="inlineStr">
+      <c r="C99" s="145" t="inlineStr">
         <is>
           <t>대기자에게 먼저 판매 알림 → 첫 매출 · 재구매 추적(S5)</t>
         </is>
       </c>
-      <c r="D82" s="145" t="n"/>
-    </row>
-    <row r="83" ht="36" customHeight="1" s="43">
-      <c r="A83" s="259" t="inlineStr">
+      <c r="D99" s="145" t="n"/>
+    </row>
+    <row r="100" ht="36" customHeight="1" s="43">
+      <c r="A100" s="259" t="inlineStr">
         <is>
           <t>프로필 소개</t>
         </is>
       </c>
-      <c r="B83" s="145" t="inlineStr">
+      <c r="B100" s="145" t="inlineStr">
         <is>
           <t>'지성·민감 피부용 무향 진정 크림, 직접 개발 중 · 출시 알림 ↓'</t>
         </is>
       </c>
-      <c r="C83" s="145" t="inlineStr">
+      <c r="C100" s="145" t="inlineStr">
         <is>
           <t>누구를 위한 무엇인지 + 할 행동 하나</t>
         </is>
       </c>
-      <c r="D83" s="145" t="n"/>
-    </row>
-    <row r="84" ht="22" customHeight="1" s="43">
-      <c r="A84" s="259" t="inlineStr">
+      <c r="D100" s="145" t="n"/>
+    </row>
+    <row r="101" ht="22" customHeight="1" s="43">
+      <c r="A101" s="259" t="inlineStr">
         <is>
           <t>영상 · 캡션 끝</t>
         </is>
       </c>
-      <c r="B84" s="145" t="inlineStr">
+      <c r="B101" s="145" t="inlineStr">
         <is>
           <t>매번 '출시 알림은 프로필 링크' 한 줄</t>
         </is>
       </c>
-      <c r="C84" s="145" t="inlineStr">
+      <c r="C101" s="145" t="inlineStr">
         <is>
           <t>행동 요청은 하나만</t>
         </is>
       </c>
-      <c r="D84" s="145" t="n"/>
-    </row>
-    <row r="85" ht="36" customHeight="1" s="43">
-      <c r="A85" s="259" t="inlineStr">
+      <c r="D101" s="145" t="n"/>
+    </row>
+    <row r="102" ht="36" customHeight="1" s="43">
+      <c r="A102" s="259" t="inlineStr">
         <is>
           <t>링크가 여러 개일 때</t>
         </is>
       </c>
-      <c r="B85" s="145" t="inlineStr">
+      <c r="B102" s="145" t="inlineStr">
         <is>
           <t>링크 모음 서비스로 하나로 묶고, 맨 위에 시기별 핵심 링크 하나</t>
         </is>
       </c>
-      <c r="C85" s="145" t="inlineStr">
+      <c r="C102" s="145" t="inlineStr">
         <is>
           <t>링크가 많으면 아무것도 안 누른다</t>
         </is>
       </c>
-      <c r="D85" s="145" t="n"/>
-    </row>
-    <row r="86" ht="44" customHeight="1" s="43">
-      <c r="A86" s="79" t="inlineStr">
+      <c r="D102" s="145" t="n"/>
+    </row>
+    <row r="103" ht="44" customHeight="1" s="43">
+      <c r="A103" s="79" t="inlineStr">
         <is>
           <t>⚠ 자격(맞춤형화장품판매업) 또는 OEM 제조 + 책임판매업 등록 전엔 집에서 만든 제품을 팔 수 없다 → 지금 링크는 상점이 아니라 대기자 폼. 나중에 OEM 제품을 팔 때는 홈랩 영상이 '개발 과정'임을 분명히(판매 제품을 집에서 만드는 것처럼 보이면 오인 표현 위험).</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88" ht="23" customHeight="1" s="43">
-      <c r="A88" s="257" t="inlineStr">
+    <row r="104" s="43"/>
+    <row r="105" ht="23" customHeight="1" s="43">
+      <c r="A105" s="257" t="inlineStr">
         <is>
           <t>§9. 블로그 — 검색으로 찾아오는 사람을 받는다 (네이버 블로그 = 네이버 검색 · 구글은 브랜드 사이트 §13)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="28" customHeight="1" s="43">
-      <c r="A89" s="140" t="inlineStr">
+    <row r="106" ht="28" customHeight="1" s="43">
+      <c r="A106" s="140" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B89" s="140" t="inlineStr">
+      <c r="B106" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C89" s="140" t="inlineStr">
+      <c r="C106" s="140" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="D89" s="258" t="n"/>
-    </row>
-    <row r="90" ht="51" customHeight="1" s="43">
-      <c r="A90" s="259" t="inlineStr">
+      <c r="D106" s="258" t="n"/>
+    </row>
+    <row r="107" ht="51" customHeight="1" s="43">
+      <c r="A107" s="259" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="B90" s="145" t="inlineStr">
+      <c r="B107" s="145" t="inlineStr">
         <is>
           <t>인스타 = 피드에서 우연히 발견. 블로그 = 고민이 있어서 직접 검색해 찾아옴(구매 의도가 높은 사람).</t>
         </is>
       </c>
-      <c r="C90" s="145" t="inlineStr">
+      <c r="C107" s="145" t="inlineStr">
         <is>
           <t>글 한 편이 몇 년간 검색 유입을 만든다 — 2년이면 복리</t>
         </is>
       </c>
-      <c r="D90" s="145" t="n"/>
-    </row>
-    <row r="91" ht="66" customHeight="1" s="43">
-      <c r="A91" s="259" t="inlineStr">
+      <c r="D107" s="145" t="n"/>
+    </row>
+    <row r="108" ht="66" customHeight="1" s="43">
+      <c r="A108" s="259" t="inlineStr">
         <is>
           <t>플랫폼 · 시작 시점</t>
         </is>
       </c>
-      <c r="B91" s="145" t="inlineStr">
+      <c r="B108" s="145" t="inlineStr">
         <is>
           <t>네이버 블로그 추천(화장품은 사기 전에 검색하는 사람이 많고, 나중에 스마트스토어와 같은 생태계). 인스타 습관이 잡힌 뒤 시작 — 4주 연속 주 2개 달성하면.</t>
         </is>
       </c>
-      <c r="C91" s="145" t="inlineStr">
+      <c r="C108" s="145" t="inlineStr">
         <is>
           <t>블로그는 시험 공부 겸용이라 추가 부담이 작다. 구글 유입은 브랜드 사이트로 따로(§13) — 같은 글 복사 ❌</t>
         </is>
       </c>
-      <c r="D91" s="145" t="n"/>
-    </row>
-    <row r="92" ht="51" customHeight="1" s="43">
-      <c r="A92" s="259" t="inlineStr">
+      <c r="D108" s="145" t="n"/>
+    </row>
+    <row r="109" ht="51" customHeight="1" s="43">
+      <c r="A109" s="259" t="inlineStr">
         <is>
           <t>주간 루틴</t>
         </is>
       </c>
-      <c r="B92" s="145" t="inlineStr">
+      <c r="B109" s="145" t="inlineStr">
         <is>
           <t>주 1편, 60분. 이번 주 공부한 성분 1개 또는 개발일지 1건 → §10 프롬프트 ① → ②·③·④ 중 하나 → 사실·사진 직접 채우기 → ⑤ 점검 → 발행.</t>
         </is>
       </c>
-      <c r="C92" s="145" t="inlineStr">
+      <c r="C109" s="145" t="inlineStr">
         <is>
           <t>남에게 설명하듯 쓰는 게 가장 강한 암기법 — 블로그 1편 = 시험 공부 1회</t>
         </is>
       </c>
-      <c r="D92" s="145" t="n"/>
-    </row>
-    <row r="93" ht="51" customHeight="1" s="43">
-      <c r="A93" s="259" t="inlineStr">
+      <c r="D109" s="145" t="n"/>
+    </row>
+    <row r="110" ht="51" customHeight="1" s="43">
+      <c r="A110" s="259" t="inlineStr">
         <is>
           <t>글감 3종 (번갈아)</t>
         </is>
       </c>
-      <c r="B93" s="145" t="inlineStr">
+      <c r="B110" s="145" t="inlineStr">
         <is>
           <t>고민 해결(①층, 예: 지성인데 속건조) / 성분 해설(②층, 시험 공부) / 개발일지(③층, 실험·실패, ASMR 영상 넣기).</t>
         </is>
       </c>
-      <c r="C93" s="145" t="inlineStr">
+      <c r="C110" s="145" t="inlineStr">
         <is>
           <t>비중은 키워드 3층과 같게. 시험대비 원료맵·개발일지 시트가 그대로 글감 창고</t>
         </is>
       </c>
-      <c r="D93" s="145" t="n"/>
-    </row>
-    <row r="94" ht="201" customHeight="1" s="43">
-      <c r="A94" s="259" t="inlineStr">
+      <c r="D110" s="145" t="n"/>
+    </row>
+    <row r="111" ht="201" customHeight="1" s="43">
+      <c r="A111" s="259" t="inlineStr">
         <is>
           <t>키워드 (3층)</t>
         </is>
       </c>
-      <c r="B94" s="145" t="inlineStr">
+      <c r="B111" s="145" t="inlineStr">
         <is>
           <t>① 고민 키워드 (약 50%) — 고객이 자기 고민을 자기 말로 검색. 살 사람이 온다.
 예) '지성 속건조' '지성 피부 수분크림' '번들거림 없는 크림' '민감성 진정 크림' '무향 크림'
@@ -14200,135 +14551,135 @@
 예) '카보머 중화' '원심분리 테스트'</t>
         </is>
       </c>
-      <c r="C94" s="145" t="inlineStr">
+      <c r="C111" s="145" t="inlineStr">
         <is>
           <t>검색량은 네이버 검색광고 키워드 도구(월간 검색수)·데이터랩(추세)으로 직접 확인 — 감으로 판단 금지.
 큰 키워드('수분크림 추천')는 대형 브랜드 몫 → 구체적인 키워드 여러 개로 이긴다.
 질환명(여드름·지루성 피부염)은 제품 효능과 연결 금지 — 지성·번들거림·속건조·민감 같은 피부 타입·상태 단어로.</t>
         </is>
       </c>
-      <c r="D94" s="145" t="n"/>
-    </row>
-    <row r="95" ht="51" customHeight="1" s="43">
-      <c r="A95" s="259" t="inlineStr">
+      <c r="D111" s="145" t="n"/>
+    </row>
+    <row r="112" ht="51" customHeight="1" s="43">
+      <c r="A112" s="259" t="inlineStr">
         <is>
           <t>글 구조</t>
         </is>
       </c>
-      <c r="B95" s="145" t="inlineStr">
+      <c r="B112" s="145" t="inlineStr">
         <is>
           <t>제목 앞쪽에 메인 키워드 → 고민으로 시작하는 도입 → 소제목 4~5개 → 직접 찍은 사진·영상 → 끝에 출시 알림 링크.</t>
         </is>
       </c>
-      <c r="C95" s="145" t="inlineStr">
+      <c r="C112" s="145" t="inlineStr">
         <is>
           <t>직접 해본 사진·기록이 AI 대량 글과의 차이</t>
         </is>
       </c>
-      <c r="D95" s="145" t="n"/>
-    </row>
-    <row r="96" ht="36" customHeight="1" s="43">
-      <c r="A96" s="259" t="inlineStr">
+      <c r="D112" s="145" t="n"/>
+    </row>
+    <row r="113" ht="36" customHeight="1" s="43">
+      <c r="A113" s="259" t="inlineStr">
         <is>
           <t>AI 사용 원칙</t>
         </is>
       </c>
-      <c r="B96" s="145" t="inlineStr">
+      <c r="B113" s="145" t="inlineStr">
         <is>
           <t>AI = 기획·초안·점검 담당. 수치·규제는 교재·고시로 직접 확인. 실험 사진·경험은 직접.</t>
         </is>
       </c>
-      <c r="C96" s="145" t="inlineStr">
+      <c r="C113" s="145" t="inlineStr">
         <is>
           <t>AI가 지어낸 수치 한 줄이 '성분 아는 사람'이라는 신뢰를 깎는다</t>
         </is>
       </c>
-      <c r="D96" s="145" t="n"/>
-    </row>
-    <row r="97" ht="51" customHeight="1" s="43">
-      <c r="A97" s="259" t="inlineStr">
+      <c r="D113" s="145" t="n"/>
+    </row>
+    <row r="114" ht="51" customHeight="1" s="43">
+      <c r="A114" s="259" t="inlineStr">
         <is>
           <t>링크 · 규정</t>
         </is>
       </c>
-      <c r="B97" s="145" t="inlineStr">
+      <c r="B114" s="145" t="inlineStr">
         <is>
           <t>글 끝은 대기자 폼(판매 전). 판매 시작 후엔 블로그도 광고 → 수요검증 §3 기준 적용. 협찬·체험단 글은 협찬 사실 표기.</t>
         </is>
       </c>
-      <c r="C97" s="145" t="inlineStr">
+      <c r="C114" s="145" t="inlineStr">
         <is>
           <t>§8 프로필 링크와 같은 원칙</t>
         </is>
       </c>
-      <c r="D97" s="145" t="n"/>
-    </row>
-    <row r="98" ht="66" customHeight="1" s="43">
-      <c r="A98" s="259" t="inlineStr">
+      <c r="D114" s="145" t="n"/>
+    </row>
+    <row r="115" ht="66" customHeight="1" s="43">
+      <c r="A115" s="259" t="inlineStr">
         <is>
           <t>측정</t>
         </is>
       </c>
-      <c r="B98" s="145" t="inlineStr">
+      <c r="B115" s="145" t="inlineStr">
         <is>
           <t>월 1회: 유입 키워드 상위 5개 · 조회수 · 대기자 폼 클릭을 키워드 층별로 비교 → 대기자를 많이 데려온 층·주제를 다음 달 글감으로. 목표는 조회수가 아니라 대기자.</t>
         </is>
       </c>
-      <c r="C98" s="145" t="inlineStr">
+      <c r="C115" s="145" t="inlineStr">
         <is>
           <t>수요검증 §4 로그에 '블로그' 줄로 기록</t>
         </is>
       </c>
-      <c r="D98" s="145" t="n"/>
-    </row>
-    <row r="99" ht="51" customHeight="1" s="43">
-      <c r="A99" s="259" t="inlineStr">
+      <c r="D115" s="145" t="n"/>
+    </row>
+    <row r="116" ht="51" customHeight="1" s="43">
+      <c r="A116" s="259" t="inlineStr">
         <is>
           <t>목표</t>
         </is>
       </c>
-      <c r="B99" s="145" t="inlineStr">
+      <c r="B116" s="145" t="inlineStr">
         <is>
           <t>2026.12 시작 → 시험(2027.5) 전 성분 해설 약 20편 → 2027년 말 누적 약 50편. (브랜드 사이트 '성분 사전'은 별도 — §13)</t>
         </is>
       </c>
-      <c r="C99" s="145" t="inlineStr">
+      <c r="C116" s="145" t="inlineStr">
         <is>
           <t>시험기에도 유지 가능(공부가 곧 글감)</t>
         </is>
       </c>
-      <c r="D99" s="145" t="n"/>
-    </row>
-    <row r="100"/>
-    <row r="101" ht="22" customHeight="1" s="43">
-      <c r="A101" s="257" t="inlineStr">
+      <c r="D116" s="145" t="n"/>
+    </row>
+    <row r="117" s="43"/>
+    <row r="118" ht="22" customHeight="1" s="43">
+      <c r="A118" s="257" t="inlineStr">
         <is>
           <t>§10. 블로그 발행 프롬프트 6종 — 셀 내용을 그대로 복사해 AI(Claude·ChatGPT 등)에 붙여넣고 [대괄호]만 채운다</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="28" customHeight="1" s="43">
-      <c r="A102" s="140" t="inlineStr">
+    <row r="119" ht="28" customHeight="1" s="43">
+      <c r="A119" s="140" t="inlineStr">
         <is>
           <t>프롬프트 · 언제</t>
         </is>
       </c>
-      <c r="B102" s="140" t="inlineStr">
+      <c r="B119" s="140" t="inlineStr">
         <is>
           <t>본문</t>
         </is>
       </c>
-      <c r="C102" s="144" t="n"/>
-      <c r="D102" s="59" t="n"/>
-    </row>
-    <row r="103" ht="267" customHeight="1" s="43">
-      <c r="A103" s="259" t="inlineStr">
+      <c r="C119" s="144" t="n"/>
+      <c r="D119" s="59" t="n"/>
+    </row>
+    <row r="120" ht="267" customHeight="1" s="43">
+      <c r="A120" s="259" t="inlineStr">
         <is>
           <t>① 키워드 · 제목 기획
 언제: 글 쓰기 전, 주제만 정했을 때</t>
         </is>
       </c>
-      <c r="B103" s="145" t="inlineStr">
+      <c r="B120" s="145" t="inlineStr">
         <is>
           <t>너는 화장품 성분 블로그의 콘텐츠 기획자야.
 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어.
@@ -14342,17 +14693,17 @@
 질환명(여드름·지루성 피부염 등)이 들어간 키워드는 '제품 효능과 연결 불가'라고 표시해.</t>
         </is>
       </c>
-      <c r="C103" s="144" t="n"/>
-      <c r="D103" s="59" t="n"/>
-    </row>
-    <row r="104" ht="402" customHeight="1" s="43">
-      <c r="A104" s="259" t="inlineStr">
+      <c r="C120" s="144" t="n"/>
+      <c r="D120" s="59" t="n"/>
+    </row>
+    <row r="121" ht="402" customHeight="1" s="43">
+      <c r="A121" s="259" t="inlineStr">
         <is>
           <t>② 고민 해결 글 초안
 언제: 피부 고민 하나로 글을 쓸 때 (①층 고민 키워드 · 블로그 글의 절반)</t>
         </is>
       </c>
-      <c r="B104" s="145" t="inlineStr">
+      <c r="B121" s="145" t="inlineStr">
         <is>
           <t>아래 정보로 네이버 블로그 '피부 고민 해결' 글 초안을 써줘. 성분 설명이 아니라 독자의 고민에서 출발하는 글이야.
 [나에 대해] 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어. 말투는 친근하지만 정확하게, 가끔 가벼운 위트 한 줄.
@@ -14376,17 +14727,17 @@
 - '완벽·100%·즉시' 같은 절대 표현, 다른 브랜드 비방·비교 금지.</t>
         </is>
       </c>
-      <c r="C104" s="144" t="n"/>
-      <c r="D104" s="59" t="n"/>
-    </row>
-    <row r="105" ht="342" customHeight="1" s="43">
-      <c r="A105" s="259" t="inlineStr">
+      <c r="C121" s="144" t="n"/>
+      <c r="D121" s="59" t="n"/>
+    </row>
+    <row r="122" ht="342" customHeight="1" s="43">
+      <c r="A122" s="259" t="inlineStr">
         <is>
           <t>③ 성분 해설 글 초안
 언제: 시험 공부한 성분으로 글을 쓸 때 (②층 성분 키워드)</t>
         </is>
       </c>
-      <c r="B105" s="145" t="inlineStr">
+      <c r="B122" s="145" t="inlineStr">
         <is>
           <t>아래 정보로 네이버 블로그 글 초안을 써줘.
 [나에 대해] 나는 지성·민감 피부용 무향 진정 크림을 직접 개발 중인 1인 화장품 브랜드 운영자이고, 맞춤형화장품조제관리사 시험을 준비하고 있어. 말투는 친근하지만 정확하게, 가끔 가벼운 위트 한 줄.
@@ -14408,17 +14759,17 @@
 - 아직 판매 전이니 구매 유도 문구 대신 출시 알림 안내만.</t>
         </is>
       </c>
-      <c r="C105" s="144" t="n"/>
-      <c r="D105" s="59" t="n"/>
-    </row>
-    <row r="106" ht="327" customHeight="1" s="43">
-      <c r="A106" s="259" t="inlineStr">
+      <c r="C122" s="144" t="n"/>
+      <c r="D122" s="59" t="n"/>
+    </row>
+    <row r="123" ht="327" customHeight="1" s="43">
+      <c r="A123" s="259" t="inlineStr">
         <is>
           <t>④ 개발일지 → 블로그 글
 언제: 주말 실험을 글로 남길 때 (③층 메이커 키워드)</t>
         </is>
       </c>
-      <c r="B106" s="145" t="inlineStr">
+      <c r="B123" s="145" t="inlineStr">
         <is>
           <t>아래 개발일지 기록을 블로그 글로 바꿔줘. 실패도 그대로 살려서 '만드는 사람의 실험 노트'처럼.
 [실험 날짜 · 제품] [ ]
@@ -14440,17 +14791,17 @@
 - 효능 단정 금지 — '내 피부에서는 이랬다' 수준으로. 질병 치료·예방 표현 금지.</t>
         </is>
       </c>
-      <c r="C106" s="144" t="n"/>
-      <c r="D106" s="59" t="n"/>
-    </row>
-    <row r="107" ht="147" customHeight="1" s="43">
-      <c r="A107" s="259" t="inlineStr">
+      <c r="C123" s="144" t="n"/>
+      <c r="D123" s="59" t="n"/>
+    </row>
+    <row r="124" ht="147" customHeight="1" s="43">
+      <c r="A124" s="259" t="inlineStr">
         <is>
           <t>⑤ 발행 전 점검
 언제: 초안을 다 채운 뒤, 발행 직전 (매번 필수)</t>
         </is>
       </c>
-      <c r="B107" s="145" t="inlineStr">
+      <c r="B124" s="145" t="inlineStr">
         <is>
           <t>아래 블로그 초안을 발행 전에 점검해줘. 고쳐 쓰기 전에 문제 목록부터 보여줘.
 1. 사실 점검: 수치·규제·성분 설명 중 근거 확인이 필요한 문장을 전부 뽑고, 왜 확인이 필요한지 적어줘.
@@ -14460,17 +14811,17 @@
 [초안 붙여넣기]</t>
         </is>
       </c>
-      <c r="C107" s="144" t="n"/>
-      <c r="D107" s="59" t="n"/>
-    </row>
-    <row r="108" ht="147" customHeight="1" s="43">
-      <c r="A108" s="259" t="inlineStr">
+      <c r="C124" s="144" t="n"/>
+      <c r="D124" s="59" t="n"/>
+    </row>
+    <row r="125" ht="147" customHeight="1" s="43">
+      <c r="A125" s="259" t="inlineStr">
         <is>
           <t>⑥ 블로그 → 인스타 재활용
 언제: 발행한 글을 ASMR 영상·캡션으로 다시 쓸 때</t>
         </is>
       </c>
-      <c r="B108" s="145" t="inlineStr">
+      <c r="B125" s="145" t="inlineStr">
         <is>
           <t>아래 블로그 글을 인스타 ASMR 제작 과정 영상용으로 바꿔줘.
 1. 영상 자막 3~5개 — 각 15자 이내, 원료명·% 위주
@@ -14480,534 +14831,272 @@
 [블로그 글 붙여넣기]</t>
         </is>
       </c>
-      <c r="C108" s="144" t="n"/>
-      <c r="D108" s="59" t="n"/>
-    </row>
-    <row r="109" ht="44" customHeight="1" s="43">
-      <c r="A109" s="79" t="inlineStr">
+      <c r="C125" s="144" t="n"/>
+      <c r="D125" s="59" t="n"/>
+    </row>
+    <row r="126" ht="44" customHeight="1" s="43">
+      <c r="A126" s="79" t="inlineStr">
         <is>
           <t>사용 순서: ① 키워드 → 초안은 ② 고민(글의 절반)·③ 성분·④ 개발일지 중 하나 → 수치·사진·경험은 내가 직접 채우고 확인 → ⑤ 점검 → 발행 → ⑥ 인스타 재활용. AI 점검은 1차 필터 — 최종 판단은 '표시·광고 컴플라이언스' 시트와 최신 고시로 사람이 한다.</t>
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111" ht="22" customHeight="1" s="43">
-      <c r="A111" s="257" t="inlineStr">
+    <row r="127" s="43"/>
+    <row r="128" ht="22" customHeight="1" s="43">
+      <c r="A128" s="257" t="inlineStr">
         <is>
           <t>§11. 촬영 시작하기 — 장비는 폰 + 3가지면 충분 (카메라·짐벌 ❌)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1" s="43">
-      <c r="A112" s="140" t="inlineStr">
+    <row r="129" ht="28" customHeight="1" s="43">
+      <c r="A129" s="140" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="B112" s="140" t="inlineStr">
+      <c r="B129" s="140" t="inlineStr">
         <is>
           <t>고르는 법</t>
         </is>
       </c>
-      <c r="C112" s="140" t="inlineStr">
+      <c r="C129" s="140" t="inlineStr">
         <is>
           <t>가격대(대략) · 메모</t>
         </is>
       </c>
-      <c r="D112" s="258" t="n"/>
-    </row>
-    <row r="113" ht="47" customHeight="1" s="43">
-      <c r="A113" s="259" t="inlineStr">
+      <c r="D129" s="258" t="n"/>
+    </row>
+    <row r="130" ht="47" customHeight="1" s="43">
+      <c r="A130" s="259" t="inlineStr">
         <is>
           <t>위에서 찍는 폰 거치대</t>
         </is>
       </c>
-      <c r="B113" s="145" t="inlineStr">
+      <c r="B130" s="145" t="inlineStr">
         <is>
           <t>책상 모서리에 집게로 고정하는 탑뷰(오버헤드) 자바라 암. 쿠팡 등에서 '탑뷰 거치대'로 검색.</t>
         </is>
       </c>
-      <c r="C113" s="145" t="inlineStr">
+      <c r="C130" s="145" t="inlineStr">
         <is>
           <t>1~3만 원</t>
         </is>
       </c>
-      <c r="D113" s="145" t="n"/>
-    </row>
-    <row r="114" ht="60" customHeight="1" s="43">
-      <c r="A114" s="259" t="inlineStr">
+      <c r="D130" s="145" t="n"/>
+    </row>
+    <row r="131" ht="60" customHeight="1" s="43">
+      <c r="A131" s="259" t="inlineStr">
         <is>
           <t>무선 핀마이크</t>
         </is>
       </c>
-      <c r="B114" s="145" t="inlineStr">
+      <c r="B131" s="145" t="inlineStr">
         <is>
           <t>폰에 수신기를 꽂는 타입. 주문 전 내 폰 충전 단자 확인(아이폰 15 이후·갤럭시 = USB-C, 아이폰 14 이전 = 라이트닝).</t>
         </is>
       </c>
-      <c r="C114" s="145" t="inlineStr">
+      <c r="C131" s="145" t="inlineStr">
         <is>
           <t>2~5만 원 · 소리가 곧 제품</t>
         </is>
       </c>
-      <c r="D114" s="145" t="n"/>
-    </row>
-    <row r="115" ht="34" customHeight="1" s="43">
-      <c r="A115" s="259" t="inlineStr">
+      <c r="D131" s="145" t="n"/>
+    </row>
+    <row r="132" ht="34" customHeight="1" s="43">
+      <c r="A132" s="259" t="inlineStr">
         <is>
           <t>배경판</t>
         </is>
       </c>
-      <c r="B115" s="145" t="inlineStr">
+      <c r="B132" s="145" t="inlineStr">
         <is>
           <t>무광 단색 폼보드·배경지(흰색 또는 연회색). 유광은 빛 반사 ❌.</t>
         </is>
       </c>
-      <c r="C115" s="145" t="inlineStr">
+      <c r="C132" s="145" t="inlineStr">
         <is>
           <t>수천 원</t>
         </is>
       </c>
-      <c r="D115" s="145" t="n"/>
-    </row>
-    <row r="116" ht="34" customHeight="1" s="43">
-      <c r="A116" s="259" t="inlineStr">
+      <c r="D132" s="145" t="n"/>
+    </row>
+    <row r="133" ht="34" customHeight="1" s="43">
+      <c r="A133" s="259" t="inlineStr">
         <is>
           <t>니트릴 장갑 (한 색)</t>
         </is>
       </c>
-      <c r="B116" s="145" t="inlineStr">
+      <c r="B133" s="145" t="inlineStr">
         <is>
           <t>색 하나로 고정해 계속 쓴다(§6 손).</t>
         </is>
       </c>
-      <c r="C116" s="145" t="inlineStr">
+      <c r="C133" s="145" t="inlineStr">
         <is>
           <t>수천 원</t>
         </is>
       </c>
-      <c r="D116" s="145" t="n"/>
-    </row>
-    <row r="117" ht="34" customHeight="1" s="43">
-      <c r="A117" s="259" t="inlineStr">
+      <c r="D133" s="145" t="n"/>
+    </row>
+    <row r="134" ht="34" customHeight="1" s="43">
+      <c r="A134" s="259" t="inlineStr">
         <is>
           <t>조명</t>
         </is>
       </c>
-      <c r="B117" s="145" t="inlineStr">
+      <c r="B134" s="145" t="inlineStr">
         <is>
           <t>주말 낮 창가 자연광이면 생략. 저녁 촬영일 때만 LED 패널 1개.</t>
         </is>
       </c>
-      <c r="C117" s="145" t="inlineStr">
+      <c r="C134" s="145" t="inlineStr">
         <is>
           <t>필요할 때 2~3만 원</t>
         </is>
       </c>
-      <c r="D117" s="145" t="n"/>
-    </row>
-    <row r="118" ht="60" customHeight="1" s="43">
-      <c r="A118" s="259" t="inlineStr">
+      <c r="D134" s="145" t="n"/>
+    </row>
+    <row r="135" ht="60" customHeight="1" s="43">
+      <c r="A135" s="259" t="inlineStr">
         <is>
           <t>이미 있는 것</t>
         </is>
       </c>
-      <c r="B118" s="145" t="inlineStr">
+      <c r="B135" s="145" t="inlineStr">
         <is>
           <t>폰 · 0.01g 저울 · 비커 · 호모나이저 · 원심분리기 = 그대로 소품(§7). 편집은 무료 앱 CapCut 하나.</t>
         </is>
       </c>
-      <c r="C118" s="145" t="inlineStr">
+      <c r="C135" s="145" t="inlineStr">
         <is>
           <t>추가 0원</t>
         </is>
       </c>
-      <c r="D118" s="145" t="n"/>
-    </row>
-    <row r="119" ht="28" customHeight="1" s="43">
-      <c r="A119" s="140" t="inlineStr">
+      <c r="D135" s="145" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1" s="43">
+      <c r="A136" s="140" t="inlineStr">
         <is>
           <t>세팅 순서 (매 촬영 15분)</t>
         </is>
       </c>
-      <c r="B119" s="140" t="inlineStr">
+      <c r="B136" s="140" t="inlineStr">
         <is>
           <t>방법</t>
         </is>
       </c>
-      <c r="C119" s="140" t="inlineStr">
+      <c r="C136" s="140" t="inlineStr">
         <is>
           <t>왜</t>
         </is>
       </c>
-      <c r="D119" s="258" t="n"/>
-    </row>
-    <row r="120" ht="22" customHeight="1" s="43">
-      <c r="A120" s="259" t="inlineStr">
+      <c r="D136" s="258" t="n"/>
+    </row>
+    <row r="137" ht="22" customHeight="1" s="43">
+      <c r="A137" s="259" t="inlineStr">
         <is>
           <t>① 책상</t>
         </is>
       </c>
-      <c r="B120" s="145" t="inlineStr">
+      <c r="B137" s="145" t="inlineStr">
         <is>
           <t>작업대에 얇은 수건 → 그 위에 배경판.</t>
         </is>
       </c>
-      <c r="C120" s="145" t="inlineStr">
+      <c r="C137" s="145" t="inlineStr">
         <is>
           <t>수건이 유리 부딪히는 울림·잡음을 잡는다</t>
         </is>
       </c>
-      <c r="D120" s="145" t="n"/>
-    </row>
-    <row r="121" ht="47" customHeight="1" s="43">
-      <c r="A121" s="259" t="inlineStr">
-        <is>
-          <t>② 소품 배치</t>
-        </is>
-      </c>
-      <c r="B121" s="145" t="inlineStr">
-        <is>
-          <t>화면에 들어올 것만, 비커는 중앙, 원료 병은 라벨이 위를 보게 일렬. 첫 배치 사진대로(§6).</t>
-        </is>
-      </c>
-      <c r="C121" s="145" t="inlineStr">
-        <is>
-          <t>계정 톤의 일관성</t>
-        </is>
-      </c>
-      <c r="D121" s="145" t="n"/>
-    </row>
-    <row r="122" ht="34" customHeight="1" s="43">
-      <c r="A122" s="259" t="inlineStr">
-        <is>
-          <t>③ 거치대 + 폰</t>
-        </is>
-      </c>
-      <c r="B122" s="145" t="inlineStr">
-        <is>
-          <t>폰을 비커 바로 위 30~40cm, 세로로. 손이 들어올 여유를 둔다.</t>
-        </is>
-      </c>
-      <c r="C122" s="145" t="inlineStr">
-        <is>
-          <t>너무 가까우면 손이 잘린다</t>
-        </is>
-      </c>
-      <c r="D122" s="145" t="n"/>
-    </row>
-    <row r="123" ht="60" customHeight="1" s="43">
-      <c r="A123" s="259" t="inlineStr">
-        <is>
-          <t>④ 폰 설정 (처음 한 번)</t>
-        </is>
-      </c>
-      <c r="B123" s="145" t="inlineStr">
-        <is>
-          <t>동영상 1080p · 60fps(아이폰: 설정 → 카메라 → 비디오 녹화 / 갤럭시: 카메라 앱 설정) · 격자 표시 켜고 비커를 정중앙 칸에.</t>
-        </is>
-      </c>
-      <c r="C123" s="145" t="inlineStr">
-        <is>
-          <t>60fps면 나중에 슬로우 가능. 한 번 해두면 유지된다</t>
-        </is>
-      </c>
-      <c r="D123" s="145" t="n"/>
-    </row>
-    <row r="124" ht="47" customHeight="1" s="43">
-      <c r="A124" s="259" t="inlineStr">
-        <is>
-          <t>⑤ 초점·노출 잠금</t>
-        </is>
-      </c>
-      <c r="B124" s="145" t="inlineStr">
-        <is>
-          <t>촬영 화면에서 비커를 길게 누르기 → 'AE/AF 잠금'(아이폰) 또는 자물쇠 표시.</t>
-        </is>
-      </c>
-      <c r="C124" s="145" t="inlineStr">
-        <is>
-          <t>안 하면 손이 들어올 때마다 화면이 밝아졌다 어두워졌다 한다</t>
-        </is>
-      </c>
-      <c r="D124" s="145" t="n"/>
-    </row>
-    <row r="125" ht="47" customHeight="1" s="43">
-      <c r="A125" s="259" t="inlineStr">
-        <is>
-          <t>⑥ 마이크</t>
-        </is>
-      </c>
-      <c r="B125" s="145" t="inlineStr">
-        <is>
-          <t>수신기를 폰에 꽂고, 핀(송신기)은 비커 옆 5~10cm 화면 밖에 집게로. 송신기 전원 확인.</t>
-        </is>
-      </c>
-      <c r="C125" s="145" t="inlineStr">
-        <is>
-          <t>잡음 크면 더 가깝게</t>
-        </is>
-      </c>
-      <c r="D125" s="145" t="n"/>
-    </row>
-    <row r="126" ht="34" customHeight="1" s="43">
-      <c r="A126" s="259" t="inlineStr">
-        <is>
-          <t>⑦ 소음 · 알림 끄기</t>
-        </is>
-      </c>
-      <c r="B126" s="145" t="inlineStr">
-        <is>
-          <t>에어컨·냉장고·선풍기 끄기 · 방해금지(또는 비행기) 모드 · 렌즈 닦기.</t>
-        </is>
-      </c>
-      <c r="C126" s="145" t="inlineStr">
-        <is>
-          <t>알림음·뿌연 화면 방지</t>
-        </is>
-      </c>
-      <c r="D126" s="145" t="n"/>
-    </row>
-    <row r="127" ht="22" customHeight="1" s="43">
-      <c r="A127" s="259" t="inlineStr">
-        <is>
-          <t>⑧ 테스트 10초</t>
-        </is>
-      </c>
-      <c r="B127" s="145" t="inlineStr">
-        <is>
-          <t>막대로 저어 찍고 이어폰으로 들어보기.</t>
-        </is>
-      </c>
-      <c r="C127" s="145" t="inlineStr">
-        <is>
-          <t>화면보다 소리 먼저 확인</t>
-        </is>
-      </c>
-      <c r="D127" s="145" t="n"/>
-    </row>
-    <row r="128" ht="28" customHeight="1" s="43">
-      <c r="A128" s="140" t="inlineStr">
-        <is>
-          <t>찍는 법</t>
-        </is>
-      </c>
-      <c r="B128" s="140" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="C128" s="140" t="inlineStr">
-        <is>
-          <t>왜</t>
-        </is>
-      </c>
-      <c r="D128" s="258" t="n"/>
-    </row>
-    <row r="129" ht="34" customHeight="1" s="43">
-      <c r="A129" s="259" t="inlineStr">
-        <is>
-          <t>한 번 녹화 = 동작 하나</t>
-        </is>
-      </c>
-      <c r="B129" s="145" t="inlineStr">
-        <is>
-          <t>녹화 시작 → 2초 가만히 → 동작 3~5초 → 2초 가만히 → 정지.</t>
-        </is>
-      </c>
-      <c r="C129" s="145" t="inlineStr">
-        <is>
-          <t>앞뒤 2초는 편집에서 자를 여유</t>
-        </is>
-      </c>
-      <c r="D129" s="145" t="n"/>
-    </row>
-    <row r="130" ht="34" customHeight="1" s="43">
-      <c r="A130" s="259" t="inlineStr">
-        <is>
-          <t>실제 공정 순서대로</t>
-        </is>
-      </c>
-      <c r="B130" s="145" t="inlineStr">
-        <is>
-          <t>실험 순서 그대로 찍는다. 첫 1초 순서는 편집에서 바꾼다(§6 구성).</t>
-        </is>
-      </c>
-      <c r="C130" s="145" t="inlineStr">
-        <is>
-          <t>실험에 집중 — 추가 시간 0분</t>
-        </is>
-      </c>
-      <c r="D130" s="145" t="n"/>
-    </row>
-    <row r="131" ht="34" customHeight="1" s="43">
-      <c r="A131" s="259" t="inlineStr">
-        <is>
-          <t>★ 장면은 미리 녹화</t>
-        </is>
-      </c>
-      <c r="B131" s="145" t="inlineStr">
-        <is>
-          <t>중화·유화처럼 한 번뿐인 순간은 그 직전에 녹화를 켜두고, 가능하면 2~3번.</t>
-        </is>
-      </c>
-      <c r="C131" s="145" t="inlineStr">
-        <is>
-          <t>놓치면 다시 못 찍는다</t>
-        </is>
-      </c>
-      <c r="D131" s="145" t="n"/>
-    </row>
-    <row r="132" ht="22" customHeight="1" s="43">
-      <c r="A132" s="259" t="inlineStr">
-        <is>
-          <t>망쳐도 계속 찍기</t>
-        </is>
-      </c>
-      <c r="B132" s="145" t="inlineStr">
-        <is>
-          <t>분리·실패 배치도 그대로 찍어둔다.</t>
-        </is>
-      </c>
-      <c r="C132" s="145" t="inlineStr">
-        <is>
-          <t>실패담 = 콘텐츠(§3 소재 은행)</t>
-        </is>
-      </c>
-      <c r="D132" s="145" t="n"/>
-    </row>
-    <row r="133" ht="22" customHeight="1" s="43">
-      <c r="A133" s="259" t="inlineStr">
-        <is>
-          <t>분량</t>
-        </is>
-      </c>
-      <c r="B133" s="145" t="inlineStr">
-        <is>
-          <t>실험 30분에 클립 7~15개면 충분.</t>
-        </is>
-      </c>
-      <c r="C133" s="145" t="inlineStr">
-        <is>
-          <t>영상 2개(다음 주 분량)가 나온다</t>
-        </is>
-      </c>
-      <c r="D133" s="145" t="n"/>
-    </row>
-    <row r="134" ht="34" customHeight="1" s="43">
-      <c r="A134" s="79" t="inlineStr">
-        <is>
-          <t>이번 주 할 일 하나: 거치대 + 핀마이크 주문(폰 단자 확인) → 기다리는 동안 §13 계정 세팅 ①~④ → 도착한 첫 주말 물로 20분 촬영(§12 1주차).</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="1" s="43">
-      <c r="A136" s="257" t="inlineStr">
-        <is>
-          <t>§12. CapCut 편집 · 3주 연습 — 원료 아끼지 말고 물로 시작 (일요일 30분)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="28" customHeight="1" s="43">
-      <c r="A137" s="140" t="inlineStr">
-        <is>
-          <t>편집 단계</t>
-        </is>
-      </c>
-      <c r="B137" s="140" t="inlineStr">
-        <is>
-          <t>하는 법</t>
-        </is>
-      </c>
-      <c r="C137" s="140" t="inlineStr">
-        <is>
-          <t>포인트</t>
-        </is>
-      </c>
-      <c r="D137" s="258" t="n"/>
+      <c r="D137" s="145" t="n"/>
     </row>
     <row r="138" ht="47" customHeight="1" s="43">
       <c r="A138" s="259" t="inlineStr">
         <is>
-          <t>① 새 프로젝트</t>
+          <t>② 소품 배치</t>
         </is>
       </c>
       <c r="B138" s="145" t="inlineStr">
         <is>
-          <t>CapCut(무료) → 새 프로젝트 → 토요일 클립을 공정 순서대로 모두 선택 → 추가.</t>
-        </is>
-      </c>
-      <c r="C138" s="145" t="inlineStr"/>
+          <t>화면에 들어올 것만, 비커는 중앙, 원료 병은 라벨이 위를 보게 일렬. 첫 배치 사진대로(§6).</t>
+        </is>
+      </c>
+      <c r="C138" s="145" t="inlineStr">
+        <is>
+          <t>계정 톤의 일관성</t>
+        </is>
+      </c>
       <c r="D138" s="145" t="n"/>
     </row>
-    <row r="139" ht="22" customHeight="1" s="43">
+    <row r="139" ht="34" customHeight="1" s="43">
       <c r="A139" s="259" t="inlineStr">
         <is>
-          <t>② 비율</t>
+          <t>③ 거치대 + 폰</t>
         </is>
       </c>
       <c r="B139" s="145" t="inlineStr">
         <is>
-          <t>하단 메뉴 '비율' → 9:16.</t>
+          <t>폰을 비커 바로 위 30~40cm, 세로로. 손이 들어올 여유를 둔다.</t>
         </is>
       </c>
       <c r="C139" s="145" t="inlineStr">
         <is>
-          <t>릴스·쇼츠·틱톡 공통</t>
+          <t>너무 가까우면 손이 잘린다</t>
         </is>
       </c>
       <c r="D139" s="145" t="n"/>
     </row>
-    <row r="140" ht="47" customHeight="1" s="43">
+    <row r="140" ht="60" customHeight="1" s="43">
       <c r="A140" s="259" t="inlineStr">
         <is>
-          <t>③ 자르기 (분할)</t>
+          <t>④ 폰 설정 (처음 한 번)</t>
         </is>
       </c>
       <c r="B140" s="145" t="inlineStr">
         <is>
-          <t>클립을 누르고 동작 시작 지점에 흰 세로선 → '분할' → 앞 군더더기 선택 → 삭제. 끝도 같게.</t>
+          <t>동영상 1080p · 60fps(아이폰: 설정 → 카메라 → 비디오 녹화 / 갤럭시: 카메라 앱 설정) · 격자 표시 켜고 비커를 정중앙 칸에.</t>
         </is>
       </c>
       <c r="C140" s="145" t="inlineStr">
         <is>
-          <t>한 컷 2~4초 — 다꾸 쇼츠의 리듬</t>
+          <t>60fps면 나중에 슬로우 가능. 한 번 해두면 유지된다</t>
         </is>
       </c>
       <c r="D140" s="145" t="n"/>
     </row>
-    <row r="141" ht="34" customHeight="1" s="43">
+    <row r="141" ht="47" customHeight="1" s="43">
       <c r="A141" s="259" t="inlineStr">
         <is>
-          <t>④ 첫 1초 옮기기</t>
+          <t>⑤ 초점·노출 잠금</t>
         </is>
       </c>
       <c r="B141" s="145" t="inlineStr">
         <is>
-          <t>★ 장면 클립을 길게 눌러 맨 앞으로 드래그.</t>
+          <t>촬영 화면에서 비커를 길게 누르기 → 'AE/AF 잠금'(아이폰) 또는 자물쇠 표시.</t>
         </is>
       </c>
       <c r="C141" s="145" t="inlineStr">
         <is>
-          <t>가장 중요한 한 단계</t>
+          <t>안 하면 손이 들어올 때마다 화면이 밝아졌다 어두워졌다 한다</t>
         </is>
       </c>
       <c r="D141" s="145" t="n"/>
     </row>
-    <row r="142" ht="34" customHeight="1" s="43">
+    <row r="142" ht="47" customHeight="1" s="43">
       <c r="A142" s="259" t="inlineStr">
         <is>
-          <t>⑤ 지루한 구간 빠르게</t>
+          <t>⑥ 마이크</t>
         </is>
       </c>
       <c r="B142" s="145" t="inlineStr">
         <is>
-          <t>젓기처럼 긴 클립 → '속도' → '일반' → 1.3~1.5배.</t>
+          <t>수신기를 폰에 꽂고, 핀(송신기)은 비커 옆 5~10cm 화면 밖에 집게로. 송신기 전원 확인.</t>
         </is>
       </c>
       <c r="C142" s="145" t="inlineStr">
         <is>
-          <t>2배를 넘기면 소리가 어색해진다</t>
+          <t>잡음 크면 더 가깝게</t>
         </is>
       </c>
       <c r="D142" s="145" t="n"/>
@@ -15015,71 +15104,71 @@
     <row r="143" ht="34" customHeight="1" s="43">
       <c r="A143" s="259" t="inlineStr">
         <is>
-          <t>⑥ 전환 효과 없음</t>
+          <t>⑦ 소음 · 알림 끄기</t>
         </is>
       </c>
       <c r="B143" s="145" t="inlineStr">
         <is>
-          <t>클립 사이 작은 흰 네모(전환)는 건드리지 않는다.</t>
+          <t>에어컨·냉장고·선풍기 끄기 · 방해금지(또는 비행기) 모드 · 렌즈 닦기.</t>
         </is>
       </c>
       <c r="C143" s="145" t="inlineStr">
         <is>
-          <t>하드컷이 ASMR에 맞다</t>
+          <t>알림음·뿌연 화면 방지</t>
         </is>
       </c>
       <c r="D143" s="145" t="n"/>
     </row>
-    <row r="144" ht="47" customHeight="1" s="43">
+    <row r="144" ht="22" customHeight="1" s="43">
       <c r="A144" s="259" t="inlineStr">
         <is>
-          <t>⑦ 소리 다듬기</t>
+          <t>⑧ 테스트 10초</t>
         </is>
       </c>
       <c r="B144" s="145" t="inlineStr">
         <is>
-          <t>클립 선택 → '음량'으로 클립끼리 크기 맞추기 → '노이즈 감소' 켜기. 배경음악 넣지 않기.</t>
+          <t>막대로 저어 찍고 이어폰으로 들어보기.</t>
         </is>
       </c>
       <c r="C144" s="145" t="inlineStr">
         <is>
-          <t>편집에서 제일 시간 쓸 곳</t>
+          <t>화면보다 소리 먼저 확인</t>
         </is>
       </c>
       <c r="D144" s="145" t="n"/>
     </row>
-    <row r="145" ht="47" customHeight="1" s="43">
-      <c r="A145" s="259" t="inlineStr">
-        <is>
-          <t>⑧ 필터 하나 고정</t>
-        </is>
-      </c>
-      <c r="B145" s="145" t="inlineStr">
-        <is>
-          <t>'필터' → 밝고 담백한 것 하나(강도 30~50%) → 모두에 적용. 매번 같은 필터.</t>
-        </is>
-      </c>
-      <c r="C145" s="145" t="inlineStr">
-        <is>
-          <t>계정 톤</t>
-        </is>
-      </c>
-      <c r="D145" s="145" t="n"/>
-    </row>
-    <row r="146" ht="73" customHeight="1" s="43">
+    <row r="145" ht="28" customHeight="1" s="43">
+      <c r="A145" s="140" t="inlineStr">
+        <is>
+          <t>찍는 법</t>
+        </is>
+      </c>
+      <c r="B145" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C145" s="140" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="D145" s="258" t="n"/>
+    </row>
+    <row r="146" ht="34" customHeight="1" s="43">
       <c r="A146" s="259" t="inlineStr">
         <is>
-          <t>⑨ 자막 1~2개</t>
+          <t>한 번 녹화 = 동작 하나</t>
         </is>
       </c>
       <c r="B146" s="145" t="inlineStr">
         <is>
-          <t>'텍스트 추가' → 원료명·%만(예: '카보머 0.5%'), 작고 깔끔한 폰트 · 흰 글씨 + 얇은 그림자. 마지막 컷에 '출시 알림은 프로필 링크'. 위트 한 줄도 여기서(§6).</t>
+          <t>녹화 시작 → 2초 가만히 → 동작 3~5초 → 2초 가만히 → 정지.</t>
         </is>
       </c>
       <c r="C146" s="145" t="inlineStr">
         <is>
-          <t>화면 중간 높이에 — 맨 아래 20%·오른쪽 끝은 좋아요·캡션 버튼에 가린다</t>
+          <t>앞뒤 2초는 편집에서 자를 여유</t>
         </is>
       </c>
       <c r="D146" s="145" t="n"/>
@@ -15087,245 +15176,262 @@
     <row r="147" ht="34" customHeight="1" s="43">
       <c r="A147" s="259" t="inlineStr">
         <is>
-          <t>⑩ CapCut 엔딩 삭제</t>
+          <t>실제 공정 순서대로</t>
         </is>
       </c>
       <c r="B147" s="145" t="inlineStr">
         <is>
-          <t>타임라인 맨 끝에 CapCut 로고 클립이 붙어 있으면 선택 → 삭제.</t>
+          <t>실험 순서 그대로 찍는다. 첫 1초 순서는 편집에서 바꾼다(§6 구성).</t>
         </is>
       </c>
       <c r="C147" s="145" t="inlineStr">
         <is>
-          <t>워터마크 없는 원본(§13 규칙)</t>
+          <t>실험에 집중 — 추가 시간 0분</t>
         </is>
       </c>
       <c r="D147" s="145" t="n"/>
     </row>
-    <row r="148" ht="47" customHeight="1" s="43">
+    <row r="148" ht="34" customHeight="1" s="43">
       <c r="A148" s="259" t="inlineStr">
         <is>
-          <t>⑪ 내보내기</t>
+          <t>★ 장면은 미리 녹화</t>
         </is>
       </c>
       <c r="B148" s="145" t="inlineStr">
         <is>
-          <t>오른쪽 위 해상도 → 1080p · 30 또는 60fps → 내보내기 → 갤러리 저장.</t>
+          <t>중화·유화처럼 한 번뿐인 순간은 그 직전에 녹화를 켜두고, 가능하면 2~3번.</t>
         </is>
       </c>
       <c r="C148" s="145" t="inlineStr">
         <is>
-          <t>이 원본 하나를 3채널에 올린다</t>
+          <t>놓치면 다시 못 찍는다</t>
         </is>
       </c>
       <c r="D148" s="145" t="n"/>
     </row>
-    <row r="149" ht="34" customHeight="1" s="43">
+    <row r="149" ht="22" customHeight="1" s="43">
       <c r="A149" s="259" t="inlineStr">
         <is>
-          <t>⑫ 다음 주 재사용</t>
+          <t>망쳐도 계속 찍기</t>
         </is>
       </c>
       <c r="B149" s="145" t="inlineStr">
         <is>
-          <t>이 프로젝트를 복제해 클립만 바꾸면 필터·자막 스타일이 그대로.</t>
+          <t>분리·실패 배치도 그대로 찍어둔다.</t>
         </is>
       </c>
       <c r="C149" s="145" t="inlineStr">
         <is>
-          <t>두 번째부터 15분</t>
+          <t>실패담 = 콘텐츠(§3 소재 은행)</t>
         </is>
       </c>
       <c r="D149" s="145" t="n"/>
     </row>
-    <row r="150" ht="30" customHeight="1" s="43">
-      <c r="A150" s="79" t="inlineStr">
-        <is>
-          <t>완성 기준 세 가지: 15~30초 · 첫 1초가 가장 만족스러운 장면 · 소리가 또렷함. 이것만 되면 올린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="28" customHeight="1" s="43">
-      <c r="A151" s="140" t="inlineStr">
-        <is>
-          <t>주차</t>
-        </is>
-      </c>
-      <c r="B151" s="140" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-      <c r="C151" s="140" t="inlineStr">
-        <is>
-          <t>통과 기준</t>
-        </is>
-      </c>
-      <c r="D151" s="258" t="n"/>
-    </row>
-    <row r="152" ht="60" customHeight="1" s="43">
-      <c r="A152" s="259" t="inlineStr">
-        <is>
-          <t>1주차 · 촬영만 (20분)</t>
-        </is>
-      </c>
-      <c r="B152" s="145" t="inlineStr">
-        <is>
-          <t>물 따르기 · 막대로 젓기 · 저울에 한 방울씩 떨어뜨리기를 §11 세팅 순서대로, 같은 장면을 거리만 바꿔 3번 찍기.</t>
-        </is>
-      </c>
-      <c r="C152" s="145" t="inlineStr">
-        <is>
-          <t>찍고 바로 이어폰으로 들어보기 — 화면보다 소리 먼저</t>
-        </is>
-      </c>
-      <c r="D152" s="145" t="n"/>
-    </row>
-    <row r="153" ht="34" customHeight="1" s="43">
-      <c r="A153" s="259" t="inlineStr">
-        <is>
-          <t>2주차 · CapCut 편집 (30분)</t>
-        </is>
-      </c>
-      <c r="B153" s="145" t="inlineStr">
-        <is>
-          <t>1주차 영상으로 위 편집 단계 ①~⑪ 따라 15초 하나 완성.</t>
-        </is>
-      </c>
-      <c r="C153" s="145" t="inlineStr">
-        <is>
-          <t>15초 1개 완성. 이번 주는 안 올려도 OK</t>
-        </is>
-      </c>
-      <c r="D153" s="145" t="n"/>
-    </row>
-    <row r="154" ht="60" customHeight="1" s="43">
-      <c r="A154" s="259" t="inlineStr">
-        <is>
-          <t>3주차 · 첫 업로드</t>
-        </is>
-      </c>
-      <c r="B154" s="145" t="inlineStr">
-        <is>
-          <t>주말 키트의 잔탄검 젤 만들기를 콘티(§7)대로 찍어 §13 업로드 방법으로 첫 영상. 카보머가 오면 다음은 '중화되는 순간'(★).</t>
-        </is>
-      </c>
-      <c r="C154" s="145" t="inlineStr">
-        <is>
-          <t>완벽 ❌, 올리기 ⭕. 10번째가 1번째보다 나으면 성공</t>
-        </is>
-      </c>
-      <c r="D154" s="145" t="n"/>
-    </row>
-    <row r="155" ht="28" customHeight="1" s="43">
-      <c r="A155" s="140" t="inlineStr">
-        <is>
-          <t>흔한 실수</t>
-        </is>
-      </c>
-      <c r="B155" s="140" t="inlineStr">
-        <is>
-          <t>대신 이렇게</t>
-        </is>
-      </c>
-      <c r="C155" s="140" t="inlineStr"/>
-      <c r="D155" s="258" t="n"/>
-    </row>
-    <row r="156" ht="34" customHeight="1" s="43">
+    <row r="150" ht="22" customHeight="1" s="43">
+      <c r="A150" s="259" t="inlineStr">
+        <is>
+          <t>분량</t>
+        </is>
+      </c>
+      <c r="B150" s="145" t="inlineStr">
+        <is>
+          <t>실험 30분에 클립 7~15개면 충분.</t>
+        </is>
+      </c>
+      <c r="C150" s="145" t="inlineStr">
+        <is>
+          <t>영상 2개(다음 주 분량)가 나온다</t>
+        </is>
+      </c>
+      <c r="D150" s="145" t="n"/>
+    </row>
+    <row r="151" ht="34" customHeight="1" s="43">
+      <c r="A151" s="79" t="inlineStr">
+        <is>
+          <t>이번 주 할 일 하나: 거치대 + 핀마이크 주문(폰 단자 확인) → 기다리는 동안 §13 계정 세팅 ①~④ → 도착한 첫 주말 물로 20분 촬영(§12 1주차).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" s="43"/>
+    <row r="153" ht="22" customHeight="1" s="43">
+      <c r="A153" s="257" t="inlineStr">
+        <is>
+          <t>§12. CapCut 편집 · 3주 연습 — 원료 아끼지 말고 물로 시작 (일요일 30분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="28" customHeight="1" s="43">
+      <c r="A154" s="140" t="inlineStr">
+        <is>
+          <t>편집 단계</t>
+        </is>
+      </c>
+      <c r="B154" s="140" t="inlineStr">
+        <is>
+          <t>하는 법</t>
+        </is>
+      </c>
+      <c r="C154" s="140" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D154" s="258" t="n"/>
+    </row>
+    <row r="155" ht="47" customHeight="1" s="43">
+      <c r="A155" s="259" t="inlineStr">
+        <is>
+          <t>① 새 프로젝트</t>
+        </is>
+      </c>
+      <c r="B155" s="145" t="inlineStr">
+        <is>
+          <t>CapCut(무료) → 새 프로젝트 → 토요일 클립을 공정 순서대로 모두 선택 → 추가.</t>
+        </is>
+      </c>
+      <c r="C155" s="145" t="inlineStr"/>
+      <c r="D155" s="145" t="n"/>
+    </row>
+    <row r="156" ht="22" customHeight="1" s="43">
       <c r="A156" s="259" t="inlineStr">
         <is>
-          <t>장비부터 많이 사기</t>
+          <t>② 비율</t>
         </is>
       </c>
       <c r="B156" s="145" t="inlineStr">
         <is>
-          <t>거치대 + 마이크로 10개 찍어본 뒤 판단</t>
-        </is>
-      </c>
-      <c r="C156" s="145" t="inlineStr"/>
+          <t>하단 메뉴 '비율' → 9:16.</t>
+        </is>
+      </c>
+      <c r="C156" s="145" t="inlineStr">
+        <is>
+          <t>릴스·쇼츠·틱톡 공통</t>
+        </is>
+      </c>
       <c r="D156" s="145" t="n"/>
     </row>
-    <row r="157" ht="34" customHeight="1" s="43">
+    <row r="157" ht="47" customHeight="1" s="43">
       <c r="A157" s="259" t="inlineStr">
         <is>
-          <t>편집 화려하게 하기</t>
+          <t>③ 자르기 (분할)</t>
         </is>
       </c>
       <c r="B157" s="145" t="inlineStr">
         <is>
-          <t>이 포맷은 편집이 적을수록 좋다 — 소리와 첫 1초가 승부</t>
-        </is>
-      </c>
-      <c r="C157" s="145" t="inlineStr"/>
+          <t>클립을 누르고 동작 시작 지점에 흰 세로선 → '분할' → 앞 군더더기 선택 → 삭제. 끝도 같게.</t>
+        </is>
+      </c>
+      <c r="C157" s="145" t="inlineStr">
+        <is>
+          <t>한 컷 2~4초 — 다꾸 쇼츠의 리듬</t>
+        </is>
+      </c>
       <c r="D157" s="145" t="n"/>
     </row>
-    <row r="158" ht="22" customHeight="1" s="43">
+    <row r="158" ht="34" customHeight="1" s="43">
       <c r="A158" s="259" t="inlineStr">
         <is>
-          <t>앵글 매번 바꾸기</t>
+          <t>④ 첫 1초 옮기기</t>
         </is>
       </c>
       <c r="B158" s="145" t="inlineStr">
         <is>
-          <t>같은 세팅 반복 = 계정의 화면 톤</t>
-        </is>
-      </c>
-      <c r="C158" s="145" t="inlineStr"/>
+          <t>★ 장면 클립을 길게 눌러 맨 앞으로 드래그.</t>
+        </is>
+      </c>
+      <c r="C158" s="145" t="inlineStr">
+        <is>
+          <t>가장 중요한 한 단계</t>
+        </is>
+      </c>
       <c r="D158" s="145" t="n"/>
     </row>
-    <row r="159" ht="22" customHeight="1" s="43">
+    <row r="159" ht="34" customHeight="1" s="43">
       <c r="A159" s="259" t="inlineStr">
         <is>
-          <t>1~2개 보고 포기</t>
+          <t>⑤ 지루한 구간 빠르게</t>
         </is>
       </c>
       <c r="B159" s="145" t="inlineStr">
         <is>
-          <t>4주(8개)는 보고 판단(§5)</t>
-        </is>
-      </c>
-      <c r="C159" s="145" t="inlineStr"/>
+          <t>젓기처럼 긴 클립 → '속도' → '일반' → 1.3~1.5배.</t>
+        </is>
+      </c>
+      <c r="C159" s="145" t="inlineStr">
+        <is>
+          <t>2배를 넘기면 소리가 어색해진다</t>
+        </is>
+      </c>
       <c r="D159" s="145" t="n"/>
     </row>
-    <row r="161" ht="22" customHeight="1" s="43">
-      <c r="A161" s="257" t="inlineStr">
-        <is>
-          <t>§13. 채널 운영 · 계정 세팅 · 업로드 — 영상은 한 번 만들어 3채널, 블로그는 역할을 나눠 2곳, 소통은 인스타로</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="28" customHeight="1" s="43">
-      <c r="A162" s="140" t="inlineStr">
-        <is>
-          <t>채널</t>
-        </is>
-      </c>
-      <c r="B162" s="140" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="C162" s="140" t="inlineStr">
-        <is>
-          <t>운영 규칙</t>
-        </is>
-      </c>
-      <c r="D162" s="258" t="n"/>
-    </row>
-    <row r="163" ht="34" customHeight="1" s="43">
+    <row r="160" ht="34" customHeight="1" s="43">
+      <c r="A160" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 전환 효과 없음</t>
+        </is>
+      </c>
+      <c r="B160" s="145" t="inlineStr">
+        <is>
+          <t>클립 사이 작은 흰 네모(전환)는 건드리지 않는다.</t>
+        </is>
+      </c>
+      <c r="C160" s="145" t="inlineStr">
+        <is>
+          <t>하드컷이 ASMR에 맞다</t>
+        </is>
+      </c>
+      <c r="D160" s="145" t="n"/>
+    </row>
+    <row r="161" ht="47" customHeight="1" s="43">
+      <c r="A161" s="259" t="inlineStr">
+        <is>
+          <t>⑦ 소리 다듬기</t>
+        </is>
+      </c>
+      <c r="B161" s="145" t="inlineStr">
+        <is>
+          <t>클립 선택 → '음량'으로 클립끼리 크기 맞추기 → '노이즈 감소' 켜기. 배경음악 넣지 않기.</t>
+        </is>
+      </c>
+      <c r="C161" s="145" t="inlineStr">
+        <is>
+          <t>편집에서 제일 시간 쓸 곳</t>
+        </is>
+      </c>
+      <c r="D161" s="145" t="n"/>
+    </row>
+    <row r="162" ht="47" customHeight="1" s="43">
+      <c r="A162" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 필터 하나 고정</t>
+        </is>
+      </c>
+      <c r="B162" s="145" t="inlineStr">
+        <is>
+          <t>'필터' → 밝고 담백한 것 하나(강도 30~50%) → 모두에 적용. 매번 같은 필터.</t>
+        </is>
+      </c>
+      <c r="C162" s="145" t="inlineStr">
+        <is>
+          <t>계정 톤</t>
+        </is>
+      </c>
+      <c r="D162" s="145" t="n"/>
+    </row>
+    <row r="163" ht="73" customHeight="1" s="43">
       <c r="A163" s="259" t="inlineStr">
         <is>
-          <t>인스타 릴스</t>
+          <t>⑨ 자막 1~2개</t>
         </is>
       </c>
       <c r="B163" s="145" t="inlineStr">
         <is>
-          <t>집: 단골·팬덤, DM, 투표, 대기자 링크(§8)</t>
+          <t>'텍스트 추가' → 원료명·%만(예: '카보머 0.5%'), 작고 깔끔한 폰트 · 흰 글씨 + 얇은 그림자. 마지막 컷에 '출시 알림은 프로필 링크'. 위트 한 줄도 여기서(§6).</t>
         </is>
       </c>
       <c r="C163" s="145" t="inlineStr">
         <is>
-          <t>24시간 안에 직접 답장(출퇴근 2번). 소통은 여기로 모은다</t>
+          <t>화면 중간 높이에 — 맨 아래 20%·오른쪽 끝은 좋아요·캡션 버튼에 가린다</t>
         </is>
       </c>
       <c r="D163" s="145" t="n"/>
@@ -15333,35 +15439,35 @@
     <row r="164" ht="34" customHeight="1" s="43">
       <c r="A164" s="259" t="inlineStr">
         <is>
-          <t>유튜브 쇼츠</t>
+          <t>⑩ CapCut 엔딩 삭제</t>
         </is>
       </c>
       <c r="B164" s="145" t="inlineStr">
         <is>
-          <t>검색: 유튜브·구글 검색에 오래 남아 몇 달 뒤에도 유입</t>
+          <t>타임라인 맨 끝에 CapCut 로고 클립이 붙어 있으면 선택 → 삭제.</t>
         </is>
       </c>
       <c r="C164" s="145" t="inlineStr">
         <is>
-          <t>제목·설명에 ①·②층 키워드. 댓글은 짧게 + '자세한 이야기는 인스타'</t>
+          <t>워터마크 없는 원본(§13 규칙)</t>
         </is>
       </c>
       <c r="D164" s="145" t="n"/>
     </row>
-    <row r="165" ht="34" customHeight="1" s="43">
+    <row r="165" ht="47" customHeight="1" s="43">
       <c r="A165" s="259" t="inlineStr">
         <is>
-          <t>틱톡</t>
+          <t>⑪ 내보내기</t>
         </is>
       </c>
       <c r="B165" s="145" t="inlineStr">
         <is>
-          <t>발견: 처음 보는 사람에게 퍼지는 곳 · 첫 1초 반응 테스트</t>
+          <t>오른쪽 위 해상도 → 1080p · 30 또는 60fps → 내보내기 → 갤러리 저장.</t>
         </is>
       </c>
       <c r="C165" s="145" t="inlineStr">
         <is>
-          <t>댓글은 짧게 + 인스타로 연결</t>
+          <t>이 원본 하나를 3채널에 올린다</t>
         </is>
       </c>
       <c r="D165" s="145" t="n"/>
@@ -15369,53 +15475,42 @@
     <row r="166" ht="34" customHeight="1" s="43">
       <c r="A166" s="259" t="inlineStr">
         <is>
-          <t>네이버 블로그</t>
+          <t>⑫ 다음 주 재사용</t>
         </is>
       </c>
       <c r="B166" s="145" t="inlineStr">
         <is>
-          <t>네이버 검색: 경험·일상 톤 — 고민 해결·개발일지(§9)</t>
+          <t>이 프로젝트를 복제해 클립만 바꾸면 필터·자막 스타일이 그대로.</t>
         </is>
       </c>
       <c r="C166" s="145" t="inlineStr">
         <is>
-          <t>주 1편</t>
+          <t>두 번째부터 15분</t>
         </is>
       </c>
       <c r="D166" s="145" t="n"/>
     </row>
-    <row r="167" ht="60" customHeight="1" s="43">
-      <c r="A167" s="259" t="inlineStr">
-        <is>
-          <t>브랜드 사이트</t>
-        </is>
-      </c>
-      <c r="B167" s="145" t="inlineStr">
-        <is>
-          <t>구글 + 네이버 웹문서: 정리형 가이드 '성분 사전'(예: 판테놀 총정리 — 역할·농도·함께 쓰는 성분). 재료 = 시험대비 원료맵</t>
-        </is>
-      </c>
-      <c r="C167" s="145" t="inlineStr">
-        <is>
-          <t>월 2편(새 페이지 또는 기존 페이지 보완). 네이버 루틴이 잡힌 1~2개월 뒤 시작</t>
-        </is>
-      </c>
-      <c r="D167" s="145" t="n"/>
+    <row r="167" ht="30" customHeight="1" s="43">
+      <c r="A167" s="79" t="inlineStr">
+        <is>
+          <t>완성 기준 세 가지: 15~30초 · 첫 1초가 가장 만족스러운 장면 · 소리가 또렷함. 이것만 되면 올린다.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="28" customHeight="1" s="43">
       <c r="A168" s="140" t="inlineStr">
         <is>
-          <t>계정 세팅 (하루 저녁 1시간)</t>
+          <t>주차</t>
         </is>
       </c>
       <c r="B168" s="140" t="inlineStr">
         <is>
-          <t>방법</t>
+          <t>할 일</t>
         </is>
       </c>
       <c r="C168" s="140" t="inlineStr">
         <is>
-          <t>포인트</t>
+          <t>통과 기준</t>
         </is>
       </c>
       <c r="D168" s="258" t="n"/>
@@ -15423,17 +15518,17 @@
     <row r="169" ht="60" customHeight="1" s="43">
       <c r="A169" s="259" t="inlineStr">
         <is>
-          <t>① 이름 정하기</t>
+          <t>1주차 · 촬영만 (20분)</t>
         </is>
       </c>
       <c r="B169" s="145" t="inlineStr">
         <is>
-          <t>3채널 모두 같은 아이디(예: @dadogi.lab). 인스타·유튜브·틱톡에서 각각 검색해 세 곳 다 비어 있는 이름으로.</t>
+          <t>물 따르기 · 막대로 젓기 · 저울에 한 방울씩 떨어뜨리기를 §11 세팅 순서대로, 같은 장면을 거리만 바꿔 3번 찍기.</t>
         </is>
       </c>
       <c r="C169" s="145" t="inlineStr">
         <is>
-          <t>찾아오는 사람이 헷갈리지 않게</t>
+          <t>찍고 바로 이어폰으로 들어보기 — 화면보다 소리 먼저</t>
         </is>
       </c>
       <c r="D169" s="145" t="n"/>
@@ -15441,470 +15536,1191 @@
     <row r="170" ht="34" customHeight="1" s="43">
       <c r="A170" s="259" t="inlineStr">
         <is>
-          <t>② 브랜드 전용 이메일</t>
+          <t>2주차 · CapCut 편집 (30분)</t>
         </is>
       </c>
       <c r="B170" s="145" t="inlineStr">
         <is>
-          <t>새 구글 계정을 하나 만들어 3채널 모두 이걸로 가입. 개인 계정과 분리.</t>
+          <t>1주차 영상으로 위 편집 단계 ①~⑪ 따라 15초 하나 완성.</t>
         </is>
       </c>
       <c r="C170" s="145" t="inlineStr">
         <is>
-          <t>나중에 사업자로 넘길 때 편하다</t>
+          <t>15초 1개 완성. 이번 주는 안 올려도 OK</t>
         </is>
       </c>
       <c r="D170" s="145" t="n"/>
     </row>
-    <row r="171" ht="73" customHeight="1" s="43">
+    <row r="171" ht="60" customHeight="1" s="43">
       <c r="A171" s="259" t="inlineStr">
         <is>
-          <t>③ 인스타 개설 · 프로페셔널 전환</t>
+          <t>3주차 · 첫 업로드</t>
         </is>
       </c>
       <c r="B171" s="145" t="inlineStr">
         <is>
-          <t>프로필 → 상단 아이디 옆 ▼ → 계정 추가 → 새 계정 만들기(개인 계정과 한 폰에서 전환). 설정 → 계정 유형 및 도구 → 프로페셔널 계정으로 전환 → '크리에이터'.</t>
+          <t>주말 키트의 잔탄검 젤 만들기를 콘티(§7)대로 찍어 §13 업로드 방법으로 첫 영상. 카보머가 오면 다음은 '중화되는 순간'(★).</t>
         </is>
       </c>
       <c r="C171" s="145" t="inlineStr">
         <is>
-          <t>조회·저장·시청 시간 통계가 열린다</t>
+          <t>완벽 ❌, 올리기 ⭕. 10번째가 1번째보다 나으면 성공</t>
         </is>
       </c>
       <c r="D171" s="145" t="n"/>
     </row>
-    <row r="172" ht="60" customHeight="1" s="43">
-      <c r="A172" s="259" t="inlineStr">
-        <is>
-          <t>④ 인스타 프로필</t>
-        </is>
-      </c>
-      <c r="B172" s="145" t="inlineStr">
-        <is>
-          <t>사진(로고 없으면 완성 용기 탑뷰) · 이름 '다도기 | 지성·민감 진정 크림 개발 중' · 소개·링크는 §8 그대로(링크 = 대기자 폼, 상점 ❌).</t>
-        </is>
-      </c>
-      <c r="C172" s="145" t="inlineStr">
-        <is>
-          <t>누구를 위한 무엇인지 + 할 행동 하나</t>
-        </is>
-      </c>
-      <c r="D172" s="145" t="n"/>
-    </row>
-    <row r="173" ht="22" customHeight="1" s="43">
+    <row r="172" ht="28" customHeight="1" s="43">
+      <c r="A172" s="140" t="inlineStr">
+        <is>
+          <t>흔한 실수</t>
+        </is>
+      </c>
+      <c r="B172" s="140" t="inlineStr">
+        <is>
+          <t>대신 이렇게</t>
+        </is>
+      </c>
+      <c r="C172" s="140" t="inlineStr"/>
+      <c r="D172" s="258" t="n"/>
+    </row>
+    <row r="173" ht="34" customHeight="1" s="43">
       <c r="A173" s="259" t="inlineStr">
         <is>
-          <t>⑤ 2단계 인증</t>
+          <t>장비부터 많이 사기</t>
         </is>
       </c>
       <c r="B173" s="145" t="inlineStr">
         <is>
-          <t>인스타·구글·틱톡 모두 켜기.</t>
-        </is>
-      </c>
-      <c r="C173" s="145" t="inlineStr">
-        <is>
-          <t>해킹당하면 2년이 날아간다</t>
-        </is>
-      </c>
+          <t>거치대 + 마이크로 10개 찍어본 뒤 판단</t>
+        </is>
+      </c>
+      <c r="C173" s="145" t="inlineStr"/>
       <c r="D173" s="145" t="n"/>
     </row>
-    <row r="174" ht="73" customHeight="1" s="43">
+    <row r="174" ht="34" customHeight="1" s="43">
       <c r="A174" s="259" t="inlineStr">
         <is>
-          <t>⑥ 유튜브 채널</t>
+          <t>편집 화려하게 하기</t>
         </is>
       </c>
       <c r="B174" s="145" t="inlineStr">
         <is>
-          <t>같은 구글 계정으로 유튜브 앱 → 프로필 → 채널 만들기(이름 '다도기', 핸들 통일). PC YouTube Studio → 맞춤설정 → 설명에 ①·②층 키워드(§9).</t>
-        </is>
-      </c>
-      <c r="C174" s="145" t="inlineStr">
-        <is>
-          <t>쇼츠는 검색에 오래 남는다</t>
-        </is>
-      </c>
+          <t>이 포맷은 편집이 적을수록 좋다 — 소리와 첫 1초가 승부</t>
+        </is>
+      </c>
+      <c r="C174" s="145" t="inlineStr"/>
       <c r="D174" s="145" t="n"/>
     </row>
-    <row r="175" ht="47" customHeight="1" s="43">
+    <row r="175" ht="22" customHeight="1" s="43">
       <c r="A175" s="259" t="inlineStr">
         <is>
-          <t>⑦ 틱톡</t>
+          <t>앵글 매번 바꾸기</t>
         </is>
       </c>
       <c r="B175" s="145" t="inlineStr">
         <is>
-          <t>같은 이메일로 가입 → 아이디 통일 → 소개는 인스타와 같게. 링크 조건은 아래 규칙 참고.</t>
+          <t>같은 세팅 반복 = 계정의 화면 톤</t>
         </is>
       </c>
       <c r="C175" s="145" t="inlineStr"/>
       <c r="D175" s="145" t="n"/>
     </row>
-    <row r="176" ht="47" customHeight="1" s="43">
+    <row r="176" ht="22" customHeight="1" s="43">
       <c r="A176" s="259" t="inlineStr">
         <is>
-          <t>⑧ 새 계정 길들이기 (3~5일)</t>
+          <t>1~2개 보고 포기</t>
         </is>
       </c>
       <c r="B176" s="145" t="inlineStr">
         <is>
-          <t>새 계정으로 하루 10분 다꾸 ASMR·화장품 만들기·크림 ASMR 쇼츠를 보고, 좋은 건 저장 → 컬렉션 '참고'.</t>
-        </is>
-      </c>
-      <c r="C176" s="145" t="inlineStr">
-        <is>
-          <t>피드가 이 장르로 채워지고, 저장한 영상 = 스와이프 파일</t>
-        </is>
-      </c>
+          <t>4주(8개)는 보고 판단(§5)</t>
+        </is>
+      </c>
+      <c r="C176" s="145" t="inlineStr"/>
       <c r="D176" s="145" t="n"/>
     </row>
-    <row r="177" ht="28" customHeight="1" s="43">
-      <c r="A177" s="140" t="inlineStr">
-        <is>
-          <t>업로드 (영상 1개 · 3채널 15분)</t>
-        </is>
-      </c>
-      <c r="B177" s="140" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="C177" s="140" t="inlineStr">
+    <row r="177" s="43"/>
+    <row r="178" ht="22" customHeight="1" s="43">
+      <c r="A178" s="257" t="inlineStr">
+        <is>
+          <t>§13. 채널 운영 · 계정 세팅 · 업로드 — 영상은 한 번 만들어 3채널, 블로그는 역할을 나눠 2곳, 소통은 인스타로</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="28" customHeight="1" s="43">
+      <c r="A179" s="140" t="inlineStr">
+        <is>
+          <t>채널</t>
+        </is>
+      </c>
+      <c r="B179" s="140" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="C179" s="140" t="inlineStr">
+        <is>
+          <t>운영 규칙</t>
+        </is>
+      </c>
+      <c r="D179" s="258" t="n"/>
+    </row>
+    <row r="180" ht="34" customHeight="1" s="43">
+      <c r="A180" s="259" t="inlineStr">
+        <is>
+          <t>인스타 릴스</t>
+        </is>
+      </c>
+      <c r="B180" s="145" t="inlineStr">
+        <is>
+          <t>집: 단골·팬덤, DM, 투표, 대기자 링크(§8)</t>
+        </is>
+      </c>
+      <c r="C180" s="145" t="inlineStr">
+        <is>
+          <t>24시간 안에 직접 답장(출퇴근 2번). 소통은 여기로 모은다</t>
+        </is>
+      </c>
+      <c r="D180" s="145" t="n"/>
+    </row>
+    <row r="181" ht="34" customHeight="1" s="43">
+      <c r="A181" s="259" t="inlineStr">
+        <is>
+          <t>유튜브 쇼츠</t>
+        </is>
+      </c>
+      <c r="B181" s="145" t="inlineStr">
+        <is>
+          <t>검색: 유튜브·구글 검색에 오래 남아 몇 달 뒤에도 유입</t>
+        </is>
+      </c>
+      <c r="C181" s="145" t="inlineStr">
+        <is>
+          <t>제목·설명에 ①·②층 키워드. 댓글은 짧게 + '자세한 이야기는 인스타'</t>
+        </is>
+      </c>
+      <c r="D181" s="145" t="n"/>
+    </row>
+    <row r="182" ht="34" customHeight="1" s="43">
+      <c r="A182" s="259" t="inlineStr">
+        <is>
+          <t>틱톡</t>
+        </is>
+      </c>
+      <c r="B182" s="145" t="inlineStr">
+        <is>
+          <t>발견: 처음 보는 사람에게 퍼지는 곳 · 첫 1초 반응 테스트</t>
+        </is>
+      </c>
+      <c r="C182" s="145" t="inlineStr">
+        <is>
+          <t>댓글은 짧게 + 인스타로 연결</t>
+        </is>
+      </c>
+      <c r="D182" s="145" t="n"/>
+    </row>
+    <row r="183" ht="34" customHeight="1" s="43">
+      <c r="A183" s="259" t="inlineStr">
+        <is>
+          <t>네이버 블로그</t>
+        </is>
+      </c>
+      <c r="B183" s="145" t="inlineStr">
+        <is>
+          <t>네이버 검색: 경험·일상 톤 — 고민 해결·개발일지(§9)</t>
+        </is>
+      </c>
+      <c r="C183" s="145" t="inlineStr">
+        <is>
+          <t>주 1편</t>
+        </is>
+      </c>
+      <c r="D183" s="145" t="n"/>
+    </row>
+    <row r="184" ht="60" customHeight="1" s="43">
+      <c r="A184" s="259" t="inlineStr">
+        <is>
+          <t>브랜드 사이트</t>
+        </is>
+      </c>
+      <c r="B184" s="145" t="inlineStr">
+        <is>
+          <t>구글 + 네이버 웹문서: 정리형 가이드 '성분 사전'(예: 판테놀 총정리 — 역할·농도·함께 쓰는 성분). 재료 = 시험대비 원료맵</t>
+        </is>
+      </c>
+      <c r="C184" s="145" t="inlineStr">
+        <is>
+          <t>월 2편(새 페이지 또는 기존 페이지 보완). 네이버 루틴이 잡힌 1~2개월 뒤 시작</t>
+        </is>
+      </c>
+      <c r="D184" s="145" t="n"/>
+    </row>
+    <row r="185" ht="28" customHeight="1" s="43">
+      <c r="A185" s="140" t="inlineStr">
+        <is>
+          <t>계정 세팅 (하루 저녁 1시간)</t>
+        </is>
+      </c>
+      <c r="B185" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C185" s="140" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="D177" s="258" t="n"/>
-    </row>
-    <row r="178" ht="86" customHeight="1" s="43">
-      <c r="A178" s="259" t="inlineStr">
-        <is>
-          <t>캡션 (한 번 써서 3곳에)</t>
-        </is>
-      </c>
-      <c r="B178" s="145" t="inlineStr">
-        <is>
-          <t>첫 줄 = 장면 한 줄(예: '카보머가 젤리가 되는 순간 🫧') / 둘째 줄 = 무엇을 만드는 중인지 / '출시 알림은 프로필 링크에서' / 해시태그 3~5개(#화장품만들기 #ASMR #지성피부 #홈랩 #카보머).</t>
-        </is>
-      </c>
-      <c r="C178" s="145" t="inlineStr">
-        <is>
-          <t>효능 표현 금지('여드름 개선' '진정 효과 입증' ❌) — 과정·질감만 말한다(수요검증 §3)</t>
-        </is>
-      </c>
-      <c r="D178" s="145" t="n"/>
-    </row>
-    <row r="179" ht="60" customHeight="1" s="43">
-      <c r="A179" s="259" t="inlineStr">
-        <is>
-          <t>인스타 릴스</t>
-        </is>
-      </c>
-      <c r="B179" s="145" t="inlineStr">
-        <is>
-          <t>+ → 릴스 → 영상 선택 → 커버 편집(완성 용기나 ★ 장면) → 캡션 → 고급 설정 → 예약(화·금 저녁 7~9시) · '프로필 그리드에 표시' 켜기.</t>
-        </is>
-      </c>
-      <c r="C179" s="145" t="inlineStr">
-        <is>
-          <t>커버 = 프로필 격자의 얼굴. 매번 비슷한 톤으로</t>
-        </is>
-      </c>
-      <c r="D179" s="145" t="n"/>
-    </row>
-    <row r="180" ht="73" customHeight="1" s="43">
-      <c r="A180" s="259" t="inlineStr">
-        <is>
-          <t>유튜브 쇼츠</t>
-        </is>
-      </c>
-      <c r="B180" s="145" t="inlineStr">
-        <is>
-          <t>유튜브 앱 + → Shorts → 갤러리에서 영상 선택 → 제목(키워드 앞에, 예: '카보머 중화 ASMR | 지성 피부 진정 크림 만들기') → 공개 범위 → 예약.</t>
-        </is>
-      </c>
-      <c r="C180" s="145" t="inlineStr">
-        <is>
-          <t>설명은 PC YouTube Studio에서 나중에 보완 OK</t>
-        </is>
-      </c>
-      <c r="D180" s="145" t="n"/>
-    </row>
-    <row r="181" ht="47" customHeight="1" s="43">
-      <c r="A181" s="259" t="inlineStr">
-        <is>
-          <t>틱톡</t>
-        </is>
-      </c>
-      <c r="B181" s="145" t="inlineStr">
-        <is>
-          <t>+ → 업로드 → 영상 선택 → 캡션 · 커버 → 게시(앱에 예약이 없으면 화·금 저녁에 직접, 1분).</t>
-        </is>
-      </c>
-      <c r="C181" s="145" t="inlineStr"/>
-      <c r="D181" s="145" t="n"/>
-    </row>
-    <row r="182" ht="73" customHeight="1" s="43">
-      <c r="A182" s="259" t="inlineStr">
-        <is>
-          <t>올린 뒤</t>
-        </is>
-      </c>
-      <c r="B182" s="145" t="inlineStr">
-        <is>
-          <t>첫 1~2시간 댓글엔 바로 답글. 48시간 뒤 수요검증 §4 로그에 한 줄 — 볼 숫자: 평균 시청 시간(끝까지 본 비율) · 저장 · 공유 · '어디서 사요?' 댓글·DM.</t>
-        </is>
-      </c>
-      <c r="C182" s="145" t="inlineStr">
-        <is>
-          <t>좋아요·조회수는 참고만. 판단은 4주(8개) 뒤(§5)</t>
-        </is>
-      </c>
-      <c r="D182" s="145" t="n"/>
-    </row>
-    <row r="183" ht="30" customHeight="1" s="43">
-      <c r="A183" s="79" t="inlineStr">
-        <is>
-          <t>메뉴 이름은 앱 업데이트로 조금씩 바뀐다 — 안 보이면 '+ 누르고 업로드'가 기본 흐름이라는 것만 기억.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="28" customHeight="1" s="43">
-      <c r="A184" s="140" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B184" s="140" t="inlineStr">
-        <is>
-          <t>방법</t>
-        </is>
-      </c>
-      <c r="C184" s="140" t="inlineStr">
-        <is>
-          <t>왜</t>
-        </is>
-      </c>
-      <c r="D184" s="258" t="n"/>
-    </row>
-    <row r="185" ht="34" customHeight="1" s="43">
-      <c r="A185" s="259" t="inlineStr">
-        <is>
-          <t>원본 업로드</t>
-        </is>
-      </c>
-      <c r="B185" s="145" t="inlineStr">
-        <is>
-          <t>CapCut에서 내보낸 워터마크 없는 원본을 채널마다 따로 올린다.</t>
-        </is>
-      </c>
-      <c r="C185" s="145" t="inlineStr">
-        <is>
-          <t>다른 앱 로고가 박힌 재업로드는 노출이 준다</t>
-        </is>
-      </c>
-      <c r="D185" s="145" t="n"/>
-    </row>
-    <row r="186" ht="47" customHeight="1" s="43">
+      <c r="D185" s="258" t="n"/>
+    </row>
+    <row r="186" ht="60" customHeight="1" s="43">
       <c r="A186" s="259" t="inlineStr">
         <is>
-          <t>블로그 중복 금지</t>
+          <t>① 이름 정하기</t>
         </is>
       </c>
       <c r="B186" s="145" t="inlineStr">
         <is>
-          <t>같은 글 복사 ❌. 같은 주제라도 구조를 다시 짠다: 네이버 = '써본 이야기' / 사이트 = '총정리'.</t>
+          <t>3채널 모두 같은 아이디(예: @dadogi.lab). 인스타·유튜브·틱톡에서 각각 검색해 세 곳 다 비어 있는 이름으로.</t>
         </is>
       </c>
       <c r="C186" s="145" t="inlineStr">
         <is>
-          <t>유사 문서로 걸러져 검색 누락·블로그 평가 하락 위험 — 노력 3배, 효과 1배</t>
+          <t>찾아오는 사람이 헷갈리지 않게</t>
         </is>
       </c>
       <c r="D186" s="145" t="n"/>
     </row>
-    <row r="187" ht="73" customHeight="1" s="43">
+    <row r="187" ht="34" customHeight="1" s="43">
       <c r="A187" s="259" t="inlineStr">
         <is>
-          <t>브랜드 도메인</t>
+          <t>② 브랜드 전용 이메일</t>
         </is>
       </c>
       <c r="B187" s="145" t="inlineStr">
         <is>
-          <t>도메인 구매 → 사이트 빌더(아임웹·워드프레스 등) 연결 → 구글 서치콘솔 + 네이버 서치어드바이저 등록(반나절). 부담되면 티스토리 + 내 도메인 연결이 중간안.</t>
+          <t>새 구글 계정을 하나 만들어 3채널 모두 이걸로 가입. 개인 계정과 분리.</t>
         </is>
       </c>
       <c r="C187" s="145" t="inlineStr">
         <is>
-          <t>나중에 자사몰과 같은 도메인 → 2년간 쌓은 검색 신뢰가 상점으로 이어진다. 플랫폼 정책이 바뀌어도 남는다</t>
+          <t>나중에 사업자로 넘길 때 편하다</t>
         </is>
       </c>
       <c r="D187" s="145" t="n"/>
     </row>
-    <row r="188" ht="47" customHeight="1" s="43">
+    <row r="188" ht="73" customHeight="1" s="43">
       <c r="A188" s="259" t="inlineStr">
         <is>
-          <t>링크 조건</t>
+          <t>③ 인스타 개설 · 프로페셔널 전환</t>
         </is>
       </c>
       <c r="B188" s="145" t="inlineStr">
         <is>
-          <t>틱톡·쇼츠는 링크에 팔로워 수·계정 유형 조건이 있거나 클릭이 제한될 수 있다 — 개설할 때 확인.</t>
+          <t>프로필 → 상단 아이디 옆 ▼ → 계정 추가 → 새 계정 만들기(개인 계정과 한 폰에서 전환). 설정 → 계정 유형 및 도구 → 프로페셔널 계정으로 전환 → '크리에이터'.</t>
         </is>
       </c>
       <c r="C188" s="145" t="inlineStr">
         <is>
-          <t>대기자 유입의 주 경로는 인스타 프로필 링크·블로그</t>
+          <t>조회·저장·시청 시간 통계가 열린다</t>
         </is>
       </c>
       <c r="D188" s="145" t="n"/>
     </row>
-    <row r="189" ht="34" customHeight="1" s="43">
+    <row r="189" ht="60" customHeight="1" s="43">
       <c r="A189" s="259" t="inlineStr">
         <is>
-          <t>유입 경로 측정</t>
+          <t>④ 인스타 프로필</t>
         </is>
       </c>
       <c r="B189" s="145" t="inlineStr">
         <is>
-          <t>대기자 폼에 '어디서 보고 오셨나요?' 항목, 또는 채널별로 다른 링크.</t>
+          <t>사진(로고 없으면 완성 용기 탑뷰) · 이름 '다도기 | 지성·민감 진정 크림 개발 중' · 소개·링크는 §8 그대로(링크 = 대기자 폼, 상점 ❌).</t>
         </is>
       </c>
       <c r="C189" s="145" t="inlineStr">
         <is>
-          <t>6개월 뒤 채널 정리를 감이 아니라 숫자로</t>
+          <t>누구를 위한 무엇인지 + 할 행동 하나</t>
         </is>
       </c>
       <c r="D189" s="145" t="n"/>
     </row>
-    <row r="190" ht="34" customHeight="1" s="43">
+    <row r="190" ht="22" customHeight="1" s="43">
       <c r="A190" s="259" t="inlineStr">
         <is>
-          <t>규정</t>
+          <t>⑤ 2단계 인증</t>
         </is>
       </c>
       <c r="B190" s="145" t="inlineStr">
         <is>
-          <t>모든 채널에 같은 표시·광고 규칙(수요검증 §3). 판매 후 협찬·광고는 표기.</t>
+          <t>인스타·구글·틱톡 모두 켜기.</t>
         </is>
       </c>
       <c r="C190" s="145" t="inlineStr">
         <is>
-          <t>채널마다 기준이 다르면 실수가 난다</t>
+          <t>해킹당하면 2년이 날아간다</t>
         </is>
       </c>
       <c r="D190" s="145" t="n"/>
     </row>
-    <row r="191" ht="28" customHeight="1" s="43">
-      <c r="A191" s="140" t="inlineStr">
-        <is>
-          <t>시기</t>
-        </is>
-      </c>
-      <c r="B191" s="140" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-      <c r="C191" s="140" t="inlineStr">
-        <is>
-          <t>판단 기준</t>
-        </is>
-      </c>
-      <c r="D191" s="258" t="n"/>
+    <row r="191" ht="73" customHeight="1" s="43">
+      <c r="A191" s="259" t="inlineStr">
+        <is>
+          <t>⑥ 유튜브 채널</t>
+        </is>
+      </c>
+      <c r="B191" s="145" t="inlineStr">
+        <is>
+          <t>같은 구글 계정으로 유튜브 앱 → 프로필 → 채널 만들기(이름 '다도기', 핸들 통일). PC YouTube Studio → 맞춤설정 → 설명에 ①·②층 키워드(§9).</t>
+        </is>
+      </c>
+      <c r="C191" s="145" t="inlineStr">
+        <is>
+          <t>쇼츠는 검색에 오래 남는다</t>
+        </is>
+      </c>
+      <c r="D191" s="145" t="n"/>
     </row>
     <row r="192" ht="47" customHeight="1" s="43">
       <c r="A192" s="259" t="inlineStr">
         <is>
+          <t>⑦ 틱톡</t>
+        </is>
+      </c>
+      <c r="B192" s="145" t="inlineStr">
+        <is>
+          <t>같은 이메일로 가입 → 아이디 통일 → 소개는 인스타와 같게. 링크 조건은 아래 규칙 참고.</t>
+        </is>
+      </c>
+      <c r="C192" s="145" t="inlineStr"/>
+      <c r="D192" s="145" t="n"/>
+    </row>
+    <row r="193" ht="47" customHeight="1" s="43">
+      <c r="A193" s="259" t="inlineStr">
+        <is>
+          <t>⑧ 새 계정 길들이기 (3~5일)</t>
+        </is>
+      </c>
+      <c r="B193" s="145" t="inlineStr">
+        <is>
+          <t>새 계정으로 하루 10분 다꾸 ASMR·화장품 만들기·크림 ASMR 쇼츠를 보고, 좋은 건 저장 → 컬렉션 '참고'.</t>
+        </is>
+      </c>
+      <c r="C193" s="145" t="inlineStr">
+        <is>
+          <t>피드가 이 장르로 채워지고, 저장한 영상 = 스와이프 파일</t>
+        </is>
+      </c>
+      <c r="D193" s="145" t="n"/>
+    </row>
+    <row r="194" ht="28" customHeight="1" s="43">
+      <c r="A194" s="140" t="inlineStr">
+        <is>
+          <t>업로드 (영상 1개 · 3채널 15분)</t>
+        </is>
+      </c>
+      <c r="B194" s="140" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="C194" s="140" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+      <c r="D194" s="258" t="n"/>
+    </row>
+    <row r="195" ht="86" customHeight="1" s="43">
+      <c r="A195" s="259" t="inlineStr">
+        <is>
+          <t>캡션 (한 번 써서 3곳에)</t>
+        </is>
+      </c>
+      <c r="B195" s="145" t="inlineStr">
+        <is>
+          <t>첫 줄 = 장면 한 줄(예: '카보머가 젤리가 되는 순간 🫧') / 둘째 줄 = 무엇을 만드는 중인지 / '출시 알림은 프로필 링크에서' / 해시태그 3~5개(#화장품만들기 #ASMR #지성피부 #홈랩 #카보머).</t>
+        </is>
+      </c>
+      <c r="C195" s="145" t="inlineStr">
+        <is>
+          <t>효능 표현 금지('여드름 개선' '진정 효과 입증' ❌) — 과정·질감만 말한다(수요검증 §3)</t>
+        </is>
+      </c>
+      <c r="D195" s="145" t="n"/>
+    </row>
+    <row r="196" ht="60" customHeight="1" s="43">
+      <c r="A196" s="259" t="inlineStr">
+        <is>
+          <t>인스타 릴스</t>
+        </is>
+      </c>
+      <c r="B196" s="145" t="inlineStr">
+        <is>
+          <t>+ → 릴스 → 영상 선택 → 커버 편집(완성 용기나 ★ 장면) → 캡션 → 고급 설정 → 예약(화·금 저녁 7~9시) · '프로필 그리드에 표시' 켜기.</t>
+        </is>
+      </c>
+      <c r="C196" s="145" t="inlineStr">
+        <is>
+          <t>커버 = 프로필 격자의 얼굴. 매번 비슷한 톤으로</t>
+        </is>
+      </c>
+      <c r="D196" s="145" t="n"/>
+    </row>
+    <row r="197" ht="73" customHeight="1" s="43">
+      <c r="A197" s="259" t="inlineStr">
+        <is>
+          <t>유튜브 쇼츠</t>
+        </is>
+      </c>
+      <c r="B197" s="145" t="inlineStr">
+        <is>
+          <t>유튜브 앱 + → Shorts → 갤러리에서 영상 선택 → 제목(키워드 앞에, 예: '카보머 중화 ASMR | 지성 피부 진정 크림 만들기') → 공개 범위 → 예약.</t>
+        </is>
+      </c>
+      <c r="C197" s="145" t="inlineStr">
+        <is>
+          <t>설명은 PC YouTube Studio에서 나중에 보완 OK</t>
+        </is>
+      </c>
+      <c r="D197" s="145" t="n"/>
+    </row>
+    <row r="198" ht="47" customHeight="1" s="43">
+      <c r="A198" s="259" t="inlineStr">
+        <is>
+          <t>틱톡</t>
+        </is>
+      </c>
+      <c r="B198" s="145" t="inlineStr">
+        <is>
+          <t>+ → 업로드 → 영상 선택 → 캡션 · 커버 → 게시(앱에 예약이 없으면 화·금 저녁에 직접, 1분).</t>
+        </is>
+      </c>
+      <c r="C198" s="145" t="inlineStr"/>
+      <c r="D198" s="145" t="n"/>
+    </row>
+    <row r="199" ht="73" customHeight="1" s="43">
+      <c r="A199" s="259" t="inlineStr">
+        <is>
+          <t>올린 뒤</t>
+        </is>
+      </c>
+      <c r="B199" s="145" t="inlineStr">
+        <is>
+          <t>첫 1~2시간 댓글엔 바로 답글. 48시간 뒤 수요검증 §4 로그에 한 줄 — 볼 숫자: 평균 시청 시간(끝까지 본 비율) · 저장 · 공유 · '어디서 사요?' 댓글·DM.</t>
+        </is>
+      </c>
+      <c r="C199" s="145" t="inlineStr">
+        <is>
+          <t>좋아요·조회수는 참고만. 판단은 4주(8개) 뒤(§5)</t>
+        </is>
+      </c>
+      <c r="D199" s="145" t="n"/>
+    </row>
+    <row r="200" ht="30" customHeight="1" s="43">
+      <c r="A200" s="79" t="inlineStr">
+        <is>
+          <t>메뉴 이름은 앱 업데이트로 조금씩 바뀐다 — 안 보이면 '+ 누르고 업로드'가 기본 흐름이라는 것만 기억.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1" s="43">
+      <c r="A201" s="140" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B201" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C201" s="140" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="D201" s="258" t="n"/>
+    </row>
+    <row r="202" ht="34" customHeight="1" s="43">
+      <c r="A202" s="259" t="inlineStr">
+        <is>
+          <t>원본 업로드</t>
+        </is>
+      </c>
+      <c r="B202" s="145" t="inlineStr">
+        <is>
+          <t>CapCut에서 내보낸 워터마크 없는 원본을 채널마다 따로 올린다.</t>
+        </is>
+      </c>
+      <c r="C202" s="145" t="inlineStr">
+        <is>
+          <t>다른 앱 로고가 박힌 재업로드는 노출이 준다</t>
+        </is>
+      </c>
+      <c r="D202" s="145" t="n"/>
+    </row>
+    <row r="203" ht="47" customHeight="1" s="43">
+      <c r="A203" s="259" t="inlineStr">
+        <is>
+          <t>블로그 중복 금지</t>
+        </is>
+      </c>
+      <c r="B203" s="145" t="inlineStr">
+        <is>
+          <t>같은 글 복사 ❌. 같은 주제라도 구조를 다시 짠다: 네이버 = '써본 이야기' / 사이트 = '총정리'.</t>
+        </is>
+      </c>
+      <c r="C203" s="145" t="inlineStr">
+        <is>
+          <t>유사 문서로 걸러져 검색 누락·블로그 평가 하락 위험 — 노력 3배, 효과 1배</t>
+        </is>
+      </c>
+      <c r="D203" s="145" t="n"/>
+    </row>
+    <row r="204" ht="73" customHeight="1" s="43">
+      <c r="A204" s="259" t="inlineStr">
+        <is>
+          <t>브랜드 도메인</t>
+        </is>
+      </c>
+      <c r="B204" s="145" t="inlineStr">
+        <is>
+          <t>도메인 구매 → 사이트 빌더(아임웹·워드프레스 등) 연결 → 구글 서치콘솔 + 네이버 서치어드바이저 등록(반나절). 부담되면 티스토리 + 내 도메인 연결이 중간안.</t>
+        </is>
+      </c>
+      <c r="C204" s="145" t="inlineStr">
+        <is>
+          <t>나중에 자사몰과 같은 도메인 → 2년간 쌓은 검색 신뢰가 상점으로 이어진다. 플랫폼 정책이 바뀌어도 남는다</t>
+        </is>
+      </c>
+      <c r="D204" s="145" t="n"/>
+    </row>
+    <row r="205" ht="47" customHeight="1" s="43">
+      <c r="A205" s="259" t="inlineStr">
+        <is>
+          <t>링크 조건</t>
+        </is>
+      </c>
+      <c r="B205" s="145" t="inlineStr">
+        <is>
+          <t>틱톡·쇼츠는 링크에 팔로워 수·계정 유형 조건이 있거나 클릭이 제한될 수 있다 — 개설할 때 확인.</t>
+        </is>
+      </c>
+      <c r="C205" s="145" t="inlineStr">
+        <is>
+          <t>대기자 유입의 주 경로는 인스타 프로필 링크·블로그</t>
+        </is>
+      </c>
+      <c r="D205" s="145" t="n"/>
+    </row>
+    <row r="206" ht="34" customHeight="1" s="43">
+      <c r="A206" s="259" t="inlineStr">
+        <is>
+          <t>유입 경로 측정</t>
+        </is>
+      </c>
+      <c r="B206" s="145" t="inlineStr">
+        <is>
+          <t>대기자 폼에 '어디서 보고 오셨나요?' 항목, 또는 채널별로 다른 링크.</t>
+        </is>
+      </c>
+      <c r="C206" s="145" t="inlineStr">
+        <is>
+          <t>6개월 뒤 채널 정리를 감이 아니라 숫자로</t>
+        </is>
+      </c>
+      <c r="D206" s="145" t="n"/>
+    </row>
+    <row r="207" ht="34" customHeight="1" s="43">
+      <c r="A207" s="259" t="inlineStr">
+        <is>
+          <t>규정</t>
+        </is>
+      </c>
+      <c r="B207" s="145" t="inlineStr">
+        <is>
+          <t>모든 채널에 같은 표시·광고 규칙(수요검증 §3). 판매 후 협찬·광고는 표기.</t>
+        </is>
+      </c>
+      <c r="C207" s="145" t="inlineStr">
+        <is>
+          <t>채널마다 기준이 다르면 실수가 난다</t>
+        </is>
+      </c>
+      <c r="D207" s="145" t="n"/>
+    </row>
+    <row r="208" ht="28" customHeight="1" s="43">
+      <c r="A208" s="140" t="inlineStr">
+        <is>
+          <t>시기</t>
+        </is>
+      </c>
+      <c r="B208" s="140" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+      <c r="C208" s="140" t="inlineStr">
+        <is>
+          <t>판단 기준</t>
+        </is>
+      </c>
+      <c r="D208" s="258" t="n"/>
+    </row>
+    <row r="209" ht="47" customHeight="1" s="43">
+      <c r="A209" s="259" t="inlineStr">
+        <is>
           <t>지금</t>
         </is>
       </c>
-      <c r="B192" s="145" t="inlineStr">
+      <c r="B209" s="145" t="inlineStr">
         <is>
           <t>영상 3채널 동시 시작(같은 영상, 영상당 +10~15분) + 네이버 블로그(§9 시작 조건대로).</t>
         </is>
       </c>
-      <c r="C192" s="145" t="inlineStr">
+      <c r="C209" s="145" t="inlineStr">
         <is>
           <t>업로드가 끊기지 않는 것이 먼저</t>
         </is>
       </c>
-      <c r="D192" s="145" t="n"/>
-    </row>
-    <row r="193" ht="34" customHeight="1" s="43">
-      <c r="A193" s="259" t="inlineStr">
+      <c r="D209" s="145" t="n"/>
+    </row>
+    <row r="210" ht="34" customHeight="1" s="43">
+      <c r="A210" s="259" t="inlineStr">
         <is>
           <t>1~2개월 뒤</t>
         </is>
       </c>
-      <c r="B193" s="145" t="inlineStr">
+      <c r="B210" s="145" t="inlineStr">
         <is>
           <t>브랜드 사이트 오픈 → 성분 사전 월 2편.</t>
         </is>
       </c>
-      <c r="C193" s="145" t="inlineStr">
+      <c r="C210" s="145" t="inlineStr">
         <is>
           <t>구글은 도메인이 쌓이는 데 시간이 걸린다 — 너무 미루지 않기</t>
         </is>
       </c>
-      <c r="D193" s="145" t="n"/>
-    </row>
-    <row r="194" ht="34" customHeight="1" s="43">
-      <c r="A194" s="259" t="inlineStr">
+      <c r="D210" s="145" t="n"/>
+    </row>
+    <row r="211" ht="34" customHeight="1" s="43">
+      <c r="A211" s="259" t="inlineStr">
         <is>
           <t>6개월 뒤</t>
         </is>
       </c>
-      <c r="B194" s="145" t="inlineStr">
+      <c r="B211" s="145" t="inlineStr">
         <is>
           <t>채널별 대기자 수 비교 → 안 되는 채널은 정리, 되는 곳에 집중.</t>
         </is>
       </c>
-      <c r="C194" s="145" t="inlineStr">
+      <c r="C211" s="145" t="inlineStr">
         <is>
           <t>조회수가 아니라 대기자를 데려온 채널</t>
         </is>
       </c>
-      <c r="D194" s="145" t="n"/>
-    </row>
-    <row r="196" ht="30" customHeight="1" s="43">
-      <c r="A196" s="79" t="inlineStr">
+      <c r="D211" s="145" t="n"/>
+    </row>
+    <row r="213" ht="30" customHeight="1" s="43">
+      <c r="A213" s="79" t="inlineStr">
         <is>
           <t>2년 × 평균 주 2개 ≈ 200개 + 블로그 약 50편. 2027년 말 누적 약 110개 — 자격을 딴 날 '이미 보는 사람과 대기자가 있는 상태'로 판매를 시작하는 게 목표.</t>
         </is>
       </c>
     </row>
+    <row r="215" ht="22" customHeight="1" s="43">
+      <c r="A215" s="257" t="inlineStr">
+        <is>
+          <t>§14. 브랜딩 · 홈페이지 · CS — 제품이 없을 때 '있어 보이게', 정직하게</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="30" customHeight="1" s="43">
+      <c r="A216" s="79" t="inlineStr">
+        <is>
+          <t>원칙 — 기술 경쟁 대신 브랜딩·CS로 간다 (기술은 OEM 제조사, 브랜드는 기준·투명성·CS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="28" customHeight="1" s="43">
+      <c r="A217" s="140" t="inlineStr">
+        <is>
+          <t>원칙</t>
+        </is>
+      </c>
+      <c r="B217" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C217" s="140" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="D217" s="258" t="n"/>
+    </row>
+    <row r="218" ht="62" customHeight="1" s="43">
+      <c r="A218" s="259" t="inlineStr">
+        <is>
+          <t>있어 보임 = 일관성</t>
+        </is>
+      </c>
+      <c r="B218" s="145" t="inlineStr">
+        <is>
+          <t>장갑 색 · 라벨 · 폰트 · 색감을 영상 · 사이트 · 패키지에 똑같이. 영상 속 '시제품' 라벨이 나중에 실제 패키지 라벨로 바뀌게 디자인.</t>
+        </is>
+      </c>
+      <c r="C218" s="145" t="inlineStr">
+        <is>
+          <t>제품 수가 아니라 톤이 브랜드를 만든다. 라벨이 바뀌는 순간 자체가 스토리</t>
+        </is>
+      </c>
+      <c r="D218" s="145" t="n"/>
+    </row>
+    <row r="219" ht="48" customHeight="1" s="43">
+      <c r="A219" s="259" t="inlineStr">
+        <is>
+          <t>제품은 적을수록</t>
+        </is>
+      </c>
+      <c r="B219" s="145" t="inlineStr">
+        <is>
+          <t>히어로 진정 크림 1개 + 출시 예정 2개(실루엣 · 이름 · '2027 예정'만).</t>
+        </is>
+      </c>
+      <c r="C219" s="145" t="inlineStr">
+        <is>
+          <t>1인 브랜드는 '집중'이 전문성으로 보인다. 기다림이 기대감</t>
+        </is>
+      </c>
+      <c r="D219" s="145" t="n"/>
+    </row>
+    <row r="220" ht="48" customHeight="1" s="43">
+      <c r="A220" s="259" t="inlineStr">
+        <is>
+          <t>약점을 바꿔 말하기</t>
+        </is>
+      </c>
+      <c r="B220" s="145" t="inlineStr">
+        <is>
+          <t>'전문성 없음'을 숨기지 말고 '공부하며 만드는 과정 공개'로. 맞춤형화장품조제관리사 공부 → 합격을 공개 증거로 쓴다.</t>
+        </is>
+      </c>
+      <c r="C220" s="145" t="inlineStr">
+        <is>
+          <t>과정을 본 사람은 결과를 믿는다</t>
+        </is>
+      </c>
+      <c r="D220" s="145" t="n"/>
+    </row>
+    <row r="221" ht="48" customHeight="1" s="43">
+      <c r="A221" s="259" t="inlineStr">
+        <is>
+          <t>하지 않는 것</t>
+        </is>
+      </c>
+      <c r="B221" s="145" t="inlineStr">
+        <is>
+          <t>없는 제품 오픈마켓 등록 · 가짜 리뷰/판매량 · 하지 않은 '임상' 문구 · 다른 브랜드 사진.</t>
+        </is>
+      </c>
+      <c r="C221" s="145" t="inlineStr">
+        <is>
+          <t>화장품은 책임판매업 등록 · 전성분 · 제조번호가 있어야 판매 가능 + 오픈마켓 페널티. 한 번 걸리면 브랜드가 끝난다</t>
+        </is>
+      </c>
+      <c r="D221" s="145" t="n"/>
+    </row>
+    <row r="222" ht="30" customHeight="1" s="43">
+      <c r="A222" s="79" t="inlineStr">
+        <is>
+          <t>홈페이지 1페이지 (지금 — 아임웹 · 카페24 무료 · 노션으로 시작, 도메인은 §13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="28" customHeight="1" s="43">
+      <c r="A223" s="140" t="inlineStr">
+        <is>
+          <t>구역</t>
+        </is>
+      </c>
+      <c r="B223" s="140" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C223" s="140" t="inlineStr">
+        <is>
+          <t>쇼츠와 연결</t>
+        </is>
+      </c>
+      <c r="D223" s="258" t="n"/>
+    </row>
+    <row r="224" ht="34" customHeight="1" s="43">
+      <c r="A224" s="259" t="inlineStr">
+        <is>
+          <t>첫 화면</t>
+        </is>
+      </c>
+      <c r="B224" s="145" t="inlineStr">
+        <is>
+          <t>브랜드 한 줄 'FM으로 만드는 지성·민감 진정 크림' + 시제품 사진.</t>
+        </is>
+      </c>
+      <c r="C224" s="145" t="inlineStr">
+        <is>
+          <t>영상 속 위생 루틴(§7 콘티 B) = 브랜드 약속</t>
+        </is>
+      </c>
+      <c r="D224" s="145" t="n"/>
+    </row>
+    <row r="225" ht="48" customHeight="1" s="43">
+      <c r="A225" s="259" t="inlineStr">
+        <is>
+          <t>히어로 제품 카드</t>
+        </is>
+      </c>
+      <c r="B225" s="145" t="inlineStr">
+        <is>
+          <t>'개발 중' + 진행 표시: 처방 ✓ → 안정성 테스트 → OEM → 출시. 버튼 '출시 알림 받기 + 얼리버드 혜택'.</t>
+        </is>
+      </c>
+      <c r="C225" s="145" t="inlineStr">
+        <is>
+          <t>단계가 바뀔 때마다 영상 1개(소재 은행 §3)</t>
+        </is>
+      </c>
+      <c r="D225" s="145" t="n"/>
+    </row>
+    <row r="226" ht="34" customHeight="1" s="43">
+      <c r="A226" s="259" t="inlineStr">
+        <is>
+          <t>출시 예정 2개</t>
+        </is>
+      </c>
+      <c r="B226" s="145" t="inlineStr">
+        <is>
+          <t>실루엣 + 이름 + '2027 예정'. 상세 · 가격 ❌.</t>
+        </is>
+      </c>
+      <c r="C226" s="145" t="inlineStr">
+        <is>
+          <t>라인업이 있는 브랜드처럼 보이되 거짓은 없음</t>
+        </is>
+      </c>
+      <c r="D226" s="145" t="n"/>
+    </row>
+    <row r="227" ht="34" customHeight="1" s="43">
+      <c r="A227" s="259" t="inlineStr">
+        <is>
+          <t>개발일지</t>
+        </is>
+      </c>
+      <c r="B227" s="145" t="inlineStr">
+        <is>
+          <t>쇼츠 임베드, Batch #01, #02 … 번호를 붙여 쌓기.</t>
+        </is>
+      </c>
+      <c r="C227" s="145" t="inlineStr">
+        <is>
+          <t>번호가 쌓이면 꾸준함이 보인다</t>
+        </is>
+      </c>
+      <c r="D227" s="145" t="n"/>
+    </row>
+    <row r="228" ht="34" customHeight="1" s="43">
+      <c r="A228" s="259" t="inlineStr">
+        <is>
+          <t>성분</t>
+        </is>
+      </c>
+      <c r="B228" s="145" t="inlineStr">
+        <is>
+          <t>전성분 + 각 원료를 넣은 이유(원료_마스터.xlsx 카드 활용).</t>
+        </is>
+      </c>
+      <c r="C228" s="145" t="inlineStr">
+        <is>
+          <t>성분을 아는 사람 = 신뢰. 블로그 성분 해설(§9)과 연결</t>
+        </is>
+      </c>
+      <c r="D228" s="145" t="n"/>
+    </row>
+    <row r="229" ht="48" customHeight="1" s="43">
+      <c r="A229" s="259" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="B229" s="145" t="inlineStr">
+        <is>
+          <t>위생 루틴 · 시험 계획(안정성 · 피부자극) · '판매 제품은 화장품 제조업체(OEM)에서 생산'.</t>
+        </is>
+      </c>
+      <c r="C229" s="145" t="inlineStr">
+        <is>
+          <t>'집에서 만든 걸 파나?' 의심을 정면으로 해소</t>
+        </is>
+      </c>
+      <c r="D229" s="145" t="n"/>
+    </row>
+    <row r="230" ht="48" customHeight="1" s="43">
+      <c r="A230" s="259" t="inlineStr">
+        <is>
+          <t>알림 신청 · FAQ · 문의</t>
+        </is>
+      </c>
+      <c r="B230" s="145" t="inlineStr">
+        <is>
+          <t>대기자 폼(§8, '어디서 보고 오셨나요?' 포함) · FAQ · 인스타 DM 또는 채널톡.</t>
+        </is>
+      </c>
+      <c r="C230" s="145" t="inlineStr">
+        <is>
+          <t>CS의 시작점</t>
+        </is>
+      </c>
+      <c r="D230" s="145" t="n"/>
+    </row>
+    <row r="231" ht="30" customHeight="1" s="43">
+      <c r="A231" s="79" t="inlineStr">
+        <is>
+          <t>오픈마켓 — 실제 제품이 나온 뒤 순서대로 (그 전엔 상점 링크 ❌, §8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="28" customHeight="1" s="43">
+      <c r="A232" s="140" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B232" s="140" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+      <c r="C232" s="140" t="inlineStr">
+        <is>
+          <t>판단 기준</t>
+        </is>
+      </c>
+      <c r="D232" s="258" t="n"/>
+    </row>
+    <row r="233" ht="62" customHeight="1" s="43">
+      <c r="A233" s="259" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="B233" s="145" t="inlineStr">
+        <is>
+          <t>OEM 생산 + 화장품책임판매업 등록(또는 맞춤형화장품판매업) + 통신판매업 신고 · 표시사항(전성분 · 제조번호 · 사용기한).</t>
+        </is>
+      </c>
+      <c r="C233" s="145" t="inlineStr">
+        <is>
+          <t>조건이 다 갖춰지기 전엔 어떤 상점도 열지 않는다</t>
+        </is>
+      </c>
+      <c r="D233" s="145" t="n"/>
+    </row>
+    <row r="234" ht="48" customHeight="1" s="43">
+      <c r="A234" s="259" t="inlineStr">
+        <is>
+          <t>① 스마트스토어</t>
+        </is>
+      </c>
+      <c r="B234" s="145" t="inlineStr">
+        <is>
+          <t>대기자에게 먼저 판매 → 리뷰 쌓기. 첫 출시는 본품 1 + 미니(체험) 1 = 2종.</t>
+        </is>
+      </c>
+      <c r="C234" s="145" t="inlineStr">
+        <is>
+          <t>수수료 낮고 네이버 블로그(§9)와 같은 생태계</t>
+        </is>
+      </c>
+      <c r="D234" s="145" t="n"/>
+    </row>
+    <row r="235" ht="34" customHeight="1" s="43">
+      <c r="A235" s="259" t="inlineStr">
+        <is>
+          <t>② 자사몰</t>
+        </is>
+      </c>
+      <c r="B235" s="145" t="inlineStr">
+        <is>
+          <t>재구매 · 정기구매 고객을 모은다(홈페이지와 같은 도메인).</t>
+        </is>
+      </c>
+      <c r="C235" s="145" t="inlineStr">
+        <is>
+          <t>수수료 0, 고객 데이터가 내 것</t>
+        </is>
+      </c>
+      <c r="D235" s="145" t="n"/>
+    </row>
+    <row r="236" ht="34" customHeight="1" s="43">
+      <c r="A236" s="259" t="inlineStr">
+        <is>
+          <t>③ 쿠팡</t>
+        </is>
+      </c>
+      <c r="B236" s="145" t="inlineStr">
+        <is>
+          <t>리뷰가 쌓인 뒤 진입.</t>
+        </is>
+      </c>
+      <c r="C236" s="145" t="inlineStr">
+        <is>
+          <t>가격 경쟁 · 물류 부담이 커서 처음부터 ❌</t>
+        </is>
+      </c>
+      <c r="D236" s="145" t="n"/>
+    </row>
+    <row r="237" ht="30" customHeight="1" s="43">
+      <c r="A237" s="79" t="inlineStr">
+        <is>
+          <t>CS — 출시 전 댓글 · DM이 연습 (CS를 확실히 하는 것 자체가 브랜딩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="28" customHeight="1" s="43">
+      <c r="A238" s="140" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B238" s="140" t="inlineStr">
+        <is>
+          <t>방법</t>
+        </is>
+      </c>
+      <c r="C238" s="140" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="D238" s="258" t="n"/>
+    </row>
+    <row r="239" ht="48" customHeight="1" s="43">
+      <c r="A239" s="259" t="inlineStr">
+        <is>
+          <t>답변 템플릿 10개</t>
+        </is>
+      </c>
+      <c r="B239" s="145" t="inlineStr">
+        <is>
+          <t>피부 타입 · 성분 · 출시일 · 사용법 · 보관 · 트러블 · 교환/환불 · 배송 · 비건/동물실험 · 해외 배송.</t>
+        </is>
+      </c>
+      <c r="C239" s="145" t="inlineStr">
+        <is>
+          <t>같은 질문엔 같은 답 = 신뢰 + 시간 절약</t>
+        </is>
+      </c>
+      <c r="D239" s="145" t="n"/>
+    </row>
+    <row r="240" ht="34" customHeight="1" s="43">
+      <c r="A240" s="259" t="inlineStr">
+        <is>
+          <t>응답 시간 약속</t>
+        </is>
+      </c>
+      <c r="B240" s="145" t="inlineStr">
+        <is>
+          <t>'24시간 안에 답변'을 프로필 · 홈페이지에 적고 지킨다.</t>
+        </is>
+      </c>
+      <c r="C240" s="145" t="inlineStr">
+        <is>
+          <t>약속을 지키는 것이 1인 브랜드의 가장 싼 차별화</t>
+        </is>
+      </c>
+      <c r="D240" s="145" t="n"/>
+    </row>
+    <row r="241" ht="48" customHeight="1" s="43">
+      <c r="A241" s="259" t="inlineStr">
+        <is>
+          <t>트러블 접수 절차</t>
+        </is>
+      </c>
+      <c r="B241" s="145" t="inlineStr">
+        <is>
+          <t>접수 → 사진 · 사용 기간 · 피부 타입 확인 → 사용 중지 안내 → 교환/환불 → 기록.</t>
+        </is>
+      </c>
+      <c r="C241" s="145" t="inlineStr">
+        <is>
+          <t>출시 후 책임판매업자는 안전성 정보 보고 의무(유통안전·OEM검수 시트) — 지금 절차를 만들어 둔다</t>
+        </is>
+      </c>
+      <c r="D241" s="145" t="n"/>
+    </row>
+    <row r="242" ht="34" customHeight="1" s="43">
+      <c r="A242" s="259" t="inlineStr">
+        <is>
+          <t>DM 기록</t>
+        </is>
+      </c>
+      <c r="B242" s="145" t="inlineStr">
+        <is>
+          <t>출시 전 질문을 모아 FAQ · 제품 기획에 반영(수요검증 §4 로그).</t>
+        </is>
+      </c>
+      <c r="C242" s="145" t="inlineStr">
+        <is>
+          <t>출시 전 DM = 무료 고객 조사</t>
+        </is>
+      </c>
+      <c r="D242" s="145" t="n"/>
+    </row>
+    <row r="243" ht="34" customHeight="1" s="43">
+      <c r="A243" s="79" t="inlineStr">
+        <is>
+          <t>⚠ 판매 · 광고 표현은 표시·광고 컴플라이언스 시트 기준. 홈페이지 문구도 효능 표방 ❌ — 과정 · 질감 · 기준만 말한다(수요검증 §3).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A150:D150"/>
-    <mergeCell ref="B107:D107"/>
+  <mergeCells count="36">
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="A126:D126"/>
+    <mergeCell ref="A215:D215"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A109:D109"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A161:D161"/>
-    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A231:D231"/>
+    <mergeCell ref="A200:D200"/>
+    <mergeCell ref="B119:D119"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="A167:D167"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A178:D178"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A222:D222"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A237:D237"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="A183:D183"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="A153:D153"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A243:D243"/>
     <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="B122:D122"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A213:D213"/>
     <mergeCell ref="A57:D57"/>
-    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="A151:D151"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -2393,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="26" customWidth="1" style="43" min="1" max="1"/>
@@ -2462,6 +2462,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
@@ -2529,6 +2530,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
         <is>
@@ -2603,7 +2605,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="43">
+    <row r="22" ht="52" customHeight="1" s="43">
       <c r="A22" s="85" t="inlineStr">
         <is>
           <t>·</t>
@@ -2611,7 +2613,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>원료 도감 : 학습용 원료 766종 한 표 — 기능성·합성 130종(INCI·전형%·왜 쓰나·천연 대안·주의) + 허브누리 원료 사전 636종(등장수·대표%·범위·특징·주 사용 제형·대체재). ▼ 필터로 구분·역할별 탐색, ✓=보유. 설계 캔버스와 무관.</t>
+          <t>원료 도감 : 학습용 원료 766종 한 표 — 기능성·합성 130종(INCI·전형%·왜 쓰나·천연 대안·주의) + 허브누리 원료 사전 636종(등장수·대표%·범위·특징·주 사용 제형·대체재). ▼ 필터로 구분·역할별 탐색, ✓=보유. 설계 캔버스와 무관. → 원료 하나를 깊게 파려면 별도 파일 '원료_마스터.xlsx'(원료 카드 247종·비교 매트릭스·제형 설계·감촉 레버·블렌드 해부).</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2744,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="72" customHeight="1" s="43">
+    <row r="34" ht="86" customHeight="1" s="43">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <t>·</t>
@@ -2750,7 +2752,7 @@
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>업로드 루틴 : 제품 개발과 병렬로 2년간 꾸준히 올리는 원칙·주간 루틴·소재 은행·단계별 목표·끊겼을 때 규칙 + ASMR 영상 포맷(다꾸 쇼츠 문법)·장면 목록·콘티 + 프로필 링크 계획 + 블로그 운영·발행 프롬프트 6종 + 처음 하는 사람용 한 흐름: 촬영(장비·세팅 순서·찍는 법) → CapCut 편집 12단계·3주 연습 → 계정 세팅·3채널 업로드 방법 + 채널 운영(영상 3채널·블로그 2곳).</t>
+          <t>업로드 루틴 : 제품 개발과 병렬로 2년간 꾸준히 올리는 원칙·주간 루틴·소재 은행·단계별 목표·끊겼을 때 규칙 + ASMR 영상 포맷(다꾸 쇼츠 문법)·장면 목록·콘티(콘티 B = FM 위생 루틴 풀 과정) + 프로필 링크 계획 + 블로그 운영·발행 프롬프트 6종 + 처음 하는 사람용 한 흐름: 촬영(장비·세팅 순서·찍는 법) → CapCut 편집 12단계·3주 연습 → 계정 세팅·3채널 업로드 방법 + 채널 운영(영상 3채널·블로그 2곳) + 브랜딩·홈페이지·CS(§14: 제품 없을 때 정직하게 '있어 보이게', 오픈마켓 순서, CS 연습).</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2930,7 @@
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>[알리기] 실험하면서 사진·영상 → 주 2개 예약 업로드 + 블로그 주 1편(업로드 루틴) → 반응을 수요검증 §4 로그에 한 줄.</t>
+          <t>[알리기] 실험하면서 사진·영상 → 주 2개 예약 업로드 + 블로그 주 1편(업로드 루틴) → 반응을 수요검증 §4 로그에 한 줄. 프로필 링크 = 대기자 폼·홈페이지(업로드 루틴 §8·§14), 상점은 출시 후.</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3486,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1" s="43">
+    <row r="110" ht="36" customHeight="1" s="43">
       <c r="A110" s="28" t="inlineStr">
         <is>
           <t>·</t>
@@ -3492,7 +3494,7 @@
       </c>
       <c r="B110" s="29" t="inlineStr">
         <is>
-          <t>소량(50~100g)으로, 라벨·기록 철저, 가열·향 작업은 환기되는 곳에서.</t>
+          <t>소량(50~100g)으로, 라벨·기록 철저, 가열·향 작업은 환기되는 곳에서. 니트릴 장갑·헤어캡·마스크(머리카락·침 차단) — 이 순서가 그대로 촬영 루틴(업로드 루틴 §7 콘티 B).</t>
         </is>
       </c>
     </row>
@@ -3508,6 +3510,7 @@
         </is>
       </c>
     </row>
+    <row r="112"/>
     <row r="113" ht="36" customHeight="1" s="43">
       <c r="A113" s="47" t="inlineStr">
         <is>
@@ -3919,8 +3922,99 @@
         </is>
       </c>
     </row>
+    <row r="154" ht="36" customHeight="1" s="43">
+      <c r="A154" s="44" t="inlineStr">
+        <is>
+          <t>브랜딩 · 홈페이지 · CS — 기술 대신 '일관성 + 투명성 + CS'로 (업로드 루틴 §14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="36" customHeight="1" s="43">
+      <c r="A155" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B155" s="29" t="inlineStr">
+        <is>
+          <t>자본·전문성으로는 기술 경쟁이 안 된다 → 기술은 OEM 제조사, 브랜드는 기준·투명성·CS. '전문성 없음'은 숨기지 말고 '공부하며 만드는 과정 공개'로(자격 합격 = 공개 증거).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="53" customHeight="1" s="43">
+      <c r="A156" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B156" s="29" t="inlineStr">
+        <is>
+          <t>'있어 보임' = 과장이 아니라 일관성: 장갑 색·라벨·폰트·색감을 영상·홈페이지·패키지에 똑같이. 영상 속 '시제품' 라벨이 실제 패키지 라벨로 바뀌는 순간이 스토리(소통 전략의 '커 보이려 하지 않기'와 같은 선).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="36" customHeight="1" s="43">
+      <c r="A157" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B157" s="29" t="inlineStr">
+        <is>
+          <t>제품 목록: 히어로 1개 + 출시 예정 2개(실루엣·이름·'2027 예정'만). 1인 브랜드는 적을수록 전문적으로 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1" s="43">
+      <c r="A158" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B158" s="29" t="inlineStr">
+        <is>
+          <t>홈페이지 1페이지(지금): 브랜드 한 줄 → 히어로 '개발 중' 카드(진행 표시) → 개발일지(쇼츠·Batch 번호) → 성분과 이유 → 기준(위생·시험·OEM 생산) → 출시 알림·FAQ·문의.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="36" customHeight="1" s="43">
+      <c r="A159" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B159" s="29" t="inlineStr">
+        <is>
+          <t>오픈마켓은 실제 제품이 나온 뒤: OEM 생산 + 책임판매업(또는 맞춤형판매업) + 통신판매업 신고 → ① 스마트스토어 → ② 자사몰 → ③ 쿠팡.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="36" customHeight="1" s="43">
+      <c r="A160" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B160" s="29" t="inlineStr">
+        <is>
+          <t>CS는 지금부터 연습: 답변 템플릿 10개 · '24시간 안에 답변' 약속 · 트러블 접수 절차(출시 후 안전성 정보 보고 의무) · DM은 수요검증 §4에 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="36" customHeight="1" s="43">
+      <c r="A161" s="28" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B161" s="29" t="inlineStr">
+        <is>
+          <t>⚠ 하지 않는 것: 없는 제품 오픈마켓 등록 · 가짜 리뷰/판매량 · 하지 않은 '임상' 문구 · 다른 브랜드 사진. 영상·캡션엔 '개발 중인 시제품, 판매 제품은 화장품 제조업체 생산' 고정.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A98:B98"/>
     <mergeCell ref="A60:B60"/>
@@ -3935,6 +4029,7 @@
     <mergeCell ref="A108:B108"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A154:B154"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A113:B113"/>
     <mergeCell ref="A42:B42"/>

--- a/제품개발_마스터.xlsx
+++ b/제품개발_마스터.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="61">
+  <fonts count="70">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -433,6 +433,55 @@
       <b val="1"/>
       <color rgb="FF2E7D32"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FF1F3A5F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FF1F3A5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="54">
     <fill>
@@ -704,7 +753,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1024,11 +1073,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1700,6 +1754,33 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2462,7 +2543,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
@@ -2530,7 +2610,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
         <is>
@@ -2783,7 +2862,7 @@
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>교재 이론 목차 : 에듀윌 한권끝장 핵심이론 목차(PDF 101~314쪽)·소제목 분류.</t>
+          <t>교재 이론 목차 : 에듀윌 한권끝장 핵심이론 전체 목차(책 14~229쪽, PART01~04·19개 Chapter)를 절·중제목·쪽까지 교재 순서대로.</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3589,6 @@
         </is>
       </c>
     </row>
-    <row r="112"/>
     <row r="113" ht="36" customHeight="1" s="43">
       <c r="A113" s="47" t="inlineStr">
         <is>
@@ -23352,7 +23430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="34" customWidth="1" style="43" min="1" max="1"/>
@@ -23362,370 +23440,1993 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="43">
-      <c r="A1" s="70" t="inlineStr">
-        <is>
-          <t>교재 핵심이론 목차 (에듀윌 한권끝장) — PDF 101~314쪽 · 소제목 분류</t>
+      <c r="A1" s="260" t="inlineStr">
+        <is>
+          <t>교재 핵심이론 목차 (에듀윌 한권끝장) — 책 14~229쪽 · 절·중제목 전체</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1" s="43">
-      <c r="A2" s="69" t="inlineStr">
-        <is>
-          <t>핵심이론(PDF 101~314쪽, 추출본 '핵심이론_101-314.pdf') 교재의 실제 절·소제목·세부 bullet 분류. A=절(대제목)/B=중제목·세부항목(- 레벨)/C=책쪽/D=시험·실무. ★CH01 대제목(1~8)은 교재 목차대로 확정. 4·6·7·8의 세부는 정독 반영 — 중제목 번호는 교재와 일부 다를 수 있어 추가 보완 가능. PART02~04 순차 작성.</t>
+      <c r="A2" s="261" t="inlineStr">
+        <is>
+          <t>교재 핵심이론(책 14~229쪽 = PDF 102~317쪽, PDF쪽 = 책쪽 + 88)을 처음부터 끝까지 정독해 절(■ 번호)·중제목((1)(2)…)·주요 수치를 교재 순서 그대로 옮긴 목차. A=절(대제목) / B=중제목·세부 항목 / C=책쪽 / D=시험·다도기 실무 연계. 출제비중: PART01 10% · PART02 25% · PART03 25% · PART04 40%. 각 Chapter 끝 '단원별 연습문제'는 생략. 수치는 교재 기준 — 시험·판매 전 최신 고시로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="43">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="262" t="inlineStr">
         <is>
           <t>절 (대제목)</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
-        <is>
-          <t>중제목 · 세부 항목 (- 레벨)</t>
-        </is>
-      </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="B3" s="262" t="inlineStr">
+        <is>
+          <t>중제목 · 세부 항목</t>
+        </is>
+      </c>
+      <c r="C3" s="262" t="inlineStr">
         <is>
           <t>책쪽</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="262" t="inlineStr">
         <is>
           <t>시험·실무 연계</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="43">
-      <c r="A5" s="82" t="inlineStr">
-        <is>
-          <t>PART 01 · 화장품법의 이해</t>
+      <c r="A5" s="263" t="inlineStr">
+        <is>
+          <t>PART 01 · 화장품법의 이해  (출제비중 10%)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="43">
-      <c r="A6" s="81" t="inlineStr">
-        <is>
-          <t>CHAPTER 01 · 화장품법</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1" s="43">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A6" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 01 · 화장품법   (책 14~38쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" s="43">
+      <c r="A7" s="265" t="inlineStr">
         <is>
           <t>1. 화장품법의 입법 취지(목적)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>- 약사법에서 분리 제정 → 개정 연혁
-- 국민 보건 향상 + 화장품산업 발전에 기여</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="B7" s="266" t="inlineStr">
+        <is>
+          <t>- 1999.9 약사법에서 분리 제정 → 2000.7 시행 / 국민 보건 향상 + 화장품산업 발전에 기여
+- 법령 체계: 화장품법(법률) · 시행령(대통령령) · 시행규칙(총리령) · 고시(행정규칙: 기능성 기준·심사규정·CGMP 등)</t>
+        </is>
+      </c>
+      <c r="C7" s="267" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="266" t="inlineStr">
         <is>
           <t>모든 규칙의 '왜'</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1" s="43">
-      <c r="A8" s="33" t="inlineStr">
+    <row r="8" ht="102" customHeight="1" s="43">
+      <c r="A8" s="265" t="inlineStr">
         <is>
           <t>2. 화장품의 정의 및 유형</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>- 화장품의 정의(인체 청결·미화, 매력 부여, 피부·모발 건강 유지; 작용 '경미')
-- 의약품·의약외품과의 구분</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="B8" s="266" t="inlineStr">
+        <is>
+          <t>- 화장품(인체 청결·미화·매력 부여·피부/모발 건강, 작용 경미) / 기능성화장품 11종(미백 2·주름·태닝·자외선·염모·제모·탈모 완화·여드름 완화(인체세정용 한정)·피부장벽(아토피 가려움)·튼살)
+- 영유아(만 3세 이하)·어린이(4~13세) 사용 화장품 / 천연(95%)·유기농(유기농 10%+천연 95%) — 2025.1.31 정의 삭제 / 맞춤형화장품 / 직접구매 해외화장품
+- 참고: 화장품 vs 기능성 구분, 자외선 차단 측정값 ±20%</t>
+        </is>
+      </c>
+      <c r="C8" s="267" t="inlineStr">
         <is>
           <t>14~15</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>효능 과장=법 위반 경계</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1" s="43">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="D8" s="266" t="inlineStr">
+        <is>
+          <t>효능 과장=법 위반 경계 / 다도기=일반화장품</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1" s="43">
+      <c r="A9" s="265" t="inlineStr">
         <is>
           <t>3. 화장품의 유형별 특성</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>- 영유아용·목욕용·인체세정용·눈화장용·기초화장용·손발톱용·두발염색용·색조화장용·두발용·체취방지용·체모제거용·방향용 제품류</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>15~17</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>다도기=기초화장용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="210" customHeight="1" s="43">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="B9" s="266" t="inlineStr">
+        <is>
+          <t>- 13개 유형: 영유아용·목욕용·인체세정용·기초화장용·손발톱용·눈화장용·색조화장용·두발염색용·두발용·면도용·체모제거용·체취방지용·방향용 제품류
+- 참고: 물휴지 범위 / 공산품→화장품 전환(화장비누·흑채·제모왁스)</t>
+        </is>
+      </c>
+      <c r="C9" s="267" t="inlineStr">
+        <is>
+          <t>16~17</t>
+        </is>
+      </c>
+      <c r="D9" s="266" t="inlineStr">
+        <is>
+          <t>다도기=기초화장용 제품류</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="228" customHeight="1" s="43">
+      <c r="A10" s="265" t="inlineStr">
         <is>
           <t>4. 화장품법에 따른 영업의 종류</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>(1) 영업의 종류: 화장품제조업 · 화장품책임판매업 · 맞춤형화장품판매업(각 정의)
-(2) 영업 등록 및 신고(소재지 관할 지방식품의약품안전청장에게 제출)
- · 필요 서류 — [제조업] 등록신청서·대표자 건강진단서·등기사항증명서(법인)·시설명세서 / [책임판매업] 등록신청서·등기사항증명서(법인)·책임판매관리자 자격 확인 서류·품질관리 및 책임판매 후 안전관리 기준 규정 / [맞춤형판매업] 신고서·조제관리사 자격증 사본·시설명세서·등기사항증명서(법인)
- · 등록 및 신고대장 포함사항 — 등록번호 및 등록연월일 / 영업자 성명·주민등록번호(법인=대표자) / 상호(법인=명칭) / 제조소(영업소) 소재지 / 제조(책임판매·맞춤형) 유형
-(3) 영업의 변경(변경 사유·기간)
-(4) 영업자의 의무사항(제조업·책임판매업·맞춤형판매업)</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t>17~23</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>★자격=맞판 진입권 / 등록·신고 실무</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1" s="43">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="266" t="inlineStr">
+        <is>
+          <t>(1) 영업의 종류: 제조업(직접·위탁·1차 포장) · 책임판매업(4유형, 수입대행형=전자상거래) · 맞춤형화장품판매업
+(2) 영업 등록 및 신고(지방식약청장): ① 등록·신고대장 포함사항 ② 제조업 등록 시설 기준(작업소·보관소·시험실) ③ 책임판매업 품질관리 기준·책임판매 후 안전관리 기준(책임판매관리자 자격, 상시근로자 10명 이하 겸직)
+(3) 영업 등록·신고의 결격사유  (4) 맞춤형화장품조제관리사의 결격사유(자격취소 후 3년)
+(5) 영업자의 의무사항(생산·수입실적 매년 2월 말, 원료목록 유통 전 보고, 교육 매년 4~8시간·최초 6개월 이내)
+(6) 변경 등록 및 신고(30일/90일)  (7) 승계  (8) 행정처분의 일반 기준(최대 12개월, 1년간 동일 위반, 1/2 감경)
+(9) 행정처분의 개별 기준: ① 등록 취소 ② 영업금지 ③ 판매금지(동물실험 예외) ④ 폐업 등의 신고(7일 이내 통지)
+(10) 벌칙(3년/3천만·1년/1천만·200만) 및 과태료(100만·50만)  (11) 과징금(10억 이하)  (12) 양벌 규정  (13) 화장품의 날(9월 7일)</t>
+        </is>
+      </c>
+      <c r="C10" s="267" t="inlineStr">
+        <is>
+          <t>17~28</t>
+        </is>
+      </c>
+      <c r="D10" s="268" t="inlineStr">
+        <is>
+          <t>★자격=맞판 진입권 / 등록·신고·행정처분 실무</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" s="43">
+      <c r="A11" s="265" t="inlineStr">
         <is>
           <t>5. 지방식품의약품안전청 업무</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>- 영업 등록·신고 수리 및 등록·신고대장 관리
-- 보고·검사·조사, 지도·감독 등 지방청장 소관 업무
-(※ 교재 중제목 세부는 추가 정독으로 보완 예정)</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="inlineStr">
-        <is>
-          <t>등록·보고 접수 창구 이해</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1" s="43">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="B11" s="266" t="inlineStr">
+        <is>
+          <t>- 식약처장 권한 위임 ①~⑰: 등록·신고 수리, 교육명령, 회수·행정처분 감경, 폐업신고 수리, 표시·광고 실증자료 요청, 보고·검사, 소비자화장품안전관리감시원 위촉, 시정·검사·개수·회수·폐기명령, 공표, 등록취소 등, 청문, 과징금·과태료 부과·징수(독촉장 15일, 납부기한 10일), 재교부</t>
+        </is>
+      </c>
+      <c r="C11" s="267" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="266" t="inlineStr">
+        <is>
+          <t>등록·보고 접수 창구</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="144" customHeight="1" s="43">
+      <c r="A12" s="265" t="inlineStr">
         <is>
           <t>6. 화장품의 품질 요소</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>- 안전성 · 안정성 · 유효성 · 사용성
-- 각 입증 자료(안정성 시험 성적 및 보존기간 등)</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>★안전성≠안정성(함정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1" s="43">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="B12" s="266" t="inlineStr">
+        <is>
+          <t>(1) 안전성: ① 안전성 자료(단회투여독성·1차피부자극·안점막·감작·광독성·광감작·인체첩포·인체누적첩포) ② 용어(유해사례·중대한 유해사례·실마리정보·안전성정보) ③ 안전성 정보 보고(중대 15일, 정기 매 반기 종료 후 1개월) ④ 위해 평가(위험성 확인→결정→노출평가→위해도 결정, 지정원료 5년 주기) ⑤ 사용 금지 해제·변경 신청(보완 60일, 결과 180일)
+(2) 안정성: ① 시험 종류(장기보존·가속·가혹·개봉 후) ② 시험별 항목·기간(장기·가속 6개월 이상, 개봉 후 6개월; 성분 안정성: 산화·열·광·미생물)
+(3) 유효성: ① 유효성·기능 자료(효력시험·인체적용시험·염모효력시험) ② 일반화장품(보습=TEWL, 수렴=혈액단백질 응고)
+(4) 사용성(향·색·발림성·흡수성·편리함)</t>
+        </is>
+      </c>
+      <c r="C12" s="267" t="inlineStr">
+        <is>
+          <t>30~32</t>
+        </is>
+      </c>
+      <c r="D12" s="268" t="inlineStr">
+        <is>
+          <t>★안전성≠안정성(함정) / 집 안정성 관찰의 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" s="43">
+      <c r="A13" s="265" t="inlineStr">
         <is>
           <t>7. 기능성화장품 심사 및 실태조사</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>- 기능성화장품의 종류(미백·주름개선·자외선차단·염모·제모·탈모완화·여드름완화(세정)·아토피건조완화·튼살)
-- 심사 vs 보고(유효성·기능 자료 제출)
-- 실태조사</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>32~33</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>라인 확장·ODM 기능성 보고</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="96" customHeight="1" s="43">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="B13" s="266" t="inlineStr">
+        <is>
+          <t>(1) 심사 제출 서류: 기원·개발경위 / 안전성 / 유효성·기능(염모=염모효력시험만) / SPF·내수성·PA 근거 / 기준·시험방법
+(2) 심사의뢰서(식약처 안전평가원장, 심사기준 3가지)  (3) 실태조사(5년마다)</t>
+        </is>
+      </c>
+      <c r="C13" s="267" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="266" t="inlineStr">
+        <is>
+          <t>라인 확장 시 ODM 기능성 심사·보고</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="144" customHeight="1" s="43">
+      <c r="A14" s="265" t="inlineStr">
         <is>
           <t>8. 화장품의 사후관리 기준</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>- 영업자 준수사항 / 보고와 조사
-- 안전성 정보의 보고(유해사례 등)
-- 위해화장품의 회수·폐기(위해성 등급 가·나·다)
-- 행정처분의 개별 기준: 등록 취소 가능 경우 / 영업금지 / 영업정지 / 과징금
-- 벌칙 및 과태료
-- 영유아·어린이 사용 화장품 관리(안전성 자료 작성·보관)</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>24~35</t>
-        </is>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>★미준수=개발·판매 중단 / 리콜·CS</t>
+      <c r="B14" s="266" t="inlineStr">
+        <is>
+          <t>(1) 화장품 판매 모니터링(감시: 정기·수시·기획·품질(수거))
+(2) 제조업자 준수사항(제조관리기준서·제품표준서·제조관리기록서·품질관리기록서, 수탁자 관리)
+(3) 책임판매업자 준수사항(제조번호별 품질검사, 레티놀·아스코빅애씨드·토코페롤·과산화화합물·효소 0.5% 이상 시 안정성시험자료 1년 보존, 생산실적·원료목록 보고)
+(4) 맞춤형화장품판매업자 준수사항(시설 점검, 혼합·소분 안전관리 기준, 판매내역서: 제조번호·사용기한·판매일자/판매량, 소비자 설명, 부작용 보고)
+(5) 소비자화장품안전관리감시원(자격·직무·반기마다 교육·해촉) / 참고: 제13조 부당한 표시·광고 금지</t>
+        </is>
+      </c>
+      <c r="C14" s="267" t="inlineStr">
+        <is>
+          <t>34~36</t>
+        </is>
+      </c>
+      <c r="D14" s="268" t="inlineStr">
+        <is>
+          <t>★맞판 준수사항=자격 후 매일 할 일</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="43">
-      <c r="A15" s="81" t="inlineStr">
-        <is>
-          <t>CHAPTER 02 · 개인정보 보호법</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1" s="43">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>1. 개인정보보호법 개요</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>- 개인정보의 정의 · 보호 원칙</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>맞춤형 고객관리 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" s="43">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>2. 개인정보의 수집·이용·제공</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>- 수집·이용 동의 · 목적 범위 내 이용 · 제3자 제공 제한</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>상담 시 동의 절차</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1" s="43">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>3. 개인정보의 관리·안전조치·파기</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>- 안전성 확보 조치 · 보유기간 후 파기</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="A15" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 02 · 개인정보 보호법   (책 39~49쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" s="43">
+      <c r="A16" s="265" t="inlineStr">
+        <is>
+          <t>1. 고객관리 프로그램 운용</t>
+        </is>
+      </c>
+      <c r="B16" s="266" t="inlineStr">
+        <is>
+          <t>(1) 개인정보 보호법의 목적  (2) 용어(개인정보·가명처리·정보주체·개인정보파일·처리자·민감정보·고유식별정보·영상정보처리기기 등; 개인정보가 아닌 정보)
+(3) 고객 데이터관리(백업·접근권한·영구삭제)  (4) 개인정보 보호 인증의 기준 및 방법</t>
+        </is>
+      </c>
+      <c r="C16" s="267" t="inlineStr">
+        <is>
+          <t>39~40</t>
+        </is>
+      </c>
+      <c r="D16" s="266" t="inlineStr">
+        <is>
+          <t>맞판 고객관리 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="116" customHeight="1" s="43">
+      <c r="A17" s="265" t="inlineStr">
+        <is>
+          <t>2. 개인정보 보호법에 근거한 고객정보 입력</t>
+        </is>
+      </c>
+      <c r="B17" s="266" t="inlineStr">
+        <is>
+          <t>(1) 수집 가능한 경우(14세 미만 법정대리인 동의)  (2) 동의 시 고지사항  (3) 처리자의 보호 원칙(최소수집·목적 외 이용 금지·안전성 확보)  (4) 정보주체의 6대 권리
+(5) 동의 없이 이용·제공 시 고려사항  (6) 정보통신서비스 제공자 예외  (7) 목적 외 이용·제3자 제공 가능한 경우  (8) 정보주체 이외로부터 수집 시 고지
+(9) 서면 동의 시 중요 내용 표시(9포인트 이상, 20% 이상 크게)  (10) 동의 요건 및 방법</t>
+        </is>
+      </c>
+      <c r="C17" s="267" t="inlineStr">
+        <is>
+          <t>40~42</t>
+        </is>
+      </c>
+      <c r="D17" s="266" t="inlineStr">
+        <is>
+          <t>상담 시 동의 절차 / 대기자 폼 동의 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" s="43">
+      <c r="A18" s="265" t="inlineStr">
+        <is>
+          <t>3. 개인정보 보호법에 근거한 고객정보관리</t>
+        </is>
+      </c>
+      <c r="B18" s="266" t="inlineStr">
+        <is>
+          <t>(1) 처리 제한(민감·고유식별정보 별도 동의)  (2) 유출 통지·신고(1천 명 이상 72시간 내 신고)  (3) 파기  (4) 안전성 확보 조치
+(5) 영상정보처리기기 설치·운영  (6) 영업양도 시 이전  (7) 가명정보 처리  (8) 과태료  (9) 벌칙</t>
+        </is>
+      </c>
+      <c r="C18" s="267" t="inlineStr">
+        <is>
+          <t>43~47</t>
+        </is>
+      </c>
+      <c r="D18" s="266" t="inlineStr">
         <is>
           <t>고객DB 안전 관리</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" s="43">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>4. 고객 상담·고객관리 프로그램 운용</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>- 고객정보 입력·관리·상담 실무</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>맞판 매장 CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="43">
-      <c r="A20" s="80" t="inlineStr">
-        <is>
-          <t>※ '표시·기재사항 / 부당표시·광고 / 실증'은 교재상 CH01 대제목에 없음(별도 위치) — 상세는 '표시·광고 컴플라이언스' 시트 참조. 교재 내 정확한 위치는 PART 진행하며 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" s="43">
-      <c r="A22" s="82" t="inlineStr">
-        <is>
-          <t>PART 02 · (제조 및 품질관리 등) — 진행 예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" s="43">
-      <c r="A23" s="80" t="inlineStr">
-        <is>
-          <t>⬜ 원료의 종류와 특성 / 사용제한 원료 / 설비·기구 / 품질·포장 / 유통화장품 안전관리 — CH01처럼 교재 대제목 그대로 정독·분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="43">
-      <c r="A25" s="82" t="inlineStr">
-        <is>
-          <t>PART 03~04 · (유통안전 · 맞춤형화장품 등) — 진행 예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" s="43">
-      <c r="A26" s="80" t="inlineStr">
-        <is>
-          <t>⬜ 유통화장품 안전관리 / 피부·모발 생리 / 혼합·소분·위생 / 관능평가·위해평가 — 순차 작성</t>
+      <c r="A19" s="265" t="inlineStr">
+        <is>
+          <t>4. 개인정보 보호법에 근거하는 고객상담</t>
+        </is>
+      </c>
+      <c r="B19" s="266" t="inlineStr">
+        <is>
+          <t>- 상담 전 안내·동의, 필수정보만, 보유기간 후 파기 / 피부진단 데이터를 연구에 쓰려면 별도 동의</t>
+        </is>
+      </c>
+      <c r="C19" s="267" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D19" s="266" t="inlineStr">
+        <is>
+          <t>맞판 매장 CRM·피부측정 상담</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="43"/>
+    <row r="21" ht="22" customHeight="1" s="43">
+      <c r="A21" s="263" t="inlineStr">
+        <is>
+          <t>PART 02 · 화장품 제조 및 품질관리  (출제비중 25% · 선다형 20 + 단답형 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="43">
+      <c r="A22" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 01 · 화장품 원료의 종류와 특성 및 제품의 제조관리   (책 52~79쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="228" customHeight="1" s="43">
+      <c r="A23" s="265" t="inlineStr">
+        <is>
+          <t>1. 화장품 원료의 종류 및 성분의 특성</t>
+        </is>
+      </c>
+      <c r="B23" s="266" t="inlineStr">
+        <is>
+          <t>(1) 용어의 정의(극성·비극성·용제·수렴제·유화제·습윤제·밀폐제·연화제·장벽대체제·착향제 등)  (2) 수성 원료(정제수·에탄올·폴리올 보습제)
+(3) 유성 원료(유지·탄화수소·실리콘·왁스·고급지방산·고급알코올·에스테르)
+(4) 계면활성제: 구조·미셀(CMC)·HLB·종류(음이온·양이온·양쪽성·비이온; 세정력 음&gt;양쪽&gt;양&gt;비, 자극 양&gt;음&gt;양쪽&gt;비)
+(5) 고분자(점증제·피막형성제)  (6) 색소(타르색소·레이크, 유기합성·무기안료, 사용 기준별 분류)  (7) 향료(탑·미들·베이스, 부향률)
+(8) 보존제(조건, 1·2차 미생물 오염)  (9) 산화방지제(토코페롤·BHT·BHA)  (10) 금속이온봉쇄제(EDTA·소듐시트레이트)
+(11) 자료 제출 생략 기능성 고시 성분: 자외선 차단(징크옥사이드·티타늄디옥사이드 25%, SPF·PA 표시) / 미백(나이아신아마이드 2~5%·알부틴 2~5% 등) / 주름(아데노신 0.04%·레티놀 2500IU/g 등) / 체모 제거 / 여드름(살리실릭애씨드 0.5%) / 염모 / 탈모 완화
+(12) 기능성화장품 제형(보고 대상, 원료 성분·성상 표)  (13) 고시 외 기타 성분(병풀·세라마이드·소듐하이알루로네이트·알란토인·AHA 등)  (14) 비타민의 종류</t>
+        </is>
+      </c>
+      <c r="C23" s="267" t="inlineStr">
+        <is>
+          <t>52~71</t>
+        </is>
+      </c>
+      <c r="D23" s="268" t="inlineStr">
+        <is>
+          <t>★보유 원료 26종이 각각 어느 칸인지 / 나이아신아마이드 2% = 미백 고시 하한</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="88" customHeight="1" s="43">
+      <c r="A24" s="265" t="inlineStr">
+        <is>
+          <t>2. 원료 및 제품의 성분 정보</t>
+        </is>
+      </c>
+      <c r="B24" s="266" t="inlineStr">
+        <is>
+          <t>(1) 전성분 표기(함량순, 1% 이하 순서 무관, 혼합원료 개별, 향료, 영업비밀 '기타 성분')  (2) 보존제 함량 표시(영유아·어린이)
+(3) 전성분 표시 생략(50mL·g 이하, 견본품·비매품)  (4) 기재·표시사항과 생략 가능 성분
+(5) 바코드(표시 대상·15mL 이하 생략·책임판매업자 표시)  (6) 바코드 종류(GTIN-13·GTIN-14·GS1-128·GS1 DataMatrix)</t>
+        </is>
+      </c>
+      <c r="C24" s="267" t="inlineStr">
+        <is>
+          <t>72~74</t>
+        </is>
+      </c>
+      <c r="D24" s="266" t="inlineStr">
+        <is>
+          <t>처방 %표 → 전성분 초안 / 라벨 검수</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" s="43">
+      <c r="A25" s="265" t="inlineStr">
+        <is>
+          <t>3. 화장품 제품의 제조관리</t>
+        </is>
+      </c>
+      <c r="B25" s="266" t="inlineStr">
+        <is>
+          <t>(1) 제조 기술: 가용화 / 유화(W/O·O/W, 판별, 분리현상: 합일·오스트발트 숙성·응집·크리밍) / 분산
+(2) 제조 공정: 1·2차 공정, 기초·색조화장품 공정 순서, 로션·크림·화장수·고형 분말·립스틱 일반 공정</t>
+        </is>
+      </c>
+      <c r="C25" s="267" t="inlineStr">
+        <is>
+          <t>74~76</t>
+        </is>
+      </c>
+      <c r="D25" s="268" t="inlineStr">
+        <is>
+          <t>★홈랩 3상 공정(A·B·C)=유화 이론 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="43">
+      <c r="A26" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 02 · 화장품의 기능과 품질   (책 80~85쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="43">
+      <c r="A27" s="265" t="inlineStr">
+        <is>
+          <t>1. 화장품의 효과</t>
+        </is>
+      </c>
+      <c r="B27" s="266" t="inlineStr">
+        <is>
+          <t>- 세정·기초·기능성·색조·네일·모발(퍼머 1제 환원제 / 2제 산화제, 염모·제모) / 참고: 화장품·의약외품·의약품 구분</t>
+        </is>
+      </c>
+      <c r="C27" s="267" t="inlineStr">
+        <is>
+          <t>80~81</t>
+        </is>
+      </c>
+      <c r="D27" s="266" t="inlineStr">
+        <is>
+          <t>제품 유형별 소구 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1" s="43">
+      <c r="A28" s="265" t="inlineStr">
+        <is>
+          <t>2. 판매 가능한 맞춤형화장품 구성</t>
+        </is>
+      </c>
+      <c r="B28" s="266" t="inlineStr">
+        <is>
+          <t>(1) 맞춤형화장품의 의미  (2) 내용물 범위: ① 책임판매업자 제공(벌크·반제품) ② 혼합 내용물(유통화장품 기준 적합) ③ 원료+원료 혼합=제조(불가)
+(3) 유형: 현장 혼합형·공장 제조 배송형·DIY 키트형·디바이스형</t>
+        </is>
+      </c>
+      <c r="C28" s="267" t="inlineStr">
+        <is>
+          <t>81~82</t>
+        </is>
+      </c>
+      <c r="D28" s="268" t="inlineStr">
+        <is>
+          <t>★자격 후 판매 모델 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1" s="43">
+      <c r="A29" s="265" t="inlineStr">
+        <is>
+          <t>3. 내용물 및 원료의 품질성적서 구비</t>
+        </is>
+      </c>
+      <c r="B29" s="266" t="inlineStr">
+        <is>
+          <t>(1) CGMP 4대 기준서: 제품표준서·제조관리기준서·품질관리기준서·제조위생관리기준서 포함사항
+(2) 원료품질성적서 인정 기준·포함사항</t>
+        </is>
+      </c>
+      <c r="C29" s="267" t="inlineStr">
+        <is>
+          <t>82~83</t>
+        </is>
+      </c>
+      <c r="D29" s="266" t="inlineStr">
+        <is>
+          <t>OEM CoA 대조·원료 구매 시 CoA 요청</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="43">
+      <c r="A30" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 03 · 화장품 사용제한 원료   (책 86~101쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="74" customHeight="1" s="43">
+      <c r="A31" s="265" t="inlineStr">
+        <is>
+          <t>1. 화장품 사용제한 원료의 종류 및 사용한도</t>
+        </is>
+      </c>
+      <c r="B31" s="266" t="inlineStr">
+        <is>
+          <t>(1) 중요 사용금지 원료([별표 1], 네거티브 시스템)
+(2) 사용상의 제한이 필요한 원료: ① 보존제 ② 자외선 차단 성분 ③ 주요 염모제 성분 ④ 주요 기타 성분(토코페롤 20% 등)
+(3) 착향제 알레르기 유발 물질 25종  (4) 표시 지침(씻어내는 0.01% / 씻어내지 않는 0.001% 초과)  (5) 표기 개선안(1~3안 가능)</t>
+        </is>
+      </c>
+      <c r="C31" s="267" t="inlineStr">
+        <is>
+          <t>86~95</t>
+        </is>
+      </c>
+      <c r="D31" s="268" t="inlineStr">
+        <is>
+          <t>★'사용제한원료' 시트·처방설계 법적 한도 칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="88" customHeight="1" s="43">
+      <c r="A32" s="265" t="inlineStr">
+        <is>
+          <t>2. 천연화장품 및 유기농화장품의 원료 기준</t>
+        </is>
+      </c>
+      <c r="B32" s="266" t="inlineStr">
+        <is>
+          <t>(1) 용어의 정의  (2) 사용 가능 원료(합성 5% 이내, 석유화학 부분 2% 초과 불가)  (3) 오염 물질  (4) 허용 합성 원료(5% / 2%)
+(5) 제조공정(허용·금지)  (6) 작업장·제조설비  (7) 용기·포장(PVC·폴리스티렌폼 금지)  (8) 원료 조성(천연 95%, 유기농 10%+천연 95%)  (9) 함량 계산 방법
+※ 화장품법 제14조의2(천연·유기농 인증) 2025.1.31 삭제</t>
+        </is>
+      </c>
+      <c r="C32" s="267" t="inlineStr">
+        <is>
+          <t>96~99</t>
+        </is>
+      </c>
+      <c r="D32" s="266" t="inlineStr">
+        <is>
+          <t>'천연' 소구 시 근거·표현 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="43">
+      <c r="A33" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 04 · 화장품 관리   (책 102~110쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="43">
+      <c r="A34" s="265" t="inlineStr">
+        <is>
+          <t>1. 용어 정리</t>
+        </is>
+      </c>
+      <c r="B34" s="266" t="inlineStr">
+        <is>
+          <t>- 원료·원자재·완제품·재작업·품질보증·사용기한</t>
+        </is>
+      </c>
+      <c r="C34" s="267" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D34" s="266" t="inlineStr">
+        <is>
+          <t>기록 용어 통일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="43">
+      <c r="A35" s="265" t="inlineStr">
+        <is>
+          <t>2. 화장품의 취급 방법</t>
+        </is>
+      </c>
+      <c r="B35" s="266" t="inlineStr">
+        <is>
+          <t>- 바닥·벽에 닿지 않게, 선입선출, 구획 보관, 보관기한 재평가, 품질부서 책임자 출고 승인</t>
+        </is>
+      </c>
+      <c r="C35" s="267" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D35" s="266" t="inlineStr">
+        <is>
+          <t>원료 보관 박스 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="43">
+      <c r="A36" s="265" t="inlineStr">
+        <is>
+          <t>3. 화장품의 보관 방법</t>
+        </is>
+      </c>
+      <c r="B36" s="266" t="inlineStr">
+        <is>
+          <t>- 보관 조건, 불출·검사 중·불합격 구분, 수동·전산 시스템, 파레트 표시(명칭·제조번호·보관 조건·불출 상태)</t>
+        </is>
+      </c>
+      <c r="C36" s="267" t="inlineStr">
+        <is>
+          <t>102~103</t>
+        </is>
+      </c>
+      <c r="D36" s="266" t="inlineStr">
+        <is>
+          <t>재고판·라벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" s="43">
+      <c r="A37" s="265" t="inlineStr">
+        <is>
+          <t>4. 화장품의 사용 방법</t>
+        </is>
+      </c>
+      <c r="B37" s="266" t="inlineStr">
+        <is>
+          <t>- ①~⑨, 내용물 이상(색·냄새·층분리) 시 사용 중지</t>
+        </is>
+      </c>
+      <c r="C37" s="267" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D37" s="266" t="inlineStr">
+        <is>
+          <t>사용법 안내 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="74" customHeight="1" s="43">
+      <c r="A38" s="265" t="inlineStr">
+        <is>
+          <t>5. 화장품 사용할 때의 주의사항</t>
+        </is>
+      </c>
+      <c r="B38" s="266" t="inlineStr">
+        <is>
+          <t>(1) 공통사항(직사광선 이상 시 상담·상처 부위·어린이 손/직사광선 피해 보관)
+(2) 유형별 주의사항(스크럽·팩·두발·퍼머·외음부 세정제·에어로졸·염모제(패치테스트 48시간)·탈염·제모제)
+(3) 함유 성분별 주의사항(과산화수소·벤잘코늄·살리실릭애씨드·알부틴 2%·AHA·카민·포름알데하이드 0.05%·파라벤류 등)</t>
+        </is>
+      </c>
+      <c r="C38" s="267" t="inlineStr">
+        <is>
+          <t>103~108</t>
+        </is>
+      </c>
+      <c r="D38" s="268" t="inlineStr">
+        <is>
+          <t>★라벨 주의사항 문구 그대로 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="43">
+      <c r="A39" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 05 · 위해사례 판단 및 보고   (책 111~118쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="102" customHeight="1" s="43">
+      <c r="A40" s="265" t="inlineStr">
+        <is>
+          <t>1. 위해 여부 판단</t>
+        </is>
+      </c>
+      <c r="B40" s="266" t="inlineStr">
+        <is>
+          <t>(1) 용어의 정의(위해요소·위해성·위해성 평가·노출평가·위해도 결정·안전역 등)  (2) 「인체적용제품의 위해성 평가에 관한 법률」 목적
+(3) 위해성 평가 정책 수립·추진(종합평가, 기본계획 5년마다)
+(4) 위해성 평가 수행: ① 대상 ② 단계(의도적/비의도적 물질) ③ 위해성 등급(가·나·다) ④ 회수 기간(가 15일, 나·다 30일)
+(5) 위해 평가 필요성 검토(필요·불필요한 경우, 소비자 요청, 일시적 금지 조치)  (6) 활성화 기반·정보 수집</t>
+        </is>
+      </c>
+      <c r="C40" s="267" t="inlineStr">
+        <is>
+          <t>111~115</t>
+        </is>
+      </c>
+      <c r="D40" s="268" t="inlineStr">
+        <is>
+          <t>★위해 등급별 회수 기간 암기</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" s="43">
+      <c r="A41" s="265" t="inlineStr">
+        <is>
+          <t>2. 위해 사례 보고</t>
+        </is>
+      </c>
+      <c r="B41" s="266" t="inlineStr">
+        <is>
+          <t>(1) 안전성 정보의 보고: ① 주체와 내용(신속보고 15일, 정기보고 매 반기 종료 후 1개월) ② 보고 방법
+(2) 위해 화장품 회수 계획·절차(회수계획서 5일 이내, 통보 자료 2년 보관, 폐기확인서 2년, 회수량별 행정처분 감경·면제, 공표)</t>
+        </is>
+      </c>
+      <c r="C41" s="267" t="inlineStr">
+        <is>
+          <t>115~116</t>
+        </is>
+      </c>
+      <c r="D41" s="266" t="inlineStr">
+        <is>
+          <t>출시 후 CS·트러블 접수 절차</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" s="43">
+      <c r="A43" s="263" t="inlineStr">
+        <is>
+          <t>PART 03 · 유통화장품 안전관리  (출제비중 25% · 선다형 25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="43">
+      <c r="A44" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 01 · 작업장 위생관리   (책 122~133쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1" s="43">
+      <c r="A45" s="265" t="inlineStr">
+        <is>
+          <t>1. 작업장 위생 기준</t>
+        </is>
+      </c>
+      <c r="B45" s="266" t="inlineStr">
+        <is>
+          <t>(1) CGMP(목적, 3대 요소)  (2) 작업소 시설 적합 기준(구획·구분·분리)  (3) 작업소 위생 기준  (4) 구역별 위생관리(보관·원료 취급·제조·포장)</t>
+        </is>
+      </c>
+      <c r="C45" s="267" t="inlineStr">
+        <is>
+          <t>122~123</t>
+        </is>
+      </c>
+      <c r="D45" s="266" t="inlineStr">
+        <is>
+          <t>홈랩 동선·클린벤치 구획</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" s="43">
+      <c r="A46" s="265" t="inlineStr">
+        <is>
+          <t>2. 작업장의 위생 상태</t>
+        </is>
+      </c>
+      <c r="B46" s="266" t="inlineStr">
+        <is>
+          <t>(1) 청정도 등급(1~4등급) 및 관리 기준(1등급 낙하균 10개/hr, 2등급 30개/hr)  (2) 에어 필터(P/F·M/F·HEPA)
+(3) 낙하균 측정법(Koch법, 세균 30~35℃ 48시간 / 진균 20~25℃ 5일)  (4) 공기 조절 4대 요소(청정도·온도·습도·기류)</t>
+        </is>
+      </c>
+      <c r="C46" s="267" t="inlineStr">
+        <is>
+          <t>123~126</t>
+        </is>
+      </c>
+      <c r="D46" s="268" t="inlineStr">
+        <is>
+          <t>★등급·수치 빈출</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1" s="43">
+      <c r="A47" s="265" t="inlineStr">
+        <is>
+          <t>3. 작업장의 위생 유지관리 활동</t>
+        </is>
+      </c>
+      <c r="B47" s="266" t="inlineStr">
+        <is>
+          <t>(1) 유지관리 기준  (2) 주요사항(점검항목)  (3) 방충·방서  (4) 청소 방법과 위생 처리</t>
+        </is>
+      </c>
+      <c r="C47" s="267" t="inlineStr">
+        <is>
+          <t>126~127</t>
+        </is>
+      </c>
+      <c r="D47" s="266" t="inlineStr">
+        <is>
+          <t>주말 실험 전 청소 루틴</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1" s="43">
+      <c r="A48" s="265" t="inlineStr">
+        <is>
+          <t>4. 작업장 위생 유지를 위한 세제의 종류와 사용법</t>
+        </is>
+      </c>
+      <c r="B48" s="266" t="inlineStr">
+        <is>
+          <t>(1) 세제 성분(계면활성제·살균제·금속이온봉쇄제 등)  (2) 구성 요건  (3) 요구조건  (4) 작업장별 청소주기·세제</t>
+        </is>
+      </c>
+      <c r="C48" s="267" t="inlineStr">
+        <is>
+          <t>127~128</t>
+        </is>
+      </c>
+      <c r="D48" s="266" t="inlineStr">
+        <is>
+          <t>세척 세제 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" s="43">
+      <c r="A49" s="265" t="inlineStr">
+        <is>
+          <t>5. 소독제와 중화제</t>
+        </is>
+      </c>
+      <c r="B49" s="266" t="inlineStr">
+        <is>
+          <t>(1) 소독제 종류: 물리적(스팀·온수) / 화학적(70% 에탄올·차아염소산나트륨·벤잘코늄클로라이드 등)  (2) 이상적 조건  (3) 선택 시 고려사항
+(4) 효과 영향 요인  (5) 소독액 보관  (6) 작업장 소독  (7) 항균활성 중화제(레시틴·폴리솔베이트80 등)</t>
+        </is>
+      </c>
+      <c r="C49" s="267" t="inlineStr">
+        <is>
+          <t>129~131</t>
+        </is>
+      </c>
+      <c r="D49" s="268" t="inlineStr">
+        <is>
+          <t>★70% 에탄올 소독=홈랩 기본</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" s="43">
+      <c r="A50" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 02 · 작업자 위생관리   (책 134~138쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1" s="43">
+      <c r="A51" s="265" t="inlineStr">
+        <is>
+          <t>1. 작업장 내 직원의 위생 기준 설정</t>
+        </is>
+      </c>
+      <c r="B51" s="266" t="inlineStr">
+        <is>
+          <t>- 교육, 작업복, 음식물 반입 금지, 외상·질병 격리, 방문객 동행·기록</t>
+        </is>
+      </c>
+      <c r="C51" s="267" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D51" s="266" t="inlineStr">
+        <is>
+          <t>촬영 위생 루틴(콘티 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1" s="43">
+      <c r="A52" s="265" t="inlineStr">
+        <is>
+          <t>2. 작업장 내 직원의 위생 상태 판정</t>
+        </is>
+      </c>
+      <c r="B52" s="266" t="inlineStr">
+        <is>
+          <t>- 점검 ①~③</t>
+        </is>
+      </c>
+      <c r="C52" s="267" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D52" s="266" t="inlineStr"/>
+    </row>
+    <row r="53" ht="32" customHeight="1" s="43">
+      <c r="A53" s="265" t="inlineStr">
+        <is>
+          <t>3. 혼합·소분 시 위생관리 규정</t>
+        </is>
+      </c>
+      <c r="B53" s="266" t="inlineStr">
+        <is>
+          <t>- 품질성적서 확인, 손 소독(일회용 장갑 시 예외), 포장용기 오염 확인, 장비 점검·세척</t>
+        </is>
+      </c>
+      <c r="C53" s="267" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D53" s="268" t="inlineStr">
+        <is>
+          <t>★맞판 실기 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1" s="43">
+      <c r="A54" s="265" t="inlineStr">
+        <is>
+          <t>4. 작업자 위생 유지를 위한 세제의 종류와 사용법</t>
+        </is>
+      </c>
+      <c r="B54" s="266" t="inlineStr">
+        <is>
+          <t>- 손 세정제 / 손 소독제(의약외품)</t>
+        </is>
+      </c>
+      <c r="C54" s="267" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D54" s="266" t="inlineStr"/>
+    </row>
+    <row r="55" ht="32" customHeight="1" s="43">
+      <c r="A55" s="265" t="inlineStr">
+        <is>
+          <t>5. 작업자 소독을 위한 소독제의 종류와 사용법</t>
+        </is>
+      </c>
+      <c r="B55" s="266" t="inlineStr">
+        <is>
+          <t>(1) 선택  (2) 사용 방법(15초 이상)  (3) 종류(알코올 70~80%·클로르헥시딘·헥사클로로펜·아이오도퍼)</t>
+        </is>
+      </c>
+      <c r="C55" s="267" t="inlineStr">
+        <is>
+          <t>135~136</t>
+        </is>
+      </c>
+      <c r="D55" s="266" t="inlineStr">
+        <is>
+          <t>손 소독 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1" s="43">
+      <c r="A56" s="265" t="inlineStr">
+        <is>
+          <t>6. 작업자 위생관리를 위한 복장 청결 상태 판단</t>
+        </is>
+      </c>
+      <c r="B56" s="266" t="inlineStr">
+        <is>
+          <t>(1) 복장 청결 판단  (2) 작업 복장 기준(방진복·작업복·실험복)  (3) 구역별 복장 기준</t>
+        </is>
+      </c>
+      <c r="C56" s="267" t="inlineStr">
+        <is>
+          <t>136~137</t>
+        </is>
+      </c>
+      <c r="D56" s="266" t="inlineStr">
+        <is>
+          <t>장갑·헤어캡·마스크 통일(브랜딩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" s="43">
+      <c r="A57" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 03 · 설비 및 기구관리   (책 139~145쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="46" customHeight="1" s="43">
+      <c r="A58" s="265" t="inlineStr">
+        <is>
+          <t>1. 설비·기구의 위생 기준 설정</t>
+        </is>
+      </c>
+      <c r="B58" s="266" t="inlineStr">
+        <is>
+          <t>(1) 설비 위생 기준(저울: 영점·수평 매일, 정기점검 1개월, 편심오차 ±0.1%)  (2) 설비 세척 원칙(물 최적, 세제 최소)  (3) 제조 시설 세척·평가  (4) 물의 품질</t>
+        </is>
+      </c>
+      <c r="C58" s="267" t="inlineStr">
+        <is>
+          <t>139~140</t>
+        </is>
+      </c>
+      <c r="D58" s="268" t="inlineStr">
+        <is>
+          <t>★정밀저울 점검 습관</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1" s="43">
+      <c r="A59" s="265" t="inlineStr">
+        <is>
+          <t>2. 설비·기구의 위생 상태 판정</t>
+        </is>
+      </c>
+      <c r="B59" s="266" t="inlineStr">
+        <is>
+          <t>- 육안·닦아내기·린스 정량법(HPLC·TLC·TOC·UV)·표면 균 측정법(면봉·콘택트 플레이트)</t>
+        </is>
+      </c>
+      <c r="C59" s="267" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D59" s="266" t="inlineStr"/>
+    </row>
+    <row r="60" ht="32" customHeight="1" s="43">
+      <c r="A60" s="265" t="inlineStr">
+        <is>
+          <t>3. 오염 물질 제거 및 소독 방법</t>
+        </is>
+      </c>
+      <c r="B60" s="266" t="inlineStr">
+        <is>
+          <t>(1) 세척 대상 물질  (2) 세척 대상 설비  (3) 세척·소독 방법(유화기=물+브러시 제1선택지)  (4) 설비 세척제 유형(pH별)</t>
+        </is>
+      </c>
+      <c r="C60" s="267" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D60" s="266" t="inlineStr">
+        <is>
+          <t>호모·비커 세척법</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1" s="43">
+      <c r="A61" s="265" t="inlineStr">
+        <is>
+          <t>4. 설비·기구의 구성 재질 구분</t>
+        </is>
+      </c>
+      <c r="B61" s="266" t="inlineStr">
+        <is>
+          <t>- 탱크(316 스테인리스)·펌프·호모게나이저·호스·필터·이송파이프·칭량장치·게이지·충전기</t>
+        </is>
+      </c>
+      <c r="C61" s="267" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D61" s="266" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="43">
+      <c r="A62" s="265" t="inlineStr">
+        <is>
+          <t>5. 설비·기구의 폐기 기준</t>
+        </is>
+      </c>
+      <c r="B62" s="266" t="inlineStr">
+        <is>
+          <t>- 점검·정비 계획, 설비 결함, 부품 교체, 이력 관리, 불용 처리</t>
+        </is>
+      </c>
+      <c r="C62" s="267" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D62" s="266" t="inlineStr">
+        <is>
+          <t>장비 이력 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" s="43">
+      <c r="A63" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 04 · 내용물 및 원료관리   (책 146~161쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="46" customHeight="1" s="43">
+      <c r="A64" s="265" t="inlineStr">
+        <is>
+          <t>1. 내용물 및 원료의 입고 기준</t>
+        </is>
+      </c>
+      <c r="B64" s="266" t="inlineStr">
+        <is>
+          <t>(1) 용어(일탈·기준일탈·뱃치 등)  (2) 입고관리 기준(구매요구서·성적서·현품 일치, 필수 기재사항)  (3) 입고 처리 순서(백색→황색→청색 적합 / 적색 부적합)</t>
+        </is>
+      </c>
+      <c r="C64" s="267" t="inlineStr">
+        <is>
+          <t>146~147</t>
+        </is>
+      </c>
+      <c r="D64" s="266" t="inlineStr">
+        <is>
+          <t>원료 입고 시 CoA·라벨 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="116" customHeight="1" s="43">
+      <c r="A65" s="265" t="inlineStr">
+        <is>
+          <t>2. 유통화장품의 안전관리 기준</t>
+        </is>
+      </c>
+      <c r="B65" s="266" t="inlineStr">
+        <is>
+          <t>(1) 공통 기준: ① 비의도적 검출 허용한도(납 20·비소 10·수은 1·디옥산 100 μg/g 등) ② 사용 금지 원료 검출 시 위해 평가 ③ 미생물 한도(영유아·눈화장 500, 기타 1,000, 대장균·녹농균·황색포도상구균 불검출) ④ 내용량(평균 97% 이상)
+(2) 유형별 추가 기준(액상 pH 3.0~9.0, 화장비누 유리알칼리 0.1%, 기능성 주원료 함량)  (3) 퍼머넌트웨이브·헤어스트레이트너 기준
+(4) 시험 방법  (5) 인체 세포·조직 배양액 안전 기준(1B Class 10,000, 기록 3년)</t>
+        </is>
+      </c>
+      <c r="C65" s="267" t="inlineStr">
+        <is>
+          <t>148~156</t>
+        </is>
+      </c>
+      <c r="D65" s="268" t="inlineStr">
+        <is>
+          <t>★'유통안전·OEM검수' 시트 / CoA 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1" s="43">
+      <c r="A66" s="265" t="inlineStr">
+        <is>
+          <t>3. 입고된 원료 및 내용물관리 기준</t>
+        </is>
+      </c>
+      <c r="B66" s="266" t="inlineStr">
+        <is>
+          <t>(1) 원료 개봉 시 주의  (2) 적절한 보관 고려사항(보관 온도)  (3) 반제품 보관 기준  (4) 벌크제품 보관 기준</t>
+        </is>
+      </c>
+      <c r="C66" s="267" t="inlineStr">
+        <is>
+          <t>156~157</t>
+        </is>
+      </c>
+      <c r="D66" s="266" t="inlineStr">
+        <is>
+          <t>재고 보관 온도</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1" s="43">
+      <c r="A67" s="265" t="inlineStr">
+        <is>
+          <t>4. 보관 중인 원료 및 내용물 출고 기준</t>
+        </is>
+      </c>
+      <c r="B67" s="266" t="inlineStr">
+        <is>
+          <t>- 뱃치 합격, 품질부서 책임자 승인, 선입선출, 바닥·벽 이격</t>
+        </is>
+      </c>
+      <c r="C67" s="267" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D67" s="266" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1" s="43">
+      <c r="A68" s="265" t="inlineStr">
+        <is>
+          <t>5. 내용물 및 원료의 폐기 기준 및 폐기 절차</t>
+        </is>
+      </c>
+      <c r="B68" s="266" t="inlineStr">
+        <is>
+          <t>(1) 기준일탈 처리 과정  (2) 폐기 기준  (3) 불만 처리  (4) 재작업 처리  (5) 폐기확인서 포함 내용</t>
+        </is>
+      </c>
+      <c r="C68" s="267" t="inlineStr">
+        <is>
+          <t>157~158</t>
+        </is>
+      </c>
+      <c r="D68" s="266" t="inlineStr">
+        <is>
+          <t>실패 배치 '접기' 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1" s="43">
+      <c r="A69" s="265" t="inlineStr">
+        <is>
+          <t>6. 내용물 및 원료의 개봉 후 사용기한 확인·판정</t>
+        </is>
+      </c>
+      <c r="B69" s="266" t="inlineStr">
+        <is>
+          <t>- 시험기준서·성적서 대조</t>
+        </is>
+      </c>
+      <c r="C69" s="267" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D69" s="266" t="inlineStr">
+        <is>
+          <t>원료 개봉일 라벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1" s="43">
+      <c r="A70" s="265" t="inlineStr">
+        <is>
+          <t>7. 내용물 및 원료의 변질 상태(변색, 변취 등) 확인</t>
+        </is>
+      </c>
+      <c r="B70" s="266" t="inlineStr">
+        <is>
+          <t>(1) 검체 채취·보관  (2) 완제품 보관 검체(2번 시험 양, 사용기한까지)  (3) 보관기간(개봉 후 사용기간 기재 시 제조일로부터 3년)</t>
+        </is>
+      </c>
+      <c r="C70" s="267" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D70" s="266" t="inlineStr">
+        <is>
+          <t>안정성 바이알 보관</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" s="43">
+      <c r="A71" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 05 · 포장재의 관리   (책 162~168쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1" s="43">
+      <c r="A72" s="265" t="inlineStr">
+        <is>
+          <t>1. 포장재의 입고 기준</t>
+        </is>
+      </c>
+      <c r="B72" s="266" t="inlineStr">
+        <is>
+          <t>(1) 입고 과정(1차·2차 포장)  (2) 관리 필요사항  (3) 선정 절차  (4) 안전용기·포장 기준(5세 미만, 대상 품목)</t>
+        </is>
+      </c>
+      <c r="C72" s="267" t="inlineStr">
+        <is>
+          <t>162~163</t>
+        </is>
+      </c>
+      <c r="D72" s="266" t="inlineStr">
+        <is>
+          <t>용기 선택·OEM 포장 사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="46" customHeight="1" s="43">
+      <c r="A73" s="265" t="inlineStr">
+        <is>
+          <t>2. 입고된 포장재 관리 기준</t>
+        </is>
+      </c>
+      <c r="B73" s="266" t="inlineStr">
+        <is>
+          <t>(1) 보관 장소  (2) 보관 방법  (3) 포장지시서 포함 내용  (4) 포장용기 종류(밀폐·기밀·밀봉·차광)  (5) 포장·용기 시험 방법(감압누설·크로스컷트 등)</t>
+        </is>
+      </c>
+      <c r="C73" s="267" t="inlineStr">
+        <is>
+          <t>163~165</t>
+        </is>
+      </c>
+      <c r="D73" s="268" t="inlineStr">
+        <is>
+          <t>★용기 종류 정의 빈출</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1" s="43">
+      <c r="A74" s="265" t="inlineStr">
+        <is>
+          <t>3. 보관 중인 포장재 출고 기준</t>
+        </is>
+      </c>
+      <c r="B74" s="266" t="inlineStr">
+        <is>
+          <t>- 선입선출(선한선출 예외)</t>
+        </is>
+      </c>
+      <c r="C74" s="267" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D74" s="266" t="inlineStr"/>
+    </row>
+    <row r="75" ht="30" customHeight="1" s="43">
+      <c r="A75" s="265" t="inlineStr">
+        <is>
+          <t>4. 포장재의 폐기 기준</t>
+        </is>
+      </c>
+      <c r="B75" s="266" t="inlineStr">
+        <is>
+          <t>- 재고조사·일탈처리, 폐기 처분 과정</t>
+        </is>
+      </c>
+      <c r="C75" s="267" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D75" s="266" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1" s="43">
+      <c r="A76" s="265" t="inlineStr">
+        <is>
+          <t>5. 포장재의 사용기간 확인·판정</t>
+        </is>
+      </c>
+      <c r="B76" s="266" t="inlineStr">
+        <is>
+          <t>- 보관기한 설정·재평가</t>
+        </is>
+      </c>
+      <c r="C76" s="267" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D76" s="266" t="inlineStr"/>
+    </row>
+    <row r="77" ht="30" customHeight="1" s="43">
+      <c r="A77" s="265" t="inlineStr">
+        <is>
+          <t>6. 포장재의 개봉 후 사용기간 확인·판정</t>
+        </is>
+      </c>
+      <c r="B77" s="266" t="inlineStr">
+        <is>
+          <t>(1) 사용기한  (2) 개봉 후 사용기간(12M 심벌)</t>
+        </is>
+      </c>
+      <c r="C77" s="267" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D77" s="266" t="inlineStr">
+        <is>
+          <t>라벨 PAO 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1" s="43">
+      <c r="A78" s="265" t="inlineStr">
+        <is>
+          <t>7. 포장재의 변질 상태 확인</t>
+        </is>
+      </c>
+      <c r="B78" s="266" t="inlineStr">
+        <is>
+          <t>(1) 변질 상태 확인  (2) 변질 예방</t>
+        </is>
+      </c>
+      <c r="C78" s="267" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D78" s="266" t="inlineStr"/>
+    </row>
+    <row r="79" ht="30" customHeight="1" s="43">
+      <c r="A79" s="265" t="inlineStr">
+        <is>
+          <t>8. 포장재의 폐기 절차</t>
+        </is>
+      </c>
+      <c r="B79" s="266" t="inlineStr">
+        <is>
+          <t>- 부적합 라벨 → 격리 → 분리수거 → 대장 기록 → 인계</t>
+        </is>
+      </c>
+      <c r="C79" s="267" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D79" s="266" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1" s="43">
+      <c r="A81" s="263" t="inlineStr">
+        <is>
+          <t>PART 04 · 맞춤형화장품의 이해  (출제비중 40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" s="43">
+      <c r="A82" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 01 · 맞춤형화장품 개요   (책 172~181쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1" s="43">
+      <c r="A83" s="265" t="inlineStr">
+        <is>
+          <t>1. 맞춤형화장품 정의</t>
+        </is>
+      </c>
+      <c r="B83" s="266" t="inlineStr">
+        <is>
+          <t>- 내용물+내용물·원료 혼합 / 내용물 소분(고형비누 단순 소분 제외)</t>
+        </is>
+      </c>
+      <c r="C83" s="267" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D83" s="268" t="inlineStr">
+        <is>
+          <t>★자격 후 판매 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="74" customHeight="1" s="43">
+      <c r="A84" s="265" t="inlineStr">
+        <is>
+          <t>2. 맞춤형화장품 주요 규정(관련 법령)</t>
+        </is>
+      </c>
+      <c r="B84" s="266" t="inlineStr">
+        <is>
+          <t>(1) 화장품법: 판매업 신고·결격사유·자격시험·조제관리사 결격·자격증 대여 금지·유사명칭·자격 취소·영업자 의무·안전용기·판매 등의 금지(제16조)
+(2) 시행규칙: 판매업 신고·변경신고(30일)·시설기준·행정처분·자격시험(매년 1회 이상)·판매업자 준수사항·교육(최초 6개월, 매년 4~8시간)·폐업 신고
+(3) 「화장품 안전 기준 등에 관한 규정」 제5조 맞춤형화장품에 사용 가능한 원료</t>
+        </is>
+      </c>
+      <c r="C84" s="267" t="inlineStr">
+        <is>
+          <t>172~176</t>
+        </is>
+      </c>
+      <c r="D84" s="268" t="inlineStr">
+        <is>
+          <t>★맞판 신고 실무 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1" s="43">
+      <c r="A85" s="265" t="inlineStr">
+        <is>
+          <t>3. 화장품의 안전성</t>
+        </is>
+      </c>
+      <c r="B85" s="266" t="inlineStr">
+        <is>
+          <t>(1) 안전성시험(단회투여독성~유전독성)  (2) 안전성 정보 관리체계  (3) 영유아·어린이 사용 화장품 안전성 자료</t>
+        </is>
+      </c>
+      <c r="C85" s="267" t="inlineStr">
+        <is>
+          <t>176~177</t>
+        </is>
+      </c>
+      <c r="D85" s="266" t="inlineStr"/>
+    </row>
+    <row r="86" ht="32" customHeight="1" s="43">
+      <c r="A86" s="265" t="inlineStr">
+        <is>
+          <t>4. 화장품의 유효성</t>
+        </is>
+      </c>
+      <c r="B86" s="266" t="inlineStr">
+        <is>
+          <t>(1) 유효성·기능 자료(효력시험·인체적용시험·염모효력시험)  (2) SPF·내수성 SPF·PA 근거자료  (3) 제출자료 면제</t>
+        </is>
+      </c>
+      <c r="C86" s="267" t="inlineStr">
+        <is>
+          <t>177~179</t>
+        </is>
+      </c>
+      <c r="D86" s="266" t="inlineStr">
+        <is>
+          <t>효능 표현 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1" s="43">
+      <c r="A87" s="265" t="inlineStr">
+        <is>
+          <t>5. 화장품의 안정성</t>
+        </is>
+      </c>
+      <c r="B87" s="266" t="inlineStr">
+        <is>
+          <t>(1) 안정성시험 가이드라인(분리·합일·응집)  (2) 종류  (3) 방법(3로트, 가속=장기+15℃)  (4) 기간·측정시기(장기 6개월 이상, 1년간 3개월마다)</t>
+        </is>
+      </c>
+      <c r="C87" s="267" t="inlineStr">
+        <is>
+          <t>179~180</t>
+        </is>
+      </c>
+      <c r="D87" s="268" t="inlineStr">
+        <is>
+          <t>★45℃·RT·4℃ 집 안정성 관찰 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" s="43">
+      <c r="A88" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 02 · 피부 및 모발의 생리구조   (책 182~191쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="88" customHeight="1" s="43">
+      <c r="A89" s="265" t="inlineStr">
+        <is>
+          <t>1. 피부의 생리구조</t>
+        </is>
+      </c>
+      <c r="B89" s="266" t="inlineStr">
+        <is>
+          <t>(1) 정의(pH 4.5~6.5)  (2) 기능(보호·감각·체온조절·면역·비타민D 합성 등)
+(3) 구조: ① 표피(각질층: 케라틴 58%·NMF 31%·세포간지질 11%, 각화주기 28±3일 / 투명·과립·유극(랑게르한스)·기저층(멜라닌형성세포·머켈)) ② 진피(유두층·망상층, 교원섬유 90%) ③ 피하조직 ④ 부속기관(피지선·아포크린·에크린)</t>
+        </is>
+      </c>
+      <c r="C89" s="267" t="inlineStr">
+        <is>
+          <t>182~185</t>
+        </is>
+      </c>
+      <c r="D89" s="268" t="inlineStr">
+        <is>
+          <t>★세라마이드·NMF=장벽 소구 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1" s="43">
+      <c r="A90" s="265" t="inlineStr">
+        <is>
+          <t>2. 모발의 생리구조</t>
+        </is>
+      </c>
+      <c r="B90" s="266" t="inlineStr">
+        <is>
+          <t>(1) 특징  (2) 구조(모간: 모표피·모피질·모수질 / 모근)  (3) 4대 화학적 결합  (4) 성장주기(성장기 3~6년)  (5) 두피의 특징과 기능</t>
+        </is>
+      </c>
+      <c r="C90" s="267" t="inlineStr">
+        <is>
+          <t>185~187</t>
+        </is>
+      </c>
+      <c r="D90" s="266" t="inlineStr"/>
+    </row>
+    <row r="91" ht="74" customHeight="1" s="43">
+      <c r="A91" s="265" t="inlineStr">
+        <is>
+          <t>3. 피부와 모발의 상태 분석</t>
+        </is>
+      </c>
+      <c r="B91" s="266" t="inlineStr">
+        <is>
+          <t>(1) 피부: ① 분석 방법(문진·견진·촉진·기기) ② 측정(수분·TEWL·pH·유분·레플리카) ③ 유형별 특징(지성·민감성·여드름·색소침착; UVA·UVB·UVC) ④ 피츠패트릭 분류
+(2) 모발 진단 방법  (3) 두피·모발 상태(탈모 증상·원인, 비듬 원인=말라쎄지아)</t>
+        </is>
+      </c>
+      <c r="C91" s="267" t="inlineStr">
+        <is>
+          <t>187~189</t>
+        </is>
+      </c>
+      <c r="D91" s="268" t="inlineStr">
+        <is>
+          <t>★말라쎄지아=히어로 컨셉의 교재 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1" s="43">
+      <c r="A92" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 03 · 관능평가 방법과 절차   (책 192~194쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1" s="43">
+      <c r="A93" s="265" t="inlineStr">
+        <is>
+          <t>(관능평가 단일 절)</t>
+        </is>
+      </c>
+      <c r="B93" s="266" t="inlineStr">
+        <is>
+          <t>(1) 관능평가  (2) 외관·색상 검사 순서  (3) 요소(탁도·변취·분리·점도/경도·증발/표면 굳음)  (4) 제품별 요소
+(5) 물리화학적 평가법(마찰감·Rheometer·Cutometer / 광택계 등)  (6) 자가평가(맹검·비맹검 사용시험, 전문가 패널)  (7) 전문가 평가</t>
+        </is>
+      </c>
+      <c r="C93" s="267" t="inlineStr">
+        <is>
+          <t>192~193</t>
+        </is>
+      </c>
+      <c r="D93" s="266" t="inlineStr">
+        <is>
+          <t>개발일지 사용감 기록 틀</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" s="43">
+      <c r="A94" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 04 · 제품 상담   (책 195~198쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1" s="43">
+      <c r="A95" s="265" t="inlineStr">
+        <is>
+          <t>1. 맞춤형화장품의 효과</t>
+        </is>
+      </c>
+      <c r="B95" s="266" t="inlineStr">
+        <is>
+          <t>- 개인 맞춤·정확한 피부 측정·원하는 혼합/소분</t>
+        </is>
+      </c>
+      <c r="C95" s="267" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D95" s="266" t="inlineStr"/>
+    </row>
+    <row r="96" ht="32" customHeight="1" s="43">
+      <c r="A96" s="265" t="inlineStr">
+        <is>
+          <t>2. 맞춤형화장품의 부작용</t>
+        </is>
+      </c>
+      <c r="B96" s="266" t="inlineStr">
+        <is>
+          <t>- 식약처장 즉시 보고, SOP / 가려움·따끔거림·부종·염증·인설·자통·작열감·홍반</t>
+        </is>
+      </c>
+      <c r="C96" s="267" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D96" s="266" t="inlineStr">
+        <is>
+          <t>CS 트러블 접수 용어</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1" s="43">
+      <c r="A97" s="265" t="inlineStr">
+        <is>
+          <t>3. 배합금지 사항 확인·배합</t>
+        </is>
+      </c>
+      <c r="B97" s="266" t="inlineStr">
+        <is>
+          <t>(1) 중요 사용금지 원료·비의도 검출 한도  (2) 미생물 허용한도</t>
+        </is>
+      </c>
+      <c r="C97" s="267" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D97" s="266" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1" s="43">
+      <c r="A98" s="265" t="inlineStr">
+        <is>
+          <t>4. 내용물 및 원료의 사용제한 사항</t>
+        </is>
+      </c>
+      <c r="B98" s="266" t="inlineStr">
+        <is>
+          <t>- [별표 2] 사용제한 원료, 기능성 고시 원료(심사받은 경우 제외)</t>
+        </is>
+      </c>
+      <c r="C98" s="267" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D98" s="268" t="inlineStr">
+        <is>
+          <t>★맞판에 못 쓰는 원료</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1" s="43">
+      <c r="A99" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 05 · 제품 안내   (책 199~210쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="74" customHeight="1" s="43">
+      <c r="A100" s="265" t="inlineStr">
+        <is>
+          <t>1. 맞춤형화장품 표시사항</t>
+        </is>
+      </c>
+      <c r="B100" s="266" t="inlineStr">
+        <is>
+          <t>(1) 표시·기재사항(1차 포장 필수 4종·외부 포장·소용량/비매품)  (2) 가격표시제 실시요령  (3) 가격 기재 주의사항  (4) 포장 표시 기준·방법
+(5) 표시·광고 실증 범위(15일 이내 제출)  (6) 실증의 원칙(실증 대상·필요 자료, 금지 표현, 주요 실증 대상)  (7) 표시·광고 행정처분  (8) 기타(알레르기 25종, 추출물 함량, 영유아·어린이 표시·광고, 안전성 자료 보관기간)</t>
+        </is>
+      </c>
+      <c r="C100" s="267" t="inlineStr">
+        <is>
+          <t>199~207</t>
+        </is>
+      </c>
+      <c r="D100" s="268" t="inlineStr">
+        <is>
+          <t>★'표시·광고 컴플라이언스' 시트의 교재 위치 / 금지 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1" s="43">
+      <c r="A101" s="265" t="inlineStr">
+        <is>
+          <t>2. 맞춤형화장품 안전 기준의 주요사항</t>
+        </is>
+      </c>
+      <c r="B101" s="266" t="inlineStr">
+        <is>
+          <t>- 판매장 점검, 혼합·소분 안전관리 기준, 미생물 샘플링, 판매내역서, 입고·사용·폐기 기록, 소비자 설명, 부작용 보고</t>
+        </is>
+      </c>
+      <c r="C101" s="267" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D101" s="268" t="inlineStr">
+        <is>
+          <t>★맞판 운영 매뉴얼 뼈대</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1" s="43">
+      <c r="A102" s="265" t="inlineStr">
+        <is>
+          <t>3. 맞춤형화장품의 특징</t>
+        </is>
+      </c>
+      <c r="B102" s="266" t="inlineStr">
+        <is>
+          <t>(1) 장점  (2) 단점(후기 확인 어려움·혼합 조건에 따른 안정성 변화)</t>
+        </is>
+      </c>
+      <c r="C102" s="267" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D102" s="266" t="inlineStr"/>
+    </row>
+    <row r="103" ht="20" customHeight="1" s="43">
+      <c r="A103" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 06 · 혼합 및 소분   (책 211~222쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="46" customHeight="1" s="43">
+      <c r="A104" s="265" t="inlineStr">
+        <is>
+          <t>1. 원료 및 제형의 물리적 특성</t>
+        </is>
+      </c>
+      <c r="B104" s="266" t="inlineStr">
+        <is>
+          <t>(1) 원료의 특성  (2) 제형의 특성(로션제·액제·크림제·침적 마스크제·겔제·에어로졸제·분말제)  (3) 혼합 시 안정성 감소 요인(투입 순서·온도·회전속도·진공)</t>
+        </is>
+      </c>
+      <c r="C104" s="267" t="inlineStr">
+        <is>
+          <t>211~212</t>
+        </is>
+      </c>
+      <c r="D104" s="268" t="inlineStr">
+        <is>
+          <t>★실험 실패 원인 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1" s="43">
+      <c r="A105" s="265" t="inlineStr">
+        <is>
+          <t>2. 원료 및 내용물의 유효성</t>
+        </is>
+      </c>
+      <c r="B105" s="266" t="inlineStr">
+        <is>
+          <t>(1) 효력시험 자료  (2) 인체적용시험 자료  (3) 염모효력시험 자료  (4) 기준 및 시험 방법 자료</t>
+        </is>
+      </c>
+      <c r="C105" s="267" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D105" s="266" t="inlineStr"/>
+    </row>
+    <row r="106" ht="46" customHeight="1" s="43">
+      <c r="A106" s="265" t="inlineStr">
+        <is>
+          <t>3. 원료 및 내용물의 규격</t>
+        </is>
+      </c>
+      <c r="B106" s="266" t="inlineStr">
+        <is>
+          <t>- 원료규격서(예: 디메치콘) / (1) 기재 항목  (2) pH 기준(미산성 5.0~6.5 등)  (3) 색  (4) 냄새  (5) 점도  (6) 농도(w/v%·ppm)  (7) 온도(상온 15~25℃·실온 1~30℃)  (8) 기타</t>
+        </is>
+      </c>
+      <c r="C106" s="267" t="inlineStr">
+        <is>
+          <t>214~217</t>
+        </is>
+      </c>
+      <c r="D106" s="268" t="inlineStr">
+        <is>
+          <t>★원료 TDS·규격서 읽는 법</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1" s="43">
+      <c r="A107" s="265" t="inlineStr">
+        <is>
+          <t>4. 혼합·소분에 필요한 도구·기기·기구</t>
+        </is>
+      </c>
+      <c r="B107" s="266" t="inlineStr">
+        <is>
+          <t>- 전자저울·스패출러·호모게나이저·디스퍼·오버헤드스터러·항온수조·pH미터·데시케이터·점도계 등</t>
+        </is>
+      </c>
+      <c r="C107" s="267" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D107" s="268" t="inlineStr">
+        <is>
+          <t>★보유 장비와 1:1 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1" s="43">
+      <c r="A108" s="265" t="inlineStr">
+        <is>
+          <t>5. 맞춤형화장품판매업 준수사항에 맞는 혼합·소분 활동</t>
+        </is>
+      </c>
+      <c r="B108" s="266" t="inlineStr">
+        <is>
+          <t>- ①~⑨ 조제관리사 채용·안전관리 기준·판매내역서·소비자 설명·시설 기준·작업자/장소/장비 위생·위생 환경 모니터링</t>
+        </is>
+      </c>
+      <c r="C108" s="267" t="inlineStr">
+        <is>
+          <t>219~220</t>
+        </is>
+      </c>
+      <c r="D108" s="266" t="inlineStr"/>
+    </row>
+    <row r="109" ht="20" customHeight="1" s="43">
+      <c r="A109" s="264" t="inlineStr">
+        <is>
+          <t>CHAPTER 07 · 충진 및 포장   (책 223~226쪽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1" s="43">
+      <c r="A110" s="265" t="inlineStr">
+        <is>
+          <t>1. 제품에 맞는 충진 방법</t>
+        </is>
+      </c>
+      <c r="B110" s="266" t="inlineStr">
+        <is>
+          <t>(1) 충진의 정의  (2) 충진기 종류(피스톤·파우치·파우더·액체·튜브·카톤)  (3) 충진 시 확인사항</t>
+        </is>
+      </c>
+      <c r="C110" s="267" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D110" s="266" t="inlineStr"/>
+    </row>
+    <row r="111" ht="46" customHeight="1" s="43">
+      <c r="A111" s="265" t="inlineStr">
+        <is>
+          <t>2. 제품에 적합한 포장 방법</t>
+        </is>
+      </c>
+      <c r="B111" s="266" t="inlineStr">
+        <is>
+          <t>(1) 포장재의 조건  (2) 포장재 종류·특성(PE·PP·PET·유리·금속)  (3) 용기 종류  (4) 포장 방법 기준(포장공간 비율·포장횟수)  (5) 재사용 가능 비율  (6) 맞춤형화장품 라벨링</t>
+        </is>
+      </c>
+      <c r="C111" s="267" t="inlineStr">
+        <is>
+          <t>223~225</t>
+        </is>
+      </c>
+      <c r="D111" s="266" t="inlineStr">
+        <is>
+          <t>용기·패키지 선택</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="25">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A82:D82"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A103:D103"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23738,7 +25439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="14" customWidth="1" style="43" min="1" max="1"/>
@@ -23746,6 +25447,7 @@
     <col width="34" customWidth="1" style="43" min="3" max="3"/>
     <col width="36" customWidth="1" style="43" min="4" max="4"/>
     <col width="24" customWidth="1" style="43" min="5" max="6"/>
+    <col width="24" customWidth="1" style="43" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="43">
@@ -23758,7 +25460,7 @@
     <row r="2" ht="60" customHeight="1" s="43">
       <c r="A2" s="63" t="inlineStr">
         <is>
-          <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 'C열=외우기용 / D열=쉬운 풀이'. ★과목1은 교재(에듀윌) 출제기준 세부 소제목 흐름으로 세분화 완료(입법취지→정의→유형→품질4요소→영업→기능성→표시·광고·실증→회수·행정처분→준수·보고→영유아→개인정보). 과목2~4는 순차 보강 예정. 수치·목록은 「화장품 안전기준 등에 관한 규정」·화장품법 기준 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
+          <t>과목1 화장품법 · 과목2 제조/품질 · 과목3 유통안전 · 과목4 맞춤형. 'C열=외우기용 / D열=쉬운 풀이'. ★과목1은 교재(에듀윌) 출제기준 세부 소제목 흐름으로 세분화 완료(입법취지→정의→유형→품질4요소→영업→기능성→표시·광고·실증→회수·행정처분→준수·보고→영유아→개인정보). 과목2~4도 교재 PART02~04 순서로 보강 완료 — 행 끝 '(책 N쪽)'은 교재 이론 목차의 쪽수. 수치·목록은 「화장품 안전기준 등에 관한 규정」·화장품법 기준 교육용 정리 — 시험·제조·판매 전 최신 고시로 반드시 재확인.</t>
         </is>
       </c>
     </row>
@@ -24274,771 +25976,3267 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1" s="43">
+    <row r="19" ht="80" customHeight="1" s="43">
       <c r="A19" s="31" t="inlineStr">
         <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>법령 체계</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>화장품법(법률)→시행령(대통령령)→시행규칙(총리령)→고시(행정규칙: 안전기준·기능성 심사·CGMP 등). 1999.9 약사법에서 분리, 2000.7 시행. (책 14쪽)</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>법은 큰 틀만 정하고, 시험에 나오는 숫자·목록은 대부분 '고시'에 있어요. 고시가 바뀌면 숫자도 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>원료 한도는 「화장품 안전기준 등에 관한 규정」(고시)에서 확인</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>규제 개정은 고시 단위로 추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="95" customHeight="1" s="43">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>천연·유기농·해외직구 정의</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>천연화장품=천연 함량 95% 이상 / 유기농화장품=유기농 10% 이상+천연 95% 이상(2025.1.31 정의·인증 조항 삭제). 직접구매 해외화장품=통신판매로 해외에서 직접 산 화장품. (책 14~15쪽)</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>'천연·유기농'에는 함량 기준이 있었어요. 인증 제도는 없어졌지만 근거 없이 쓰면 여전히 부당광고 위험.</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>다도기는 천연 표방 안 함(합성 유화제·방부제 사용)</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>천연 소구는 ISO 16128 지수 등 실증 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="95" customHeight="1" s="43">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>영업 결격사유·자격 취소</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>영업 결격: 정신질환자·마약 중독자·피성년후견인·금고 이상 형 관련·등록 취소 후 1년 미경과 등. 조제관리사는 자격 취소 후 3년 미경과 시 결격. 자격증 대여·유사 명칭 사용 금지. (책 21~22쪽)</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>이런 사유가 있으면 화장품 영업을 못 해요. 조제관리사 자격을 잃으면 3년간 다시 못 받습니다.</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>책임판매업 등록 전 자기 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="95" customHeight="1" s="43">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>영업자 의무·교육</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>생산·수입실적 매년 2월 말까지 보고, 원료 목록은 유통·판매 전 보고. 책임판매관리자·조제관리사 교육 매년 1회 4~8시간(최초는 종사 후 6개월 이내). (책 22·175쪽)</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>매년 '얼마나 만들었나'를 보고하고, 담당자는 해마다 교육을 받아요. 놓치면 과태료.</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>연간 생산기록=개발일지·입출고 습관</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>연간 컴플라이언스 달력(2월 실적 보고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" s="43">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>변경 신고 기한</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>변경 등록·신고는 30일 이내(행정구역 개편 등은 90일). 맞판 변경신고 처리 기간 10일(조제관리사 변경은 7일). (책 22·174쪽)</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>상호·소재지·담당자가 바뀌면 한 달 안에 신고해야 해요.</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>사무실 이전·담당자 교체 시 체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="95" customHeight="1" s="43">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>행정처분 기준</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>1년간 같은 위반 반복 시 가중, 업무정지 최대 12개월, 감경은 2분의 1까지. 과징금 10억 원 이하(업무정지 갈음). 양벌 규정(법인도 처벌). 화장품의 날 9월 7일. (책 23~28쪽)</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>같은 잘못을 1년 안에 또 하면 더 세게, 사정이 있으면 절반까지 깎아줘요.</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>위반 이력 관리=사업 지속성</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" s="43">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>벌칙·과태료 등급</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>3년 이하 징역 또는 3천만 원 이하 벌금(가장 무거움: 무등록 영업 등) / 1년·1천만 원 / 200만 원 이하 벌금. 과태료 100만·50만 원. (책 26~27쪽)</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>벌칙(형벌)과 과태료(행정벌)는 다른 것. 등록 없이 팔면 가장 무거운 등급.</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>집 제조품 판매=무등록 영업</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>판매는 OEM 제조+책임판매업 등록 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1" s="43">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>안전성 정보 보고 기한</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>신속보고(중대한 유해사례 등)=알게 된 날부터 15일 이내 / 정기보고=매 반기 종료 후 1개월 이내. 실마리정보=인과관계가 불확실하지만 보고된 정보. (책 31·115쪽)</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>큰 부작용은 15일 안에, 나머지는 반년치를 모아 한 달 안에 보고해요.</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>집 테스트 반응도 개발일지에 기록</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>출시 후 CS 접수→기록→보고 흐름</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1" s="43">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>회수 기간·처분 감경</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>위해성 가등급 15일 이내, 나·다등급 30일 이내 회수. 회수계획 5일 이내 보고, 회수·폐기 기록 2년 보관. 회수량 5분의 4 이상이면 처분 면제, 그보다 적어도 비율에 따라 감경. (책 113·116쪽)</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>위험할수록 빨리(15일) 거둬들여야 하고, 성실히 회수하면 처분을 깎아줘요.</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>배치별 제조번호가 있어야 회수 범위를 좁힘</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>리콜 시나리오·제조번호 추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1" s="43">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>안전성 자료(시험 종류)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>단회투여독성·1차피부자극·안점막자극·피부감작성·광독성·광감작성·인체첩포 시험 자료. (책 30·176쪽)</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>새 원료·기능성은 '피부에 발라도 안전한지'를 이런 시험으로 증명해요.</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>집에선 불가 — 패치 관찰까지만</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>'저자극' 표방=인체첩포 자료 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1" s="43">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>0.5% 이상 안정성 자료 보존</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>레티놀(유도체)·아스코빅애씨드(유도체)·토코페롤·과산화화합물·효소를 0.5% 이상 넣으면 책임판매업자가 안정성시험 자료를 사용기한 만료 후 1년간 보존. (책 34~35쪽)</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>잘 변하는 5가지 성분을 0.5% 넘게 쓰면 '안 변한다'는 증빙을 보관해야 해요.</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>★클렌징오일 토코페롤 1% → 해당</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>위탁 시 ODM에 안정성 자료 요구</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="95" customHeight="1" s="43">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>1.화장품법</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>맞판 준수사항·판매내역서</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>판매내역서=제조번호(식별번호)·사용기한(개봉 후 사용기간)·판매일자·판매량. 혼합·소분 안전관리 기준 준수, 소비자에게 내용물·원료·주의사항 설명, 부작용 보고. (책 35·175쪽)</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>맞춤형으로 판 것은 '무엇을 언제 얼마나'를 기록해 둬야 해요.</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>개발일지 배치 기록=판매내역서 연습</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>맞판 매장 판매기록 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" s="43">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
           <t>1.개인정보보호법</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>고객정보 수집·이용·관리·상담</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>수집·이용 동의, 목적 범위 내 이용, 안전조치, 보유기간 후 파기. 맞춤형 고객관리 근거.</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>맞춤형 매장서 고객 피부정보·연락처를 다룰 때 동의받고 안전하게 관리·파기하는 규칙.</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>맞춤형 상담 기록 관리</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>맞판 매장 고객DB 운영 기본</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" s="43">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>원료 분류</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·실리콘)/계면활성제/보습/고분자(점증)/활성/색소/보존제/착향.</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>화장품 원료는 큰 가족으로 나뉨 — 물 쪽, 기름 쪽, 둘을 섞는 것, 보습, 걸쭉하게, 효능, 색, 방부, 향. 내 26종도 다 이 중 하나.</t>
-        </is>
-      </c>
-      <c r="E20" s="34" t="inlineStr">
-        <is>
-          <t>보유 26종이 각 분류에 해당</t>
-        </is>
-      </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>CoA·규격서 읽는 눈</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1" s="43">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>계면활성제 4분류</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>음이온(세정)·양이온(살균·헤어)·양쪽성(저자극)·비이온(유화·가용화). 자극: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>물·기름 사이를 중개하는 게 계면활성제. 4종류이고 자극 세기가 다름(양이온 최강, 비이온 최순).</t>
-        </is>
-      </c>
-      <c r="E21" s="34" t="inlineStr">
-        <is>
-          <t>몬타노브68=비이온 유화제</t>
-        </is>
-      </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>세안 라인 베이스 선택 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1" s="43">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>HLB</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>친수-친유 균형값. 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화 15~18).</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>유화제가 물/기름 중 뭘 더 좋아하냐를 숫자로. 내 크림(O/W)에 맞는 유화제 고르는 기준.</t>
-        </is>
-      </c>
-      <c r="E22" s="34" t="inlineStr">
-        <is>
-          <t>크림=O/W → 유화제 HLB 맞춤</t>
-        </is>
-      </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>처방 안정성의 이론 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1" s="43">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>유화·가용화·분산</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>유화=두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일 투명 분산. 분산=고체 입자를 액에.</t>
-        </is>
-      </c>
-      <c r="D23" s="34" t="inlineStr">
-        <is>
-          <t>셋 다 '안 섞이는 걸 섞는' 기술. 뽀얗게=유화, 소량 기름 투명=가용화, 가루 퍼뜨림=분산.</t>
-        </is>
-      </c>
-      <c r="E23" s="34" t="inlineStr">
-        <is>
-          <t>크림=유화, 워시오프=가용화</t>
-        </is>
-      </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>제형 기획·제품유형 결정</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1" s="43">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>점증제·유변학</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성. 분말 검은 글리세린 선분산 후 투입.</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>묽은 액을 걸쭉하게. 잔탄검은 꼭 글리세린에 먼저 개서 넣어야 피시아이가 안 생김.</t>
-        </is>
-      </c>
-      <c r="E24" s="34" t="inlineStr">
-        <is>
-          <t>잔탄검 0.1%p 단위 점도 튜닝</t>
-        </is>
-      </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>사용감 차별화 설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1" s="43">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>보존제 사용한도</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>페녹시에탄올 1.0%·벤질알코올 1.0%·소르빅애씨드 0.6%·파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올=지정 보존제 아님.</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>물 든 화장품은 방부 필수. 단 보존제마다 '여기까지만' 한도가 있음(페녹시 1.0%).</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="inlineStr">
-        <is>
-          <t>페녹시+헥산다이올 방부</t>
-        </is>
-      </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>★챌린지테스트·방부 설계(→사용제한원료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1" s="43">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>산화방지제 ≠ 보존제</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>토코페롤·BHT='산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 목적·분류 다름.</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>토코페롤은 기름 쩐내를 막지 세균을 막는 게 아님. 보존제랑 헷갈리게 내는 단골 함정.</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>토코페롤로 오일 산패 방지</t>
-        </is>
-      </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>전성분 역할 표기 정확성</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1" s="43">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>기능성 주성분·함량</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU.</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>미백·주름은 '정해진 성분을 정해진 양'으로. 많다고 좋은 게 아니라 고시 범위 준수가 핵심.</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>나이아신아마이드 2~4% 사용</t>
-        </is>
-      </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>미백 '보고' 시 주성분 스펙</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1" s="43">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>2.제조품질</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>CGMP</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>우수화장품 제조·품질관리기준. 3요소=인적자원·시설·원자재. 문서화: 제조기록서·제조번호·일탈·재작업.</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>화장품을 깨끗하고 늘 똑같이 만드는 공장 관리 규칙. 내 개발일지가 그 작은 버전.</t>
-        </is>
-      </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t>개발일지=배치기록서 축소판</t>
-        </is>
-      </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>ODM이 CGMP 업소인지 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="80" customHeight="1" s="43">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>중금속·유해물질 한도</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈 35·색조 30)·디옥산 100·포름알데하이드 2,000(물휴지 20)·프탈레이트 100. 메탄올 0.2%(물휴지 0.002%).</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>일부러 안 넣어도 원료에 미량 섞여올 수 있는 나쁜 물질의 '넘으면 안 되는 선'. 출고 전 시험으로 확인.</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>비의도 유래물질 개념(→유통안전)</t>
-        </is>
-      </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>출고 로트별 시험성적서 요구</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1" s="43">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>미생물 한도</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>영유아·눈화장 500·물휴지 세균·진균 각 100·기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>완제품에 있어도 되는 세균 수 한계. 아기·눈 제품은 더 엄격(500), 3대 병원균은 아예 불검출.</t>
-        </is>
-      </c>
-      <c r="E30" s="34" t="inlineStr">
-        <is>
-          <t>소독·방부·1개월 내 사용</t>
-        </is>
-      </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>미생물 시험성적서 확보</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1" s="43">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>pH 기준</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>영유아·눈화장·색조·로션/크림 등 특정 액상류 pH 3.0~9.0(물로 씻어내는 제품 제외). 화장비누 유리알칼리 0.1%.</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>피부에 바르는 많은 제품은 pH 3.0~9.0. 다도기는 약산성(5.0~5.5)으로 더 좁게.</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>목표 pH 5.0~5.5 적정</t>
-        </is>
-      </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>자극 저감·라벨 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1" s="43">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>내용량 기준</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>제품 3개 평균 내용량이 표기량의 97% 이상(미달 시 6개 추가, 9개 평균 97%).</t>
-        </is>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>'50mL'이라 적었으면 실제도 평균 97% 이상 들어야 함. 덜 넣으면 안 됨.</t>
-        </is>
-      </c>
-      <c r="E32" s="34" t="inlineStr">
-        <is>
-          <t>충진량 관리</t>
-        </is>
-      </c>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>과충진 원가·미달 CS 방지</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1" s="43">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>착향 알레르기 성분</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>지정 유발성분 25종. 씻어내는 0.01%·씻어내지 않는 0.001% 초과 시 성분명 표시.</t>
-        </is>
-      </c>
-      <c r="D33" s="34" t="inlineStr">
-        <is>
-          <t>향료 속 알레르기 25종은 일정량 넘으면 이름을 따로 표시. 다도기는 무향이라 걱정 없음.</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>다도기=무향 → 알레르겐 0</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>★무향이 규제·소구 동시 이점</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1" s="43">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>3.유통안전</t>
-        </is>
-      </c>
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t>안정성 시험</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>장기·가속(45℃)·가혹(동결융해·광)·개봉후. 경시변화로 사용기한·PAO 산정.</t>
-        </is>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>시간·온도가 지나도 안 변하는지 미리 괴롭혀 보는 시험. 결과로 '언제까지 쓰세요'를 정함.</t>
-        </is>
-      </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>4조건 보관+원심 실습</t>
-        </is>
-      </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>사용기한 설정 근거</t>
+    <row r="32" ht="110" customHeight="1" s="43">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>1.개인정보보호법</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>수집 요건·동의 고지</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>수집 가능: 동의·법률 특별규정·계약 이행 등 7가지. 14세 미만은 법정대리인 동의. 동의 시 고지 5가지(목적·항목·보유기간·거부 권리·거부 시 불이익). 서면 동의의 중요 내용은 9포인트 이상·20% 이상 크게. (책 40~42쪽)</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>정보를 받을 땐 '왜·무엇을·얼마나 보관·거부해도 되는지'를 알려야 해요.</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>수요검증 설문 동의 문구</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>설문·체험단 모집 폼 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="95" customHeight="1" s="43">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>1.개인정보보호법</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>민감정보·유출·파기</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>민감정보(건강 등)·고유식별정보는 별도 동의. 유출 시 정보주체에게 지체 없이 통지, 1천 명 이상이면 72시간 내 신고·7일 이상 게재. 보유기간이 끝나면 지체 없이 복구 불가능하게 파기. (책 43쪽)</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>피부 상태·질환 정보는 '민감정보'라 따로 동의받아요. 새면 빨리 알리고 신고.</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>피부 고민 설문=민감정보 가능성</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>고객 DB는 최소 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="95" customHeight="1" s="43">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>1.개인정보보호법</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>보호 원칙·벌칙</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>3대 핵심=최소 수집·목적 외 이용 금지·안전성 확보. 정보주체 6대 권리. 벌칙 최고 10년 이하 징역/1억 원 이하 벌금. 피부진단 데이터를 연구에 쓰려면 별도 동의. (책 41·46~47쪽)</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>필요한 만큼만 받고, 말한 목적에만 쓰고, 안전하게 지키는 게 핵심.</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>고객 데이터 활용 범위 설계</t>
         </is>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" s="43">
       <c r="A35" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>맞춤형화장품 정의</t>
+          <t>원료 분류</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>제조·수입된 '내용물'에 다른 내용물/식약처 허용 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
+          <t>수성(정제수·에탄올·폴리올)/유성(오일·왁스·에스터·실리콘)/계면활성제/보습/고분자(점증)/활성/색소/보존제/착향.</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>이미 만들어진 내용물에 뭘 더 섞거나 덜어 담아 파는 것. 매장에서 '맞춤 조제'.</t>
+          <t>화장품 원료는 큰 가족으로 나뉨 — 물 쪽, 기름 쪽, 둘을 섞는 것, 보습, 걸쭉하게, 효능, 색, 방부, 향. 내 26종도 다 이 중 하나.</t>
         </is>
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>혼합·소분 개념</t>
+          <t>보유 26종이 각 분류에 해당</t>
         </is>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>맞판 매장 사업 모델</t>
+          <t>CoA·규격서 읽는 눈</t>
         </is>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" s="43">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>혼합·소분 금지 원료</t>
+          <t>계면활성제 4분류</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>사용제한 원료(보존제·자외선차단·색소)·기능성 주성분(심사/보고 제외)은 임의 혼합 불가.</t>
+          <t>음이온(세정)·양이온(살균·헤어)·양쪽성(저자극)·비이온(유화·가용화). 자극: 양이온&gt;음이온&gt;양쪽성&gt;비이온.</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>맞춤형이라고 아무거나 못 섞음. 보존제·자외선차단제·기능성 주성분은 매장서 임의 추가 금지.</t>
+          <t>물·기름 사이를 중개하는 게 계면활성제. 4종류이고 자극 세기가 다름(양이온 최강, 비이온 최순).</t>
         </is>
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>방부·자차 임의 추가 불가</t>
+          <t>몬타노브68=비이온 유화제</t>
         </is>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>조제 상담의 법적 한계</t>
+          <t>세안 라인 베이스 선택 기준</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1" s="43">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>조제관리사 의무</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>혼합·소분 안전·품질·위생관리, 오염 방지, 기구·작업자 위생.</t>
+          <t>친수-친유 균형값. 3~6=W/O 유화, 8~18=O/W 유화·가용화(가용화 15~18).</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>맞춤형 매장서 섞고 나누는 일을 안전·위생적으로 책임지는 사람. 소독·오염방지가 핵심.</t>
+          <t>유화제가 물/기름 중 뭘 더 좋아하냐를 숫자로. 내 크림(O/W)에 맞는 유화제 고르는 기준.</t>
         </is>
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>70% 에탄올 소독·전용도구</t>
+          <t>크림=O/W → 유화제 HLB 맞춤</t>
         </is>
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>자격의 직접 수익화(매장)</t>
+          <t>처방 안정성의 이론 근거</t>
         </is>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" s="43">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>피부 구조</t>
+          <t>유화·가용화·분산</t>
         </is>
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>표피(기저·유극·과립·투명·각질)·진피(콜라겐·엘라스틴·섬유아세포)·피하. 멜라노사이트=기저층.</t>
+          <t>유화=두 상을 계면활성제로 분산(O/W·W/O). 가용화=소량 오일 투명 분산. 분산=고체 입자를 액에.</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>피부는 3층. 멜라닌 공장(멜라노사이트)은 표피 맨 아래 기저층에.</t>
+          <t>셋 다 '안 섞이는 걸 섞는' 기술. 뽀얗게=유화, 소량 기름 투명=가용화, 가루 퍼뜨림=분산.</t>
         </is>
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>진정·보습 타깃 이해</t>
+          <t>크림=유화, 워시오프=가용화</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>맞춤 상담·소구 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="48" customHeight="1" s="43">
+          <t>제형 기획·제품유형 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="43">
       <c r="A39" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>각질층·장벽·NMF</t>
+          <t>점증제·유변학</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>벽돌(각질)+시멘트(세포간지질·세라마이드). NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
+          <t>고분자(잔탄검·카보머·셀룰로스)로 점도·요변성. 분말 검은 글리세린 선분산 후 투입.</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>피부 맨 바깥=벽돌·시멘트 담벼락. 튼튼해야 수분이 안 샘 — 다도기가 노리는 장벽·진정.</t>
+          <t>묽은 액을 걸쭉하게. 잔탄검은 꼭 글리세린에 먼저 개서 넣어야 피시아이가 안 생김.</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>HA·글리세린·세이프 유분 보습</t>
+          <t>잔탄검 0.1%p 단위 점도 튜닝</t>
         </is>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>'장벽·진정' 브랜드 서사</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1" s="43">
+          <t>사용감 차별화 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" s="43">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>모발 구조</t>
+          <t>보존제 사용한도</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질. 주성분 케라틴, 디설파이드(S-S) 결합.</t>
+          <t>페녹시에탄올 1.0%·벤질알코올 1.0%·소르빅애씨드 0.6%·파라벤 단일 0.4%/혼합 0.8%. ★1,2-헥산다이올=지정 보존제 아님.</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>머리카락은 3겹, 케라틴이 주재료. 파마·염색이 이 구조를 건드림.</t>
+          <t>물 든 화장품은 방부 필수. 단 보존제마다 '여기까지만' 한도가 있음(페녹시 1.0%).</t>
         </is>
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>헤어 라인 확장 시 기초</t>
+          <t>페녹시+헥산다이올 방부</t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>라인 확장 판단</t>
+          <t>★챌린지테스트·방부 설계(→사용제한원료)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1" s="43">
       <c r="A41" s="33" t="inlineStr">
         <is>
-          <t>4.맞춤형</t>
+          <t>2.제조품질</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>관능평가</t>
+          <t>산화방지제 ≠ 보존제</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점으로 주관 최소화.</t>
+          <t>토코페롤·BHT='산화방지제'(오일 산패 방지). 미생물 억제 '보존제'와 목적·분류 다름.</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>기계 말고 사람의 눈·코·손으로 평가하되 기준 샘플과 비교해 주관을 줄임.</t>
+          <t>토코페롤은 기름 쩐내를 막지 세균을 막는 게 아님. 보존제랑 헷갈리게 내는 단골 함정.</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>바이알 변색·냄새·pH 눈 비교</t>
+          <t>토코페롤로 오일 산패 방지</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>품질 합부·배치 재현 기준</t>
+          <t>전성분 역할 표기 정확성</t>
         </is>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" s="43">
       <c r="A42" s="33" t="inlineStr">
         <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>기능성 주성분·함량</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>미백: 나이아신아마이드 2~5%·알부틴 2~5%·아스코빌글루코사이드 2%. 주름: 아데노신 0.04%·레티놀 2,500IU.</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>미백·주름은 '정해진 성분을 정해진 양'으로. 많다고 좋은 게 아니라 고시 범위 준수가 핵심.</t>
+        </is>
+      </c>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>나이아신아마이드 2~4% 사용</t>
+        </is>
+      </c>
+      <c r="F42" s="34" t="inlineStr">
+        <is>
+          <t>미백 '보고' 시 주성분 스펙</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1" s="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>CGMP</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>우수화장품 제조·품질관리기준. 3대 요소=①인위적 과오 최소화 ②미생물 오염·교차오염으로 인한 품질 저하 방지 ③고도의 품질관리체계 확립(책 122쪽). 문서화: 제조기록서·제조번호·일탈·재작업.</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>화장품을 깨끗하고 늘 똑같이 만드는 공장 관리 규칙. 내 개발일지가 그 작은 버전.</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>개발일지=배치기록서 축소판</t>
+        </is>
+      </c>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>ODM이 CGMP 업소인지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="66" customHeight="1" s="43">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>원료 역할 용어</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>극성·비극성·용제·수렴제·습윤제·밀폐제(수분 증발 차단)·연화제(에몰리언트)·장벽대체제·유화안정제·착향제·유효성분 등. (책 52~53쪽)</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>원료의 '역할 이름'이 시험 단골이에요. 같은 원료도 역할로 불립니다.</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>원료 시트 '역할' 12종과 대응</t>
+        </is>
+      </c>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>전성분 역할 설명 카피</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="66" customHeight="1" s="43">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>수성 원료</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>정제수(기제)·에탄올(수렴·청량·가용화)·폴리올 보습제: 글리세린·부틸렌글라이콜·프로필렌글라이콜. (책 53쪽)</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>물 쪽 원료. 글리세린류는 물을 붙잡아 두는 보습제예요.</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>글리세린 4%·프로판디올 3%</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="124" customHeight="1" s="43">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>유성 원료 7분류</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>유지(식물·동물 오일)·탄화수소(미네랄오일·바세린·스쿠알렌)·실리콘(디메티콘·사이클로메티콘)·왁스(카나우바·칸데릴라·비즈왁스·라놀린·호호바)·고급지방산(스테아릭애씨드)·고급알코올(세틸·스테아릴)·에스터(IPM·카프릴릭/카프릭트리글리세라이드). ★호호바=왁스. (책 54~56쪽)</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>기름도 7가족. 호호바는 '오일'이라 불려도 분류는 왁스(액상 왁스)라 단골 함정이에요.</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>스쿠알란=탄화수소·MCT=에스터·디메치콘=실리콘·세틸알코올=고급알코올</t>
+        </is>
+      </c>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>말라세지아-세이프 오일 선택의 분류 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="95" customHeight="1" s="43">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>계면활성제 세정력·미셀</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>세정력: 음이온&gt;양쪽성&gt;양이온&gt;비이온 (자극: 양이온&gt;음이온&gt;양쪽성&gt;비이온). 친수기+친유기 구조로 표면장력을 낮추고, CMC(임계미셀농도) 이상에서 미셀 형성. (책 57~58쪽)</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>세정 세기와 자극 세기의 순서가 달라요. 둘 다 외워야 합니다.</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>폴리글리세릴-4 카프레이트=비이온</t>
+        </is>
+      </c>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>세안 라인 저자극 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1" s="43">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>HLB 용도표</t>
+        </is>
+      </c>
+      <c r="C48" s="34" t="inlineStr">
+        <is>
+          <t>1~3 소포제 · 3~6 W/O 유화제 · 7~9 습윤제 · 8~18 O/W 유화제 · 13~15 세정제 · 15~18 가용화제. 값이 클수록 친수성. (책 57쪽)</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>숫자가 클수록 물을 좋아해요. 크림(O/W)은 8~18, 투명하게 녹이는 가용화는 15~18.</t>
+        </is>
+      </c>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>몬타노브68=O/W 유화</t>
+        </is>
+      </c>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="95" customHeight="1" s="43">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>유화 분리 현상·판별</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>크리밍(밀도 차로 뜸)·응집(입자끼리 뭉침)·합일(입자가 합쳐져 커짐→분리)·오스트발트 숙성(작은 입자가 큰 입자로 흡수). W/O·O/W 판별: 희석법·색소법·전기전도도법. (책 74~75쪽)</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>크림이 갈라지는 과정에도 이름이 있어요. 뜨기→뭉치기→합쳐지기 순으로 진행.</t>
+        </is>
+      </c>
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>원심분리 분리mm·45℃ 관찰과 직결</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>ODM 샘플 안정성 소통 용어</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="80" customHeight="1" s="43">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>고분자(점증·피막)</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>점증제: 천연(잔탄검·구아검·카라기난)·반합성(셀룰로스 유도체)·합성(카보머). 피막형성제(PVP·니트로셀룰로스 등, 마스카라·네일). (책 59쪽)</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>걸쭉하게 하는 것과 얇은 막을 만드는 것. 잔탄검은 천연 점증제예요.</t>
+        </is>
+      </c>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>잔탄검 0.2~0.6%</t>
+        </is>
+      </c>
+      <c r="F50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="110" customHeight="1" s="43">
+      <c r="A51" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>색소 분류</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>유기합성(염료=녹음·레이크=염료를 기질에 흡착·유기안료) / 무기안료(백색 TiO₂·ZnO, 착색 산화철, 체질 탈크·마이카) / 천연색소 / 진주광택안료. 적색 2호·102호=영유아·13세 이하 어린이 제품 금지. (책 59~60쪽)</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>물·기름에 녹는 '염료', 안 녹는 '안료'. 아이 제품에 못 쓰는 색소 번호가 단골.</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>다도기 무색</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>색조 확장 시 학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1" s="43">
+      <c r="A52" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>향료·부향률</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="inlineStr">
+        <is>
+          <t>퍼퓸 15~25% · 오드퍼퓸 10~15% · 오드뚜왈렛 5~10% · 오드콜로뉴 3~5% · 샤워콜로뉴 1~3%. 발향: 탑→미들→베이스. (책 61쪽)</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>향 농도로 향수 이름이 정해져요.</t>
+        </is>
+      </c>
+      <c r="E52" s="34" t="inlineStr">
+        <is>
+          <t>다도기 무향</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="95" customHeight="1" s="43">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>보존제 조건·미생물 오염</t>
+        </is>
+      </c>
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>보존제 조건: 넓은 항균 범위·낮은 농도에서 효과·무자극·pH·온도 안정 등. 1차 오염(제조 중)·2차 오염(소비자 사용 중). 미생물=세균·효모·곰팡이. (책 61~62쪽)</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>공장에서 묻는 게 1차, 쓰다가 손으로 들어가는 게 2차 오염이에요.</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>자(jar) 용기=2차 오염 위험↑</t>
+        </is>
+      </c>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>에어리스·펌프 선택 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="66" customHeight="1" s="43">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>금속이온봉쇄제·pH 조절</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>디소듐EDTA·소듐시트레이트(금속이온을 묶어 산화·변색 방지). pH 조절: 시트릭애씨드·트리에탄올아민 등. (책 63쪽)</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>물속 금속이 변색·산패를 부추겨서 묶어 두는 성분이에요.</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>구연산=pH 조절</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="138" customHeight="1" s="43">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>자외선 차단 표시</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>징크옥사이드·티타늄디옥사이드 각 25%. SPF는 측정값 ±20% 범위로 표시, 50 이상은 'SPF50+'. PA+~PA++++. UVB 290~320nm·UVA 320~400nm. 자차 성분을 0.5% 미만 변색 방지용으로 쓰면 자외선차단 제품 아님. (책 63~67·91·188쪽)</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="inlineStr">
+        <is>
+          <t>SPF는 UVB(화상), PA는 UVA(흑화)를 막는 정도예요.</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>선크림=기능성 인증 전제</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="110" customHeight="1" s="43">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>미백 고시 성분 전체</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
+        <is>
+          <t>닥나무추출물 2%·알부틴 2~5%·에칠아스코빌에텔 1~2%·유용성감초추출물 0.05%·아스코빌글루코사이드 2%·마그네슘아스코빌포스페이트 3%·나이아신아마이드 2~5%·알파-비사보롤 0.5%·아스코빌테트라이소팔미테이트 2%. (책 63~67쪽)</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>미백 9종과 함량. 나이아신아마이드가 가장 흔해요.</t>
+        </is>
+      </c>
+      <c r="E56" s="34" t="inlineStr">
+        <is>
+          <t>★토너 2%·앰플 4%=고시 범위 안</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="inlineStr">
+        <is>
+          <t>미백 기능성 '보고' 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="138" customHeight="1" s="43">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="inlineStr">
+        <is>
+          <t>주름·여드름·탈모·제모 고시</t>
+        </is>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>주름: 레티놀 2,500IU/g·레티닐팔미테이트 10,000IU/g·아데노신 0.04%·폴리에톡실레이티드레틴아마이드 0.05~0.2%. 여드름: 살리실릭애씨드 0.5%(인체세정용만). 탈모: 덱스판테놀·비오틴·엘-멘톨·징크피리치온. 제모: 치오글리콜산 80% 3~4.5%(pH 7~12.7). (책 63~67쪽)</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="inlineStr">
+        <is>
+          <t>기능성마다 정해진 성분이 있어요. 여드름 기능성은 '씻어내는 제품'만 가능.</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>판테놀을 써도 탈모 효능 표방은 불가</t>
+        </is>
+      </c>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>지성 세안 라인=살리실릭 0.5% 옵션</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="66" customHeight="1" s="43">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>비타민 분류</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>지용성 A(레티놀)·D·E(토코페롤)·F·K / 수용성 B군(B3 나이아신아마이드·B5 판테놀 등)·C(아스코빅애씨드)·P. (책 71쪽)</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>기름에 녹는 비타민은 ADEFK, 물에 녹는 건 B·C.</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>판테놀=B5·나이아신아마이드=B3·토코페롤=E</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>원료 서사 카피</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="138" customHeight="1" s="43">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>전성분·바코드 세부</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>글자 5포인트 이상, 혼합원료는 개별 성분으로, pH 조절 산·알칼리는 중화 생성물로 표기 가능, 영업비밀은 '기타 성분'. 50mL(g) 이하는 전성분 일부 생략 가능(타르색소·기능성 주성분·보존제 등은 표기). 바코드: 15mL(g) 이하·견본품 생략, 의무자=책임판매업자. (책 72~73쪽)</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>작은 용량은 라벨에 다 못 쓰니 생략 규칙이 있어요. 그래도 꼭 써야 하는 성분은 있음.</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>★히어로 50mL=생략 가능 구간(labeling.py 'reduced')</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>신뢰 위해 전성분 전체 표기 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="95" customHeight="1" s="43">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="inlineStr">
+        <is>
+          <t>제조 공정 흐름</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
+          <t>기초(로션·크림): 칭량→수상·유상 각각 가열 용해→유화(호모믹서)→냉각(열에 약한 성분 투입)→탈기·여과→저장(숙성)→충진·포장. 1차 공정(벌크 제조)·2차 공정(충진·포장). (책 76쪽)</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>벌크를 만드는 게 1차, 용기에 담는 게 2차 공정이에요.</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>A·B·C상 순서 그대로</t>
+        </is>
+      </c>
+      <c r="F60" s="34" t="inlineStr">
+        <is>
+          <t>공정 표준화</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="66" customHeight="1" s="43">
+      <c r="A61" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="inlineStr">
+        <is>
+          <t>퍼머넌트 웨이브 1제·2제</t>
+        </is>
+      </c>
+      <c r="C61" s="34" t="inlineStr">
+        <is>
+          <t>1제 환원제: 치오글라이콜릭애씨드·시스테인(시스틴 결합을 끊음) / 2제 산화제: 브롬산나트륨·과산화수소(다시 결합). (책 80쪽)</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>1제로 머리카락의 결합을 끊고, 2제로 새 모양으로 다시 붙여요.</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="34" t="inlineStr">
+        <is>
+          <t>헤어 확장 시 기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="80" customHeight="1" s="43">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="inlineStr">
+        <is>
+          <t>맞춤형 내용물·유형</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="inlineStr">
+        <is>
+          <t>내용물=책임판매업자에게 받은 벌크·반제품. 원료+원료 혼합은 '제조'라 불가. 유형: 현장 혼합형·공장 제조 배송형·DIY 키트형·디바이스형. (책 81~82쪽)</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>매장에선 '완성된 내용물'에 섞는 것만 가능. 원료끼리 섞어 새로 만들면 제조예요.</t>
+        </is>
+      </c>
+      <c r="E62" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>온라인 '공장 제조 배송형' 모델 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1" s="43">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="inlineStr">
+        <is>
+          <t>CGMP 4대 기준서</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>제품표준서·제조관리기준서·품질관리기준서·제조위생관리기준서. 원료품질성적서는 제조업자·공급자·검사기관 등이 발행한 것 인정. (책 82~83쪽)</t>
+        </is>
+      </c>
+      <c r="D63" s="34" t="inlineStr">
+        <is>
+          <t>좋은 공장이 꼭 갖춘 '4대 문서'예요.</t>
+        </is>
+      </c>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>레시피 시트=제품표준서 축소판</t>
+        </is>
+      </c>
+      <c r="F63" s="34" t="inlineStr">
+        <is>
+          <t>ODM 실사 1번 확인 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="80" customHeight="1" s="43">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>사용금지·제한 체계</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>네거티브 방식: 별표1 '사용할 수 없는 원료' 외에는 사용 가능. 별표2 '사용상 제한 원료'(보존제·자외선차단·염모·기타)는 한도 내에서만. (책 86~94쪽)</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>금지 목록에 없으면 쓸 수 있되, 제한 목록에 있으면 한도를 지켜야 해요.</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>원료 시트 '법적한도' 열</t>
+        </is>
+      </c>
+      <c r="F64" s="34" t="inlineStr">
+        <is>
+          <t>해외 처방 1차 필터</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="95" customHeight="1" s="43">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>알레르기 표시 세부</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>착향제 알레르기 유발 25종: 씻어내는 0.01%·씻어내지 않는 0.001% 초과 시 성분명 표시. 10mL 초과 50mL 이하는 생략 가능하되 홈페이지 등에 공개. (책 95쪽)</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="inlineStr">
+        <is>
+          <t>향 속 알레르기 성분은 일정량 넘으면 이름을 써야 해요. 작은 용량은 홈페이지 공개로 대신.</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>다도기 무향=해당 없음</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>무향 소구</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1" s="43">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B66" s="34" t="inlineStr">
+        <is>
+          <t>천연·유기농 원료 기준</t>
+        </is>
+      </c>
+      <c r="C66" s="34" t="inlineStr">
+        <is>
+          <t>합성 원료 5% 이내(석유화학 부분 2% 초과 불가). 천연 95%·유기농 10%+천연 95%. 용기에 PVC·폴리스티렌폼 금지. (책 96~99쪽)</t>
+        </is>
+      </c>
+      <c r="D66" s="34" t="inlineStr">
+        <is>
+          <t>'천연'이라 하려면 합성 원료를 5% 안으로 써야 했어요.</t>
+        </is>
+      </c>
+      <c r="E66" s="34" t="inlineStr">
+        <is>
+          <t>페녹시에탄올·디메치콘 사용=천연 기준 밖</t>
+        </is>
+      </c>
+      <c r="F66" s="34" t="inlineStr">
+        <is>
+          <t>천연 표방 안 하는 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="80" customHeight="1" s="43">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B67" s="34" t="inlineStr">
+        <is>
+          <t>화장품 취급·보관</t>
+        </is>
+      </c>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>바닥·벽에 닿지 않게 보관, 선입선출, 검사 중·불합격품 구분 보관, 출고는 품질부서 책임자 승인. 파레트 표시=명칭·제조번호·보관조건·불출상태. (책 102~103쪽)</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>먼저 들어온 것부터 내보내고, 상태별로 나눠 둬요.</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>원료 냉장·냉동·방습 분리</t>
+        </is>
+      </c>
+      <c r="F67" s="34" t="inlineStr">
+        <is>
+          <t>재고 운영 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="110" customHeight="1" s="43">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B68" s="34" t="inlineStr">
+        <is>
+          <t>사용 시 주의사항</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="inlineStr">
+        <is>
+          <t>공통: 사용 중 이상 증상 시 전문의 상담 / 상처 부위 사용 자제 / 어린이 손에 닿지 않게·직사광선 피해 보관. 유형별(염모제 패치테스트 48시간 등)·성분별(AHA·알부틴 2% 이상·살리실릭애씨드 등) 문구 별도. (책 103~108쪽)</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>모든 화장품에 들어가는 공통 문구 + 성분마다 붙는 추가 문구가 있어요.</t>
+        </is>
+      </c>
+      <c r="E68" s="34" t="inlineStr">
+        <is>
+          <t>라벨 주의사항 초안</t>
+        </is>
+      </c>
+      <c r="F68" s="34" t="inlineStr">
+        <is>
+          <t>라벨 시안 검수</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="80" customHeight="1" s="43">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>2.제조품질</t>
+        </is>
+      </c>
+      <c r="B69" s="34" t="inlineStr">
+        <is>
+          <t>위해성 평가 용어</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>위해지수·안전역(MoS, 클수록 안전)·인체노출안전기준. 위해성 평가 기본계획 5년마다. 소비자 위해성 평가 요청 시 1년 이내 완료. (책 111~114쪽)</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>'얼마나 위험하냐×얼마나 노출되냐'를 숫자로 따지는 말들이에요.</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="80" customHeight="1" s="43">
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B70" s="34" t="inlineStr">
+        <is>
+          <t>중금속·유해물질 한도</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="inlineStr">
+        <is>
+          <t>(µg/g 이하) 납 20(점토 50)·비소 10·수은 1·안티몬 10·카드뮴 5·니켈 10(눈 35·색조 30)·디옥산 100·포름알데하이드 2,000(물휴지 20)·프탈레이트 100. 메탄올 0.2%(물휴지 0.002%).</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>일부러 안 넣어도 원료에 미량 섞여올 수 있는 나쁜 물질의 '넘으면 안 되는 선'. 출고 전 시험으로 확인.</t>
+        </is>
+      </c>
+      <c r="E70" s="34" t="inlineStr">
+        <is>
+          <t>비의도 유래물질 개념(→유통안전)</t>
+        </is>
+      </c>
+      <c r="F70" s="34" t="inlineStr">
+        <is>
+          <t>출고 로트별 시험성적서 요구</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1" s="43">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B71" s="34" t="inlineStr">
+        <is>
+          <t>미생물 한도</t>
+        </is>
+      </c>
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>영유아·눈화장 500·물휴지 세균·진균 각 100·기타 1,000 CFU/g 이하. 대장균·녹농균·황색포도상구균 불검출.</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>완제품에 있어도 되는 세균 수 한계. 아기·눈 제품은 더 엄격(500), 3대 병원균은 아예 불검출.</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>소독·방부·1개월 내 사용</t>
+        </is>
+      </c>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>미생물 시험성적서 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1" s="43">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B72" s="34" t="inlineStr">
+        <is>
+          <t>pH 기준</t>
+        </is>
+      </c>
+      <c r="C72" s="34" t="inlineStr">
+        <is>
+          <t>영유아·눈화장·색조·로션/크림 등 특정 액상류 pH 3.0~9.0(물로 씻어내는 제품 제외). 화장비누 유리알칼리 0.1%.</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>피부에 바르는 많은 제품은 pH 3.0~9.0. 다도기는 약산성(5.0~5.5)으로 더 좁게.</t>
+        </is>
+      </c>
+      <c r="E72" s="34" t="inlineStr">
+        <is>
+          <t>목표 pH 5.0~5.5 적정</t>
+        </is>
+      </c>
+      <c r="F72" s="34" t="inlineStr">
+        <is>
+          <t>자극 저감·라벨 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1" s="43">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B73" s="34" t="inlineStr">
+        <is>
+          <t>내용량 기준</t>
+        </is>
+      </c>
+      <c r="C73" s="34" t="inlineStr">
+        <is>
+          <t>제품 3개 평균 내용량이 표기량의 97% 이상(미달 시 6개 추가, 9개 평균 97%).</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="inlineStr">
+        <is>
+          <t>'50mL'이라 적었으면 실제도 평균 97% 이상 들어야 함. 덜 넣으면 안 됨.</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>충진량 관리</t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>과충진 원가·미달 CS 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1" s="43">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B74" s="34" t="inlineStr">
+        <is>
+          <t>착향 알레르기 성분</t>
+        </is>
+      </c>
+      <c r="C74" s="34" t="inlineStr">
+        <is>
+          <t>지정 유발성분 25종. 씻어내는 0.01%·씻어내지 않는 0.001% 초과 시 성분명 표시.</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>향료 속 알레르기 25종은 일정량 넘으면 이름을 따로 표시. 다도기는 무향이라 걱정 없음.</t>
+        </is>
+      </c>
+      <c r="E74" s="34" t="inlineStr">
+        <is>
+          <t>다도기=무향 → 알레르겐 0</t>
+        </is>
+      </c>
+      <c r="F74" s="34" t="inlineStr">
+        <is>
+          <t>★무향이 규제·소구 동시 이점</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1" s="43">
+      <c r="A75" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B75" s="34" t="inlineStr">
+        <is>
+          <t>안정성 시험</t>
+        </is>
+      </c>
+      <c r="C75" s="34" t="inlineStr">
+        <is>
+          <t>장기·가속(45℃)·가혹(동결융해·광)·개봉후. 경시변화로 사용기한·PAO 산정.</t>
+        </is>
+      </c>
+      <c r="D75" s="34" t="inlineStr">
+        <is>
+          <t>시간·온도가 지나도 안 변하는지 미리 괴롭혀 보는 시험. 결과로 '언제까지 쓰세요'를 정함.</t>
+        </is>
+      </c>
+      <c r="E75" s="34" t="inlineStr">
+        <is>
+          <t>4조건 보관+원심 실습</t>
+        </is>
+      </c>
+      <c r="F75" s="34" t="inlineStr">
+        <is>
+          <t>사용기한 설정 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="95" customHeight="1" s="43">
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B76" s="34" t="inlineStr">
+        <is>
+          <t>CGMP 3대 요소·작업소 구분</t>
+        </is>
+      </c>
+      <c r="C76" s="34" t="inlineStr">
+        <is>
+          <t>①인위적 과오 최소화 ②미생물 오염·교차오염으로 인한 품질 저하 방지 ③고도의 품질관리체계 확립. 작업소: 분리(벽 등으로 별개)·구획(동일 건물 내 칸막이)·구분(선·줄 등으로 나눔). (책 122쪽)</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>CGMP의 목표는 '사람 실수 줄이기·오염 막기·품질 보증' 세 가지예요.</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="inlineStr">
+        <is>
+          <t>집 작업대도 원료·완제품 구역 나누기</t>
+        </is>
+      </c>
+      <c r="F76" s="34" t="inlineStr">
+        <is>
+          <t>ODM 실사 관점</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="138" customHeight="1" s="43">
+      <c r="A77" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B77" s="34" t="inlineStr">
+        <is>
+          <t>청정도 등급</t>
+        </is>
+      </c>
+      <c r="C77" s="34" t="inlineStr">
+        <is>
+          <t>1등급(클린벤치) 낙하균 10개/hr·부유균 20개/㎥·환기 20회/hr / 2등급(제조실·충전실·내용물 보관소·원료 칭량실·미생물 실험실) 낙하균 30개/hr·부유균 200개/㎥·환기 10회/hr / 3등급(포장실) / 4등급(원료·포장재 보관소 등). HEPA=0.3㎛ 99.97%. (책 123~124쪽)</t>
+        </is>
+      </c>
+      <c r="D77" s="34" t="inlineStr">
+        <is>
+          <t>공장은 방마다 공기 속 균 수 기준이 달라요. 충전실이 2등급.</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="inlineStr">
+        <is>
+          <t>냉각상 투입·충전은 뚜껑 덮고 빨리</t>
+        </is>
+      </c>
+      <c r="F77" s="34" t="inlineStr">
+        <is>
+          <t>ODM 충전실 등급 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="95" customHeight="1" s="43">
+      <c r="A78" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B78" s="34" t="inlineStr">
+        <is>
+          <t>낙하균 측정(Koch법)</t>
+        </is>
+      </c>
+      <c r="C78" s="34" t="inlineStr">
+        <is>
+          <t>배지: 세균=대두카제인소화한천, 진균=사부로포도당한천. 5개소 이상, 벽에서 30cm·바닥 20~30cm 높이, 30분 이상 노출. 배양: 세균 30~35℃ 48시간, 진균 20~25℃ 5일. (책 125쪽)</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>뚜껑 연 배지를 놓아두고 떨어지는 균을 세는 방법이에요.</t>
+        </is>
+      </c>
+      <c r="E78" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="52" customHeight="1" s="43">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>공기 조절 4대 요소</t>
+        </is>
+      </c>
+      <c r="C79" s="34" t="inlineStr">
+        <is>
+          <t>청정도-공기정화기, 실내 온도-열교환기, 습도-가습기, 기류-송풍기. (책 126쪽)</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="inlineStr">
+        <is>
+          <t>공장 공기를 관리하는 4가지와 담당 설비.</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="124" customHeight="1" s="43">
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B80" s="34" t="inlineStr">
+        <is>
+          <t>소독제·중화제</t>
+        </is>
+      </c>
+      <c r="C80" s="34" t="inlineStr">
+        <is>
+          <t>70% 에탄올(가장 흔함)·크레졸수 3%·페놀수 3%·차아염소산나트륨·벤잘코늄클로라이드·글루콘산클로르헥시딘. 이상적 소독제=5분 이내 99.9% 사멸 등. 작업장 소독 월 1회 이상. 항균 활성 중화제: 레시틴·폴리솔베이트80 등. (책 129~131쪽)</t>
+        </is>
+      </c>
+      <c r="D80" s="34" t="inlineStr">
+        <is>
+          <t>소독제는 짧은 시간에 거의 다 죽여야 좋은 것. 미생물 시험 땐 소독제를 중화해야 균이 제대로 잡혀요.</t>
+        </is>
+      </c>
+      <c r="E80" s="34" t="inlineStr">
+        <is>
+          <t>70% 에탄올 스프레이</t>
+        </is>
+      </c>
+      <c r="F80" s="34" t="inlineStr">
+        <is>
+          <t>매장 위생 SOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="110" customHeight="1" s="43">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B81" s="34" t="inlineStr">
+        <is>
+          <t>설비 세척제 pH 분류</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
+        <is>
+          <t>무기산·약산성(pH 0.2~5.5)·중성(5.5~8.5)·약알칼리(8.5~12.5)·부식성 알칼리(12.5~14). 세척 원칙: 물이 최적·세제는 최소·증기 세척 권장·브러시 사용. 유화기 세척 제1선택지=물+브러시. (책 140~142쪽)</t>
+        </is>
+      </c>
+      <c r="D81" s="34" t="inlineStr">
+        <is>
+          <t>세척은 물이 기본이고 세제는 꼭 필요할 때만. 세제가 남으면 그게 또 오염이에요.</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>호모 헤드는 물+브러시로</t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="110" customHeight="1" s="43">
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B82" s="34" t="inlineStr">
+        <is>
+          <t>작업자 위생</t>
+        </is>
+      </c>
+      <c r="C82" s="34" t="inlineStr">
+        <is>
+          <t>손 소독 15초 이상(일회용 장갑 착용 시 예외), 소독제: 알코올 70~80%·클로르헥시딘 0.5~4%·아이오도퍼. 작업복 착용, 음식물 반입 금지, 질병·외상자 작업 제외, 방문객은 교육·동행·기록. (책 134~136쪽)</t>
+        </is>
+      </c>
+      <c r="D82" s="34" t="inlineStr">
+        <is>
+          <t>사람이 가장 큰 오염원이에요. 손·옷·머리카락 관리가 핵심.</t>
+        </is>
+      </c>
+      <c r="E82" s="34" t="inlineStr">
+        <is>
+          <t>머리망·장갑·실험복</t>
+        </is>
+      </c>
+      <c r="F82" s="34" t="inlineStr">
+        <is>
+          <t>매장 복장 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="124" customHeight="1" s="43">
+      <c r="A83" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B83" s="34" t="inlineStr">
+        <is>
+          <t>설비 재질·저울 관리</t>
+        </is>
+      </c>
+      <c r="C83" s="34" t="inlineStr">
+        <is>
+          <t>탱크·접촉부=316 스테인리스(304도 사용). 저울: 영점·수평 매일 확인, 정기점검 1개월, 직선성·정밀성 ±0.5%, 편심오차 ±0.1%. 위생 판정: 육안·닦아내기(흰 천)·린스 정량(HPLC·TLC·TOC·UV)·표면 균(면봉·콘택트 플레이트). (책 139~143쪽)</t>
+        </is>
+      </c>
+      <c r="D83" s="34" t="inlineStr">
+        <is>
+          <t>저울은 매일 영점, 한 달에 한 번 정기점검. 닦은 뒤 흰 천에 묻어나는지 보는 것도 판정법.</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>정밀저울 0.01g 매일 영점</t>
+        </is>
+      </c>
+      <c r="F83" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="52" customHeight="1" s="43">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B84" s="34" t="inlineStr">
+        <is>
+          <t>물의 품질</t>
+        </is>
+      </c>
+      <c r="C84" s="34" t="inlineStr">
+        <is>
+          <t>제품용=정제수, 설비 세척=정제수 또는 상수, 손 세척=상수. (책 140쪽)</t>
+        </is>
+      </c>
+      <c r="D84" s="34" t="inlineStr">
+        <is>
+          <t>제품에 들어가는 물은 반드시 정제수.</t>
+        </is>
+      </c>
+      <c r="E84" s="34" t="inlineStr">
+        <is>
+          <t>정제수만 사용</t>
+        </is>
+      </c>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="80" customHeight="1" s="43">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B85" s="34" t="inlineStr">
+        <is>
+          <t>입고 판정 라벨 색</t>
+        </is>
+      </c>
+      <c r="C85" s="34" t="inlineStr">
+        <is>
+          <t>판정 대기(백색)→시험 중(황색)→적합(청색, 입고) / 부적합(적색, 반품). 입고 필수 기재=공급자 제품명·공급자명·수령일자·제조번호. (책 147쪽)</t>
+        </is>
+      </c>
+      <c r="D85" s="34" t="inlineStr">
+        <is>
+          <t>원료 통에 붙는 라벨 색으로 상태를 알아요. 흰→노→파(통과)/빨(불합격).</t>
+        </is>
+      </c>
+      <c r="E85" s="34" t="inlineStr">
+        <is>
+          <t>원료 통에 수령일·로트 스티커</t>
+        </is>
+      </c>
+      <c r="F85" s="34" t="inlineStr">
+        <is>
+          <t>ODM 창고 라벨 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="110" customHeight="1" s="43">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B86" s="34" t="inlineStr">
+        <is>
+          <t>원료·반제품 보관</t>
+        </is>
+      </c>
+      <c r="C86" s="34" t="inlineStr">
+        <is>
+          <t>보관 온도 구분(냉동·냉장·상온 15~25℃ 등), 샘플링 조도 540럭스 이상. 반제품=명칭·제조번호·완료 공정·보관 조건 표시, 최대 보관기한 설정. 출고=선입선출·품질부서 승인·바닥과 벽에서 띄워 보관. (책 156~157쪽)</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="inlineStr">
+        <is>
+          <t>원료는 성질대로 온도를 나눠 보관하고, 먼저 온 것부터 써요.</t>
+        </is>
+      </c>
+      <c r="E86" s="34" t="inlineStr">
+        <is>
+          <t>녹차·베타글루칸 냉장, 마데카소사이드 냉동</t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="110" customHeight="1" s="43">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>기준일탈·재작업·폐기</t>
+        </is>
+      </c>
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>기준일탈=적합 판정 기준을 벗어남. 재작업=기준을 벗어난 완제품·벌크·반제품을 재처리해 적합하게 만드는 것(품질책임자 승인·원인 조사). 폐기도 품질책임자 승인, 폐기확인서=의뢰자·현황·사유. (책 157~158쪽)</t>
+        </is>
+      </c>
+      <c r="D87" s="34" t="inlineStr">
+        <is>
+          <t>불합격품을 다시 살릴 땐 승인과 기록이 필요하고, 버릴 때도 이유를 남겨요.</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
+          <t>분리 배치 재유화=재작업</t>
+        </is>
+      </c>
+      <c r="F87" s="34" t="inlineStr">
+        <is>
+          <t>재작업품 납품 여부 계약 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="80" customHeight="1" s="43">
+      <c r="A88" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
+        <is>
+          <t>보관용 검체</t>
+        </is>
+      </c>
+      <c r="C88" s="34" t="inlineStr">
+        <is>
+          <t>완제품을 그대로, 시험 2번 할 양을 보관. 보관기간=사용기한 경과 후 1년 / 개봉 후 사용기간 기재 시 제조일로부터 3년. (책 159쪽)</t>
+        </is>
+      </c>
+      <c r="D88" s="34" t="inlineStr">
+        <is>
+          <t>로트마다 샘플을 남겨 두면 나중에 클레임이 와도 비교할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E88" s="34" t="inlineStr">
+        <is>
+          <t>배치마다 바이알 1개 보관</t>
+        </is>
+      </c>
+      <c r="F88" s="34" t="inlineStr">
+        <is>
+          <t>CS 분쟁 증거</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="80" customHeight="1" s="43">
+      <c r="A89" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B89" s="34" t="inlineStr">
+        <is>
+          <t>퍼머넌트 웨이브 기준</t>
+        </is>
+      </c>
+      <c r="C89" s="34" t="inlineStr">
+        <is>
+          <t>제1제: 중금속 20·비소 5·철 2μg/g 이하. 제2제: 브롬산나트륨 pH 4.0~10.5, 과산화수소수 pH 2.5~4.5. (책 149~151쪽)</t>
+        </is>
+      </c>
+      <c r="D89" s="34" t="inlineStr">
+        <is>
+          <t>파마약은 따로 정한 기준이 있어요.</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="66" customHeight="1" s="43">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B90" s="34" t="inlineStr">
+        <is>
+          <t>인체 세포·조직 배양액</t>
+        </is>
+      </c>
+      <c r="C90" s="34" t="inlineStr">
+        <is>
+          <t>공여자 적격성검사, 배양시설 청정 1B(Class 10,000), 기록 3년 보관. (책 154~156쪽)</t>
+        </is>
+      </c>
+      <c r="D90" s="34" t="inlineStr">
+        <is>
+          <t>'줄기세포 배양액' 원료는 별도 안전 기준이 있어요.</t>
+        </is>
+      </c>
+      <c r="E90" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="34" t="inlineStr">
+        <is>
+          <t>'줄기세포' 광고 표현 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="124" customHeight="1" s="43">
+      <c r="A91" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B91" s="34" t="inlineStr">
+        <is>
+          <t>포장재 1·2차·안전용기</t>
+        </is>
+      </c>
+      <c r="C91" s="34" t="inlineStr">
+        <is>
+          <t>1차 포장=내용물과 직접 닿는 용기, 2차 포장=1차를 넣는 상자 등. 안전용기 대상: 아세톤 네일 리무버·탄화수소 10% 이상이고 운동점도 21cSt 이하인 오일·메틸살리실레이트 5% 이상 액체(5세 미만이 열기 어렵게, 일회용·분무용기 제외). (책 162~163쪽)</t>
+        </is>
+      </c>
+      <c r="D91" s="34" t="inlineStr">
+        <is>
+          <t>아이가 열어 삼키면 위험한 제품은 잠금 용기를 써야 해요.</t>
+        </is>
+      </c>
+      <c r="E91" s="34" t="inlineStr">
+        <is>
+          <t>★클렌징오일=스쿠알란(탄화수소) 함량·점도 확인</t>
+        </is>
+      </c>
+      <c r="F91" s="34" t="inlineStr">
+        <is>
+          <t>오일 제품 용기 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="95" customHeight="1" s="43">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B92" s="34" t="inlineStr">
+        <is>
+          <t>용기 4종·포장 시험</t>
+        </is>
+      </c>
+      <c r="C92" s="34" t="inlineStr">
+        <is>
+          <t>밀폐(고형 이물 차단)·기밀(액체·고형 이물·수분 차단)·밀봉(기체·미생물 차단)·차광(빛 차단). 시험: 내용물 감량·감압누설·내열/내한·낙하·펌프 누름강도 등. (책 164~165쪽)</t>
+        </is>
+      </c>
+      <c r="D92" s="34" t="inlineStr">
+        <is>
+          <t>막는 대상에 따라 용기 이름이 달라요. 밀봉이 가장 촘촘.</t>
+        </is>
+      </c>
+      <c r="E92" s="34" t="inlineStr">
+        <is>
+          <t>바이알 무게 감량 측정</t>
+        </is>
+      </c>
+      <c r="F92" s="34" t="inlineStr">
+        <is>
+          <t>용기 선정 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="80" customHeight="1" s="43">
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>3.유통안전</t>
+        </is>
+      </c>
+      <c r="B93" s="34" t="inlineStr">
+        <is>
+          <t>포장재 출고·사용기한</t>
+        </is>
+      </c>
+      <c r="C93" s="34" t="inlineStr">
+        <is>
+          <t>출고=선입선출(사용기한 짧은 것 먼저 내는 선한선출도 가능), 장기 보관품은 재평가. 개봉 후 사용기간 심벌(예: 12M). (책 165~166쪽)</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>포장재에도 사용기한이 있고 오래되면 다시 검사해요.</t>
+        </is>
+      </c>
+      <c r="E93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="34" t="inlineStr">
+        <is>
+          <t>용기 재고 회전</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1" s="43">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
           <t>4.맞춤형</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
+        <is>
+          <t>맞춤형화장품 정의</t>
+        </is>
+      </c>
+      <c r="C94" s="34" t="inlineStr">
+        <is>
+          <t>제조·수입된 '내용물'에 다른 내용물/식약처 허용 '원료'를 혼합, 또는 내용물을 소분한 것.</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>이미 만들어진 내용물에 뭘 더 섞거나 덜어 담아 파는 것. 매장에서 '맞춤 조제'.</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="inlineStr">
+        <is>
+          <t>혼합·소분 개념</t>
+        </is>
+      </c>
+      <c r="F94" s="34" t="inlineStr">
+        <is>
+          <t>맞판 매장 사업 모델</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1" s="43">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B95" s="34" t="inlineStr">
+        <is>
+          <t>혼합·소분 금지 원료</t>
+        </is>
+      </c>
+      <c r="C95" s="34" t="inlineStr">
+        <is>
+          <t>사용제한 원료(보존제·자외선차단·색소)·기능성 주성분(심사/보고 제외)은 임의 혼합 불가.</t>
+        </is>
+      </c>
+      <c r="D95" s="34" t="inlineStr">
+        <is>
+          <t>맞춤형이라고 아무거나 못 섞음. 보존제·자외선차단제·기능성 주성분은 매장서 임의 추가 금지.</t>
+        </is>
+      </c>
+      <c r="E95" s="34" t="inlineStr">
+        <is>
+          <t>방부·자차 임의 추가 불가</t>
+        </is>
+      </c>
+      <c r="F95" s="34" t="inlineStr">
+        <is>
+          <t>조제 상담의 법적 한계</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1" s="43">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>조제관리사 의무</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="inlineStr">
+        <is>
+          <t>혼합·소분 안전·품질·위생관리, 오염 방지, 기구·작업자 위생.</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>맞춤형 매장서 섞고 나누는 일을 안전·위생적으로 책임지는 사람. 소독·오염방지가 핵심.</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="inlineStr">
+        <is>
+          <t>70% 에탄올 소독·전용도구</t>
+        </is>
+      </c>
+      <c r="F96" s="34" t="inlineStr">
+        <is>
+          <t>자격의 직접 수익화(매장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1" s="43">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B97" s="34" t="inlineStr">
+        <is>
+          <t>피부 구조</t>
+        </is>
+      </c>
+      <c r="C97" s="34" t="inlineStr">
+        <is>
+          <t>표피(기저·유극·과립·투명·각질)·진피(콜라겐·엘라스틴·섬유아세포)·피하. 멜라노사이트=기저층.</t>
+        </is>
+      </c>
+      <c r="D97" s="34" t="inlineStr">
+        <is>
+          <t>피부는 3층. 멜라닌 공장(멜라노사이트)은 표피 맨 아래 기저층에.</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="inlineStr">
+        <is>
+          <t>진정·보습 타깃 이해</t>
+        </is>
+      </c>
+      <c r="F97" s="34" t="inlineStr">
+        <is>
+          <t>맞춤 상담·소구 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1" s="43">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B98" s="34" t="inlineStr">
+        <is>
+          <t>각질층·장벽·NMF</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="inlineStr">
+        <is>
+          <t>벽돌(각질)+시멘트(세포간지질·세라마이드). NMF(아미노산·PCA·젖산). 산성막 pH 4.5~6.5.</t>
+        </is>
+      </c>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>피부 맨 바깥=벽돌·시멘트 담벼락. 튼튼해야 수분이 안 샘 — 다도기가 노리는 장벽·진정.</t>
+        </is>
+      </c>
+      <c r="E98" s="34" t="inlineStr">
+        <is>
+          <t>HA·글리세린·세이프 유분 보습</t>
+        </is>
+      </c>
+      <c r="F98" s="34" t="inlineStr">
+        <is>
+          <t>'장벽·진정' 브랜드 서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1" s="43">
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B99" s="34" t="inlineStr">
+        <is>
+          <t>모발 구조</t>
+        </is>
+      </c>
+      <c r="C99" s="34" t="inlineStr">
+        <is>
+          <t>모표피(큐티클)·모피질(코르텍스, 멜라닌)·모수질. 주성분 케라틴, 디설파이드(S-S) 결합.</t>
+        </is>
+      </c>
+      <c r="D99" s="34" t="inlineStr">
+        <is>
+          <t>머리카락은 3겹, 케라틴이 주재료. 파마·염색이 이 구조를 건드림.</t>
+        </is>
+      </c>
+      <c r="E99" s="34" t="inlineStr">
+        <is>
+          <t>헤어 라인 확장 시 기초</t>
+        </is>
+      </c>
+      <c r="F99" s="34" t="inlineStr">
+        <is>
+          <t>라인 확장 판단</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1" s="43">
+      <c r="A100" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B100" s="34" t="inlineStr">
+        <is>
+          <t>관능평가</t>
+        </is>
+      </c>
+      <c r="C100" s="34" t="inlineStr">
+        <is>
+          <t>성상·색·향·사용감을 표준품/비교시료와 대조 평가. 패널·채점으로 주관 최소화.</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="inlineStr">
+        <is>
+          <t>기계 말고 사람의 눈·코·손으로 평가하되 기준 샘플과 비교해 주관을 줄임.</t>
+        </is>
+      </c>
+      <c r="E100" s="34" t="inlineStr">
+        <is>
+          <t>바이알 변색·냄새·pH 눈 비교</t>
+        </is>
+      </c>
+      <c r="F100" s="34" t="inlineStr">
+        <is>
+          <t>품질 합부·배치 재현 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1" s="43">
+      <c r="A101" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B101" s="34" t="inlineStr">
         <is>
           <t>위해평가 4단계</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C101" s="34" t="inlineStr">
         <is>
           <t>위험성 확인→위험성 결정→노출평가→위해도 결정. 안전역(MoS)으로 판단.</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D101" s="34" t="inlineStr">
         <is>
           <t>성분이 '얼마나 위험×얼마나 노출→그래서 안전?'을 순서대로 따지는 법. 활성 농도 상향 판단에 사용.</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
+      <c r="E101" s="34" t="inlineStr">
         <is>
           <t>활성 농도 상향 판단틀</t>
         </is>
       </c>
-      <c r="F42" s="34" t="inlineStr">
+      <c r="F101" s="34" t="inlineStr">
         <is>
           <t>신규·고농도 원료 도입 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="95" customHeight="1" s="43">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B102" s="34" t="inlineStr">
+        <is>
+          <t>자격시험·맞판 신고</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="inlineStr">
+        <is>
+          <t>맞판=신고(조제관리사 선임). 자격시험 매년 1회 이상, 90일 전 공고. 합격: 전 과목 60% 이상+과목별 40% 이상. 부정행위 시 3년 응시 제한. (책 172~175쪽)</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t>전체 60점, 과목마다 40점을 넘어야 합격. 과락 주의.</t>
+        </is>
+      </c>
+      <c r="E102" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="34" t="inlineStr">
+        <is>
+          <t>★합격 기준=과목별 학습 배분</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="110" customHeight="1" s="43">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B103" s="34" t="inlineStr">
+        <is>
+          <t>영유아 안전성 자료 보관</t>
+        </is>
+      </c>
+      <c r="C103" s="34" t="inlineStr">
+        <is>
+          <t>표시·광고 시 제품별 안전성 자료(제품·제조방법 설명, 안전성 평가 결과, 효능·효과 실증) 작성·보관. 보관기간: 사용기한 표시=만료일 이후 1년 / 개봉 후 사용기간 표시=제조연월일 이후 3년. (책 177·207쪽)</t>
+        </is>
+      </c>
+      <c r="D103" s="34" t="inlineStr">
+        <is>
+          <t>아이용이라고 쓰면 안전 증빙을 정해진 기간 동안 보관해야 해요.</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="34" t="inlineStr">
+        <is>
+          <t>키즈 라인 진입 비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="95" customHeight="1" s="43">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B104" s="34" t="inlineStr">
+        <is>
+          <t>유효성 자료</t>
+        </is>
+      </c>
+      <c r="C104" s="34" t="inlineStr">
+        <is>
+          <t>효력시험(국내외 대학·연구기관, 개발국 정부 제출, SCI 게재 자료)·인체적용시험·염모효력시험. 일반화장품 보습=TEWL(경피수분손실) 측정, 수렴=단백질 응고. (책 32·177~178·213쪽)</t>
+        </is>
+      </c>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
+          <t>효과를 말하려면 이런 자료가 근거가 돼요. 보습은 수분 손실량으로 측정.</t>
+        </is>
+      </c>
+      <c r="E104" s="34" t="inlineStr">
+        <is>
+          <t>체감 대신 TEWL로 보습 확인</t>
+        </is>
+      </c>
+      <c r="F104" s="34" t="inlineStr">
+        <is>
+          <t>보습 소구 실증</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="124" customHeight="1" s="43">
+      <c r="A105" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B105" s="34" t="inlineStr">
+        <is>
+          <t>안정성 시험 방법</t>
+        </is>
+      </c>
+      <c r="C105" s="34" t="inlineStr">
+        <is>
+          <t>3로트 이상. 장기보존·가속 6개월 이상(가속=장기보다 15℃ 이상 높게), 가혹=-15~45℃ 반복 등, 개봉 후 6개월 이상. 장기 측정: 1년차 3개월마다·2년차 6개월마다·이후 1년마다, 가속은 최소 3번. 물리적 변화=분리·합일·응집. (책 179~180쪽)</t>
+        </is>
+      </c>
+      <c r="D105" s="34" t="inlineStr">
+        <is>
+          <t>공식 사용기한은 6개월 이상 데이터가 필요해요. 집 8주 관찰은 '조기 판정'.</t>
+        </is>
+      </c>
+      <c r="E105" s="34" t="inlineStr">
+        <is>
+          <t>45℃·동결융해·1~8주 관찰</t>
+        </is>
+      </c>
+      <c r="F105" s="34" t="inlineStr">
+        <is>
+          <t>사용기한 산정은 ODM 데이터로</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="95" customHeight="1" s="43">
+      <c r="A106" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B106" s="34" t="inlineStr">
+        <is>
+          <t>피부 기본 수치</t>
+        </is>
+      </c>
+      <c r="C106" s="34" t="inlineStr">
+        <is>
+          <t>면적 1.5~2.0㎡, pH 4.5~6.5, 각화주기 28±3일. 각질층=케라틴 58%·NMF 31%·세포간지질 11%. NMF=아미노산 40%·PCA 12%·젖산염 12%·요소 7%. (책 182~183쪽)</t>
+        </is>
+      </c>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>각질층은 대부분 케라틴, 그다음 NMF(천연보습인자). NMF의 주인공은 아미노산.</t>
+        </is>
+      </c>
+      <c r="E106" s="34" t="inlineStr">
+        <is>
+          <t>아연PCA·베타인=NMF 계열 보습</t>
+        </is>
+      </c>
+      <c r="F106" s="34" t="inlineStr">
+        <is>
+          <t>'장벽' 서사 수치</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="95" customHeight="1" s="43">
+      <c r="A107" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B107" s="34" t="inlineStr">
+        <is>
+          <t>표피 4대 세포</t>
+        </is>
+      </c>
+      <c r="C107" s="34" t="inlineStr">
+        <is>
+          <t>각질형성세포·멜라닌형성세포(기저층, 기저세포:멜라닌세포=4:1~10:1, 티로시나아제)·랑게르한스세포(유극층, 면역)·머켈세포(기저층, 촉각). 피부색=멜라닌·헤모글로빈·카로티노이드. (책 183~184쪽)</t>
+        </is>
+      </c>
+      <c r="D107" s="34" t="inlineStr">
+        <is>
+          <t>표피에는 4가지 세포가 있어요. 면역 담당 랑게르한스는 유극층.</t>
+        </is>
+      </c>
+      <c r="E107" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="34" t="inlineStr">
+        <is>
+          <t>미백 원리 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="124" customHeight="1" s="43">
+      <c r="A108" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B108" s="34" t="inlineStr">
+        <is>
+          <t>진피·피지·땀샘</t>
+        </is>
+      </c>
+      <c r="C108" s="34" t="inlineStr">
+        <is>
+          <t>진피=유두층·망상층, 교원섬유(콜라겐) 약 90%·탄력섬유 1.5~4.7%·섬유아세포. 피지=트리글리세라이드 41%·왁스에스터 25%·지방산 16%·스쿠알렌 12%. 한선: 아포크린(대한선, pH 5.5~6.5)·에크린(소한선, pH 3.8~5.6). (책 184~185쪽)</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>피지의 대부분이 트리글리세라이드와 지방산이에요. 이게 말라세지아 효모의 먹이.</t>
+        </is>
+      </c>
+      <c r="E108" s="34" t="inlineStr">
+        <is>
+          <t>★말라세지아-세이프: 피지 같은 지방산 오일 배제</t>
+        </is>
+      </c>
+      <c r="F108" s="34" t="inlineStr">
+        <is>
+          <t>히어로 서사의 생리학 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="124" customHeight="1" s="43">
+      <c r="A109" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B109" s="34" t="inlineStr">
+        <is>
+          <t>모발 수치·결합·주기</t>
+        </is>
+      </c>
+      <c r="C109" s="34" t="inlineStr">
+        <is>
+          <t>하루 0.3~0.5mm 성장, 하루 50~100가닥 탈모. 모피질 80~90%. 4대 결합=시스틴(S-S)·염(이온)·수소·펩타이드. 성장기 3~6년(80~90%)·퇴행기 약 3주(1~2%)·휴지기 3~4개월(10~15%). (책 185~186쪽)</t>
+        </is>
+      </c>
+      <c r="D109" s="34" t="inlineStr">
+        <is>
+          <t>머리카락의 대부분은 모피질. 파마는 시스틴 결합을 끊고 다시 붙이는 것.</t>
+        </is>
+      </c>
+      <c r="E109" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="34" t="inlineStr">
+        <is>
+          <t>헤어 확장 시 기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="95" customHeight="1" s="43">
+      <c r="A110" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B110" s="34" t="inlineStr">
+        <is>
+          <t>피부 분석·유형</t>
+        </is>
+      </c>
+      <c r="C110" s="34" t="inlineStr">
+        <is>
+          <t>문진·견진·촉진·기기 측정(수분·TEWL·유분·pH·탄력·주름 레플리카). 유형: 정상·건성·지성·복합성·민감성·노화·여드름·색소침착. 피츠패트릭 피부 분류 6형. (책 187~188쪽)</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="inlineStr">
+        <is>
+          <t>묻고·보고·만지고·기계로 재는 4가지 방법으로 피부를 판단해요.</t>
+        </is>
+      </c>
+      <c r="E110" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="34" t="inlineStr">
+        <is>
+          <t>맞춤 상담 프로토콜</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="66" customHeight="1" s="43">
+      <c r="A111" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B111" s="34" t="inlineStr">
+        <is>
+          <t>탈모·비듬</t>
+        </is>
+      </c>
+      <c r="C111" s="34" t="inlineStr">
+        <is>
+          <t>남성형 탈모=DHT(남성호르몬 대사물). 비듬 원인=말라쎄지아(효모) 증식·피지 과다·각질 탈락 등. (책 189쪽)</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="inlineStr">
+        <is>
+          <t>교재가 비듬 원인으로 말라쎄지아를 직접 다뤄요.</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="inlineStr">
+        <is>
+          <t>★히어로 컨셉의 교재 근거</t>
+        </is>
+      </c>
+      <c r="F111" s="34" t="inlineStr">
+        <is>
+          <t>단 '비듬 개선·치료' 표방은 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="138" customHeight="1" s="43">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B112" s="34" t="inlineStr">
+        <is>
+          <t>관능평가 요소·방법</t>
+        </is>
+      </c>
+      <c r="C112" s="34" t="inlineStr">
+        <is>
+          <t>요소: 탁도·변취·분리(성상)·점도·경도·증발/표면 굳음. 물리화학적: Rheometer(점탄성)·Cutometer(탄력)·Glossmeter(광택)·분광측색계(색). 소비자 시험: 맹검(Blind Use Test)·비맹검(Concept Use Test). (책 192~193쪽)</t>
+        </is>
+      </c>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>사람 감각 평가를 기계 측정으로 보완해요. 브랜드를 가리면 맹검.</t>
+        </is>
+      </c>
+      <c r="E112" s="34" t="inlineStr">
+        <is>
+          <t>바이알 비교+지인 맹검 테스트</t>
+        </is>
+      </c>
+      <c r="F112" s="34" t="inlineStr">
+        <is>
+          <t>체험단 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="80" customHeight="1" s="43">
+      <c r="A113" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B113" s="34" t="inlineStr">
+        <is>
+          <t>부작용 용어</t>
+        </is>
+      </c>
+      <c r="C113" s="34" t="inlineStr">
+        <is>
+          <t>홍반(붉어짐)·부종(부어오름)·인설(각질이 일어남)·자통(찌르는 통증)·작열감(타는 느낌)·가려움. 부작용 발생 시 식약처장에게 지체 없이 보고. (책 195쪽)</t>
+        </is>
+      </c>
+      <c r="D113" s="34" t="inlineStr">
+        <is>
+          <t>고객이 말하는 증상을 정확한 용어로 기록해야 보고할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E113" s="34" t="inlineStr">
+        <is>
+          <t>집 테스트 반응도 이 용어로</t>
+        </is>
+      </c>
+      <c r="F113" s="34" t="inlineStr">
+        <is>
+          <t>CS 부작용 접수 양식</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="110" customHeight="1" s="43">
+      <c r="A114" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>맞춤형 표시·가격</t>
+        </is>
+      </c>
+      <c r="C114" s="34" t="inlineStr">
+        <is>
+          <t>1차 포장 필수=명칭·영업자 상호·제조번호(식별번호)·사용기한(개봉 후 사용기간). 10mL(g) 이하 소용량·비매품은 명칭·상호·가격·제조번호·사용기한만. 가격 표시 의무자=소매업자(실제 판매자). (책 199~201쪽)</t>
+        </is>
+      </c>
+      <c r="D114" s="34" t="inlineStr">
+        <is>
+          <t>아주 작은 용량은 최소 항목만 쓰면 돼요. 가격은 파는 사람이 표시.</t>
+        </is>
+      </c>
+      <c r="E114" s="34" t="inlineStr">
+        <is>
+          <t>샘플 파우치 라벨</t>
+        </is>
+      </c>
+      <c r="F114" s="34" t="inlineStr">
+        <is>
+          <t>견본품·미니어처 라벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="110" customHeight="1" s="43">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B115" s="34" t="inlineStr">
+        <is>
+          <t>표시·광고 실증·금지 표현</t>
+        </is>
+      </c>
+      <c r="C115" s="34" t="inlineStr">
+        <is>
+          <t>실증 요청을 받으면 15일 이내 자료 제출. 금지 표현: 질병 치료·예방, 피부 재생·세포 활성, '줄기세포'(배양액 원료 외), 특정인·기관 지정·공인 오인 등. 위반 시 판매·광고 업무정지(1~4차 가중). (책 202~206쪽)</t>
+        </is>
+      </c>
+      <c r="D115" s="34" t="inlineStr">
+        <is>
+          <t>광고 문구는 요청받으면 15일 안에 증명해야 해요. 못 하면 업무정지까지.</t>
+        </is>
+      </c>
+      <c r="E115" s="34" t="inlineStr">
+        <is>
+          <t>문구검사(checks.py) 금지어와 대조</t>
+        </is>
+      </c>
+      <c r="F115" s="34" t="inlineStr">
+        <is>
+          <t>상세페이지 근거 폴더</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="52" customHeight="1" s="43">
+      <c r="A116" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="inlineStr">
+        <is>
+          <t>혼합 안정성 저하 요인</t>
+        </is>
+      </c>
+      <c r="C116" s="34" t="inlineStr">
+        <is>
+          <t>①원료 투입 순서 ②가용화·유화 시 제조 온도와 설정 온도 차이 ③회전속도 ④진공 세기. (책 212쪽)</t>
+        </is>
+      </c>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>같은 처방도 순서·온도·속도·진공이 다르면 결과가 달라져요.</t>
+        </is>
+      </c>
+      <c r="E116" s="34" t="inlineStr">
+        <is>
+          <t>★실패 원인 체크리스트 4항목</t>
+        </is>
+      </c>
+      <c r="F116" s="34" t="inlineStr">
+        <is>
+          <t>스케일업 시 공정 조건 전달</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="168" customHeight="1" s="43">
+      <c r="A117" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B117" s="34" t="inlineStr">
+        <is>
+          <t>규격 용어(pH·온도·점도)</t>
+        </is>
+      </c>
+      <c r="C117" s="34" t="inlineStr">
+        <is>
+          <t>pH: 미산성 5.0~6.5·약산성 3.0~5.0·강산성 3.0 이하·미알칼리성 7.5~9.0·약알칼리성 9.0~11.0·강알칼리성 11.0 이상. 온도: 표준 20℃·상온 15~25℃·실온 1~30℃·미온 30~40℃·냉소 15℃ 이하. 점도: 절대점도 포아즈(P)·운동점도 스톡스(St). '직후·곧'=30초 이내, '약'=±10%. (책 216~217쪽)</t>
+        </is>
+      </c>
+      <c r="D117" s="34" t="inlineStr">
+        <is>
+          <t>교재 용어로 다도기 pH 5.0~5.5는 '미산성'. '실온'과 '상온'의 범위도 달라요.</t>
+        </is>
+      </c>
+      <c r="E117" s="34" t="inlineStr">
+        <is>
+          <t>★목표 pH 5.0~5.5=미산성</t>
+        </is>
+      </c>
+      <c r="F117" s="34" t="inlineStr">
+        <is>
+          <t>카피 '약산성' 사용 시 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="66" customHeight="1" s="43">
+      <c r="A118" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B118" s="34" t="inlineStr">
+        <is>
+          <t>혼합·소분 기구</t>
+        </is>
+      </c>
+      <c r="C118" s="34" t="inlineStr">
+        <is>
+          <t>전자저울·스패출러·헤라·호모게나이저·디스퍼·오버헤드스터러·마그네틱바·항온수조·pH미터·점도계·자외선 살균기 등. (책 218쪽)</t>
+        </is>
+      </c>
+      <c r="D118" s="34" t="inlineStr">
+        <is>
+          <t>매장·실험실에서 쓰는 도구 이름과 용도가 나와요.</t>
+        </is>
+      </c>
+      <c r="E118" s="34" t="inlineStr">
+        <is>
+          <t>HZ-400·OC-15S·HS5Pro와 대응</t>
+        </is>
+      </c>
+      <c r="F118" s="34" t="inlineStr">
+        <is>
+          <t>매장 장비 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="95" customHeight="1" s="43">
+      <c r="A119" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B119" s="34" t="inlineStr">
+        <is>
+          <t>충진기·포장 재질</t>
+        </is>
+      </c>
+      <c r="C119" s="34" t="inlineStr">
+        <is>
+          <t>충진기: 피스톤·파우치·파우더·액체·튜브·카톤. 플라스틱: LDPE·HDPE·PP·PS·AS·ABS·PVC·PET. 유리: 소다석회·칼리납·유백. 금속: 알루미늄·스테인리스 등. (책 223~224쪽)</t>
+        </is>
+      </c>
+      <c r="D119" s="34" t="inlineStr">
+        <is>
+          <t>용기 재질 약자가 시험에 나와요. 투명 병은 주로 PET, 캡은 PP.</t>
+        </is>
+      </c>
+      <c r="E119" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="34" t="inlineStr">
+        <is>
+          <t>용기 사양서 읽기</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="80" customHeight="1" s="43">
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t>4.맞춤형</t>
+        </is>
+      </c>
+      <c r="B120" s="34" t="inlineStr">
+        <is>
+          <t>포장공간비율</t>
+        </is>
+      </c>
+      <c r="C120" s="34" t="inlineStr">
+        <is>
+          <t>단위제품: 인체·두발 세정용 15% 이하, 그 밖 화장품 10% 이하(2차 포장까지). 종합제품(세트) 25% 이하. 맞춤형 소분·혼합 제품은 오버라벨링. (책 225쪽)</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>상자 속 빈 공간이 너무 크면 과대포장이에요.</t>
+        </is>
+      </c>
+      <c r="E120" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="34" t="inlineStr">
+        <is>
+          <t>세트·옵션 상자 설계</t>
         </is>
       </c>
     </row>
@@ -27284,7 +31482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="19" customWidth="1" style="43" min="1" max="1"/>
@@ -27882,6 +32080,678 @@
       <c r="F20" s="16" t="inlineStr">
         <is>
           <t>해외 트렌드 성분 도입 리스크</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1" s="43">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>[법] 영업자 의무·교육</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>생산실적 매년 2월 말·원료 목록 유통 전 보고, 책임판매관리자 교육 매년 4~8시간</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>등록만 하면 끝이 아니라 매년 보고하고 교육받아야 해요.</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>출시 연도부터 컴플라이언스 달력 운영</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>생산실적 보고용 로트·수량 자료를 주나?</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>미이행=과태료</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="88" customHeight="1" s="43">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>[법] 0.5% 이상 안정성 자료</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>레티놀·아스코빅애씨드·토코페롤·과산화화합물·효소 0.5% 이상 → 안정성 자료를 사용기한 만료 후 1년 보존</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>잘 변하는 성분을 많이 넣으면 증빙을 보관해야 해요. 책임은 책임판매업자(나).</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>클렌징오일(토코페롤 1%) 위탁 시 자료 확보</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>토코페롤 0.5% 이상 품목 안정성시험 자료를 제공하나?</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>책임판매업자 보존 의무</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1" s="43">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>[법] 회수·위해 등급</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>가등급 15일·나·다등급 30일, 회수계획 5일 이내, 기록 2년</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>리콜은 기간이 정해진 의무예요. 제조번호별로 어디에 팔았는지 알아야 빨리 거둬요.</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>판매 채널별 출고 로트 기록 → 회수 범위 최소화</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>제조번호 체계와 로트별 출고 기록을 공유하나?</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>회수 4/5 이상이면 처분 면제</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1" s="43">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>[법] 안전성 정보 보고</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>신속보고 15일·정기보고 매 반기 종료 후 1개월</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>고객 부작용 문의도 보고 대상이 될 수 있어요.</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>CS 스크립트에 '부작용 접수→기록→보고' 단계</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>부작용 발생 시 원인 조사 협조 범위는?</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>리뷰 속 부작용도 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="72" customHeight="1" s="43">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>[법] 표시·광고 실증</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>실증 요청 시 15일 이내 제출, 금지 표현(치료·재생·세포 활성·줄기세포 등), 위반 시 업무정지</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>'진정·저자극' 같은 문구는 자료부터 갖추고 써요.</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>상세페이지 문구마다 근거 파일 폴더</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>인체적용(저자극) 시험 연계 기관·비용은?</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>근거 없는 문구는 안 쓰는 게 최선</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1" s="43">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>[법] 천연·유기농 표시</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>인증 조항 삭제(2025.1.31), 천연 95%·유기농 10%+천연 95% 기준·합성 5% 이내</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>인증마크 시대는 끝났지만 '천연' 주장에는 여전히 근거가 필요해요.</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>천연 대신 '말라세지아-세이프·무향' 사실 소구</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>천연유래지수(ISO 16128) 산출이 가능한가?</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>근거 없는 '천연' 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1" s="43">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>[법] 개인정보 민감정보·유출</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>민감정보 별도 동의, 1천 명 이상 유출 시 72시간 내 신고, 보유기간 후 지체 없이 파기</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>피부 고민 설문도 민감정보가 될 수 있어요.</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>수요검증 설문은 최소 항목·별도 동의</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>(자체검토) 설문 도구의 보관기간·파기 설정</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>체험단 DB 최소 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="104" customHeight="1" s="43">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>[제조품질] 50mL 이하 표시 생략</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>50mL(g) 이하 전성분 일부 생략 가능(타르색소·기능성 주성분·보존제 등은 표기), 알레르겐 생략 시 홈페이지 공개, 바코드 15mL(g) 이하 생략</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>작은 용량에는 라벨 생략 규칙이 있어요. 히어로 50mL가 바로 이 구간.</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>히어로는 신뢰를 위해 전성분 전체 표기</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>라벨에 전성분 전체가 들어가는 디자인이 가능한가?</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>생략해도 홈페이지에 공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1" s="43">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>[제조품질] CGMP 4대 기준서</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>제품표준서·제조관리기준서·품질관리기준서·제조위생관리기준서</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>좋은 공장은 이 네 문서를 갖추고 있어요.</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>ODM 실사 체크리스트 1번</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>4대 기준서를 열람할 수 있나? CGMP 적합 판정서는?</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>서류가 없으면 위탁 재검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="72" customHeight="1" s="43">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>[제조품질] 맞춤형 유형 4가지</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>현장 혼합형·공장 제조 배송형·DIY 키트형·디바이스형, 원료+원료 혼합=제조(불가)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>맞춤형에도 여러 사업 모델이 있어요.</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>온라인 '공장 제조 배송형'으로 자격 수익화 검토</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>벌크 소량 공급·맞춤 배합 OEM이 가능한가?</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>매장은 완성 내용물에만 혼합</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1" s="43">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>[제조품질] 유성원료 분류</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>유지·탄화수소·실리콘·왁스·고급지방산·고급알코올·에스터, ★호호바=왁스</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>오일을 분류로 고르면 '왜 이 오일인지' 설명이 쉬워져요.</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>말라세지아-세이프 원료 선택을 교재 분류로 설명</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>대체 오일 제안 시 탄소수(C11~24) 확인해 주나?</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>호호바·올리브 등은 히어로에서 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="72" customHeight="1" s="43">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>[유통안전] 보관용 검체</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>사용기한 경과 후 1년(개봉 후 사용기간 기재 시 제조일로부터 3년) 보관, 시험 2번 할 양</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>로트마다 샘플이 남아 있어야 클레임 때 비교할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>내 보관 샘플=CS 분쟁 증거</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>로트별 보관 검체는 누가 보관하나? 열람 가능한가?</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>나도 로트별 2개 보관 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1" s="43">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>[유통안전] 입고 라벨·재작업</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>대기 백색·시험중 황색·적합 청색·부적합 적색, 재작업·폐기는 품질책임자 승인</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>공장 원료는 색 라벨로 상태를 관리해요.</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ODM 실사 시 창고 라벨 확인</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>부적합 원료 처리·재작업 기준은? 재작업품 납품 시 통보하나?</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>재작업품 수령 여부를 계약에 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1" s="43">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>[유통안전] 청정도·작업장</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>충전실=2등급(낙하균 30개/hr·부유균 200개/㎥), HEPA 0.3㎛ 99.97%</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>공장의 '깨끗함'에도 숫자 기준이 있어요.</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ODM 충전실 등급·환경 모니터링 기록 요구</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>충전실 청정도 등급과 낙하균 측정 주기는?</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>미생물 클레임 예방</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1" s="43">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>[유통안전] 용기 종류·포장 시험</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>밀폐·기밀·밀봉·차광, 감량·감압누설·내열/내한·낙하 시험</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>용기도 시험을 통과해야 해요. 자(jar)는 2차 오염 위험이 큼.</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>50mL 자 vs 에어리스 결정 근거</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>용기 감량·내열/내한 시험 데이터가 있나?</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>용기 선택이 안정성·브랜드 메시지 좌우</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="88" customHeight="1" s="43">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>[유통안전] 안전용기</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>아세톤 네일 리무버·탄화수소 10% 이상+21cSt 이하 오일·메틸살리실레이트 5% 이상(일회용·분무용기 제외)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>아이가 열어 삼키면 위험한 제품은 잠금 용기 의무예요.</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>클렌징오일 확장 시 해당 여부 먼저 판정</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>클렌징오일 조성이 안전용기 대상인가(탄화수소 함량·점도)?</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>스쿠알란=탄화수소 → 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="43">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>[맞춤형] 부작용 용어·보고</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>홍반·부종·인설·자통·작열감·가려움, 지체 없이 보고</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>고객이 말한 증상을 정확한 용어로 남겨야 보고·원인 분석이 돼요.</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>CS 부작용 접수 양식 항목</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>부작용 원인 분석에 협조하나(로트 검체 재시험)?</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="88" customHeight="1" s="43">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>[맞춤형] 관능평가 맹검</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Blind Use Test·Concept Use Test, Rheometer·Cutometer·Glossmeter</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>브랜드를 가리고 써보게 해야 진짜 평가가 나와요.</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>수요검증·체험단을 맹검으로 설계 → 리뷰 신뢰</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>ODM 사용감 평가 패널 결과를 공유하나?</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1" s="43">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>[맞춤형] 피지·말라쎄지아</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>피지=트리글리세라이드 41%·지방산 16%, 비듬 원인=말라쎄지아</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>교재가 피지와 효모의 관계를 직접 다뤄요.</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>히어로 '말라세지아-세이프' 서사의 교과서 근거</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>처방에서 C11~24 지방산 오일 배제를 유지할 수 있나?</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>치료·개선 표방 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1" s="43">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>[맞춤형] pH 용어</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>미산성 5.0~6.5·약산성 3.0~5.0</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>교재 기준으로 다도기(5.0~5.5)는 '미산성'이에요.</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>카피에 '약산성'을 쓸지 용어 범위 확인 후 결정</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>완제품 pH 시험성적서를 주나?</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>시험에선 용어 범위를 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="56" customHeight="1" s="43">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>[맞춤형] 포장공간비율</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>단위제품 10%(인체·두발 세정 15%), 종합제품(세트) 25% 이하</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>세트 상자 속 빈 공간이 크면 과대포장이에요.</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>옵션·세트 구성 시 상자 설계</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>세트 박스 포장공간비율 검사를 해주나?</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>위반 시 과태료</t>
         </is>
       </c>
     </row>
@@ -27901,7 +32771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="17" customWidth="1" style="43" min="1" max="1"/>
@@ -28531,6 +33401,710 @@
       <c r="F21" s="16" t="inlineStr">
         <is>
           <t>CoA 없는 원료=품질 불확실</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1" s="43">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>[분리 현상 진단]</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>원심 후 위 크림층·아래 물층, 45℃ 오일 맺힘 관찰</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>유화 분리 4현상(크리밍·응집·합일·오스트발트 숙성), 물리적 변화=분리·합일·응집</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>위에 하얗게 뜨면 크리밍(아직 되돌릴 수 있음), 기름이 맺히면 합일(이미 깨짐). 관찰을 교재 용어로 적으면 그게 시험 공부예요.</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>ODM 샘플 평가를 같은 용어로 소통</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>개발일지 판정에 용어 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1" s="43">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>[투입 순서·호모 조건]</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>냉각상 40℃ 이하 투입, 호모 시간·속도 기록</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>혼합 안정성 저하 4요인: 투입 순서·온도 차이·회전속도·진공 세기</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>같은 처방도 넣는 순서·온도·속도가 다르면 결과가 달라져요. 교재의 4요인이 곧 내 실패 원인 체크리스트.</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>공정 조건을 ODM에 전달(스케일업)</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>집엔 진공 없음 → 기포는 정치·탈기로</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="72" customHeight="1" s="43">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>[온도 용어]</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>수상 70~75℃, 냉각 40℃ 이하, 보관 4℃·실온·45℃</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>표준 20℃·상온 15~25℃·실온 1~30℃·미온 30~40℃·냉소 15℃ 이하</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>'실온'(1~30℃)과 '상온'(15~25℃)은 범위가 달라요. 냉각상 투입 40℃는 '미온' 경계.</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>라벨 보관 문구의 근거</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1" s="43">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>[pH 용어]</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>목표 pH 5.0~5.5</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>pH 용어: 미산성 5.0~6.5·약산성 3.0~5.0</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>교재 기준으로 다도기 크림은 '미산성'이에요. 시험은 용어 범위를 물어요.</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>카피 '약산성' 사용 시 용어 확인</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1" s="43">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>[보관용 샘플]</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>배치마다 투명 바이알 1개 남겨 두기</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>보관용 검체: 시험 2번 할 양, 사용기한 경과 후 1년 / 개봉 후 사용기간 기재 시 제조일로부터 3년</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>공장은 로트마다 샘플을 남겨 나중에 비교해요. 내 바이알 보관이 그 축소판.</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>클레임 시 로트 비교</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="88" customHeight="1" s="43">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>[원료 입고 표시]</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>입출고 장부·CoA 확인, 통에 수령일·로트 기록</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>입고 라벨 색(대기 백색·시험중 황색·적합 청색·부적합 적색), 필수 기재=공급자 제품명·공급자명·수령일자·제조번호</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>원료 통에 '받은 날·로트' 스티커만 붙여도 교재의 입고관리예요.</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>원료 추적성</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1" s="43">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>[저울 일상점검]</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>계량 전 영점·수평 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>저울: 영점·수평 매일, 정기점검 1개월, 직선성·정밀성 ±0.5%, 편심오차 ±0.1%</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>매일 영점을 맞추는 습관이 시험 숫자 그대로예요.</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>소량 생산 품질 통제</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>[계량·검교정] 행과 함께</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1" s="43">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>[도구 세척·판정]</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>사용 후 세척 → 70% 에탄올 → 완전 건조</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>세척 원칙(물 최적·세제 최소·브러시), 위생 판정(육안·닦아내기·린스 정량·면봉 표면균)</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>닦은 뒤 흰 키친타월로 문질러 묻어나는지 보는 게 '닦아내기 판정'이에요.</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>매장 위생 SOP</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>호모 헤드는 물+브러시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1" s="43">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>[소독제 농도]</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>70% 에탄올 스프레이</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>알코올 70~80%, 손 소독 15초 이상, 이상적 소독제=5분 이내 99.9%</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>100% 알코올보다 70%가 잘 들어요. 물이 있어야 균 속으로 스며들기 때문.</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>에탄올이 마른 뒤 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1" s="43">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>[작업 복장]</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>머리망·장갑·실험복 착용</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>작업자 위생: 작업복, 음식물 반입 금지, 일회용 장갑 착용 시 손 소독 예외</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>집에서도 머리카락·손이 가장 큰 오염원이에요.</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>매장 복장 기준</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1" s="43">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>[냉각상 투입·충전]</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>40℃ 이하에서 활성·방부 투입, 바로 충전</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>청정도 등급(제조실·충전실=2등급, 낙하균 30개/hr)</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>공장 충전실은 공기 속 균 수까지 관리해요. 집에선 뚜껑 덮기·빠른 충전이 대신.</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>ODM 충전실 등급 확인</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1" s="43">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>[재유화]</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>분리된 배치를 다시 가열·호모로 살리기</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>재작업=기준 벗어난 벌크·완제품 재처리, 품질책임자 승인·원인 조사</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>공장에선 함부로 다시 섞지 못하고 승인·기록이 필요해요. 집에서도 재작업 배치는 따로 표시.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>재작업품 납품 통보 계약</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="43">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>[실패 배치 폐기]</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>변색·냄새난 배치 폐기, 개발일지에 판정 기록</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>폐기 기준·폐기확인서(의뢰자·현황·사유)</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>버릴 때도 '왜 버렸는지' 남기는 게 폐기확인서예요.</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>접은 실험도 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1" s="43">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>[점도 비교]</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>손 감각·스패출러 늘어짐으로 되기 비교</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>점도 단위(포아즈·스톡스), 관능 요소(점도·경도), Rheometer</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>손 느낌을 숫자로 바꾸는 게 점도계예요. 관찰을 교재 용어로 적어 두기.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>점도 사양을 ODM에 전달</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="72" customHeight="1" s="43">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>[맹검 사용감 테스트]</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>지인에게 샘플 사용감 듣기</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>소비자 사용시험: 맹검(Blind Use Test)·비맹검(Concept Use Test)</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>라벨을 가리고 A·B로 주면 맹검. 브랜드 선입견 없는 평가가 나와요.</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>수요검증 신뢰도↑</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1" s="43">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>[보습 확인]</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>바른 뒤 당김·촉촉함 체감</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>보습 유효성=TEWL(경피수분손실)·수분량 측정</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>체감 말고 숫자로 보려면 TEWL. 교재 '일반화장품 유효성' 내용이에요.</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>보습 소구 실증</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="43">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>[용기 감량 측정]</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>바이알 무게를 주차별로 재기</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>포장 시험: 내용물 감량·감압누설·내열/내한</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>무게가 줄면 수분이 새는 것 → 용기 밀폐력 문제예요.</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>용기 선정</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="72" customHeight="1" s="43">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>[충진량 확인]</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>50mL 자에 충진 후 무게 확인</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>내용량 기준: 3개 평균이 표기량의 97% 이상(미달 시 6개 추가, 9개 평균 97%)</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>3개 무게 평균이 표기량의 97% 이상이어야 합격. mL 표기면 비중으로 g 환산.</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>충진 공차 설정</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1" s="43">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>[비타민 원료]</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>판테놀·나이아신아마이드·토코페롤 사용</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>비타민 분류: 판테놀=B5·나이아신아마이드=B3(수용성), 토코페롤=E(지용성)</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>내 원료가 곧 비타민 문제의 보기예요.</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>원료 서사</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="72" customHeight="1" s="43">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>[토코페롤 1%]</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>클렌징오일 토코페롤 1%</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>0.5% 이상 함유 시 안정성시험 자료를 사용기한 만료 후 1년 보존(책임판매업자)</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>내 처방이 바로 이 조항의 대상이에요.</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>위탁 시 자료 요구</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>★시험·실무 동시 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="56" customHeight="1" s="43">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>[유성원료 분류]</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>스쿠알란·MCT·디메치콘·세틸알코올 사용</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>유성원료 7분류: 탄화수소·에스터·실리콘·고급알코올 등, 호호바=왁스</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>내 유상 4종이 각각 다른 분류예요. 호호바를 뺀 이유도 분류로 설명할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>말라세지아-세이프 설명</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="72" customHeight="1" s="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>[안정성 일정]</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>1·2·4·8주 관찰</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>장기 측정: 1년차 3개월마다·2년차 6개월마다·이후 1년, 가속 6개월 최소 3번, 3로트 이상</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>내 8주 관찰은 '조기 판정'. 공식 사용기한은 6개월 이상 데이터가 필요해요.</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>사용기한은 ODM 데이터로</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
